--- a/tables_and_figures/input_tables/national_errors.xlsx
+++ b/tables_and_figures/input_tables/national_errors.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:S377"/>
+  <dimension ref="A1:S381"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -5670,10 +5670,10 @@
         <v>19.71418188895098</v>
       </c>
       <c r="N78">
-        <v>21.68983558756392</v>
+        <v>21.68983558756369</v>
       </c>
       <c r="O78">
-        <v>21.68983558756405</v>
+        <v>21.68983558756393</v>
       </c>
       <c r="P78">
         <v>55400</v>
@@ -5738,10 +5738,10 @@
         <v>19.71418188895098</v>
       </c>
       <c r="N79">
-        <v>21.68983558756392</v>
+        <v>21.68983558756369</v>
       </c>
       <c r="O79">
-        <v>21.68983558756405</v>
+        <v>21.68983558756393</v>
       </c>
       <c r="P79">
         <v>55400</v>
@@ -5806,10 +5806,10 @@
         <v>19.71418188895098</v>
       </c>
       <c r="N80">
-        <v>21.68983558756392</v>
+        <v>21.68983558756369</v>
       </c>
       <c r="O80">
-        <v>21.68983558756405</v>
+        <v>21.68983558756393</v>
       </c>
       <c r="P80">
         <v>55400</v>
@@ -5820,7 +5820,7 @@
         </is>
       </c>
       <c r="S80">
-        <v>1.936748087924742</v>
+        <v>1.936748087924511</v>
       </c>
     </row>
     <row r="81">
@@ -5874,10 +5874,10 @@
         <v>19.71418188895098</v>
       </c>
       <c r="N81">
-        <v>21.68983558756392</v>
+        <v>21.68983558756369</v>
       </c>
       <c r="O81">
-        <v>21.68983558756405</v>
+        <v>21.68983558756393</v>
       </c>
       <c r="P81">
         <v>55400</v>
@@ -5888,7 +5888,7 @@
         </is>
       </c>
       <c r="S81">
-        <v>1.936748087924864</v>
+        <v>1.936748087924747</v>
       </c>
     </row>
     <row r="82">
@@ -5942,10 +5942,10 @@
         <v>34.574542787282</v>
       </c>
       <c r="N82">
-        <v>32.13108402346401</v>
+        <v>32.131084023464</v>
       </c>
       <c r="O82">
-        <v>32.13108402346418</v>
+        <v>32.13108402346392</v>
       </c>
       <c r="P82">
         <v>55400</v>
@@ -6010,10 +6010,10 @@
         <v>34.574542787282</v>
       </c>
       <c r="N83">
-        <v>32.13108402346401</v>
+        <v>32.131084023464</v>
       </c>
       <c r="O83">
-        <v>32.13108402346418</v>
+        <v>32.13108402346392</v>
       </c>
       <c r="P83">
         <v>55400</v>
@@ -6078,10 +6078,10 @@
         <v>34.574542787282</v>
       </c>
       <c r="N84">
-        <v>32.13108402346401</v>
+        <v>32.131084023464</v>
       </c>
       <c r="O84">
-        <v>32.13108402346418</v>
+        <v>32.13108402346392</v>
       </c>
       <c r="P84">
         <v>55400</v>
@@ -6092,7 +6092,7 @@
         </is>
       </c>
       <c r="S84">
-        <v>0.4445337920600756</v>
+        <v>0.44453379206007</v>
       </c>
     </row>
     <row r="85">
@@ -6146,10 +6146,10 @@
         <v>34.574542787282</v>
       </c>
       <c r="N85">
-        <v>32.13108402346401</v>
+        <v>32.131084023464</v>
       </c>
       <c r="O85">
-        <v>32.13108402346418</v>
+        <v>32.13108402346392</v>
       </c>
       <c r="P85">
         <v>55400</v>
@@ -6160,7 +6160,7 @@
         </is>
       </c>
       <c r="S85">
-        <v>0.4445337920602477</v>
+        <v>0.4445337920599868</v>
       </c>
     </row>
     <row r="86">
@@ -6214,10 +6214,10 @@
         <v>49.75314441747606</v>
       </c>
       <c r="N86">
-        <v>60.64538348494989</v>
+        <v>60.64538348495072</v>
       </c>
       <c r="O86">
-        <v>60.64538348495076</v>
+        <v>60.64538348495044</v>
       </c>
       <c r="P86">
         <v>55400</v>
@@ -6282,10 +6282,10 @@
         <v>49.75314441747606</v>
       </c>
       <c r="N87">
-        <v>60.64538348494989</v>
+        <v>60.64538348495072</v>
       </c>
       <c r="O87">
-        <v>60.64538348495076</v>
+        <v>60.64538348495044</v>
       </c>
       <c r="P87">
         <v>55400</v>
@@ -6350,10 +6350,10 @@
         <v>49.75314441747606</v>
       </c>
       <c r="N88">
-        <v>60.64538348494989</v>
+        <v>60.64538348495072</v>
       </c>
       <c r="O88">
-        <v>60.64538348495076</v>
+        <v>60.64538348495044</v>
       </c>
       <c r="P88">
         <v>55400</v>
@@ -6364,7 +6364,7 @@
         </is>
       </c>
       <c r="S88">
-        <v>-0.2387361085909201</v>
+        <v>-0.2387361085900874</v>
       </c>
     </row>
     <row r="89">
@@ -6418,10 +6418,10 @@
         <v>49.75314441747606</v>
       </c>
       <c r="N89">
-        <v>60.64538348494989</v>
+        <v>60.64538348495072</v>
       </c>
       <c r="O89">
-        <v>60.64538348495076</v>
+        <v>60.64538348495044</v>
       </c>
       <c r="P89">
         <v>55400</v>
@@ -6432,7 +6432,7 @@
         </is>
       </c>
       <c r="S89">
-        <v>-0.238736108590043</v>
+        <v>-0.238736108590365</v>
       </c>
     </row>
     <row r="90">
@@ -6486,10 +6486,10 @@
         <v>22.91056164538115</v>
       </c>
       <c r="N90">
-        <v>23.19167199619754</v>
+        <v>23.19167199619718</v>
       </c>
       <c r="O90">
-        <v>23.19287782028184</v>
+        <v>23.19287782028157</v>
       </c>
       <c r="P90">
         <v>48612</v>
@@ -6554,10 +6554,10 @@
         <v>22.91056164538115</v>
       </c>
       <c r="N91">
-        <v>23.19167199619754</v>
+        <v>23.19167199619718</v>
       </c>
       <c r="O91">
-        <v>23.19287782028184</v>
+        <v>23.19287782028157</v>
       </c>
       <c r="P91">
         <v>48612</v>
@@ -6622,10 +6622,10 @@
         <v>22.91056164538115</v>
       </c>
       <c r="N92">
-        <v>23.19167199619754</v>
+        <v>23.19167199619718</v>
       </c>
       <c r="O92">
-        <v>23.19287782028184</v>
+        <v>23.19287782028157</v>
       </c>
       <c r="P92">
         <v>48612</v>
@@ -6636,7 +6636,7 @@
         </is>
       </c>
       <c r="S92">
-        <v>-0.2830345174885757</v>
+        <v>-0.2830345174889337</v>
       </c>
     </row>
     <row r="93">
@@ -6690,10 +6690,10 @@
         <v>22.91056164538115</v>
       </c>
       <c r="N93">
-        <v>23.19167199619754</v>
+        <v>23.19167199619718</v>
       </c>
       <c r="O93">
-        <v>23.19287782028184</v>
+        <v>23.19287782028157</v>
       </c>
       <c r="P93">
         <v>48612</v>
@@ -6704,7 +6704,7 @@
         </is>
       </c>
       <c r="S93">
-        <v>-0.2818286934042763</v>
+        <v>-0.2818286934045483</v>
       </c>
     </row>
     <row r="94">
@@ -6758,10 +6758,10 @@
         <v>97.35418313024078</v>
       </c>
       <c r="N94">
-        <v>90.07772910426883</v>
+        <v>90.07772910426878</v>
       </c>
       <c r="O94">
-        <v>95.56945283348823</v>
+        <v>95.5694528334882</v>
       </c>
       <c r="P94">
         <v>49058</v>
@@ -6826,10 +6826,10 @@
         <v>97.35418313024078</v>
       </c>
       <c r="N95">
-        <v>90.07772910426883</v>
+        <v>90.07772910426878</v>
       </c>
       <c r="O95">
-        <v>95.56945283348823</v>
+        <v>95.5694528334882</v>
       </c>
       <c r="P95">
         <v>49058</v>
@@ -6894,10 +6894,10 @@
         <v>97.35418313024078</v>
       </c>
       <c r="N96">
-        <v>90.07772910426883</v>
+        <v>90.07772910426878</v>
       </c>
       <c r="O96">
-        <v>95.56945283348823</v>
+        <v>95.5694528334882</v>
       </c>
       <c r="P96">
         <v>49058</v>
@@ -6908,7 +6908,7 @@
         </is>
       </c>
       <c r="S96">
-        <v>-2.036080868973866</v>
+        <v>-2.0360808689739</v>
       </c>
     </row>
     <row r="97">
@@ -6962,10 +6962,10 @@
         <v>97.35418313024078</v>
       </c>
       <c r="N97">
-        <v>90.07772910426883</v>
+        <v>90.07772910426878</v>
       </c>
       <c r="O97">
-        <v>95.56945283348823</v>
+        <v>95.5694528334882</v>
       </c>
       <c r="P97">
         <v>49058</v>
@@ -6976,7 +6976,7 @@
         </is>
       </c>
       <c r="S97">
-        <v>3.455642860245545</v>
+        <v>3.455642860245511</v>
       </c>
     </row>
     <row r="98">
@@ -7030,10 +7030,10 @@
         <v>61.33920356117392</v>
       </c>
       <c r="N98">
-        <v>60.39792154911977</v>
+        <v>60.39792154911988</v>
       </c>
       <c r="O98">
-        <v>61.3884842702589</v>
+        <v>61.38848427025866</v>
       </c>
       <c r="P98">
         <v>55325</v>
@@ -7098,10 +7098,10 @@
         <v>61.33920356117392</v>
       </c>
       <c r="N99">
-        <v>60.39792154911977</v>
+        <v>60.39792154911988</v>
       </c>
       <c r="O99">
-        <v>61.3884842702589</v>
+        <v>61.38848427025866</v>
       </c>
       <c r="P99">
         <v>55325</v>
@@ -7166,10 +7166,10 @@
         <v>61.33920356117392</v>
       </c>
       <c r="N100">
-        <v>60.39792154911977</v>
+        <v>60.39792154911988</v>
       </c>
       <c r="O100">
-        <v>61.3884842702589</v>
+        <v>61.38848427025866</v>
       </c>
       <c r="P100">
         <v>55325</v>
@@ -7180,7 +7180,7 @@
         </is>
       </c>
       <c r="S100">
-        <v>-1.447053910698781</v>
+        <v>-1.44705391069867</v>
       </c>
     </row>
     <row r="101">
@@ -7234,10 +7234,10 @@
         <v>61.33920356117392</v>
       </c>
       <c r="N101">
-        <v>60.39792154911977</v>
+        <v>60.39792154911988</v>
       </c>
       <c r="O101">
-        <v>61.3884842702589</v>
+        <v>61.38848427025866</v>
       </c>
       <c r="P101">
         <v>55325</v>
@@ -7248,7 +7248,7 @@
         </is>
       </c>
       <c r="S101">
-        <v>-0.4564911895596491</v>
+        <v>-0.4564911895598933</v>
       </c>
     </row>
     <row r="102">
@@ -7302,10 +7302,10 @@
         <v>51.97518434916385</v>
       </c>
       <c r="N102">
-        <v>51.9685103540086</v>
+        <v>51.96851035400858</v>
       </c>
       <c r="O102">
-        <v>55.16820532599615</v>
+        <v>55.16820532599596</v>
       </c>
       <c r="P102">
         <v>55400</v>
@@ -7370,10 +7370,10 @@
         <v>51.97518434916385</v>
       </c>
       <c r="N103">
-        <v>51.9685103540086</v>
+        <v>51.96851035400858</v>
       </c>
       <c r="O103">
-        <v>55.16820532599615</v>
+        <v>55.16820532599596</v>
       </c>
       <c r="P103">
         <v>55400</v>
@@ -7438,10 +7438,10 @@
         <v>51.97518434916385</v>
       </c>
       <c r="N104">
-        <v>51.9685103540086</v>
+        <v>51.96851035400858</v>
       </c>
       <c r="O104">
-        <v>55.16820532599615</v>
+        <v>55.16820532599596</v>
       </c>
       <c r="P104">
         <v>55400</v>
@@ -7452,7 +7452,7 @@
         </is>
       </c>
       <c r="S104">
-        <v>-0.4053152415142924</v>
+        <v>-0.4053152415143146</v>
       </c>
     </row>
     <row r="105">
@@ -7506,10 +7506,10 @@
         <v>51.97518434916385</v>
       </c>
       <c r="N105">
-        <v>51.9685103540086</v>
+        <v>51.96851035400858</v>
       </c>
       <c r="O105">
-        <v>55.16820532599615</v>
+        <v>55.16820532599596</v>
       </c>
       <c r="P105">
         <v>55400</v>
@@ -7520,7 +7520,7 @@
         </is>
       </c>
       <c r="S105">
-        <v>2.794379730473251</v>
+        <v>2.794379730473062</v>
       </c>
     </row>
     <row r="106">
@@ -7574,10 +7574,10 @@
         <v>92.92783958842196</v>
       </c>
       <c r="N106">
-        <v>87.32994267910608</v>
+        <v>87.32994267910654</v>
       </c>
       <c r="O106">
-        <v>92.33804839648158</v>
+        <v>92.33804839648147</v>
       </c>
       <c r="P106">
         <v>55242</v>
@@ -7642,10 +7642,10 @@
         <v>92.92783958842196</v>
       </c>
       <c r="N107">
-        <v>87.32994267910608</v>
+        <v>87.32994267910654</v>
       </c>
       <c r="O107">
-        <v>92.33804839648158</v>
+        <v>92.33804839648147</v>
       </c>
       <c r="P107">
         <v>55242</v>
@@ -7710,10 +7710,10 @@
         <v>92.92783958842196</v>
       </c>
       <c r="N108">
-        <v>87.32994267910608</v>
+        <v>87.32994267910654</v>
       </c>
       <c r="O108">
-        <v>92.33804839648158</v>
+        <v>92.33804839648147</v>
       </c>
       <c r="P108">
         <v>55242</v>
@@ -7724,7 +7724,7 @@
         </is>
       </c>
       <c r="S108">
-        <v>-0.1009559809642679</v>
+        <v>-0.1009559809638128</v>
       </c>
     </row>
     <row r="109">
@@ -7778,10 +7778,10 @@
         <v>92.92783958842196</v>
       </c>
       <c r="N109">
-        <v>87.32994267910608</v>
+        <v>87.32994267910654</v>
       </c>
       <c r="O109">
-        <v>92.33804839648158</v>
+        <v>92.33804839648147</v>
       </c>
       <c r="P109">
         <v>55242</v>
@@ -7792,7 +7792,7 @@
         </is>
       </c>
       <c r="S109">
-        <v>4.907149736411231</v>
+        <v>4.907149736411109</v>
       </c>
     </row>
     <row r="110">
@@ -7846,10 +7846,10 @@
         <v>86.30129201699636</v>
       </c>
       <c r="N110">
-        <v>90.29738719024508</v>
+        <v>90.29738719024533</v>
       </c>
       <c r="O110">
-        <v>85.14002215874885</v>
+        <v>85.14002215874858</v>
       </c>
       <c r="P110">
         <v>55400</v>
@@ -7914,10 +7914,10 @@
         <v>86.30129201699636</v>
       </c>
       <c r="N111">
-        <v>90.29738719024508</v>
+        <v>90.29738719024533</v>
       </c>
       <c r="O111">
-        <v>85.14002215874885</v>
+        <v>85.14002215874858</v>
       </c>
       <c r="P111">
         <v>55400</v>
@@ -7982,10 +7982,10 @@
         <v>86.30129201699636</v>
       </c>
       <c r="N112">
-        <v>90.29738719024508</v>
+        <v>90.29738719024533</v>
       </c>
       <c r="O112">
-        <v>85.14002215874885</v>
+        <v>85.14002215874858</v>
       </c>
       <c r="P112">
         <v>55400</v>
@@ -7996,7 +7996,7 @@
         </is>
       </c>
       <c r="S112">
-        <v>0.729413685619984</v>
+        <v>0.7294136856202504</v>
       </c>
     </row>
     <row r="113">
@@ -8050,10 +8050,10 @@
         <v>86.30129201699636</v>
       </c>
       <c r="N113">
-        <v>90.29738719024508</v>
+        <v>90.29738719024533</v>
       </c>
       <c r="O113">
-        <v>85.14002215874885</v>
+        <v>85.14002215874858</v>
       </c>
       <c r="P113">
         <v>55400</v>
@@ -8064,7 +8064,7 @@
         </is>
       </c>
       <c r="S113">
-        <v>-4.427951345876235</v>
+        <v>-4.427951345876502</v>
       </c>
     </row>
     <row r="114">
@@ -8118,10 +8118,10 @@
         <v>78.40310703823478</v>
       </c>
       <c r="N114">
-        <v>81.97678428265853</v>
+        <v>81.97678428265843</v>
       </c>
       <c r="O114">
-        <v>78.85814310205289</v>
+        <v>78.85814310205271</v>
       </c>
       <c r="P114">
         <v>37859</v>
@@ -8186,10 +8186,10 @@
         <v>78.40310703823478</v>
       </c>
       <c r="N115">
-        <v>81.97678428265853</v>
+        <v>81.97678428265843</v>
       </c>
       <c r="O115">
-        <v>78.85814310205289</v>
+        <v>78.85814310205271</v>
       </c>
       <c r="P115">
         <v>37859</v>
@@ -8254,10 +8254,10 @@
         <v>78.40310703823478</v>
       </c>
       <c r="N116">
-        <v>81.97678428265853</v>
+        <v>81.97678428265843</v>
       </c>
       <c r="O116">
-        <v>78.85814310205289</v>
+        <v>78.85814310205271</v>
       </c>
       <c r="P116">
         <v>37859</v>
@@ -8268,7 +8268,7 @@
         </is>
       </c>
       <c r="S116">
-        <v>-0.8086498910109485</v>
+        <v>-0.8086498910110373</v>
       </c>
     </row>
     <row r="117">
@@ -8322,10 +8322,10 @@
         <v>78.40310703823478</v>
       </c>
       <c r="N117">
-        <v>81.97678428265853</v>
+        <v>81.97678428265843</v>
       </c>
       <c r="O117">
-        <v>78.85814310205289</v>
+        <v>78.85814310205271</v>
       </c>
       <c r="P117">
         <v>37859</v>
@@ -8336,7 +8336,7 @@
         </is>
       </c>
       <c r="S117">
-        <v>-3.927291071616579</v>
+        <v>-3.927291071616756</v>
       </c>
     </row>
     <row r="118">
@@ -8390,10 +8390,10 @@
         <v>27.81811575108459</v>
       </c>
       <c r="N118">
-        <v>61.84561105159655</v>
+        <v>61.84561105159537</v>
       </c>
       <c r="O118">
-        <v>26.29907721541566</v>
+        <v>26.29907721541595</v>
       </c>
       <c r="P118">
         <v>44776</v>
@@ -8458,10 +8458,10 @@
         <v>27.81811575108459</v>
       </c>
       <c r="N119">
-        <v>61.84561105159655</v>
+        <v>61.84561105159537</v>
       </c>
       <c r="O119">
-        <v>26.29907721541566</v>
+        <v>26.29907721541595</v>
       </c>
       <c r="P119">
         <v>44776</v>
@@ -8526,10 +8526,10 @@
         <v>27.81811575108459</v>
       </c>
       <c r="N120">
-        <v>61.84561105159655</v>
+        <v>61.84561105159537</v>
       </c>
       <c r="O120">
-        <v>26.29907721541566</v>
+        <v>26.29907721541595</v>
       </c>
       <c r="P120">
         <v>44776</v>
@@ -8540,7 +8540,7 @@
         </is>
       </c>
       <c r="S120">
-        <v>0.3570698780801185</v>
+        <v>0.3570698780789416</v>
       </c>
     </row>
     <row r="121">
@@ -8594,10 +8594,10 @@
         <v>27.81811575108459</v>
       </c>
       <c r="N121">
-        <v>61.84561105159655</v>
+        <v>61.84561105159537</v>
       </c>
       <c r="O121">
-        <v>26.29907721541566</v>
+        <v>26.29907721541595</v>
       </c>
       <c r="P121">
         <v>44776</v>
@@ -8608,7 +8608,7 @@
         </is>
       </c>
       <c r="S121">
-        <v>-35.18946395810077</v>
+        <v>-35.18946395810048</v>
       </c>
     </row>
     <row r="122">
@@ -8662,10 +8662,10 @@
         <v>19.55956107979261</v>
       </c>
       <c r="N122">
-        <v>18.78381922591106</v>
+        <v>18.78381922591102</v>
       </c>
       <c r="O122">
-        <v>18.78376405592467</v>
+        <v>18.78376405592434</v>
       </c>
       <c r="P122">
         <v>54535</v>
@@ -8730,10 +8730,10 @@
         <v>19.55956107979261</v>
       </c>
       <c r="N123">
-        <v>18.78381922591106</v>
+        <v>18.78381922591102</v>
       </c>
       <c r="O123">
-        <v>18.78376405592467</v>
+        <v>18.78376405592434</v>
       </c>
       <c r="P123">
         <v>54535</v>
@@ -8798,10 +8798,10 @@
         <v>19.55956107979261</v>
       </c>
       <c r="N124">
-        <v>18.78381922591106</v>
+        <v>18.78381922591102</v>
       </c>
       <c r="O124">
-        <v>18.78376405592467</v>
+        <v>18.78376405592434</v>
       </c>
       <c r="P124">
         <v>54535</v>
@@ -8812,7 +8812,7 @@
         </is>
       </c>
       <c r="S124">
-        <v>-0.5877807213773428</v>
+        <v>-0.5877807213773845</v>
       </c>
     </row>
     <row r="125">
@@ -8866,10 +8866,10 @@
         <v>19.55956107979261</v>
       </c>
       <c r="N125">
-        <v>18.78381922591106</v>
+        <v>18.78381922591102</v>
       </c>
       <c r="O125">
-        <v>18.78376405592467</v>
+        <v>18.78376405592434</v>
       </c>
       <c r="P125">
         <v>54535</v>
@@ -8880,7 +8880,7 @@
         </is>
       </c>
       <c r="S125">
-        <v>-0.587835891363736</v>
+        <v>-0.5878358913640636</v>
       </c>
     </row>
     <row r="126">
@@ -8934,10 +8934,10 @@
         <v>30.49659378673363</v>
       </c>
       <c r="N126">
-        <v>30.53786279215646</v>
+        <v>30.53786279215657</v>
       </c>
       <c r="O126">
-        <v>30.53774451303555</v>
+        <v>30.53774451303544</v>
       </c>
       <c r="P126">
         <v>54535</v>
@@ -9002,10 +9002,10 @@
         <v>30.49659378673363</v>
       </c>
       <c r="N127">
-        <v>30.53786279215646</v>
+        <v>30.53786279215657</v>
       </c>
       <c r="O127">
-        <v>30.53774451303555</v>
+        <v>30.53774451303544</v>
       </c>
       <c r="P127">
         <v>54535</v>
@@ -9070,10 +9070,10 @@
         <v>30.49659378673363</v>
       </c>
       <c r="N128">
-        <v>30.53786279215646</v>
+        <v>30.53786279215657</v>
       </c>
       <c r="O128">
-        <v>30.53774451303555</v>
+        <v>30.53774451303544</v>
       </c>
       <c r="P128">
         <v>54535</v>
@@ -9084,7 +9084,7 @@
         </is>
       </c>
       <c r="S128">
-        <v>-0.1367483492706933</v>
+        <v>-0.1367483492705823</v>
       </c>
     </row>
     <row r="129">
@@ -9138,10 +9138,10 @@
         <v>30.49659378673363</v>
       </c>
       <c r="N129">
-        <v>30.53786279215646</v>
+        <v>30.53786279215657</v>
       </c>
       <c r="O129">
-        <v>30.53774451303555</v>
+        <v>30.53774451303544</v>
       </c>
       <c r="P129">
         <v>54535</v>
@@ -9152,7 +9152,7 @@
         </is>
       </c>
       <c r="S129">
-        <v>-0.136866628391602</v>
+        <v>-0.136866628391713</v>
       </c>
     </row>
     <row r="130">
@@ -9206,10 +9206,10 @@
         <v>46.0408366864019</v>
       </c>
       <c r="N130">
-        <v>60.0704815986113</v>
+        <v>60.07048159861138</v>
       </c>
       <c r="O130">
-        <v>60.07051969567441</v>
+        <v>60.07051969567385</v>
       </c>
       <c r="P130">
         <v>54535</v>
@@ -9274,10 +9274,10 @@
         <v>46.0408366864019</v>
       </c>
       <c r="N131">
-        <v>60.0704815986113</v>
+        <v>60.07048159861138</v>
       </c>
       <c r="O131">
-        <v>60.07051969567441</v>
+        <v>60.07051969567385</v>
       </c>
       <c r="P131">
         <v>54535</v>
@@ -9342,10 +9342,10 @@
         <v>46.0408366864019</v>
       </c>
       <c r="N132">
-        <v>60.0704815986113</v>
+        <v>60.07048159861138</v>
       </c>
       <c r="O132">
-        <v>60.07051969567441</v>
+        <v>60.07051969567385</v>
       </c>
       <c r="P132">
         <v>54535</v>
@@ -9356,7 +9356,7 @@
         </is>
       </c>
       <c r="S132">
-        <v>-0.7931925941981666</v>
+        <v>-0.7931925941980889</v>
       </c>
     </row>
     <row r="133">
@@ -9410,10 +9410,10 @@
         <v>46.0408366864019</v>
       </c>
       <c r="N133">
-        <v>60.0704815986113</v>
+        <v>60.07048159861138</v>
       </c>
       <c r="O133">
-        <v>60.07051969567441</v>
+        <v>60.07051969567385</v>
       </c>
       <c r="P133">
         <v>54535</v>
@@ -9424,7 +9424,7 @@
         </is>
       </c>
       <c r="S133">
-        <v>-0.7931544971350624</v>
+        <v>-0.7931544971356175</v>
       </c>
     </row>
     <row r="134">
@@ -9478,10 +9478,10 @@
         <v>22.21829840823713</v>
       </c>
       <c r="N134">
-        <v>22.8075281326633</v>
+        <v>22.80752813266336</v>
       </c>
       <c r="O134">
-        <v>22.80764277056721</v>
+        <v>22.80764277056756</v>
       </c>
       <c r="P134">
         <v>47918</v>
@@ -9546,10 +9546,10 @@
         <v>22.21829840823713</v>
       </c>
       <c r="N135">
-        <v>22.8075281326633</v>
+        <v>22.80752813266336</v>
       </c>
       <c r="O135">
-        <v>22.80764277056721</v>
+        <v>22.80764277056756</v>
       </c>
       <c r="P135">
         <v>47918</v>
@@ -9614,10 +9614,10 @@
         <v>22.21829840823713</v>
       </c>
       <c r="N136">
-        <v>22.8075281326633</v>
+        <v>22.80752813266336</v>
       </c>
       <c r="O136">
-        <v>22.80764277056721</v>
+        <v>22.80764277056756</v>
       </c>
       <c r="P136">
         <v>47918</v>
@@ -9628,7 +9628,7 @@
         </is>
       </c>
       <c r="S136">
-        <v>-0.6564727659102182</v>
+        <v>-0.6564727659101488</v>
       </c>
     </row>
     <row r="137">
@@ -9682,10 +9682,10 @@
         <v>22.21829840823713</v>
       </c>
       <c r="N137">
-        <v>22.8075281326633</v>
+        <v>22.80752813266336</v>
       </c>
       <c r="O137">
-        <v>22.80764277056721</v>
+        <v>22.80764277056756</v>
       </c>
       <c r="P137">
         <v>47918</v>
@@ -9696,7 +9696,7 @@
         </is>
       </c>
       <c r="S137">
-        <v>-0.6563581280063013</v>
+        <v>-0.6563581280059488</v>
       </c>
     </row>
     <row r="138">
@@ -9750,7 +9750,7 @@
         <v>97.70353186034932</v>
       </c>
       <c r="N138">
-        <v>89.057646837029</v>
+        <v>89.05764683702921</v>
       </c>
       <c r="O138">
         <v>96.53969112716689</v>
@@ -9818,7 +9818,7 @@
         <v>97.70353186034932</v>
       </c>
       <c r="N139">
-        <v>89.057646837029</v>
+        <v>89.05764683702921</v>
       </c>
       <c r="O139">
         <v>96.53969112716689</v>
@@ -9886,7 +9886,7 @@
         <v>97.70353186034932</v>
       </c>
       <c r="N140">
-        <v>89.057646837029</v>
+        <v>89.05764683702921</v>
       </c>
       <c r="O140">
         <v>96.53969112716689</v>
@@ -9900,7 +9900,7 @@
         </is>
       </c>
       <c r="S140">
-        <v>-2.609675776510978</v>
+        <v>-2.609675776510767</v>
       </c>
     </row>
     <row r="141">
@@ -9954,7 +9954,7 @@
         <v>97.70353186034932</v>
       </c>
       <c r="N141">
-        <v>89.057646837029</v>
+        <v>89.05764683702921</v>
       </c>
       <c r="O141">
         <v>96.53969112716689</v>
@@ -10022,10 +10022,10 @@
         <v>60.16767859230833</v>
       </c>
       <c r="N142">
-        <v>61.88484918229447</v>
+        <v>61.88484918229459</v>
       </c>
       <c r="O142">
-        <v>61.4772745944154</v>
+        <v>61.47727459441587</v>
       </c>
       <c r="P142">
         <v>54426</v>
@@ -10090,10 +10090,10 @@
         <v>60.16767859230833</v>
       </c>
       <c r="N143">
-        <v>61.88484918229447</v>
+        <v>61.88484918229459</v>
       </c>
       <c r="O143">
-        <v>61.4772745944154</v>
+        <v>61.47727459441587</v>
       </c>
       <c r="P143">
         <v>54426</v>
@@ -10158,10 +10158,10 @@
         <v>60.16767859230833</v>
       </c>
       <c r="N144">
-        <v>61.88484918229447</v>
+        <v>61.88484918229459</v>
       </c>
       <c r="O144">
-        <v>61.4772745944154</v>
+        <v>61.47727459441587</v>
       </c>
       <c r="P144">
         <v>54426</v>
@@ -10172,7 +10172,7 @@
         </is>
       </c>
       <c r="S144">
-        <v>-1.127829715025674</v>
+        <v>-1.127829715025552</v>
       </c>
     </row>
     <row r="145">
@@ -10226,10 +10226,10 @@
         <v>60.16767859230833</v>
       </c>
       <c r="N145">
-        <v>61.88484918229447</v>
+        <v>61.88484918229459</v>
       </c>
       <c r="O145">
-        <v>61.4772745944154</v>
+        <v>61.47727459441587</v>
       </c>
       <c r="P145">
         <v>54426</v>
@@ -10240,7 +10240,7 @@
         </is>
       </c>
       <c r="S145">
-        <v>-1.535404302904742</v>
+        <v>-1.535404302904275</v>
       </c>
     </row>
     <row r="146">
@@ -10294,10 +10294,10 @@
         <v>51.81970969080953</v>
       </c>
       <c r="N146">
-        <v>52.10416026488397</v>
+        <v>52.10416026488398</v>
       </c>
       <c r="O146">
-        <v>53.71180101699645</v>
+        <v>53.71180101699651</v>
       </c>
       <c r="P146">
         <v>54535</v>
@@ -10362,10 +10362,10 @@
         <v>51.81970969080953</v>
       </c>
       <c r="N147">
-        <v>52.10416026488397</v>
+        <v>52.10416026488398</v>
       </c>
       <c r="O147">
-        <v>53.71180101699645</v>
+        <v>53.71180101699651</v>
       </c>
       <c r="P147">
         <v>54535</v>
@@ -10430,10 +10430,10 @@
         <v>51.81970969080953</v>
       </c>
       <c r="N148">
-        <v>52.10416026488397</v>
+        <v>52.10416026488398</v>
       </c>
       <c r="O148">
-        <v>53.71180101699645</v>
+        <v>53.71180101699651</v>
       </c>
       <c r="P148">
         <v>54535</v>
@@ -10444,7 +10444,7 @@
         </is>
       </c>
       <c r="S148">
-        <v>-0.1882192833705831</v>
+        <v>-0.188219283370572</v>
       </c>
     </row>
     <row r="149">
@@ -10498,10 +10498,10 @@
         <v>51.81970969080953</v>
       </c>
       <c r="N149">
-        <v>52.10416026488397</v>
+        <v>52.10416026488398</v>
       </c>
       <c r="O149">
-        <v>53.71180101699645</v>
+        <v>53.71180101699651</v>
       </c>
       <c r="P149">
         <v>54535</v>
@@ -10512,7 +10512,7 @@
         </is>
       </c>
       <c r="S149">
-        <v>1.419421468741899</v>
+        <v>1.419421468741955</v>
       </c>
     </row>
     <row r="150">
@@ -10566,10 +10566,10 @@
         <v>93.85406722827751</v>
       </c>
       <c r="N150">
-        <v>88.10981089169665</v>
+        <v>88.10981089169675</v>
       </c>
       <c r="O150">
-        <v>92.81601489807952</v>
+        <v>92.81601489807957</v>
       </c>
       <c r="P150">
         <v>54281</v>
@@ -10634,10 +10634,10 @@
         <v>93.85406722827751</v>
       </c>
       <c r="N151">
-        <v>88.10981089169665</v>
+        <v>88.10981089169675</v>
       </c>
       <c r="O151">
-        <v>92.81601489807952</v>
+        <v>92.81601489807957</v>
       </c>
       <c r="P151">
         <v>54281</v>
@@ -10702,10 +10702,10 @@
         <v>93.85406722827751</v>
       </c>
       <c r="N152">
-        <v>88.10981089169665</v>
+        <v>88.10981089169675</v>
       </c>
       <c r="O152">
-        <v>92.81601489807952</v>
+        <v>92.81601489807957</v>
       </c>
       <c r="P152">
         <v>54281</v>
@@ -10716,7 +10716,7 @@
         </is>
       </c>
       <c r="S152">
-        <v>0.03641639628380045</v>
+        <v>0.03641639628391147</v>
       </c>
     </row>
     <row r="153">
@@ -10770,10 +10770,10 @@
         <v>93.85406722827751</v>
       </c>
       <c r="N153">
-        <v>88.10981089169665</v>
+        <v>88.10981089169675</v>
       </c>
       <c r="O153">
-        <v>92.81601489807952</v>
+        <v>92.81601489807957</v>
       </c>
       <c r="P153">
         <v>54281</v>
@@ -10784,7 +10784,7 @@
         </is>
       </c>
       <c r="S153">
-        <v>4.742620402666664</v>
+        <v>4.742620402666731</v>
       </c>
     </row>
     <row r="154">
@@ -10838,10 +10838,10 @@
         <v>87.6320105705225</v>
       </c>
       <c r="N154">
-        <v>90.59641787470704</v>
+        <v>90.59641787470699</v>
       </c>
       <c r="O154">
-        <v>86.4560265318876</v>
+        <v>86.45602653188774</v>
       </c>
       <c r="P154">
         <v>54534</v>
@@ -10906,10 +10906,10 @@
         <v>87.6320105705225</v>
       </c>
       <c r="N155">
-        <v>90.59641787470704</v>
+        <v>90.59641787470699</v>
       </c>
       <c r="O155">
-        <v>86.4560265318876</v>
+        <v>86.45602653188774</v>
       </c>
       <c r="P155">
         <v>54534</v>
@@ -10974,10 +10974,10 @@
         <v>87.6320105705225</v>
       </c>
       <c r="N156">
-        <v>90.59641787470704</v>
+        <v>90.59641787470699</v>
       </c>
       <c r="O156">
-        <v>86.4560265318876</v>
+        <v>86.45602653188774</v>
       </c>
       <c r="P156">
         <v>54534</v>
@@ -10988,7 +10988,7 @@
         </is>
       </c>
       <c r="S156">
-        <v>0.6425753431986925</v>
+        <v>0.642575343198637</v>
       </c>
     </row>
     <row r="157">
@@ -11042,10 +11042,10 @@
         <v>87.6320105705225</v>
       </c>
       <c r="N157">
-        <v>90.59641787470704</v>
+        <v>90.59641787470699</v>
       </c>
       <c r="O157">
-        <v>86.4560265318876</v>
+        <v>86.45602653188774</v>
       </c>
       <c r="P157">
         <v>54534</v>
@@ -11056,7 +11056,7 @@
         </is>
       </c>
       <c r="S157">
-        <v>-3.497815999620746</v>
+        <v>-3.497815999620613</v>
       </c>
     </row>
     <row r="158">
@@ -11110,10 +11110,10 @@
         <v>77.14401961658972</v>
       </c>
       <c r="N158">
-        <v>81.45050683818823</v>
+        <v>81.45050683818815</v>
       </c>
       <c r="O158">
-        <v>77.4884120909541</v>
+        <v>77.48841209095431</v>
       </c>
       <c r="P158">
         <v>39772</v>
@@ -11178,10 +11178,10 @@
         <v>77.14401961658972</v>
       </c>
       <c r="N159">
-        <v>81.45050683818823</v>
+        <v>81.45050683818815</v>
       </c>
       <c r="O159">
-        <v>77.4884120909541</v>
+        <v>77.48841209095431</v>
       </c>
       <c r="P159">
         <v>39772</v>
@@ -11246,10 +11246,10 @@
         <v>77.14401961658972</v>
       </c>
       <c r="N160">
-        <v>81.45050683818823</v>
+        <v>81.45050683818815</v>
       </c>
       <c r="O160">
-        <v>77.4884120909541</v>
+        <v>77.48841209095431</v>
       </c>
       <c r="P160">
         <v>39772</v>
@@ -11260,7 +11260,7 @@
         </is>
       </c>
       <c r="S160">
-        <v>-0.5301548422915192</v>
+        <v>-0.5301548422915969</v>
       </c>
     </row>
     <row r="161">
@@ -11314,10 +11314,10 @@
         <v>77.14401961658972</v>
       </c>
       <c r="N161">
-        <v>81.45050683818823</v>
+        <v>81.45050683818815</v>
       </c>
       <c r="O161">
-        <v>77.4884120909541</v>
+        <v>77.48841209095431</v>
       </c>
       <c r="P161">
         <v>39772</v>
@@ -11328,7 +11328,7 @@
         </is>
       </c>
       <c r="S161">
-        <v>-4.492249589525644</v>
+        <v>-4.492249589525443</v>
       </c>
     </row>
     <row r="162">
@@ -11382,10 +11382,10 @@
         <v>94.73858354545469</v>
       </c>
       <c r="N162">
-        <v>53.97907512970576</v>
+        <v>53.97907512970481</v>
       </c>
       <c r="O162">
-        <v>90.77842736117594</v>
+        <v>90.77842736117616</v>
       </c>
       <c r="P162">
         <v>42552</v>
@@ -11450,10 +11450,10 @@
         <v>94.73858354545469</v>
       </c>
       <c r="N163">
-        <v>53.97907512970576</v>
+        <v>53.97907512970481</v>
       </c>
       <c r="O163">
-        <v>90.77842736117594</v>
+        <v>90.77842736117616</v>
       </c>
       <c r="P163">
         <v>42552</v>
@@ -11518,10 +11518,10 @@
         <v>94.73858354545469</v>
       </c>
       <c r="N164">
-        <v>53.97907512970576</v>
+        <v>53.97907512970481</v>
       </c>
       <c r="O164">
-        <v>90.77842736117594</v>
+        <v>90.77842736117616</v>
       </c>
       <c r="P164">
         <v>42552</v>
@@ -11532,7 +11532,7 @@
         </is>
       </c>
       <c r="S164">
-        <v>0.0008416705650216016</v>
+        <v>0.0008416705640779121</v>
       </c>
     </row>
     <row r="165">
@@ -11586,10 +11586,10 @@
         <v>94.73858354545469</v>
       </c>
       <c r="N165">
-        <v>53.97907512970576</v>
+        <v>53.97907512970481</v>
       </c>
       <c r="O165">
-        <v>90.77842736117594</v>
+        <v>90.77842736117616</v>
       </c>
       <c r="P165">
         <v>42552</v>
@@ -11600,7 +11600,7 @@
         </is>
       </c>
       <c r="S165">
-        <v>36.8001939020352</v>
+        <v>36.80019390203542</v>
       </c>
     </row>
     <row r="166">
@@ -20358,10 +20358,10 @@
         <v>13.71421764662618</v>
       </c>
       <c r="N294">
-        <v>15.41815523864194</v>
+        <v>15.41815523864195</v>
       </c>
       <c r="O294">
-        <v>15.39358401703903</v>
+        <v>15.39358401703959</v>
       </c>
       <c r="P294">
         <v>61000</v>
@@ -20426,10 +20426,10 @@
         <v>13.71421764662618</v>
       </c>
       <c r="N295">
-        <v>15.41815523864194</v>
+        <v>15.41815523864195</v>
       </c>
       <c r="O295">
-        <v>15.39358401703903</v>
+        <v>15.39358401703959</v>
       </c>
       <c r="P295">
         <v>61000</v>
@@ -20494,10 +20494,10 @@
         <v>13.71421764662618</v>
       </c>
       <c r="N296">
-        <v>15.41815523864194</v>
+        <v>15.41815523864195</v>
       </c>
       <c r="O296">
-        <v>15.39358401703903</v>
+        <v>15.39358401703959</v>
       </c>
       <c r="P296">
         <v>61000</v>
@@ -20508,7 +20508,7 @@
         </is>
       </c>
       <c r="S296">
-        <v>-2.434066014787231</v>
+        <v>-2.43406601478722</v>
       </c>
     </row>
     <row r="297">
@@ -20562,10 +20562,10 @@
         <v>13.71421764662618</v>
       </c>
       <c r="N297">
-        <v>15.41815523864194</v>
+        <v>15.41815523864195</v>
       </c>
       <c r="O297">
-        <v>15.39358401703903</v>
+        <v>15.39358401703959</v>
       </c>
       <c r="P297">
         <v>61000</v>
@@ -20576,7 +20576,7 @@
         </is>
       </c>
       <c r="S297">
-        <v>-2.458637236390146</v>
+        <v>-2.458637236389585</v>
       </c>
     </row>
     <row r="298">
@@ -20630,10 +20630,10 @@
         <v>29.42277298055462</v>
       </c>
       <c r="N298">
-        <v>28.57244554318082</v>
+        <v>28.57244554318077</v>
       </c>
       <c r="O298">
-        <v>28.56364349950706</v>
+        <v>28.56364349950802</v>
       </c>
       <c r="P298">
         <v>61000</v>
@@ -20698,10 +20698,10 @@
         <v>29.42277298055462</v>
       </c>
       <c r="N299">
-        <v>28.57244554318082</v>
+        <v>28.57244554318077</v>
       </c>
       <c r="O299">
-        <v>28.56364349950706</v>
+        <v>28.56364349950802</v>
       </c>
       <c r="P299">
         <v>61000</v>
@@ -20766,10 +20766,10 @@
         <v>29.42277298055462</v>
       </c>
       <c r="N300">
-        <v>28.57244554318082</v>
+        <v>28.57244554318077</v>
       </c>
       <c r="O300">
-        <v>28.56364349950706</v>
+        <v>28.56364349950802</v>
       </c>
       <c r="P300">
         <v>61000</v>
@@ -20780,7 +20780,7 @@
         </is>
       </c>
       <c r="S300">
-        <v>-0.5880716505328953</v>
+        <v>-0.5880716505329397</v>
       </c>
     </row>
     <row r="301">
@@ -20834,10 +20834,10 @@
         <v>29.42277298055462</v>
       </c>
       <c r="N301">
-        <v>28.57244554318082</v>
+        <v>28.57244554318077</v>
       </c>
       <c r="O301">
-        <v>28.56364349950706</v>
+        <v>28.56364349950802</v>
       </c>
       <c r="P301">
         <v>61000</v>
@@ -20848,7 +20848,7 @@
         </is>
       </c>
       <c r="S301">
-        <v>-0.5968736942066566</v>
+        <v>-0.5968736942056962</v>
       </c>
     </row>
     <row r="302">
@@ -20902,10 +20902,10 @@
         <v>45.4639903673616</v>
       </c>
       <c r="N302">
-        <v>57.98657659676807</v>
+        <v>57.98657659676809</v>
       </c>
       <c r="O302">
-        <v>58.0108328128641</v>
+        <v>58.0108328128659</v>
       </c>
       <c r="P302">
         <v>60966</v>
@@ -20970,10 +20970,10 @@
         <v>45.4639903673616</v>
       </c>
       <c r="N303">
-        <v>57.98657659676807</v>
+        <v>57.98657659676809</v>
       </c>
       <c r="O303">
-        <v>58.0108328128641</v>
+        <v>58.0108328128659</v>
       </c>
       <c r="P303">
         <v>60966</v>
@@ -21038,10 +21038,10 @@
         <v>45.4639903673616</v>
       </c>
       <c r="N304">
-        <v>57.98657659676807</v>
+        <v>57.98657659676809</v>
       </c>
       <c r="O304">
-        <v>58.0108328128641</v>
+        <v>58.0108328128659</v>
       </c>
       <c r="P304">
         <v>60966</v>
@@ -21052,7 +21052,7 @@
         </is>
       </c>
       <c r="S304">
-        <v>0.9354526786854334</v>
+        <v>0.9354526786854556</v>
       </c>
     </row>
     <row r="305">
@@ -21106,10 +21106,10 @@
         <v>45.4639903673616</v>
       </c>
       <c r="N305">
-        <v>57.98657659676807</v>
+        <v>57.98657659676809</v>
       </c>
       <c r="O305">
-        <v>58.0108328128641</v>
+        <v>58.0108328128659</v>
       </c>
       <c r="P305">
         <v>60966</v>
@@ -21120,7 +21120,7 @@
         </is>
       </c>
       <c r="S305">
-        <v>0.9597088947814636</v>
+        <v>0.9597088947832622</v>
       </c>
     </row>
     <row r="306">
@@ -21174,10 +21174,10 @@
         <v>22.87686769960688</v>
       </c>
       <c r="N306">
-        <v>24.28635160555295</v>
+        <v>24.28635160555294</v>
       </c>
       <c r="O306">
-        <v>24.30807920702731</v>
+        <v>24.30807920702841</v>
       </c>
       <c r="P306">
         <v>54906</v>
@@ -21242,10 +21242,10 @@
         <v>22.87686769960688</v>
       </c>
       <c r="N307">
-        <v>24.28635160555295</v>
+        <v>24.28635160555294</v>
       </c>
       <c r="O307">
-        <v>24.30807920702731</v>
+        <v>24.30807920702841</v>
       </c>
       <c r="P307">
         <v>54906</v>
@@ -21310,10 +21310,10 @@
         <v>22.87686769960688</v>
       </c>
       <c r="N308">
-        <v>24.28635160555295</v>
+        <v>24.28635160555294</v>
       </c>
       <c r="O308">
-        <v>24.30807920702731</v>
+        <v>24.30807920702841</v>
       </c>
       <c r="P308">
         <v>54906</v>
@@ -21324,7 +21324,7 @@
         </is>
       </c>
       <c r="S308">
-        <v>-0.3936985826528183</v>
+        <v>-0.3936985826528322</v>
       </c>
     </row>
     <row r="309">
@@ -21378,10 +21378,10 @@
         <v>22.87686769960688</v>
       </c>
       <c r="N309">
-        <v>24.28635160555295</v>
+        <v>24.28635160555294</v>
       </c>
       <c r="O309">
-        <v>24.30807920702731</v>
+        <v>24.30807920702841</v>
       </c>
       <c r="P309">
         <v>54906</v>
@@ -21392,7 +21392,7 @@
         </is>
       </c>
       <c r="S309">
-        <v>-0.3719709811784599</v>
+        <v>-0.3719709811773608</v>
       </c>
     </row>
     <row r="310">
@@ -21446,10 +21446,10 @@
         <v>96.75096455756443</v>
       </c>
       <c r="N310">
-        <v>86.70056156845874</v>
+        <v>86.70056156845875</v>
       </c>
       <c r="O310">
-        <v>96.82340183287779</v>
+        <v>96.82340183287785</v>
       </c>
       <c r="P310">
         <v>55751</v>
@@ -21514,10 +21514,10 @@
         <v>96.75096455756443</v>
       </c>
       <c r="N311">
-        <v>86.70056156845874</v>
+        <v>86.70056156845875</v>
       </c>
       <c r="O311">
-        <v>96.82340183287779</v>
+        <v>96.82340183287785</v>
       </c>
       <c r="P311">
         <v>55751</v>
@@ -21582,10 +21582,10 @@
         <v>96.75096455756443</v>
       </c>
       <c r="N312">
-        <v>86.70056156845874</v>
+        <v>86.70056156845875</v>
       </c>
       <c r="O312">
-        <v>96.82340183287779</v>
+        <v>96.82340183287785</v>
       </c>
       <c r="P312">
         <v>55751</v>
@@ -21596,7 +21596,7 @@
         </is>
       </c>
       <c r="S312">
-        <v>-3.506571111293733</v>
+        <v>-3.50657111129371</v>
       </c>
     </row>
     <row r="313">
@@ -21650,10 +21650,10 @@
         <v>96.75096455756443</v>
       </c>
       <c r="N313">
-        <v>86.70056156845874</v>
+        <v>86.70056156845875</v>
       </c>
       <c r="O313">
-        <v>96.82340183287779</v>
+        <v>96.82340183287785</v>
       </c>
       <c r="P313">
         <v>55751</v>
@@ -21664,7 +21664,7 @@
         </is>
       </c>
       <c r="S313">
-        <v>6.61626915312532</v>
+        <v>6.616269153125376</v>
       </c>
     </row>
     <row r="314">
@@ -21718,10 +21718,10 @@
         <v>60.51866627019677</v>
       </c>
       <c r="N314">
-        <v>59.81528043082663</v>
+        <v>59.81528043082665</v>
       </c>
       <c r="O314">
-        <v>60.34381502084364</v>
+        <v>60.34381502084475</v>
       </c>
       <c r="P314">
         <v>60920</v>
@@ -21786,10 +21786,10 @@
         <v>60.51866627019677</v>
       </c>
       <c r="N315">
-        <v>59.81528043082663</v>
+        <v>59.81528043082665</v>
       </c>
       <c r="O315">
-        <v>60.34381502084364</v>
+        <v>60.34381502084475</v>
       </c>
       <c r="P315">
         <v>60920</v>
@@ -21854,10 +21854,10 @@
         <v>60.51866627019677</v>
       </c>
       <c r="N316">
-        <v>59.81528043082663</v>
+        <v>59.81528043082665</v>
       </c>
       <c r="O316">
-        <v>60.34381502084364</v>
+        <v>60.34381502084475</v>
       </c>
       <c r="P316">
         <v>60920</v>
@@ -21868,7 +21868,7 @@
         </is>
       </c>
       <c r="S316">
-        <v>-1.367740548997154</v>
+        <v>-1.367740548997121</v>
       </c>
     </row>
     <row r="317">
@@ -21922,10 +21922,10 @@
         <v>60.51866627019677</v>
       </c>
       <c r="N317">
-        <v>59.81528043082663</v>
+        <v>59.81528043082665</v>
       </c>
       <c r="O317">
-        <v>60.34381502084364</v>
+        <v>60.34381502084475</v>
       </c>
       <c r="P317">
         <v>60920</v>
@@ -21936,7 +21936,7 @@
         </is>
       </c>
       <c r="S317">
-        <v>-0.8392059589801382</v>
+        <v>-0.8392059589790279</v>
       </c>
     </row>
     <row r="318">
@@ -21990,10 +21990,10 @@
         <v>51.49802933758593</v>
       </c>
       <c r="N318">
-        <v>51.87442533665201</v>
+        <v>51.87442533665195</v>
       </c>
       <c r="O318">
-        <v>55.19320995384727</v>
+        <v>55.19320995384758</v>
       </c>
       <c r="P318">
         <v>61000</v>
@@ -22058,10 +22058,10 @@
         <v>51.49802933758593</v>
       </c>
       <c r="N319">
-        <v>51.87442533665201</v>
+        <v>51.87442533665195</v>
       </c>
       <c r="O319">
-        <v>55.19320995384727</v>
+        <v>55.19320995384758</v>
       </c>
       <c r="P319">
         <v>61000</v>
@@ -22126,10 +22126,10 @@
         <v>51.49802933758593</v>
       </c>
       <c r="N320">
-        <v>51.87442533665201</v>
+        <v>51.87442533665195</v>
       </c>
       <c r="O320">
-        <v>55.19320995384727</v>
+        <v>55.19320995384758</v>
       </c>
       <c r="P320">
         <v>61000</v>
@@ -22140,7 +22140,7 @@
         </is>
       </c>
       <c r="S320">
-        <v>-0.2309273630906716</v>
+        <v>-0.2309273630907271</v>
       </c>
     </row>
     <row r="321">
@@ -22194,10 +22194,10 @@
         <v>51.49802933758593</v>
       </c>
       <c r="N321">
-        <v>51.87442533665201</v>
+        <v>51.87442533665195</v>
       </c>
       <c r="O321">
-        <v>55.19320995384727</v>
+        <v>55.19320995384758</v>
       </c>
       <c r="P321">
         <v>61000</v>
@@ -22208,7 +22208,7 @@
         </is>
       </c>
       <c r="S321">
-        <v>3.087857254104587</v>
+        <v>3.087857254104898</v>
       </c>
     </row>
     <row r="322">
@@ -22262,10 +22262,10 @@
         <v>94.03767983644056</v>
       </c>
       <c r="N322">
-        <v>88.60775405607029</v>
+        <v>88.60775405607038</v>
       </c>
       <c r="O322">
-        <v>92.81092514217536</v>
+        <v>92.81092514217534</v>
       </c>
       <c r="P322">
         <v>60928</v>
@@ -22330,10 +22330,10 @@
         <v>94.03767983644056</v>
       </c>
       <c r="N323">
-        <v>88.60775405607029</v>
+        <v>88.60775405607038</v>
       </c>
       <c r="O323">
-        <v>92.81092514217536</v>
+        <v>92.81092514217534</v>
       </c>
       <c r="P323">
         <v>60928</v>
@@ -22398,10 +22398,10 @@
         <v>94.03767983644056</v>
       </c>
       <c r="N324">
-        <v>88.60775405607029</v>
+        <v>88.60775405607038</v>
       </c>
       <c r="O324">
-        <v>92.81092514217536</v>
+        <v>92.81092514217534</v>
       </c>
       <c r="P324">
         <v>60928</v>
@@ -22412,7 +22412,7 @@
         </is>
       </c>
       <c r="S324">
-        <v>-0.3433119337774126</v>
+        <v>-0.3433119337773349</v>
       </c>
     </row>
     <row r="325">
@@ -22466,10 +22466,10 @@
         <v>94.03767983644056</v>
       </c>
       <c r="N325">
-        <v>88.60775405607029</v>
+        <v>88.60775405607038</v>
       </c>
       <c r="O325">
-        <v>92.81092514217536</v>
+        <v>92.81092514217534</v>
       </c>
       <c r="P325">
         <v>60928</v>
@@ -22480,7 +22480,7 @@
         </is>
       </c>
       <c r="S325">
-        <v>3.859859152327649</v>
+        <v>3.859859152327627</v>
       </c>
     </row>
     <row r="326">
@@ -22534,10 +22534,10 @@
         <v>90.12539655528288</v>
       </c>
       <c r="N326">
-        <v>92.49798818801627</v>
+        <v>92.49798818801629</v>
       </c>
       <c r="O326">
-        <v>89.42387194359372</v>
+        <v>89.42387194359381</v>
       </c>
       <c r="P326">
         <v>61000</v>
@@ -22602,10 +22602,10 @@
         <v>90.12539655528288</v>
       </c>
       <c r="N327">
-        <v>92.49798818801627</v>
+        <v>92.49798818801629</v>
       </c>
       <c r="O327">
-        <v>89.42387194359372</v>
+        <v>89.42387194359381</v>
       </c>
       <c r="P327">
         <v>61000</v>
@@ -22670,10 +22670,10 @@
         <v>90.12539655528288</v>
       </c>
       <c r="N328">
-        <v>92.49798818801627</v>
+        <v>92.49798818801629</v>
       </c>
       <c r="O328">
-        <v>89.42387194359372</v>
+        <v>89.42387194359381</v>
       </c>
       <c r="P328">
         <v>61000</v>
@@ -22684,7 +22684,7 @@
         </is>
       </c>
       <c r="S328">
-        <v>0.9126431762666365</v>
+        <v>0.9126431762666587</v>
       </c>
     </row>
     <row r="329">
@@ -22738,10 +22738,10 @@
         <v>90.12539655528288</v>
       </c>
       <c r="N329">
-        <v>92.49798818801627</v>
+        <v>92.49798818801629</v>
       </c>
       <c r="O329">
-        <v>89.42387194359372</v>
+        <v>89.42387194359381</v>
       </c>
       <c r="P329">
         <v>61000</v>
@@ -22752,7 +22752,7 @@
         </is>
       </c>
       <c r="S329">
-        <v>-2.161473068155906</v>
+        <v>-2.161473068155828</v>
       </c>
     </row>
     <row r="330">
@@ -22806,10 +22806,10 @@
         <v>56.56833363518013</v>
       </c>
       <c r="N330">
-        <v>56.80719956100185</v>
+        <v>56.80719956100195</v>
       </c>
       <c r="O330">
-        <v>53.77092581252928</v>
+        <v>53.77092581252965</v>
       </c>
       <c r="P330">
         <v>45790</v>
@@ -22874,10 +22874,10 @@
         <v>56.56833363518013</v>
       </c>
       <c r="N331">
-        <v>56.80719956100185</v>
+        <v>56.80719956100195</v>
       </c>
       <c r="O331">
-        <v>53.77092581252928</v>
+        <v>53.77092581252965</v>
       </c>
       <c r="P331">
         <v>45790</v>
@@ -22942,10 +22942,10 @@
         <v>56.56833363518013</v>
       </c>
       <c r="N332">
-        <v>56.80719956100185</v>
+        <v>56.80719956100195</v>
       </c>
       <c r="O332">
-        <v>53.77092581252928</v>
+        <v>53.77092581252965</v>
       </c>
       <c r="P332">
         <v>45790</v>
@@ -22956,7 +22956,7 @@
         </is>
       </c>
       <c r="S332">
-        <v>0.3061338125184943</v>
+        <v>0.3061338125185942</v>
       </c>
     </row>
     <row r="333">
@@ -23010,10 +23010,10 @@
         <v>56.56833363518013</v>
       </c>
       <c r="N333">
-        <v>56.80719956100185</v>
+        <v>56.80719956100195</v>
       </c>
       <c r="O333">
-        <v>53.77092581252928</v>
+        <v>53.77092581252965</v>
       </c>
       <c r="P333">
         <v>45790</v>
@@ -23024,7 +23024,7 @@
         </is>
       </c>
       <c r="S333">
-        <v>-2.730139935954079</v>
+        <v>-2.730139935953713</v>
       </c>
     </row>
     <row r="334">
@@ -23078,10 +23078,10 @@
         <v>90.08926438227013</v>
       </c>
       <c r="N334">
-        <v>62.0772182760082</v>
+        <v>62.07721827600816</v>
       </c>
       <c r="O334">
-        <v>94.75407612852116</v>
+        <v>94.75407612852125</v>
       </c>
       <c r="P334">
         <v>48462</v>
@@ -23146,10 +23146,10 @@
         <v>90.08926438227013</v>
       </c>
       <c r="N335">
-        <v>62.0772182760082</v>
+        <v>62.07721827600816</v>
       </c>
       <c r="O335">
-        <v>94.75407612852116</v>
+        <v>94.75407612852125</v>
       </c>
       <c r="P335">
         <v>48462</v>
@@ -23214,10 +23214,10 @@
         <v>90.08926438227013</v>
       </c>
       <c r="N336">
-        <v>62.0772182760082</v>
+        <v>62.07721827600816</v>
       </c>
       <c r="O336">
-        <v>94.75407612852116</v>
+        <v>94.75407612852125</v>
       </c>
       <c r="P336">
         <v>48462</v>
@@ -23228,7 +23228,7 @@
         </is>
       </c>
       <c r="S336">
-        <v>0.2443851464968394</v>
+        <v>0.244385146496795</v>
       </c>
     </row>
     <row r="337">
@@ -23282,10 +23282,10 @@
         <v>90.08926438227013</v>
       </c>
       <c r="N337">
-        <v>62.0772182760082</v>
+        <v>62.07721827600816</v>
       </c>
       <c r="O337">
-        <v>94.75407612852116</v>
+        <v>94.75407612852125</v>
       </c>
       <c r="P337">
         <v>48462</v>
@@ -23296,7 +23296,7 @@
         </is>
       </c>
       <c r="S337">
-        <v>32.92124299900981</v>
+        <v>32.92124299900988</v>
       </c>
     </row>
     <row r="338">
@@ -23350,10 +23350,10 @@
         <v>13.63679623448249</v>
       </c>
       <c r="N338">
-        <v>15.79902661390823</v>
+        <v>15.79903111329061</v>
       </c>
       <c r="O338">
-        <v>15.7990265685755</v>
+        <v>15.79902656857579</v>
       </c>
       <c r="P338">
         <v>60000</v>
@@ -23418,10 +23418,10 @@
         <v>13.63679623448249</v>
       </c>
       <c r="N339">
-        <v>15.79902661390823</v>
+        <v>15.79903111329061</v>
       </c>
       <c r="O339">
-        <v>15.7990265685755</v>
+        <v>15.79902656857579</v>
       </c>
       <c r="P339">
         <v>60000</v>
@@ -23486,10 +23486,10 @@
         <v>13.63679623448249</v>
       </c>
       <c r="N340">
-        <v>15.79902661390823</v>
+        <v>15.79903111329061</v>
       </c>
       <c r="O340">
-        <v>15.7990265685755</v>
+        <v>15.79902656857579</v>
       </c>
       <c r="P340">
         <v>60000</v>
@@ -23500,7 +23500,7 @@
         </is>
       </c>
       <c r="S340">
-        <v>-2.973347407419533</v>
+        <v>-2.973342908037155</v>
       </c>
     </row>
     <row r="341">
@@ -23554,10 +23554,10 @@
         <v>13.63679623448249</v>
       </c>
       <c r="N341">
-        <v>15.79902661390823</v>
+        <v>15.79903111329061</v>
       </c>
       <c r="O341">
-        <v>15.7990265685755</v>
+        <v>15.79902656857579</v>
       </c>
       <c r="P341">
         <v>60000</v>
@@ -23568,7 +23568,7 @@
         </is>
       </c>
       <c r="S341">
-        <v>-2.97334745275227</v>
+        <v>-2.973347452751979</v>
       </c>
     </row>
     <row r="342">
@@ -23622,10 +23622,10 @@
         <v>28.71709917682972</v>
       </c>
       <c r="N342">
-        <v>29.12343032366759</v>
+        <v>29.1234330717829</v>
       </c>
       <c r="O342">
-        <v>29.12342358088552</v>
+        <v>29.12342358088578</v>
       </c>
       <c r="P342">
         <v>60000</v>
@@ -23690,10 +23690,10 @@
         <v>28.71709917682972</v>
       </c>
       <c r="N343">
-        <v>29.12343032366759</v>
+        <v>29.1234330717829</v>
       </c>
       <c r="O343">
-        <v>29.12342358088552</v>
+        <v>29.12342358088578</v>
       </c>
       <c r="P343">
         <v>60000</v>
@@ -23758,10 +23758,10 @@
         <v>28.71709917682972</v>
       </c>
       <c r="N344">
-        <v>29.12343032366759</v>
+        <v>29.1234330717829</v>
       </c>
       <c r="O344">
-        <v>29.12342358088552</v>
+        <v>29.12342358088578</v>
       </c>
       <c r="P344">
         <v>60000</v>
@@ -23772,7 +23772,7 @@
         </is>
       </c>
       <c r="S344">
-        <v>-0.3447549026368069</v>
+        <v>-0.3447521545214938</v>
       </c>
     </row>
     <row r="345">
@@ -23826,10 +23826,10 @@
         <v>28.71709917682972</v>
       </c>
       <c r="N345">
-        <v>29.12343032366759</v>
+        <v>29.1234330717829</v>
       </c>
       <c r="O345">
-        <v>29.12342358088552</v>
+        <v>29.12342358088578</v>
       </c>
       <c r="P345">
         <v>60000</v>
@@ -23840,7 +23840,7 @@
         </is>
       </c>
       <c r="S345">
-        <v>-0.3447616454188729</v>
+        <v>-0.3447616454186175</v>
       </c>
     </row>
     <row r="346">
@@ -23894,10 +23894,10 @@
         <v>49.38494464192657</v>
       </c>
       <c r="N346">
-        <v>60.91533786695899</v>
+        <v>60.91535036081953</v>
       </c>
       <c r="O346">
-        <v>60.91538488022654</v>
+        <v>60.91538488022671</v>
       </c>
       <c r="P346">
         <v>59952</v>
@@ -23962,10 +23962,10 @@
         <v>49.38494464192657</v>
       </c>
       <c r="N347">
-        <v>60.91533786695899</v>
+        <v>60.91535036081953</v>
       </c>
       <c r="O347">
-        <v>60.91538488022654</v>
+        <v>60.91538488022671</v>
       </c>
       <c r="P347">
         <v>59952</v>
@@ -24030,10 +24030,10 @@
         <v>49.38494464192657</v>
       </c>
       <c r="N348">
-        <v>60.91533786695899</v>
+        <v>60.91535036081953</v>
       </c>
       <c r="O348">
-        <v>60.91538488022654</v>
+        <v>60.91538488022671</v>
       </c>
       <c r="P348">
         <v>59952</v>
@@ -24044,7 +24044,7 @@
         </is>
       </c>
       <c r="S348">
-        <v>2.019571604702652</v>
+        <v>2.019584098563187</v>
       </c>
     </row>
     <row r="349">
@@ -24098,10 +24098,10 @@
         <v>49.38494464192657</v>
       </c>
       <c r="N349">
-        <v>60.91533786695899</v>
+        <v>60.91535036081953</v>
       </c>
       <c r="O349">
-        <v>60.91538488022654</v>
+        <v>60.91538488022671</v>
       </c>
       <c r="P349">
         <v>59952</v>
@@ -24112,7 +24112,7 @@
         </is>
       </c>
       <c r="S349">
-        <v>2.019618617970198</v>
+        <v>2.019618617970365</v>
       </c>
     </row>
     <row r="350">
@@ -24166,10 +24166,10 @@
         <v>22.5997561136882</v>
       </c>
       <c r="N350">
-        <v>23.77362719719695</v>
+        <v>23.77362779864108</v>
       </c>
       <c r="O350">
-        <v>23.77362873790585</v>
+        <v>23.77362873790611</v>
       </c>
       <c r="P350">
         <v>55143</v>
@@ -24234,10 +24234,10 @@
         <v>22.5997561136882</v>
       </c>
       <c r="N351">
-        <v>23.77362719719695</v>
+        <v>23.77362779864108</v>
       </c>
       <c r="O351">
-        <v>23.77362873790585</v>
+        <v>23.77362873790611</v>
       </c>
       <c r="P351">
         <v>55143</v>
@@ -24302,10 +24302,10 @@
         <v>22.5997561136882</v>
       </c>
       <c r="N352">
-        <v>23.77362719719695</v>
+        <v>23.77362779864108</v>
       </c>
       <c r="O352">
-        <v>23.77362873790585</v>
+        <v>23.77362873790611</v>
       </c>
       <c r="P352">
         <v>55143</v>
@@ -24316,7 +24316,7 @@
         </is>
       </c>
       <c r="S352">
-        <v>-0.3448168947264851</v>
+        <v>-0.3448162932823545</v>
       </c>
     </row>
     <row r="353">
@@ -24370,10 +24370,10 @@
         <v>22.5997561136882</v>
       </c>
       <c r="N353">
-        <v>23.77362719719695</v>
+        <v>23.77362779864108</v>
       </c>
       <c r="O353">
-        <v>23.77362873790585</v>
+        <v>23.77362873790611</v>
       </c>
       <c r="P353">
         <v>55143</v>
@@ -24384,7 +24384,7 @@
         </is>
       </c>
       <c r="S353">
-        <v>-0.3448153540175858</v>
+        <v>-0.3448153540173249</v>
       </c>
     </row>
     <row r="354">
@@ -24438,10 +24438,10 @@
         <v>91.09254484367177</v>
       </c>
       <c r="N354">
-        <v>86.61759446798273</v>
+        <v>86.61759427225223</v>
       </c>
       <c r="O354">
-        <v>90.83563195911086</v>
+        <v>90.83563195911087</v>
       </c>
       <c r="P354">
         <v>57277</v>
@@ -24506,10 +24506,10 @@
         <v>91.09254484367177</v>
       </c>
       <c r="N355">
-        <v>86.61759446798273</v>
+        <v>86.61759427225223</v>
       </c>
       <c r="O355">
-        <v>90.83563195911086</v>
+        <v>90.83563195911087</v>
       </c>
       <c r="P355">
         <v>57277</v>
@@ -24574,10 +24574,10 @@
         <v>91.09254484367177</v>
       </c>
       <c r="N356">
-        <v>86.61759446798273</v>
+        <v>86.61759427225223</v>
       </c>
       <c r="O356">
-        <v>90.83563195911086</v>
+        <v>90.83563195911087</v>
       </c>
       <c r="P356">
         <v>57277</v>
@@ -24588,7 +24588,7 @@
         </is>
       </c>
       <c r="S356">
-        <v>-2.943012570225256</v>
+        <v>-2.943012765955744</v>
       </c>
     </row>
     <row r="357">
@@ -24642,10 +24642,10 @@
         <v>91.09254484367177</v>
       </c>
       <c r="N357">
-        <v>86.61759446798273</v>
+        <v>86.61759427225223</v>
       </c>
       <c r="O357">
-        <v>90.83563195911086</v>
+        <v>90.83563195911087</v>
       </c>
       <c r="P357">
         <v>57277</v>
@@ -24656,7 +24656,7 @@
         </is>
       </c>
       <c r="S357">
-        <v>1.275024920902879</v>
+        <v>1.27502492090289</v>
       </c>
     </row>
     <row r="358">
@@ -24675,17 +24675,17 @@
       </c>
       <c r="D358" t="inlineStr">
         <is>
-          <t>Sex</t>
+          <t>Residence Duration</t>
         </is>
       </c>
       <c r="E358" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>5 years or longer</t>
         </is>
       </c>
       <c r="F358" t="inlineStr">
         <is>
-          <t>Primary</t>
+          <t>Secondary</t>
         </is>
       </c>
       <c r="G358" t="b">
@@ -24698,25 +24698,25 @@
         <v>0</v>
       </c>
       <c r="J358" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K358">
-        <v>52.08816782768694</v>
+        <v>62.78175698310654</v>
       </c>
       <c r="L358">
-        <v>53.54498598122996</v>
+        <v>61.71963677639047</v>
       </c>
       <c r="M358">
-        <v>52.20547113980047</v>
+        <v>60.99375995409059</v>
       </c>
       <c r="N358">
-        <v>51.5832883890784</v>
+        <v>61.01690685229683</v>
       </c>
       <c r="O358">
-        <v>51.69280674241715</v>
+        <v>60.71393243350647</v>
       </c>
       <c r="P358">
-        <v>59563</v>
+        <v>59908</v>
       </c>
       <c r="R358" t="inlineStr">
         <is>
@@ -24724,7 +24724,7 @@
         </is>
       </c>
       <c r="S358">
-        <v>1.456818153543016</v>
+        <v>-1.062120206716077</v>
       </c>
     </row>
     <row r="359">
@@ -24743,17 +24743,17 @@
       </c>
       <c r="D359" t="inlineStr">
         <is>
-          <t>Sex</t>
+          <t>Residence Duration</t>
         </is>
       </c>
       <c r="E359" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>5 years or longer</t>
         </is>
       </c>
       <c r="F359" t="inlineStr">
         <is>
-          <t>Primary</t>
+          <t>Secondary</t>
         </is>
       </c>
       <c r="G359" t="b">
@@ -24766,25 +24766,25 @@
         <v>0</v>
       </c>
       <c r="J359" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K359">
-        <v>52.08816782768694</v>
+        <v>62.78175698310654</v>
       </c>
       <c r="L359">
-        <v>53.54498598122996</v>
+        <v>61.71963677639047</v>
       </c>
       <c r="M359">
-        <v>52.20547113980047</v>
+        <v>60.99375995409059</v>
       </c>
       <c r="N359">
-        <v>51.5832883890784</v>
+        <v>61.01690685229683</v>
       </c>
       <c r="O359">
-        <v>51.69280674241715</v>
+        <v>60.71393243350647</v>
       </c>
       <c r="P359">
-        <v>59563</v>
+        <v>59908</v>
       </c>
       <c r="R359" t="inlineStr">
         <is>
@@ -24792,7 +24792,7 @@
         </is>
       </c>
       <c r="S359">
-        <v>0.1173033121135258</v>
+        <v>-1.787997029015953</v>
       </c>
     </row>
     <row r="360">
@@ -24811,17 +24811,17 @@
       </c>
       <c r="D360" t="inlineStr">
         <is>
-          <t>Sex</t>
+          <t>Residence Duration</t>
         </is>
       </c>
       <c r="E360" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>5 years or longer</t>
         </is>
       </c>
       <c r="F360" t="inlineStr">
         <is>
-          <t>Primary</t>
+          <t>Secondary</t>
         </is>
       </c>
       <c r="G360" t="b">
@@ -24834,25 +24834,25 @@
         <v>0</v>
       </c>
       <c r="J360" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K360">
-        <v>52.08816782768694</v>
+        <v>62.78175698310654</v>
       </c>
       <c r="L360">
-        <v>53.54498598122996</v>
+        <v>61.71963677639047</v>
       </c>
       <c r="M360">
-        <v>52.20547113980047</v>
+        <v>60.99375995409059</v>
       </c>
       <c r="N360">
-        <v>51.5832883890784</v>
+        <v>61.01690685229683</v>
       </c>
       <c r="O360">
-        <v>51.69280674241715</v>
+        <v>60.71393243350647</v>
       </c>
       <c r="P360">
-        <v>59563</v>
+        <v>59908</v>
       </c>
       <c r="R360" t="inlineStr">
         <is>
@@ -24860,7 +24860,7 @@
         </is>
       </c>
       <c r="S360">
-        <v>-0.5048794386085298</v>
+        <v>-1.764850130809714</v>
       </c>
     </row>
     <row r="361">
@@ -24879,17 +24879,17 @@
       </c>
       <c r="D361" t="inlineStr">
         <is>
-          <t>Sex</t>
+          <t>Residence Duration</t>
         </is>
       </c>
       <c r="E361" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>5 years or longer</t>
         </is>
       </c>
       <c r="F361" t="inlineStr">
         <is>
-          <t>Primary</t>
+          <t>Secondary</t>
         </is>
       </c>
       <c r="G361" t="b">
@@ -24902,25 +24902,25 @@
         <v>0</v>
       </c>
       <c r="J361" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K361">
-        <v>52.08816782768694</v>
+        <v>62.78175698310654</v>
       </c>
       <c r="L361">
-        <v>53.54498598122996</v>
+        <v>61.71963677639047</v>
       </c>
       <c r="M361">
-        <v>52.20547113980047</v>
+        <v>60.99375995409059</v>
       </c>
       <c r="N361">
-        <v>51.5832883890784</v>
+        <v>61.01690685229683</v>
       </c>
       <c r="O361">
-        <v>51.69280674241715</v>
+        <v>60.71393243350647</v>
       </c>
       <c r="P361">
-        <v>59563</v>
+        <v>59908</v>
       </c>
       <c r="R361" t="inlineStr">
         <is>
@@ -24928,7 +24928,7 @@
         </is>
       </c>
       <c r="S361">
-        <v>-0.3953610852697853</v>
+        <v>-2.067824549600072</v>
       </c>
     </row>
     <row r="362">
@@ -24947,17 +24947,17 @@
       </c>
       <c r="D362" t="inlineStr">
         <is>
-          <t>Union Membership</t>
+          <t>Sex</t>
         </is>
       </c>
       <c r="E362" t="inlineStr">
         <is>
-          <t>Not current union member</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="F362" t="inlineStr">
         <is>
-          <t>Secondary</t>
+          <t>Primary</t>
         </is>
       </c>
       <c r="G362" t="b">
@@ -24970,25 +24970,25 @@
         <v>0</v>
       </c>
       <c r="J362" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K362">
-        <v>89.75011666878791</v>
+        <v>52.08816782768694</v>
       </c>
       <c r="L362">
-        <v>93.26294368828397</v>
+        <v>53.54498598122996</v>
       </c>
       <c r="M362">
-        <v>94.03545595788032</v>
+        <v>52.20547113980047</v>
       </c>
       <c r="N362">
-        <v>89.30448547879433</v>
+        <v>51.58328699371187</v>
       </c>
       <c r="O362">
-        <v>92.04660792596596</v>
+        <v>51.69280674241718</v>
       </c>
       <c r="P362">
-        <v>59952</v>
+        <v>59563</v>
       </c>
       <c r="R362" t="inlineStr">
         <is>
@@ -24996,7 +24996,7 @@
         </is>
       </c>
       <c r="S362">
-        <v>3.512827019496045</v>
+        <v>1.456818153543016</v>
       </c>
     </row>
     <row r="363">
@@ -25015,17 +25015,17 @@
       </c>
       <c r="D363" t="inlineStr">
         <is>
-          <t>Union Membership</t>
+          <t>Sex</t>
         </is>
       </c>
       <c r="E363" t="inlineStr">
         <is>
-          <t>Not current union member</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="F363" t="inlineStr">
         <is>
-          <t>Secondary</t>
+          <t>Primary</t>
         </is>
       </c>
       <c r="G363" t="b">
@@ -25038,25 +25038,25 @@
         <v>0</v>
       </c>
       <c r="J363" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K363">
-        <v>89.75011666878791</v>
+        <v>52.08816782768694</v>
       </c>
       <c r="L363">
-        <v>93.26294368828397</v>
+        <v>53.54498598122996</v>
       </c>
       <c r="M363">
-        <v>94.03545595788032</v>
+        <v>52.20547113980047</v>
       </c>
       <c r="N363">
-        <v>89.30448547879433</v>
+        <v>51.58328699371187</v>
       </c>
       <c r="O363">
-        <v>92.04660792596596</v>
+        <v>51.69280674241718</v>
       </c>
       <c r="P363">
-        <v>59952</v>
+        <v>59563</v>
       </c>
       <c r="R363" t="inlineStr">
         <is>
@@ -25064,7 +25064,7 @@
         </is>
       </c>
       <c r="S363">
-        <v>4.285339289092393</v>
+        <v>0.1173033121135258</v>
       </c>
     </row>
     <row r="364">
@@ -25083,17 +25083,17 @@
       </c>
       <c r="D364" t="inlineStr">
         <is>
-          <t>Union Membership</t>
+          <t>Sex</t>
         </is>
       </c>
       <c r="E364" t="inlineStr">
         <is>
-          <t>Not current union member</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="F364" t="inlineStr">
         <is>
-          <t>Secondary</t>
+          <t>Primary</t>
         </is>
       </c>
       <c r="G364" t="b">
@@ -25106,25 +25106,25 @@
         <v>0</v>
       </c>
       <c r="J364" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K364">
-        <v>89.75011666878791</v>
+        <v>52.08816782768694</v>
       </c>
       <c r="L364">
-        <v>93.26294368828397</v>
+        <v>53.54498598122996</v>
       </c>
       <c r="M364">
-        <v>94.03545595788032</v>
+        <v>52.20547113980047</v>
       </c>
       <c r="N364">
-        <v>89.30448547879433</v>
+        <v>51.58328699371187</v>
       </c>
       <c r="O364">
-        <v>92.04660792596596</v>
+        <v>51.69280674241718</v>
       </c>
       <c r="P364">
-        <v>59952</v>
+        <v>59563</v>
       </c>
       <c r="R364" t="inlineStr">
         <is>
@@ -25132,7 +25132,7 @@
         </is>
       </c>
       <c r="S364">
-        <v>-0.4456311899935783</v>
+        <v>-0.5048808339750743</v>
       </c>
     </row>
     <row r="365">
@@ -25151,17 +25151,17 @@
       </c>
       <c r="D365" t="inlineStr">
         <is>
-          <t>Union Membership</t>
+          <t>Sex</t>
         </is>
       </c>
       <c r="E365" t="inlineStr">
         <is>
-          <t>Not current union member</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="F365" t="inlineStr">
         <is>
-          <t>Secondary</t>
+          <t>Primary</t>
         </is>
       </c>
       <c r="G365" t="b">
@@ -25174,25 +25174,25 @@
         <v>0</v>
       </c>
       <c r="J365" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K365">
-        <v>89.75011666878791</v>
+        <v>52.08816782768694</v>
       </c>
       <c r="L365">
-        <v>93.26294368828397</v>
+        <v>53.54498598122996</v>
       </c>
       <c r="M365">
-        <v>94.03545595788032</v>
+        <v>52.20547113980047</v>
       </c>
       <c r="N365">
-        <v>89.30448547879433</v>
+        <v>51.58328699371187</v>
       </c>
       <c r="O365">
-        <v>92.04660792596596</v>
+        <v>51.69280674241718</v>
       </c>
       <c r="P365">
-        <v>59952</v>
+        <v>59563</v>
       </c>
       <c r="R365" t="inlineStr">
         <is>
@@ -25200,7 +25200,7 @@
         </is>
       </c>
       <c r="S365">
-        <v>2.296491257178046</v>
+        <v>-0.395361085269752</v>
       </c>
     </row>
     <row r="366">
@@ -25219,12 +25219,12 @@
       </c>
       <c r="D366" t="inlineStr">
         <is>
-          <t>Veteran Status</t>
+          <t>Union Membership</t>
         </is>
       </c>
       <c r="E366" t="inlineStr">
         <is>
-          <t>Non-veteran</t>
+          <t>Not current union member</t>
         </is>
       </c>
       <c r="F366" t="inlineStr">
@@ -25245,22 +25245,22 @@
         <v>1</v>
       </c>
       <c r="K366">
-        <v>92.01159398266043</v>
+        <v>89.75011666878791</v>
       </c>
       <c r="L366">
-        <v>89.36833333333334</v>
+        <v>93.26294368828397</v>
       </c>
       <c r="M366">
-        <v>90.81416282496983</v>
+        <v>94.03545595788032</v>
       </c>
       <c r="N366">
-        <v>92.88968287704053</v>
+        <v>89.30448482920681</v>
       </c>
       <c r="O366">
-        <v>89.6150820305524</v>
+        <v>92.04660792596593</v>
       </c>
       <c r="P366">
-        <v>60000</v>
+        <v>59952</v>
       </c>
       <c r="R366" t="inlineStr">
         <is>
@@ -25268,7 +25268,7 @@
         </is>
       </c>
       <c r="S366">
-        <v>-2.643260649327084</v>
+        <v>3.512827019496045</v>
       </c>
     </row>
     <row r="367">
@@ -25287,12 +25287,12 @@
       </c>
       <c r="D367" t="inlineStr">
         <is>
-          <t>Veteran Status</t>
+          <t>Union Membership</t>
         </is>
       </c>
       <c r="E367" t="inlineStr">
         <is>
-          <t>Non-veteran</t>
+          <t>Not current union member</t>
         </is>
       </c>
       <c r="F367" t="inlineStr">
@@ -25313,22 +25313,22 @@
         <v>1</v>
       </c>
       <c r="K367">
-        <v>92.01159398266043</v>
+        <v>89.75011666878791</v>
       </c>
       <c r="L367">
-        <v>89.36833333333334</v>
+        <v>93.26294368828397</v>
       </c>
       <c r="M367">
-        <v>90.81416282496983</v>
+        <v>94.03545595788032</v>
       </c>
       <c r="N367">
-        <v>92.88968287704053</v>
+        <v>89.30448482920681</v>
       </c>
       <c r="O367">
-        <v>89.6150820305524</v>
+        <v>92.04660792596593</v>
       </c>
       <c r="P367">
-        <v>60000</v>
+        <v>59952</v>
       </c>
       <c r="R367" t="inlineStr">
         <is>
@@ -25336,7 +25336,7 @@
         </is>
       </c>
       <c r="S367">
-        <v>-1.197431157690598</v>
+        <v>4.285339289092393</v>
       </c>
     </row>
     <row r="368">
@@ -25355,12 +25355,12 @@
       </c>
       <c r="D368" t="inlineStr">
         <is>
-          <t>Veteran Status</t>
+          <t>Union Membership</t>
         </is>
       </c>
       <c r="E368" t="inlineStr">
         <is>
-          <t>Non-veteran</t>
+          <t>Not current union member</t>
         </is>
       </c>
       <c r="F368" t="inlineStr">
@@ -25381,22 +25381,22 @@
         <v>1</v>
       </c>
       <c r="K368">
-        <v>92.01159398266043</v>
+        <v>89.75011666878791</v>
       </c>
       <c r="L368">
-        <v>89.36833333333334</v>
+        <v>93.26294368828397</v>
       </c>
       <c r="M368">
-        <v>90.81416282496983</v>
+        <v>94.03545595788032</v>
       </c>
       <c r="N368">
-        <v>92.88968287704053</v>
+        <v>89.30448482920681</v>
       </c>
       <c r="O368">
-        <v>89.6150820305524</v>
+        <v>92.04660792596593</v>
       </c>
       <c r="P368">
-        <v>60000</v>
+        <v>59952</v>
       </c>
       <c r="R368" t="inlineStr">
         <is>
@@ -25404,7 +25404,7 @@
         </is>
       </c>
       <c r="S368">
-        <v>0.8780888943801024</v>
+        <v>-0.4456318395810954</v>
       </c>
     </row>
     <row r="369">
@@ -25423,12 +25423,12 @@
       </c>
       <c r="D369" t="inlineStr">
         <is>
-          <t>Veteran Status</t>
+          <t>Union Membership</t>
         </is>
       </c>
       <c r="E369" t="inlineStr">
         <is>
-          <t>Non-veteran</t>
+          <t>Not current union member</t>
         </is>
       </c>
       <c r="F369" t="inlineStr">
@@ -25449,22 +25449,22 @@
         <v>1</v>
       </c>
       <c r="K369">
-        <v>92.01159398266043</v>
+        <v>89.75011666878791</v>
       </c>
       <c r="L369">
-        <v>89.36833333333334</v>
+        <v>93.26294368828397</v>
       </c>
       <c r="M369">
-        <v>90.81416282496983</v>
+        <v>94.03545595788032</v>
       </c>
       <c r="N369">
-        <v>92.88968287704053</v>
+        <v>89.30448482920681</v>
       </c>
       <c r="O369">
-        <v>89.6150820305524</v>
+        <v>92.04660792596593</v>
       </c>
       <c r="P369">
-        <v>60000</v>
+        <v>59952</v>
       </c>
       <c r="R369" t="inlineStr">
         <is>
@@ -25472,7 +25472,7 @@
         </is>
       </c>
       <c r="S369">
-        <v>-2.396511952108016</v>
+        <v>2.296491257178013</v>
       </c>
     </row>
     <row r="370">
@@ -25486,17 +25486,17 @@
       </c>
       <c r="C370" t="inlineStr">
         <is>
-          <t>Voting Administration</t>
+          <t>Demographic</t>
         </is>
       </c>
       <c r="D370" t="inlineStr">
         <is>
-          <t>Voting Method</t>
+          <t>Veteran Status</t>
         </is>
       </c>
       <c r="E370" t="inlineStr">
         <is>
-          <t>In person</t>
+          <t>Non-veteran</t>
         </is>
       </c>
       <c r="F370" t="inlineStr">
@@ -25517,22 +25517,22 @@
         <v>1</v>
       </c>
       <c r="K370">
-        <v>67.38796807857581</v>
+        <v>92.01159398266043</v>
       </c>
       <c r="L370">
-        <v>64.47793326157158</v>
+        <v>89.36833333333334</v>
       </c>
       <c r="M370">
-        <v>66.36932631856995</v>
+        <v>90.81416282496983</v>
       </c>
       <c r="N370">
-        <v>68.08470929799424</v>
+        <v>92.88968438627357</v>
       </c>
       <c r="O370">
-        <v>65.01271796233409</v>
+        <v>89.61508203055229</v>
       </c>
       <c r="P370">
-        <v>40876</v>
+        <v>60000</v>
       </c>
       <c r="R370" t="inlineStr">
         <is>
@@ -25540,7 +25540,7 @@
         </is>
       </c>
       <c r="S370">
-        <v>-2.910034817004226</v>
+        <v>-2.643260649327084</v>
       </c>
     </row>
     <row r="371">
@@ -25554,17 +25554,17 @@
       </c>
       <c r="C371" t="inlineStr">
         <is>
-          <t>Voting Administration</t>
+          <t>Demographic</t>
         </is>
       </c>
       <c r="D371" t="inlineStr">
         <is>
-          <t>Voting Method</t>
+          <t>Veteran Status</t>
         </is>
       </c>
       <c r="E371" t="inlineStr">
         <is>
-          <t>In person</t>
+          <t>Non-veteran</t>
         </is>
       </c>
       <c r="F371" t="inlineStr">
@@ -25585,22 +25585,22 @@
         <v>1</v>
       </c>
       <c r="K371">
-        <v>67.38796807857581</v>
+        <v>92.01159398266043</v>
       </c>
       <c r="L371">
-        <v>64.47793326157158</v>
+        <v>89.36833333333334</v>
       </c>
       <c r="M371">
-        <v>66.36932631856995</v>
+        <v>90.81416282496983</v>
       </c>
       <c r="N371">
-        <v>68.08470929799424</v>
+        <v>92.88968438627357</v>
       </c>
       <c r="O371">
-        <v>65.01271796233409</v>
+        <v>89.61508203055229</v>
       </c>
       <c r="P371">
-        <v>40876</v>
+        <v>60000</v>
       </c>
       <c r="R371" t="inlineStr">
         <is>
@@ -25608,7 +25608,7 @@
         </is>
       </c>
       <c r="S371">
-        <v>-1.018641760005867</v>
+        <v>-1.197431157690598</v>
       </c>
     </row>
     <row r="372">
@@ -25622,17 +25622,17 @@
       </c>
       <c r="C372" t="inlineStr">
         <is>
-          <t>Voting Administration</t>
+          <t>Demographic</t>
         </is>
       </c>
       <c r="D372" t="inlineStr">
         <is>
-          <t>Voting Method</t>
+          <t>Veteran Status</t>
         </is>
       </c>
       <c r="E372" t="inlineStr">
         <is>
-          <t>In person</t>
+          <t>Non-veteran</t>
         </is>
       </c>
       <c r="F372" t="inlineStr">
@@ -25653,22 +25653,22 @@
         <v>1</v>
       </c>
       <c r="K372">
-        <v>67.38796807857581</v>
+        <v>92.01159398266043</v>
       </c>
       <c r="L372">
-        <v>64.47793326157158</v>
+        <v>89.36833333333334</v>
       </c>
       <c r="M372">
-        <v>66.36932631856995</v>
+        <v>90.81416282496983</v>
       </c>
       <c r="N372">
-        <v>68.08470929799424</v>
+        <v>92.88968438627357</v>
       </c>
       <c r="O372">
-        <v>65.01271796233409</v>
+        <v>89.61508203055229</v>
       </c>
       <c r="P372">
-        <v>40876</v>
+        <v>60000</v>
       </c>
       <c r="R372" t="inlineStr">
         <is>
@@ -25676,7 +25676,7 @@
         </is>
       </c>
       <c r="S372">
-        <v>0.6967412194184286</v>
+        <v>0.878090403613152</v>
       </c>
     </row>
     <row r="373">
@@ -25690,17 +25690,17 @@
       </c>
       <c r="C373" t="inlineStr">
         <is>
-          <t>Voting Administration</t>
+          <t>Demographic</t>
         </is>
       </c>
       <c r="D373" t="inlineStr">
         <is>
-          <t>Voting Method</t>
+          <t>Veteran Status</t>
         </is>
       </c>
       <c r="E373" t="inlineStr">
         <is>
-          <t>In person</t>
+          <t>Non-veteran</t>
         </is>
       </c>
       <c r="F373" t="inlineStr">
@@ -25721,22 +25721,22 @@
         <v>1</v>
       </c>
       <c r="K373">
-        <v>67.38796807857581</v>
+        <v>92.01159398266043</v>
       </c>
       <c r="L373">
-        <v>64.47793326157158</v>
+        <v>89.36833333333334</v>
       </c>
       <c r="M373">
-        <v>66.36932631856995</v>
+        <v>90.81416282496983</v>
       </c>
       <c r="N373">
-        <v>68.08470929799424</v>
+        <v>92.88968438627357</v>
       </c>
       <c r="O373">
-        <v>65.01271796233409</v>
+        <v>89.61508203055229</v>
       </c>
       <c r="P373">
-        <v>40876</v>
+        <v>60000</v>
       </c>
       <c r="R373" t="inlineStr">
         <is>
@@ -25744,7 +25744,7 @@
         </is>
       </c>
       <c r="S373">
-        <v>-2.375250116241723</v>
+        <v>-2.396511952108138</v>
       </c>
     </row>
     <row r="374">
@@ -25763,12 +25763,12 @@
       </c>
       <c r="D374" t="inlineStr">
         <is>
-          <t>Voting Turnout</t>
+          <t>Voting Method</t>
         </is>
       </c>
       <c r="E374" t="inlineStr">
         <is>
-          <t>Did not vote</t>
+          <t>In person</t>
         </is>
       </c>
       <c r="F374" t="inlineStr">
@@ -25789,22 +25789,22 @@
         <v>1</v>
       </c>
       <c r="K374">
-        <v>57.1867220532585</v>
+        <v>67.38796807857581</v>
       </c>
       <c r="L374">
-        <v>15.30204431796782</v>
+        <v>64.47793326157158</v>
       </c>
       <c r="M374">
-        <v>7.294531710394677</v>
+        <v>66.36932631856995</v>
       </c>
       <c r="N374">
-        <v>57.18662972561633</v>
+        <v>68.08470983266751</v>
       </c>
       <c r="O374">
-        <v>14.73483535187088</v>
+        <v>65.01271796233431</v>
       </c>
       <c r="P374">
-        <v>47791</v>
+        <v>40876</v>
       </c>
       <c r="R374" t="inlineStr">
         <is>
@@ -25812,7 +25812,7 @@
         </is>
       </c>
       <c r="S374">
-        <v>-41.88467773529068</v>
+        <v>-2.910034817004226</v>
       </c>
     </row>
     <row r="375">
@@ -25831,12 +25831,12 @@
       </c>
       <c r="D375" t="inlineStr">
         <is>
-          <t>Voting Turnout</t>
+          <t>Voting Method</t>
         </is>
       </c>
       <c r="E375" t="inlineStr">
         <is>
-          <t>Did not vote</t>
+          <t>In person</t>
         </is>
       </c>
       <c r="F375" t="inlineStr">
@@ -25857,22 +25857,22 @@
         <v>1</v>
       </c>
       <c r="K375">
-        <v>57.1867220532585</v>
+        <v>67.38796807857581</v>
       </c>
       <c r="L375">
-        <v>15.30204431796782</v>
+        <v>64.47793326157158</v>
       </c>
       <c r="M375">
-        <v>7.294531710394677</v>
+        <v>66.36932631856995</v>
       </c>
       <c r="N375">
-        <v>57.18662972561633</v>
+        <v>68.08470983266751</v>
       </c>
       <c r="O375">
-        <v>14.73483535187088</v>
+        <v>65.01271796233431</v>
       </c>
       <c r="P375">
-        <v>47791</v>
+        <v>40876</v>
       </c>
       <c r="R375" t="inlineStr">
         <is>
@@ -25880,7 +25880,7 @@
         </is>
       </c>
       <c r="S375">
-        <v>-49.89219034286382</v>
+        <v>-1.018641760005867</v>
       </c>
     </row>
     <row r="376">
@@ -25899,12 +25899,12 @@
       </c>
       <c r="D376" t="inlineStr">
         <is>
-          <t>Voting Turnout</t>
+          <t>Voting Method</t>
         </is>
       </c>
       <c r="E376" t="inlineStr">
         <is>
-          <t>Did not vote</t>
+          <t>In person</t>
         </is>
       </c>
       <c r="F376" t="inlineStr">
@@ -25925,22 +25925,22 @@
         <v>1</v>
       </c>
       <c r="K376">
-        <v>57.1867220532585</v>
+        <v>67.38796807857581</v>
       </c>
       <c r="L376">
-        <v>15.30204431796782</v>
+        <v>64.47793326157158</v>
       </c>
       <c r="M376">
-        <v>7.294531710394677</v>
+        <v>66.36932631856995</v>
       </c>
       <c r="N376">
-        <v>57.18662972561633</v>
+        <v>68.08470983266751</v>
       </c>
       <c r="O376">
-        <v>14.73483535187088</v>
+        <v>65.01271796233431</v>
       </c>
       <c r="P376">
-        <v>47791</v>
+        <v>40876</v>
       </c>
       <c r="R376" t="inlineStr">
         <is>
@@ -25948,7 +25948,7 @@
         </is>
       </c>
       <c r="S376">
-        <v>-9.23276421649355E-05</v>
+        <v>0.6967417540917009</v>
       </c>
     </row>
     <row r="377">
@@ -25967,56 +25967,328 @@
       </c>
       <c r="D377" t="inlineStr">
         <is>
+          <t>Voting Method</t>
+        </is>
+      </c>
+      <c r="E377" t="inlineStr">
+        <is>
+          <t>In person</t>
+        </is>
+      </c>
+      <c r="F377" t="inlineStr">
+        <is>
+          <t>Secondary</t>
+        </is>
+      </c>
+      <c r="G377" t="b">
+        <v>1</v>
+      </c>
+      <c r="H377" t="b">
+        <v>0</v>
+      </c>
+      <c r="I377" t="b">
+        <v>0</v>
+      </c>
+      <c r="J377" t="b">
+        <v>1</v>
+      </c>
+      <c r="K377">
+        <v>67.38796807857581</v>
+      </c>
+      <c r="L377">
+        <v>64.47793326157158</v>
+      </c>
+      <c r="M377">
+        <v>66.36932631856995</v>
+      </c>
+      <c r="N377">
+        <v>68.08470983266751</v>
+      </c>
+      <c r="O377">
+        <v>65.01271796233431</v>
+      </c>
+      <c r="P377">
+        <v>40876</v>
+      </c>
+      <c r="R377" t="inlineStr">
+        <is>
+          <t>ANESRake-Restricted</t>
+        </is>
+      </c>
+      <c r="S377">
+        <v>-2.375250116241501</v>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378">
+        <v>2022</v>
+      </c>
+      <c r="B378" t="inlineStr">
+        <is>
+          <t>NATIONAL</t>
+        </is>
+      </c>
+      <c r="C378" t="inlineStr">
+        <is>
+          <t>Voting Administration</t>
+        </is>
+      </c>
+      <c r="D378" t="inlineStr">
+        <is>
           <t>Voting Turnout</t>
         </is>
       </c>
-      <c r="E377" t="inlineStr">
+      <c r="E378" t="inlineStr">
         <is>
           <t>Did not vote</t>
         </is>
       </c>
-      <c r="F377" t="inlineStr">
-        <is>
-          <t>Secondary</t>
-        </is>
-      </c>
-      <c r="G377" t="b">
-        <v>1</v>
-      </c>
-      <c r="H377" t="b">
-        <v>0</v>
-      </c>
-      <c r="I377" t="b">
-        <v>0</v>
-      </c>
-      <c r="J377" t="b">
-        <v>1</v>
-      </c>
-      <c r="K377">
+      <c r="F378" t="inlineStr">
+        <is>
+          <t>Secondary</t>
+        </is>
+      </c>
+      <c r="G378" t="b">
+        <v>1</v>
+      </c>
+      <c r="H378" t="b">
+        <v>0</v>
+      </c>
+      <c r="I378" t="b">
+        <v>0</v>
+      </c>
+      <c r="J378" t="b">
+        <v>1</v>
+      </c>
+      <c r="K378">
         <v>57.1867220532585</v>
       </c>
-      <c r="L377">
+      <c r="L378">
         <v>15.30204431796782</v>
       </c>
-      <c r="M377">
+      <c r="M378">
         <v>7.294531710394677</v>
       </c>
-      <c r="N377">
-        <v>57.18662972561633</v>
-      </c>
-      <c r="O377">
-        <v>14.73483535187088</v>
-      </c>
-      <c r="P377">
+      <c r="N378">
+        <v>57.18663105574594</v>
+      </c>
+      <c r="O378">
+        <v>14.7348353518708</v>
+      </c>
+      <c r="P378">
         <v>47791</v>
       </c>
-      <c r="R377" t="inlineStr">
+      <c r="R378" t="inlineStr">
+        <is>
+          <t>CES-Unweighted</t>
+        </is>
+      </c>
+      <c r="S378">
+        <v>-41.88467773529068</v>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379">
+        <v>2022</v>
+      </c>
+      <c r="B379" t="inlineStr">
+        <is>
+          <t>NATIONAL</t>
+        </is>
+      </c>
+      <c r="C379" t="inlineStr">
+        <is>
+          <t>Voting Administration</t>
+        </is>
+      </c>
+      <c r="D379" t="inlineStr">
+        <is>
+          <t>Voting Turnout</t>
+        </is>
+      </c>
+      <c r="E379" t="inlineStr">
+        <is>
+          <t>Did not vote</t>
+        </is>
+      </c>
+      <c r="F379" t="inlineStr">
+        <is>
+          <t>Secondary</t>
+        </is>
+      </c>
+      <c r="G379" t="b">
+        <v>1</v>
+      </c>
+      <c r="H379" t="b">
+        <v>0</v>
+      </c>
+      <c r="I379" t="b">
+        <v>0</v>
+      </c>
+      <c r="J379" t="b">
+        <v>1</v>
+      </c>
+      <c r="K379">
+        <v>57.1867220532585</v>
+      </c>
+      <c r="L379">
+        <v>15.30204431796782</v>
+      </c>
+      <c r="M379">
+        <v>7.294531710394677</v>
+      </c>
+      <c r="N379">
+        <v>57.18663105574594</v>
+      </c>
+      <c r="O379">
+        <v>14.7348353518708</v>
+      </c>
+      <c r="P379">
+        <v>47791</v>
+      </c>
+      <c r="R379" t="inlineStr">
+        <is>
+          <t>CES-Provided Weights</t>
+        </is>
+      </c>
+      <c r="S379">
+        <v>-49.89219034286382</v>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380">
+        <v>2022</v>
+      </c>
+      <c r="B380" t="inlineStr">
+        <is>
+          <t>NATIONAL</t>
+        </is>
+      </c>
+      <c r="C380" t="inlineStr">
+        <is>
+          <t>Voting Administration</t>
+        </is>
+      </c>
+      <c r="D380" t="inlineStr">
+        <is>
+          <t>Voting Turnout</t>
+        </is>
+      </c>
+      <c r="E380" t="inlineStr">
+        <is>
+          <t>Did not vote</t>
+        </is>
+      </c>
+      <c r="F380" t="inlineStr">
+        <is>
+          <t>Secondary</t>
+        </is>
+      </c>
+      <c r="G380" t="b">
+        <v>1</v>
+      </c>
+      <c r="H380" t="b">
+        <v>0</v>
+      </c>
+      <c r="I380" t="b">
+        <v>0</v>
+      </c>
+      <c r="J380" t="b">
+        <v>1</v>
+      </c>
+      <c r="K380">
+        <v>57.1867220532585</v>
+      </c>
+      <c r="L380">
+        <v>15.30204431796782</v>
+      </c>
+      <c r="M380">
+        <v>7.294531710394677</v>
+      </c>
+      <c r="N380">
+        <v>57.18663105574594</v>
+      </c>
+      <c r="O380">
+        <v>14.7348353518708</v>
+      </c>
+      <c r="P380">
+        <v>47791</v>
+      </c>
+      <c r="R380" t="inlineStr">
+        <is>
+          <t>ANESRake-Full</t>
+        </is>
+      </c>
+      <c r="S380">
+        <v>-9.099751255847721E-05</v>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381">
+        <v>2022</v>
+      </c>
+      <c r="B381" t="inlineStr">
+        <is>
+          <t>NATIONAL</t>
+        </is>
+      </c>
+      <c r="C381" t="inlineStr">
+        <is>
+          <t>Voting Administration</t>
+        </is>
+      </c>
+      <c r="D381" t="inlineStr">
+        <is>
+          <t>Voting Turnout</t>
+        </is>
+      </c>
+      <c r="E381" t="inlineStr">
+        <is>
+          <t>Did not vote</t>
+        </is>
+      </c>
+      <c r="F381" t="inlineStr">
+        <is>
+          <t>Secondary</t>
+        </is>
+      </c>
+      <c r="G381" t="b">
+        <v>1</v>
+      </c>
+      <c r="H381" t="b">
+        <v>0</v>
+      </c>
+      <c r="I381" t="b">
+        <v>0</v>
+      </c>
+      <c r="J381" t="b">
+        <v>1</v>
+      </c>
+      <c r="K381">
+        <v>57.1867220532585</v>
+      </c>
+      <c r="L381">
+        <v>15.30204431796782</v>
+      </c>
+      <c r="M381">
+        <v>7.294531710394677</v>
+      </c>
+      <c r="N381">
+        <v>57.18663105574594</v>
+      </c>
+      <c r="O381">
+        <v>14.7348353518708</v>
+      </c>
+      <c r="P381">
+        <v>47791</v>
+      </c>
+      <c r="R381" t="inlineStr">
         <is>
           <t>ANESRake-Restricted</t>
         </is>
       </c>
-      <c r="S377">
-        <v>-42.45188670138761</v>
+      <c r="S381">
+        <v>-42.4518867013877</v>
       </c>
     </row>
   </sheetData>

--- a/tables_and_figures/input_tables/national_errors.xlsx
+++ b/tables_and_figures/input_tables/national_errors.xlsx
@@ -5670,10 +5670,10 @@
         <v>19.71418188895098</v>
       </c>
       <c r="N78">
-        <v>21.68983558756369</v>
+        <v>21.68983558756392</v>
       </c>
       <c r="O78">
-        <v>21.68983558756393</v>
+        <v>21.68983558756405</v>
       </c>
       <c r="P78">
         <v>55400</v>
@@ -5738,10 +5738,10 @@
         <v>19.71418188895098</v>
       </c>
       <c r="N79">
-        <v>21.68983558756369</v>
+        <v>21.68983558756392</v>
       </c>
       <c r="O79">
-        <v>21.68983558756393</v>
+        <v>21.68983558756405</v>
       </c>
       <c r="P79">
         <v>55400</v>
@@ -5806,10 +5806,10 @@
         <v>19.71418188895098</v>
       </c>
       <c r="N80">
-        <v>21.68983558756369</v>
+        <v>21.68983558756392</v>
       </c>
       <c r="O80">
-        <v>21.68983558756393</v>
+        <v>21.68983558756405</v>
       </c>
       <c r="P80">
         <v>55400</v>
@@ -5820,7 +5820,7 @@
         </is>
       </c>
       <c r="S80">
-        <v>1.936748087924511</v>
+        <v>1.936748087924742</v>
       </c>
     </row>
     <row r="81">
@@ -5874,10 +5874,10 @@
         <v>19.71418188895098</v>
       </c>
       <c r="N81">
-        <v>21.68983558756369</v>
+        <v>21.68983558756392</v>
       </c>
       <c r="O81">
-        <v>21.68983558756393</v>
+        <v>21.68983558756405</v>
       </c>
       <c r="P81">
         <v>55400</v>
@@ -5888,7 +5888,7 @@
         </is>
       </c>
       <c r="S81">
-        <v>1.936748087924747</v>
+        <v>1.936748087924864</v>
       </c>
     </row>
     <row r="82">
@@ -5942,10 +5942,10 @@
         <v>34.574542787282</v>
       </c>
       <c r="N82">
-        <v>32.131084023464</v>
+        <v>32.13108402346401</v>
       </c>
       <c r="O82">
-        <v>32.13108402346392</v>
+        <v>32.13108402346418</v>
       </c>
       <c r="P82">
         <v>55400</v>
@@ -6010,10 +6010,10 @@
         <v>34.574542787282</v>
       </c>
       <c r="N83">
-        <v>32.131084023464</v>
+        <v>32.13108402346401</v>
       </c>
       <c r="O83">
-        <v>32.13108402346392</v>
+        <v>32.13108402346418</v>
       </c>
       <c r="P83">
         <v>55400</v>
@@ -6078,10 +6078,10 @@
         <v>34.574542787282</v>
       </c>
       <c r="N84">
-        <v>32.131084023464</v>
+        <v>32.13108402346401</v>
       </c>
       <c r="O84">
-        <v>32.13108402346392</v>
+        <v>32.13108402346418</v>
       </c>
       <c r="P84">
         <v>55400</v>
@@ -6092,7 +6092,7 @@
         </is>
       </c>
       <c r="S84">
-        <v>0.44453379206007</v>
+        <v>0.4445337920600756</v>
       </c>
     </row>
     <row r="85">
@@ -6146,10 +6146,10 @@
         <v>34.574542787282</v>
       </c>
       <c r="N85">
-        <v>32.131084023464</v>
+        <v>32.13108402346401</v>
       </c>
       <c r="O85">
-        <v>32.13108402346392</v>
+        <v>32.13108402346418</v>
       </c>
       <c r="P85">
         <v>55400</v>
@@ -6160,7 +6160,7 @@
         </is>
       </c>
       <c r="S85">
-        <v>0.4445337920599868</v>
+        <v>0.4445337920602477</v>
       </c>
     </row>
     <row r="86">
@@ -6214,10 +6214,10 @@
         <v>49.75314441747606</v>
       </c>
       <c r="N86">
-        <v>60.64538348495072</v>
+        <v>60.64538348494989</v>
       </c>
       <c r="O86">
-        <v>60.64538348495044</v>
+        <v>60.64538348495076</v>
       </c>
       <c r="P86">
         <v>55400</v>
@@ -6282,10 +6282,10 @@
         <v>49.75314441747606</v>
       </c>
       <c r="N87">
-        <v>60.64538348495072</v>
+        <v>60.64538348494989</v>
       </c>
       <c r="O87">
-        <v>60.64538348495044</v>
+        <v>60.64538348495076</v>
       </c>
       <c r="P87">
         <v>55400</v>
@@ -6350,10 +6350,10 @@
         <v>49.75314441747606</v>
       </c>
       <c r="N88">
-        <v>60.64538348495072</v>
+        <v>60.64538348494989</v>
       </c>
       <c r="O88">
-        <v>60.64538348495044</v>
+        <v>60.64538348495076</v>
       </c>
       <c r="P88">
         <v>55400</v>
@@ -6364,7 +6364,7 @@
         </is>
       </c>
       <c r="S88">
-        <v>-0.2387361085900874</v>
+        <v>-0.2387361085909201</v>
       </c>
     </row>
     <row r="89">
@@ -6418,10 +6418,10 @@
         <v>49.75314441747606</v>
       </c>
       <c r="N89">
-        <v>60.64538348495072</v>
+        <v>60.64538348494989</v>
       </c>
       <c r="O89">
-        <v>60.64538348495044</v>
+        <v>60.64538348495076</v>
       </c>
       <c r="P89">
         <v>55400</v>
@@ -6432,7 +6432,7 @@
         </is>
       </c>
       <c r="S89">
-        <v>-0.238736108590365</v>
+        <v>-0.238736108590043</v>
       </c>
     </row>
     <row r="90">
@@ -6486,10 +6486,10 @@
         <v>22.91056164538115</v>
       </c>
       <c r="N90">
-        <v>23.19167199619718</v>
+        <v>23.19167199619754</v>
       </c>
       <c r="O90">
-        <v>23.19287782028157</v>
+        <v>23.19287782028184</v>
       </c>
       <c r="P90">
         <v>48612</v>
@@ -6554,10 +6554,10 @@
         <v>22.91056164538115</v>
       </c>
       <c r="N91">
-        <v>23.19167199619718</v>
+        <v>23.19167199619754</v>
       </c>
       <c r="O91">
-        <v>23.19287782028157</v>
+        <v>23.19287782028184</v>
       </c>
       <c r="P91">
         <v>48612</v>
@@ -6622,10 +6622,10 @@
         <v>22.91056164538115</v>
       </c>
       <c r="N92">
-        <v>23.19167199619718</v>
+        <v>23.19167199619754</v>
       </c>
       <c r="O92">
-        <v>23.19287782028157</v>
+        <v>23.19287782028184</v>
       </c>
       <c r="P92">
         <v>48612</v>
@@ -6636,7 +6636,7 @@
         </is>
       </c>
       <c r="S92">
-        <v>-0.2830345174889337</v>
+        <v>-0.2830345174885757</v>
       </c>
     </row>
     <row r="93">
@@ -6690,10 +6690,10 @@
         <v>22.91056164538115</v>
       </c>
       <c r="N93">
-        <v>23.19167199619718</v>
+        <v>23.19167199619754</v>
       </c>
       <c r="O93">
-        <v>23.19287782028157</v>
+        <v>23.19287782028184</v>
       </c>
       <c r="P93">
         <v>48612</v>
@@ -6704,7 +6704,7 @@
         </is>
       </c>
       <c r="S93">
-        <v>-0.2818286934045483</v>
+        <v>-0.2818286934042763</v>
       </c>
     </row>
     <row r="94">
@@ -6758,10 +6758,10 @@
         <v>97.35418313024078</v>
       </c>
       <c r="N94">
-        <v>90.07772910426878</v>
+        <v>90.07772910426883</v>
       </c>
       <c r="O94">
-        <v>95.5694528334882</v>
+        <v>95.56945283348823</v>
       </c>
       <c r="P94">
         <v>49058</v>
@@ -6826,10 +6826,10 @@
         <v>97.35418313024078</v>
       </c>
       <c r="N95">
-        <v>90.07772910426878</v>
+        <v>90.07772910426883</v>
       </c>
       <c r="O95">
-        <v>95.5694528334882</v>
+        <v>95.56945283348823</v>
       </c>
       <c r="P95">
         <v>49058</v>
@@ -6894,10 +6894,10 @@
         <v>97.35418313024078</v>
       </c>
       <c r="N96">
-        <v>90.07772910426878</v>
+        <v>90.07772910426883</v>
       </c>
       <c r="O96">
-        <v>95.5694528334882</v>
+        <v>95.56945283348823</v>
       </c>
       <c r="P96">
         <v>49058</v>
@@ -6908,7 +6908,7 @@
         </is>
       </c>
       <c r="S96">
-        <v>-2.0360808689739</v>
+        <v>-2.036080868973866</v>
       </c>
     </row>
     <row r="97">
@@ -6962,10 +6962,10 @@
         <v>97.35418313024078</v>
       </c>
       <c r="N97">
-        <v>90.07772910426878</v>
+        <v>90.07772910426883</v>
       </c>
       <c r="O97">
-        <v>95.5694528334882</v>
+        <v>95.56945283348823</v>
       </c>
       <c r="P97">
         <v>49058</v>
@@ -6976,7 +6976,7 @@
         </is>
       </c>
       <c r="S97">
-        <v>3.455642860245511</v>
+        <v>3.455642860245545</v>
       </c>
     </row>
     <row r="98">
@@ -7030,10 +7030,10 @@
         <v>61.33920356117392</v>
       </c>
       <c r="N98">
-        <v>60.39792154911988</v>
+        <v>60.39792154911977</v>
       </c>
       <c r="O98">
-        <v>61.38848427025866</v>
+        <v>61.3884842702589</v>
       </c>
       <c r="P98">
         <v>55325</v>
@@ -7098,10 +7098,10 @@
         <v>61.33920356117392</v>
       </c>
       <c r="N99">
-        <v>60.39792154911988</v>
+        <v>60.39792154911977</v>
       </c>
       <c r="O99">
-        <v>61.38848427025866</v>
+        <v>61.3884842702589</v>
       </c>
       <c r="P99">
         <v>55325</v>
@@ -7166,10 +7166,10 @@
         <v>61.33920356117392</v>
       </c>
       <c r="N100">
-        <v>60.39792154911988</v>
+        <v>60.39792154911977</v>
       </c>
       <c r="O100">
-        <v>61.38848427025866</v>
+        <v>61.3884842702589</v>
       </c>
       <c r="P100">
         <v>55325</v>
@@ -7180,7 +7180,7 @@
         </is>
       </c>
       <c r="S100">
-        <v>-1.44705391069867</v>
+        <v>-1.447053910698781</v>
       </c>
     </row>
     <row r="101">
@@ -7234,10 +7234,10 @@
         <v>61.33920356117392</v>
       </c>
       <c r="N101">
-        <v>60.39792154911988</v>
+        <v>60.39792154911977</v>
       </c>
       <c r="O101">
-        <v>61.38848427025866</v>
+        <v>61.3884842702589</v>
       </c>
       <c r="P101">
         <v>55325</v>
@@ -7248,7 +7248,7 @@
         </is>
       </c>
       <c r="S101">
-        <v>-0.4564911895598933</v>
+        <v>-0.4564911895596491</v>
       </c>
     </row>
     <row r="102">
@@ -7302,10 +7302,10 @@
         <v>51.97518434916385</v>
       </c>
       <c r="N102">
-        <v>51.96851035400858</v>
+        <v>51.9685103540086</v>
       </c>
       <c r="O102">
-        <v>55.16820532599596</v>
+        <v>55.16820532599615</v>
       </c>
       <c r="P102">
         <v>55400</v>
@@ -7370,10 +7370,10 @@
         <v>51.97518434916385</v>
       </c>
       <c r="N103">
-        <v>51.96851035400858</v>
+        <v>51.9685103540086</v>
       </c>
       <c r="O103">
-        <v>55.16820532599596</v>
+        <v>55.16820532599615</v>
       </c>
       <c r="P103">
         <v>55400</v>
@@ -7438,10 +7438,10 @@
         <v>51.97518434916385</v>
       </c>
       <c r="N104">
-        <v>51.96851035400858</v>
+        <v>51.9685103540086</v>
       </c>
       <c r="O104">
-        <v>55.16820532599596</v>
+        <v>55.16820532599615</v>
       </c>
       <c r="P104">
         <v>55400</v>
@@ -7452,7 +7452,7 @@
         </is>
       </c>
       <c r="S104">
-        <v>-0.4053152415143146</v>
+        <v>-0.4053152415142924</v>
       </c>
     </row>
     <row r="105">
@@ -7506,10 +7506,10 @@
         <v>51.97518434916385</v>
       </c>
       <c r="N105">
-        <v>51.96851035400858</v>
+        <v>51.9685103540086</v>
       </c>
       <c r="O105">
-        <v>55.16820532599596</v>
+        <v>55.16820532599615</v>
       </c>
       <c r="P105">
         <v>55400</v>
@@ -7520,7 +7520,7 @@
         </is>
       </c>
       <c r="S105">
-        <v>2.794379730473062</v>
+        <v>2.794379730473251</v>
       </c>
     </row>
     <row r="106">
@@ -7574,10 +7574,10 @@
         <v>92.92783958842196</v>
       </c>
       <c r="N106">
-        <v>87.32994267910654</v>
+        <v>87.32994267910608</v>
       </c>
       <c r="O106">
-        <v>92.33804839648147</v>
+        <v>92.33804839648158</v>
       </c>
       <c r="P106">
         <v>55242</v>
@@ -7642,10 +7642,10 @@
         <v>92.92783958842196</v>
       </c>
       <c r="N107">
-        <v>87.32994267910654</v>
+        <v>87.32994267910608</v>
       </c>
       <c r="O107">
-        <v>92.33804839648147</v>
+        <v>92.33804839648158</v>
       </c>
       <c r="P107">
         <v>55242</v>
@@ -7710,10 +7710,10 @@
         <v>92.92783958842196</v>
       </c>
       <c r="N108">
-        <v>87.32994267910654</v>
+        <v>87.32994267910608</v>
       </c>
       <c r="O108">
-        <v>92.33804839648147</v>
+        <v>92.33804839648158</v>
       </c>
       <c r="P108">
         <v>55242</v>
@@ -7724,7 +7724,7 @@
         </is>
       </c>
       <c r="S108">
-        <v>-0.1009559809638128</v>
+        <v>-0.1009559809642679</v>
       </c>
     </row>
     <row r="109">
@@ -7778,10 +7778,10 @@
         <v>92.92783958842196</v>
       </c>
       <c r="N109">
-        <v>87.32994267910654</v>
+        <v>87.32994267910608</v>
       </c>
       <c r="O109">
-        <v>92.33804839648147</v>
+        <v>92.33804839648158</v>
       </c>
       <c r="P109">
         <v>55242</v>
@@ -7792,7 +7792,7 @@
         </is>
       </c>
       <c r="S109">
-        <v>4.907149736411109</v>
+        <v>4.907149736411231</v>
       </c>
     </row>
     <row r="110">
@@ -7846,10 +7846,10 @@
         <v>86.30129201699636</v>
       </c>
       <c r="N110">
-        <v>90.29738719024533</v>
+        <v>90.29738719024508</v>
       </c>
       <c r="O110">
-        <v>85.14002215874858</v>
+        <v>85.14002215874885</v>
       </c>
       <c r="P110">
         <v>55400</v>
@@ -7914,10 +7914,10 @@
         <v>86.30129201699636</v>
       </c>
       <c r="N111">
-        <v>90.29738719024533</v>
+        <v>90.29738719024508</v>
       </c>
       <c r="O111">
-        <v>85.14002215874858</v>
+        <v>85.14002215874885</v>
       </c>
       <c r="P111">
         <v>55400</v>
@@ -7982,10 +7982,10 @@
         <v>86.30129201699636</v>
       </c>
       <c r="N112">
-        <v>90.29738719024533</v>
+        <v>90.29738719024508</v>
       </c>
       <c r="O112">
-        <v>85.14002215874858</v>
+        <v>85.14002215874885</v>
       </c>
       <c r="P112">
         <v>55400</v>
@@ -7996,7 +7996,7 @@
         </is>
       </c>
       <c r="S112">
-        <v>0.7294136856202504</v>
+        <v>0.729413685619984</v>
       </c>
     </row>
     <row r="113">
@@ -8050,10 +8050,10 @@
         <v>86.30129201699636</v>
       </c>
       <c r="N113">
-        <v>90.29738719024533</v>
+        <v>90.29738719024508</v>
       </c>
       <c r="O113">
-        <v>85.14002215874858</v>
+        <v>85.14002215874885</v>
       </c>
       <c r="P113">
         <v>55400</v>
@@ -8064,7 +8064,7 @@
         </is>
       </c>
       <c r="S113">
-        <v>-4.427951345876502</v>
+        <v>-4.427951345876235</v>
       </c>
     </row>
     <row r="114">
@@ -8118,10 +8118,10 @@
         <v>78.40310703823478</v>
       </c>
       <c r="N114">
-        <v>81.97678428265843</v>
+        <v>81.97678428265853</v>
       </c>
       <c r="O114">
-        <v>78.85814310205271</v>
+        <v>78.85814310205289</v>
       </c>
       <c r="P114">
         <v>37859</v>
@@ -8186,10 +8186,10 @@
         <v>78.40310703823478</v>
       </c>
       <c r="N115">
-        <v>81.97678428265843</v>
+        <v>81.97678428265853</v>
       </c>
       <c r="O115">
-        <v>78.85814310205271</v>
+        <v>78.85814310205289</v>
       </c>
       <c r="P115">
         <v>37859</v>
@@ -8254,10 +8254,10 @@
         <v>78.40310703823478</v>
       </c>
       <c r="N116">
-        <v>81.97678428265843</v>
+        <v>81.97678428265853</v>
       </c>
       <c r="O116">
-        <v>78.85814310205271</v>
+        <v>78.85814310205289</v>
       </c>
       <c r="P116">
         <v>37859</v>
@@ -8268,7 +8268,7 @@
         </is>
       </c>
       <c r="S116">
-        <v>-0.8086498910110373</v>
+        <v>-0.8086498910109485</v>
       </c>
     </row>
     <row r="117">
@@ -8322,10 +8322,10 @@
         <v>78.40310703823478</v>
       </c>
       <c r="N117">
-        <v>81.97678428265843</v>
+        <v>81.97678428265853</v>
       </c>
       <c r="O117">
-        <v>78.85814310205271</v>
+        <v>78.85814310205289</v>
       </c>
       <c r="P117">
         <v>37859</v>
@@ -8336,7 +8336,7 @@
         </is>
       </c>
       <c r="S117">
-        <v>-3.927291071616756</v>
+        <v>-3.927291071616579</v>
       </c>
     </row>
     <row r="118">
@@ -8390,10 +8390,10 @@
         <v>27.81811575108459</v>
       </c>
       <c r="N118">
-        <v>61.84561105159537</v>
+        <v>61.84561105159655</v>
       </c>
       <c r="O118">
-        <v>26.29907721541595</v>
+        <v>26.29907721541566</v>
       </c>
       <c r="P118">
         <v>44776</v>
@@ -8458,10 +8458,10 @@
         <v>27.81811575108459</v>
       </c>
       <c r="N119">
-        <v>61.84561105159537</v>
+        <v>61.84561105159655</v>
       </c>
       <c r="O119">
-        <v>26.29907721541595</v>
+        <v>26.29907721541566</v>
       </c>
       <c r="P119">
         <v>44776</v>
@@ -8526,10 +8526,10 @@
         <v>27.81811575108459</v>
       </c>
       <c r="N120">
-        <v>61.84561105159537</v>
+        <v>61.84561105159655</v>
       </c>
       <c r="O120">
-        <v>26.29907721541595</v>
+        <v>26.29907721541566</v>
       </c>
       <c r="P120">
         <v>44776</v>
@@ -8540,7 +8540,7 @@
         </is>
       </c>
       <c r="S120">
-        <v>0.3570698780789416</v>
+        <v>0.3570698780801185</v>
       </c>
     </row>
     <row r="121">
@@ -8594,10 +8594,10 @@
         <v>27.81811575108459</v>
       </c>
       <c r="N121">
-        <v>61.84561105159537</v>
+        <v>61.84561105159655</v>
       </c>
       <c r="O121">
-        <v>26.29907721541595</v>
+        <v>26.29907721541566</v>
       </c>
       <c r="P121">
         <v>44776</v>
@@ -8608,7 +8608,7 @@
         </is>
       </c>
       <c r="S121">
-        <v>-35.18946395810048</v>
+        <v>-35.18946395810077</v>
       </c>
     </row>
     <row r="122">
@@ -8662,10 +8662,10 @@
         <v>19.55956107979261</v>
       </c>
       <c r="N122">
-        <v>18.78381922591102</v>
+        <v>18.78381922591106</v>
       </c>
       <c r="O122">
-        <v>18.78376405592434</v>
+        <v>18.78376405592467</v>
       </c>
       <c r="P122">
         <v>54535</v>
@@ -8730,10 +8730,10 @@
         <v>19.55956107979261</v>
       </c>
       <c r="N123">
-        <v>18.78381922591102</v>
+        <v>18.78381922591106</v>
       </c>
       <c r="O123">
-        <v>18.78376405592434</v>
+        <v>18.78376405592467</v>
       </c>
       <c r="P123">
         <v>54535</v>
@@ -8798,10 +8798,10 @@
         <v>19.55956107979261</v>
       </c>
       <c r="N124">
-        <v>18.78381922591102</v>
+        <v>18.78381922591106</v>
       </c>
       <c r="O124">
-        <v>18.78376405592434</v>
+        <v>18.78376405592467</v>
       </c>
       <c r="P124">
         <v>54535</v>
@@ -8812,7 +8812,7 @@
         </is>
       </c>
       <c r="S124">
-        <v>-0.5877807213773845</v>
+        <v>-0.5877807213773428</v>
       </c>
     </row>
     <row r="125">
@@ -8866,10 +8866,10 @@
         <v>19.55956107979261</v>
       </c>
       <c r="N125">
-        <v>18.78381922591102</v>
+        <v>18.78381922591106</v>
       </c>
       <c r="O125">
-        <v>18.78376405592434</v>
+        <v>18.78376405592467</v>
       </c>
       <c r="P125">
         <v>54535</v>
@@ -8880,7 +8880,7 @@
         </is>
       </c>
       <c r="S125">
-        <v>-0.5878358913640636</v>
+        <v>-0.587835891363736</v>
       </c>
     </row>
     <row r="126">
@@ -8934,10 +8934,10 @@
         <v>30.49659378673363</v>
       </c>
       <c r="N126">
-        <v>30.53786279215657</v>
+        <v>30.53786279215646</v>
       </c>
       <c r="O126">
-        <v>30.53774451303544</v>
+        <v>30.53774451303555</v>
       </c>
       <c r="P126">
         <v>54535</v>
@@ -9002,10 +9002,10 @@
         <v>30.49659378673363</v>
       </c>
       <c r="N127">
-        <v>30.53786279215657</v>
+        <v>30.53786279215646</v>
       </c>
       <c r="O127">
-        <v>30.53774451303544</v>
+        <v>30.53774451303555</v>
       </c>
       <c r="P127">
         <v>54535</v>
@@ -9070,10 +9070,10 @@
         <v>30.49659378673363</v>
       </c>
       <c r="N128">
-        <v>30.53786279215657</v>
+        <v>30.53786279215646</v>
       </c>
       <c r="O128">
-        <v>30.53774451303544</v>
+        <v>30.53774451303555</v>
       </c>
       <c r="P128">
         <v>54535</v>
@@ -9084,7 +9084,7 @@
         </is>
       </c>
       <c r="S128">
-        <v>-0.1367483492705823</v>
+        <v>-0.1367483492706933</v>
       </c>
     </row>
     <row r="129">
@@ -9138,10 +9138,10 @@
         <v>30.49659378673363</v>
       </c>
       <c r="N129">
-        <v>30.53786279215657</v>
+        <v>30.53786279215646</v>
       </c>
       <c r="O129">
-        <v>30.53774451303544</v>
+        <v>30.53774451303555</v>
       </c>
       <c r="P129">
         <v>54535</v>
@@ -9152,7 +9152,7 @@
         </is>
       </c>
       <c r="S129">
-        <v>-0.136866628391713</v>
+        <v>-0.136866628391602</v>
       </c>
     </row>
     <row r="130">
@@ -9206,10 +9206,10 @@
         <v>46.0408366864019</v>
       </c>
       <c r="N130">
-        <v>60.07048159861138</v>
+        <v>60.0704815986113</v>
       </c>
       <c r="O130">
-        <v>60.07051969567385</v>
+        <v>60.07051969567441</v>
       </c>
       <c r="P130">
         <v>54535</v>
@@ -9274,10 +9274,10 @@
         <v>46.0408366864019</v>
       </c>
       <c r="N131">
-        <v>60.07048159861138</v>
+        <v>60.0704815986113</v>
       </c>
       <c r="O131">
-        <v>60.07051969567385</v>
+        <v>60.07051969567441</v>
       </c>
       <c r="P131">
         <v>54535</v>
@@ -9342,10 +9342,10 @@
         <v>46.0408366864019</v>
       </c>
       <c r="N132">
-        <v>60.07048159861138</v>
+        <v>60.0704815986113</v>
       </c>
       <c r="O132">
-        <v>60.07051969567385</v>
+        <v>60.07051969567441</v>
       </c>
       <c r="P132">
         <v>54535</v>
@@ -9356,7 +9356,7 @@
         </is>
       </c>
       <c r="S132">
-        <v>-0.7931925941980889</v>
+        <v>-0.7931925941981666</v>
       </c>
     </row>
     <row r="133">
@@ -9410,10 +9410,10 @@
         <v>46.0408366864019</v>
       </c>
       <c r="N133">
-        <v>60.07048159861138</v>
+        <v>60.0704815986113</v>
       </c>
       <c r="O133">
-        <v>60.07051969567385</v>
+        <v>60.07051969567441</v>
       </c>
       <c r="P133">
         <v>54535</v>
@@ -9424,7 +9424,7 @@
         </is>
       </c>
       <c r="S133">
-        <v>-0.7931544971356175</v>
+        <v>-0.7931544971350624</v>
       </c>
     </row>
     <row r="134">
@@ -9478,10 +9478,10 @@
         <v>22.21829840823713</v>
       </c>
       <c r="N134">
-        <v>22.80752813266336</v>
+        <v>22.8075281326633</v>
       </c>
       <c r="O134">
-        <v>22.80764277056756</v>
+        <v>22.80764277056721</v>
       </c>
       <c r="P134">
         <v>47918</v>
@@ -9546,10 +9546,10 @@
         <v>22.21829840823713</v>
       </c>
       <c r="N135">
-        <v>22.80752813266336</v>
+        <v>22.8075281326633</v>
       </c>
       <c r="O135">
-        <v>22.80764277056756</v>
+        <v>22.80764277056721</v>
       </c>
       <c r="P135">
         <v>47918</v>
@@ -9614,10 +9614,10 @@
         <v>22.21829840823713</v>
       </c>
       <c r="N136">
-        <v>22.80752813266336</v>
+        <v>22.8075281326633</v>
       </c>
       <c r="O136">
-        <v>22.80764277056756</v>
+        <v>22.80764277056721</v>
       </c>
       <c r="P136">
         <v>47918</v>
@@ -9628,7 +9628,7 @@
         </is>
       </c>
       <c r="S136">
-        <v>-0.6564727659101488</v>
+        <v>-0.6564727659102182</v>
       </c>
     </row>
     <row r="137">
@@ -9682,10 +9682,10 @@
         <v>22.21829840823713</v>
       </c>
       <c r="N137">
-        <v>22.80752813266336</v>
+        <v>22.8075281326633</v>
       </c>
       <c r="O137">
-        <v>22.80764277056756</v>
+        <v>22.80764277056721</v>
       </c>
       <c r="P137">
         <v>47918</v>
@@ -9696,7 +9696,7 @@
         </is>
       </c>
       <c r="S137">
-        <v>-0.6563581280059488</v>
+        <v>-0.6563581280063013</v>
       </c>
     </row>
     <row r="138">
@@ -9750,7 +9750,7 @@
         <v>97.70353186034932</v>
       </c>
       <c r="N138">
-        <v>89.05764683702921</v>
+        <v>89.057646837029</v>
       </c>
       <c r="O138">
         <v>96.53969112716689</v>
@@ -9818,7 +9818,7 @@
         <v>97.70353186034932</v>
       </c>
       <c r="N139">
-        <v>89.05764683702921</v>
+        <v>89.057646837029</v>
       </c>
       <c r="O139">
         <v>96.53969112716689</v>
@@ -9886,7 +9886,7 @@
         <v>97.70353186034932</v>
       </c>
       <c r="N140">
-        <v>89.05764683702921</v>
+        <v>89.057646837029</v>
       </c>
       <c r="O140">
         <v>96.53969112716689</v>
@@ -9900,7 +9900,7 @@
         </is>
       </c>
       <c r="S140">
-        <v>-2.609675776510767</v>
+        <v>-2.609675776510978</v>
       </c>
     </row>
     <row r="141">
@@ -9954,7 +9954,7 @@
         <v>97.70353186034932</v>
       </c>
       <c r="N141">
-        <v>89.05764683702921</v>
+        <v>89.057646837029</v>
       </c>
       <c r="O141">
         <v>96.53969112716689</v>
@@ -10022,10 +10022,10 @@
         <v>60.16767859230833</v>
       </c>
       <c r="N142">
-        <v>61.88484918229459</v>
+        <v>61.88484918229447</v>
       </c>
       <c r="O142">
-        <v>61.47727459441587</v>
+        <v>61.4772745944154</v>
       </c>
       <c r="P142">
         <v>54426</v>
@@ -10090,10 +10090,10 @@
         <v>60.16767859230833</v>
       </c>
       <c r="N143">
-        <v>61.88484918229459</v>
+        <v>61.88484918229447</v>
       </c>
       <c r="O143">
-        <v>61.47727459441587</v>
+        <v>61.4772745944154</v>
       </c>
       <c r="P143">
         <v>54426</v>
@@ -10158,10 +10158,10 @@
         <v>60.16767859230833</v>
       </c>
       <c r="N144">
-        <v>61.88484918229459</v>
+        <v>61.88484918229447</v>
       </c>
       <c r="O144">
-        <v>61.47727459441587</v>
+        <v>61.4772745944154</v>
       </c>
       <c r="P144">
         <v>54426</v>
@@ -10172,7 +10172,7 @@
         </is>
       </c>
       <c r="S144">
-        <v>-1.127829715025552</v>
+        <v>-1.127829715025674</v>
       </c>
     </row>
     <row r="145">
@@ -10226,10 +10226,10 @@
         <v>60.16767859230833</v>
       </c>
       <c r="N145">
-        <v>61.88484918229459</v>
+        <v>61.88484918229447</v>
       </c>
       <c r="O145">
-        <v>61.47727459441587</v>
+        <v>61.4772745944154</v>
       </c>
       <c r="P145">
         <v>54426</v>
@@ -10240,7 +10240,7 @@
         </is>
       </c>
       <c r="S145">
-        <v>-1.535404302904275</v>
+        <v>-1.535404302904742</v>
       </c>
     </row>
     <row r="146">
@@ -10294,10 +10294,10 @@
         <v>51.81970969080953</v>
       </c>
       <c r="N146">
-        <v>52.10416026488398</v>
+        <v>52.10416026488397</v>
       </c>
       <c r="O146">
-        <v>53.71180101699651</v>
+        <v>53.71180101699645</v>
       </c>
       <c r="P146">
         <v>54535</v>
@@ -10362,10 +10362,10 @@
         <v>51.81970969080953</v>
       </c>
       <c r="N147">
-        <v>52.10416026488398</v>
+        <v>52.10416026488397</v>
       </c>
       <c r="O147">
-        <v>53.71180101699651</v>
+        <v>53.71180101699645</v>
       </c>
       <c r="P147">
         <v>54535</v>
@@ -10430,10 +10430,10 @@
         <v>51.81970969080953</v>
       </c>
       <c r="N148">
-        <v>52.10416026488398</v>
+        <v>52.10416026488397</v>
       </c>
       <c r="O148">
-        <v>53.71180101699651</v>
+        <v>53.71180101699645</v>
       </c>
       <c r="P148">
         <v>54535</v>
@@ -10444,7 +10444,7 @@
         </is>
       </c>
       <c r="S148">
-        <v>-0.188219283370572</v>
+        <v>-0.1882192833705831</v>
       </c>
     </row>
     <row r="149">
@@ -10498,10 +10498,10 @@
         <v>51.81970969080953</v>
       </c>
       <c r="N149">
-        <v>52.10416026488398</v>
+        <v>52.10416026488397</v>
       </c>
       <c r="O149">
-        <v>53.71180101699651</v>
+        <v>53.71180101699645</v>
       </c>
       <c r="P149">
         <v>54535</v>
@@ -10512,7 +10512,7 @@
         </is>
       </c>
       <c r="S149">
-        <v>1.419421468741955</v>
+        <v>1.419421468741899</v>
       </c>
     </row>
     <row r="150">
@@ -10566,10 +10566,10 @@
         <v>93.85406722827751</v>
       </c>
       <c r="N150">
-        <v>88.10981089169675</v>
+        <v>88.10981089169665</v>
       </c>
       <c r="O150">
-        <v>92.81601489807957</v>
+        <v>92.81601489807952</v>
       </c>
       <c r="P150">
         <v>54281</v>
@@ -10634,10 +10634,10 @@
         <v>93.85406722827751</v>
       </c>
       <c r="N151">
-        <v>88.10981089169675</v>
+        <v>88.10981089169665</v>
       </c>
       <c r="O151">
-        <v>92.81601489807957</v>
+        <v>92.81601489807952</v>
       </c>
       <c r="P151">
         <v>54281</v>
@@ -10702,10 +10702,10 @@
         <v>93.85406722827751</v>
       </c>
       <c r="N152">
-        <v>88.10981089169675</v>
+        <v>88.10981089169665</v>
       </c>
       <c r="O152">
-        <v>92.81601489807957</v>
+        <v>92.81601489807952</v>
       </c>
       <c r="P152">
         <v>54281</v>
@@ -10716,7 +10716,7 @@
         </is>
       </c>
       <c r="S152">
-        <v>0.03641639628391147</v>
+        <v>0.03641639628380045</v>
       </c>
     </row>
     <row r="153">
@@ -10770,10 +10770,10 @@
         <v>93.85406722827751</v>
       </c>
       <c r="N153">
-        <v>88.10981089169675</v>
+        <v>88.10981089169665</v>
       </c>
       <c r="O153">
-        <v>92.81601489807957</v>
+        <v>92.81601489807952</v>
       </c>
       <c r="P153">
         <v>54281</v>
@@ -10784,7 +10784,7 @@
         </is>
       </c>
       <c r="S153">
-        <v>4.742620402666731</v>
+        <v>4.742620402666664</v>
       </c>
     </row>
     <row r="154">
@@ -10838,10 +10838,10 @@
         <v>87.6320105705225</v>
       </c>
       <c r="N154">
-        <v>90.59641787470699</v>
+        <v>90.59641787470704</v>
       </c>
       <c r="O154">
-        <v>86.45602653188774</v>
+        <v>86.4560265318876</v>
       </c>
       <c r="P154">
         <v>54534</v>
@@ -10906,10 +10906,10 @@
         <v>87.6320105705225</v>
       </c>
       <c r="N155">
-        <v>90.59641787470699</v>
+        <v>90.59641787470704</v>
       </c>
       <c r="O155">
-        <v>86.45602653188774</v>
+        <v>86.4560265318876</v>
       </c>
       <c r="P155">
         <v>54534</v>
@@ -10974,10 +10974,10 @@
         <v>87.6320105705225</v>
       </c>
       <c r="N156">
-        <v>90.59641787470699</v>
+        <v>90.59641787470704</v>
       </c>
       <c r="O156">
-        <v>86.45602653188774</v>
+        <v>86.4560265318876</v>
       </c>
       <c r="P156">
         <v>54534</v>
@@ -10988,7 +10988,7 @@
         </is>
       </c>
       <c r="S156">
-        <v>0.642575343198637</v>
+        <v>0.6425753431986925</v>
       </c>
     </row>
     <row r="157">
@@ -11042,10 +11042,10 @@
         <v>87.6320105705225</v>
       </c>
       <c r="N157">
-        <v>90.59641787470699</v>
+        <v>90.59641787470704</v>
       </c>
       <c r="O157">
-        <v>86.45602653188774</v>
+        <v>86.4560265318876</v>
       </c>
       <c r="P157">
         <v>54534</v>
@@ -11056,7 +11056,7 @@
         </is>
       </c>
       <c r="S157">
-        <v>-3.497815999620613</v>
+        <v>-3.497815999620746</v>
       </c>
     </row>
     <row r="158">
@@ -11110,10 +11110,10 @@
         <v>77.14401961658972</v>
       </c>
       <c r="N158">
-        <v>81.45050683818815</v>
+        <v>81.45050683818823</v>
       </c>
       <c r="O158">
-        <v>77.48841209095431</v>
+        <v>77.4884120909541</v>
       </c>
       <c r="P158">
         <v>39772</v>
@@ -11178,10 +11178,10 @@
         <v>77.14401961658972</v>
       </c>
       <c r="N159">
-        <v>81.45050683818815</v>
+        <v>81.45050683818823</v>
       </c>
       <c r="O159">
-        <v>77.48841209095431</v>
+        <v>77.4884120909541</v>
       </c>
       <c r="P159">
         <v>39772</v>
@@ -11246,10 +11246,10 @@
         <v>77.14401961658972</v>
       </c>
       <c r="N160">
-        <v>81.45050683818815</v>
+        <v>81.45050683818823</v>
       </c>
       <c r="O160">
-        <v>77.48841209095431</v>
+        <v>77.4884120909541</v>
       </c>
       <c r="P160">
         <v>39772</v>
@@ -11260,7 +11260,7 @@
         </is>
       </c>
       <c r="S160">
-        <v>-0.5301548422915969</v>
+        <v>-0.5301548422915192</v>
       </c>
     </row>
     <row r="161">
@@ -11314,10 +11314,10 @@
         <v>77.14401961658972</v>
       </c>
       <c r="N161">
-        <v>81.45050683818815</v>
+        <v>81.45050683818823</v>
       </c>
       <c r="O161">
-        <v>77.48841209095431</v>
+        <v>77.4884120909541</v>
       </c>
       <c r="P161">
         <v>39772</v>
@@ -11328,7 +11328,7 @@
         </is>
       </c>
       <c r="S161">
-        <v>-4.492249589525443</v>
+        <v>-4.492249589525644</v>
       </c>
     </row>
     <row r="162">
@@ -11382,10 +11382,10 @@
         <v>94.73858354545469</v>
       </c>
       <c r="N162">
-        <v>53.97907512970481</v>
+        <v>53.97907512970576</v>
       </c>
       <c r="O162">
-        <v>90.77842736117616</v>
+        <v>90.77842736117594</v>
       </c>
       <c r="P162">
         <v>42552</v>
@@ -11450,10 +11450,10 @@
         <v>94.73858354545469</v>
       </c>
       <c r="N163">
-        <v>53.97907512970481</v>
+        <v>53.97907512970576</v>
       </c>
       <c r="O163">
-        <v>90.77842736117616</v>
+        <v>90.77842736117594</v>
       </c>
       <c r="P163">
         <v>42552</v>
@@ -11518,10 +11518,10 @@
         <v>94.73858354545469</v>
       </c>
       <c r="N164">
-        <v>53.97907512970481</v>
+        <v>53.97907512970576</v>
       </c>
       <c r="O164">
-        <v>90.77842736117616</v>
+        <v>90.77842736117594</v>
       </c>
       <c r="P164">
         <v>42552</v>
@@ -11532,7 +11532,7 @@
         </is>
       </c>
       <c r="S164">
-        <v>0.0008416705640779121</v>
+        <v>0.0008416705650216016</v>
       </c>
     </row>
     <row r="165">
@@ -11586,10 +11586,10 @@
         <v>94.73858354545469</v>
       </c>
       <c r="N165">
-        <v>53.97907512970481</v>
+        <v>53.97907512970576</v>
       </c>
       <c r="O165">
-        <v>90.77842736117616</v>
+        <v>90.77842736117594</v>
       </c>
       <c r="P165">
         <v>42552</v>
@@ -11600,7 +11600,7 @@
         </is>
       </c>
       <c r="S165">
-        <v>36.80019390203542</v>
+        <v>36.8001939020352</v>
       </c>
     </row>
     <row r="166">
@@ -20358,10 +20358,10 @@
         <v>13.71421764662618</v>
       </c>
       <c r="N294">
-        <v>15.41815523864195</v>
+        <v>15.41815523864194</v>
       </c>
       <c r="O294">
-        <v>15.39358401703959</v>
+        <v>15.39358401703903</v>
       </c>
       <c r="P294">
         <v>61000</v>
@@ -20426,10 +20426,10 @@
         <v>13.71421764662618</v>
       </c>
       <c r="N295">
-        <v>15.41815523864195</v>
+        <v>15.41815523864194</v>
       </c>
       <c r="O295">
-        <v>15.39358401703959</v>
+        <v>15.39358401703903</v>
       </c>
       <c r="P295">
         <v>61000</v>
@@ -20494,10 +20494,10 @@
         <v>13.71421764662618</v>
       </c>
       <c r="N296">
-        <v>15.41815523864195</v>
+        <v>15.41815523864194</v>
       </c>
       <c r="O296">
-        <v>15.39358401703959</v>
+        <v>15.39358401703903</v>
       </c>
       <c r="P296">
         <v>61000</v>
@@ -20508,7 +20508,7 @@
         </is>
       </c>
       <c r="S296">
-        <v>-2.43406601478722</v>
+        <v>-2.434066014787231</v>
       </c>
     </row>
     <row r="297">
@@ -20562,10 +20562,10 @@
         <v>13.71421764662618</v>
       </c>
       <c r="N297">
-        <v>15.41815523864195</v>
+        <v>15.41815523864194</v>
       </c>
       <c r="O297">
-        <v>15.39358401703959</v>
+        <v>15.39358401703903</v>
       </c>
       <c r="P297">
         <v>61000</v>
@@ -20576,7 +20576,7 @@
         </is>
       </c>
       <c r="S297">
-        <v>-2.458637236389585</v>
+        <v>-2.458637236390146</v>
       </c>
     </row>
     <row r="298">
@@ -20630,10 +20630,10 @@
         <v>29.42277298055462</v>
       </c>
       <c r="N298">
-        <v>28.57244554318077</v>
+        <v>28.57244554318082</v>
       </c>
       <c r="O298">
-        <v>28.56364349950802</v>
+        <v>28.56364349950706</v>
       </c>
       <c r="P298">
         <v>61000</v>
@@ -20698,10 +20698,10 @@
         <v>29.42277298055462</v>
       </c>
       <c r="N299">
-        <v>28.57244554318077</v>
+        <v>28.57244554318082</v>
       </c>
       <c r="O299">
-        <v>28.56364349950802</v>
+        <v>28.56364349950706</v>
       </c>
       <c r="P299">
         <v>61000</v>
@@ -20766,10 +20766,10 @@
         <v>29.42277298055462</v>
       </c>
       <c r="N300">
-        <v>28.57244554318077</v>
+        <v>28.57244554318082</v>
       </c>
       <c r="O300">
-        <v>28.56364349950802</v>
+        <v>28.56364349950706</v>
       </c>
       <c r="P300">
         <v>61000</v>
@@ -20780,7 +20780,7 @@
         </is>
       </c>
       <c r="S300">
-        <v>-0.5880716505329397</v>
+        <v>-0.5880716505328953</v>
       </c>
     </row>
     <row r="301">
@@ -20834,10 +20834,10 @@
         <v>29.42277298055462</v>
       </c>
       <c r="N301">
-        <v>28.57244554318077</v>
+        <v>28.57244554318082</v>
       </c>
       <c r="O301">
-        <v>28.56364349950802</v>
+        <v>28.56364349950706</v>
       </c>
       <c r="P301">
         <v>61000</v>
@@ -20848,7 +20848,7 @@
         </is>
       </c>
       <c r="S301">
-        <v>-0.5968736942056962</v>
+        <v>-0.5968736942066566</v>
       </c>
     </row>
     <row r="302">
@@ -20902,10 +20902,10 @@
         <v>45.4639903673616</v>
       </c>
       <c r="N302">
-        <v>57.98657659676809</v>
+        <v>57.98657659676807</v>
       </c>
       <c r="O302">
-        <v>58.0108328128659</v>
+        <v>58.0108328128641</v>
       </c>
       <c r="P302">
         <v>60966</v>
@@ -20970,10 +20970,10 @@
         <v>45.4639903673616</v>
       </c>
       <c r="N303">
-        <v>57.98657659676809</v>
+        <v>57.98657659676807</v>
       </c>
       <c r="O303">
-        <v>58.0108328128659</v>
+        <v>58.0108328128641</v>
       </c>
       <c r="P303">
         <v>60966</v>
@@ -21038,10 +21038,10 @@
         <v>45.4639903673616</v>
       </c>
       <c r="N304">
-        <v>57.98657659676809</v>
+        <v>57.98657659676807</v>
       </c>
       <c r="O304">
-        <v>58.0108328128659</v>
+        <v>58.0108328128641</v>
       </c>
       <c r="P304">
         <v>60966</v>
@@ -21052,7 +21052,7 @@
         </is>
       </c>
       <c r="S304">
-        <v>0.9354526786854556</v>
+        <v>0.9354526786854334</v>
       </c>
     </row>
     <row r="305">
@@ -21106,10 +21106,10 @@
         <v>45.4639903673616</v>
       </c>
       <c r="N305">
-        <v>57.98657659676809</v>
+        <v>57.98657659676807</v>
       </c>
       <c r="O305">
-        <v>58.0108328128659</v>
+        <v>58.0108328128641</v>
       </c>
       <c r="P305">
         <v>60966</v>
@@ -21120,7 +21120,7 @@
         </is>
       </c>
       <c r="S305">
-        <v>0.9597088947832622</v>
+        <v>0.9597088947814636</v>
       </c>
     </row>
     <row r="306">
@@ -21174,10 +21174,10 @@
         <v>22.87686769960688</v>
       </c>
       <c r="N306">
-        <v>24.28635160555294</v>
+        <v>24.28635160555295</v>
       </c>
       <c r="O306">
-        <v>24.30807920702841</v>
+        <v>24.30807920702731</v>
       </c>
       <c r="P306">
         <v>54906</v>
@@ -21242,10 +21242,10 @@
         <v>22.87686769960688</v>
       </c>
       <c r="N307">
-        <v>24.28635160555294</v>
+        <v>24.28635160555295</v>
       </c>
       <c r="O307">
-        <v>24.30807920702841</v>
+        <v>24.30807920702731</v>
       </c>
       <c r="P307">
         <v>54906</v>
@@ -21310,10 +21310,10 @@
         <v>22.87686769960688</v>
       </c>
       <c r="N308">
-        <v>24.28635160555294</v>
+        <v>24.28635160555295</v>
       </c>
       <c r="O308">
-        <v>24.30807920702841</v>
+        <v>24.30807920702731</v>
       </c>
       <c r="P308">
         <v>54906</v>
@@ -21324,7 +21324,7 @@
         </is>
       </c>
       <c r="S308">
-        <v>-0.3936985826528322</v>
+        <v>-0.3936985826528183</v>
       </c>
     </row>
     <row r="309">
@@ -21378,10 +21378,10 @@
         <v>22.87686769960688</v>
       </c>
       <c r="N309">
-        <v>24.28635160555294</v>
+        <v>24.28635160555295</v>
       </c>
       <c r="O309">
-        <v>24.30807920702841</v>
+        <v>24.30807920702731</v>
       </c>
       <c r="P309">
         <v>54906</v>
@@ -21392,7 +21392,7 @@
         </is>
       </c>
       <c r="S309">
-        <v>-0.3719709811773608</v>
+        <v>-0.3719709811784599</v>
       </c>
     </row>
     <row r="310">
@@ -21446,10 +21446,10 @@
         <v>96.75096455756443</v>
       </c>
       <c r="N310">
-        <v>86.70056156845875</v>
+        <v>86.70056156845874</v>
       </c>
       <c r="O310">
-        <v>96.82340183287785</v>
+        <v>96.82340183287779</v>
       </c>
       <c r="P310">
         <v>55751</v>
@@ -21514,10 +21514,10 @@
         <v>96.75096455756443</v>
       </c>
       <c r="N311">
-        <v>86.70056156845875</v>
+        <v>86.70056156845874</v>
       </c>
       <c r="O311">
-        <v>96.82340183287785</v>
+        <v>96.82340183287779</v>
       </c>
       <c r="P311">
         <v>55751</v>
@@ -21582,10 +21582,10 @@
         <v>96.75096455756443</v>
       </c>
       <c r="N312">
-        <v>86.70056156845875</v>
+        <v>86.70056156845874</v>
       </c>
       <c r="O312">
-        <v>96.82340183287785</v>
+        <v>96.82340183287779</v>
       </c>
       <c r="P312">
         <v>55751</v>
@@ -21596,7 +21596,7 @@
         </is>
       </c>
       <c r="S312">
-        <v>-3.50657111129371</v>
+        <v>-3.506571111293733</v>
       </c>
     </row>
     <row r="313">
@@ -21650,10 +21650,10 @@
         <v>96.75096455756443</v>
       </c>
       <c r="N313">
-        <v>86.70056156845875</v>
+        <v>86.70056156845874</v>
       </c>
       <c r="O313">
-        <v>96.82340183287785</v>
+        <v>96.82340183287779</v>
       </c>
       <c r="P313">
         <v>55751</v>
@@ -21664,7 +21664,7 @@
         </is>
       </c>
       <c r="S313">
-        <v>6.616269153125376</v>
+        <v>6.61626915312532</v>
       </c>
     </row>
     <row r="314">
@@ -21718,10 +21718,10 @@
         <v>60.51866627019677</v>
       </c>
       <c r="N314">
-        <v>59.81528043082665</v>
+        <v>59.81528043082663</v>
       </c>
       <c r="O314">
-        <v>60.34381502084475</v>
+        <v>60.34381502084364</v>
       </c>
       <c r="P314">
         <v>60920</v>
@@ -21786,10 +21786,10 @@
         <v>60.51866627019677</v>
       </c>
       <c r="N315">
-        <v>59.81528043082665</v>
+        <v>59.81528043082663</v>
       </c>
       <c r="O315">
-        <v>60.34381502084475</v>
+        <v>60.34381502084364</v>
       </c>
       <c r="P315">
         <v>60920</v>
@@ -21854,10 +21854,10 @@
         <v>60.51866627019677</v>
       </c>
       <c r="N316">
-        <v>59.81528043082665</v>
+        <v>59.81528043082663</v>
       </c>
       <c r="O316">
-        <v>60.34381502084475</v>
+        <v>60.34381502084364</v>
       </c>
       <c r="P316">
         <v>60920</v>
@@ -21868,7 +21868,7 @@
         </is>
       </c>
       <c r="S316">
-        <v>-1.367740548997121</v>
+        <v>-1.367740548997154</v>
       </c>
     </row>
     <row r="317">
@@ -21922,10 +21922,10 @@
         <v>60.51866627019677</v>
       </c>
       <c r="N317">
-        <v>59.81528043082665</v>
+        <v>59.81528043082663</v>
       </c>
       <c r="O317">
-        <v>60.34381502084475</v>
+        <v>60.34381502084364</v>
       </c>
       <c r="P317">
         <v>60920</v>
@@ -21936,7 +21936,7 @@
         </is>
       </c>
       <c r="S317">
-        <v>-0.8392059589790279</v>
+        <v>-0.8392059589801382</v>
       </c>
     </row>
     <row r="318">
@@ -21990,10 +21990,10 @@
         <v>51.49802933758593</v>
       </c>
       <c r="N318">
-        <v>51.87442533665195</v>
+        <v>51.87442533665201</v>
       </c>
       <c r="O318">
-        <v>55.19320995384758</v>
+        <v>55.19320995384727</v>
       </c>
       <c r="P318">
         <v>61000</v>
@@ -22058,10 +22058,10 @@
         <v>51.49802933758593</v>
       </c>
       <c r="N319">
-        <v>51.87442533665195</v>
+        <v>51.87442533665201</v>
       </c>
       <c r="O319">
-        <v>55.19320995384758</v>
+        <v>55.19320995384727</v>
       </c>
       <c r="P319">
         <v>61000</v>
@@ -22126,10 +22126,10 @@
         <v>51.49802933758593</v>
       </c>
       <c r="N320">
-        <v>51.87442533665195</v>
+        <v>51.87442533665201</v>
       </c>
       <c r="O320">
-        <v>55.19320995384758</v>
+        <v>55.19320995384727</v>
       </c>
       <c r="P320">
         <v>61000</v>
@@ -22140,7 +22140,7 @@
         </is>
       </c>
       <c r="S320">
-        <v>-0.2309273630907271</v>
+        <v>-0.2309273630906716</v>
       </c>
     </row>
     <row r="321">
@@ -22194,10 +22194,10 @@
         <v>51.49802933758593</v>
       </c>
       <c r="N321">
-        <v>51.87442533665195</v>
+        <v>51.87442533665201</v>
       </c>
       <c r="O321">
-        <v>55.19320995384758</v>
+        <v>55.19320995384727</v>
       </c>
       <c r="P321">
         <v>61000</v>
@@ -22208,7 +22208,7 @@
         </is>
       </c>
       <c r="S321">
-        <v>3.087857254104898</v>
+        <v>3.087857254104587</v>
       </c>
     </row>
     <row r="322">
@@ -22262,10 +22262,10 @@
         <v>94.03767983644056</v>
       </c>
       <c r="N322">
-        <v>88.60775405607038</v>
+        <v>88.60775405607029</v>
       </c>
       <c r="O322">
-        <v>92.81092514217534</v>
+        <v>92.81092514217536</v>
       </c>
       <c r="P322">
         <v>60928</v>
@@ -22330,10 +22330,10 @@
         <v>94.03767983644056</v>
       </c>
       <c r="N323">
-        <v>88.60775405607038</v>
+        <v>88.60775405607029</v>
       </c>
       <c r="O323">
-        <v>92.81092514217534</v>
+        <v>92.81092514217536</v>
       </c>
       <c r="P323">
         <v>60928</v>
@@ -22398,10 +22398,10 @@
         <v>94.03767983644056</v>
       </c>
       <c r="N324">
-        <v>88.60775405607038</v>
+        <v>88.60775405607029</v>
       </c>
       <c r="O324">
-        <v>92.81092514217534</v>
+        <v>92.81092514217536</v>
       </c>
       <c r="P324">
         <v>60928</v>
@@ -22412,7 +22412,7 @@
         </is>
       </c>
       <c r="S324">
-        <v>-0.3433119337773349</v>
+        <v>-0.3433119337774126</v>
       </c>
     </row>
     <row r="325">
@@ -22466,10 +22466,10 @@
         <v>94.03767983644056</v>
       </c>
       <c r="N325">
-        <v>88.60775405607038</v>
+        <v>88.60775405607029</v>
       </c>
       <c r="O325">
-        <v>92.81092514217534</v>
+        <v>92.81092514217536</v>
       </c>
       <c r="P325">
         <v>60928</v>
@@ -22480,7 +22480,7 @@
         </is>
       </c>
       <c r="S325">
-        <v>3.859859152327627</v>
+        <v>3.859859152327649</v>
       </c>
     </row>
     <row r="326">
@@ -22534,10 +22534,10 @@
         <v>90.12539655528288</v>
       </c>
       <c r="N326">
-        <v>92.49798818801629</v>
+        <v>92.49798818801627</v>
       </c>
       <c r="O326">
-        <v>89.42387194359381</v>
+        <v>89.42387194359372</v>
       </c>
       <c r="P326">
         <v>61000</v>
@@ -22602,10 +22602,10 @@
         <v>90.12539655528288</v>
       </c>
       <c r="N327">
-        <v>92.49798818801629</v>
+        <v>92.49798818801627</v>
       </c>
       <c r="O327">
-        <v>89.42387194359381</v>
+        <v>89.42387194359372</v>
       </c>
       <c r="P327">
         <v>61000</v>
@@ -22670,10 +22670,10 @@
         <v>90.12539655528288</v>
       </c>
       <c r="N328">
-        <v>92.49798818801629</v>
+        <v>92.49798818801627</v>
       </c>
       <c r="O328">
-        <v>89.42387194359381</v>
+        <v>89.42387194359372</v>
       </c>
       <c r="P328">
         <v>61000</v>
@@ -22684,7 +22684,7 @@
         </is>
       </c>
       <c r="S328">
-        <v>0.9126431762666587</v>
+        <v>0.9126431762666365</v>
       </c>
     </row>
     <row r="329">
@@ -22738,10 +22738,10 @@
         <v>90.12539655528288</v>
       </c>
       <c r="N329">
-        <v>92.49798818801629</v>
+        <v>92.49798818801627</v>
       </c>
       <c r="O329">
-        <v>89.42387194359381</v>
+        <v>89.42387194359372</v>
       </c>
       <c r="P329">
         <v>61000</v>
@@ -22752,7 +22752,7 @@
         </is>
       </c>
       <c r="S329">
-        <v>-2.161473068155828</v>
+        <v>-2.161473068155906</v>
       </c>
     </row>
     <row r="330">
@@ -22806,10 +22806,10 @@
         <v>56.56833363518013</v>
       </c>
       <c r="N330">
-        <v>56.80719956100195</v>
+        <v>56.80719956100185</v>
       </c>
       <c r="O330">
-        <v>53.77092581252965</v>
+        <v>53.77092581252928</v>
       </c>
       <c r="P330">
         <v>45790</v>
@@ -22874,10 +22874,10 @@
         <v>56.56833363518013</v>
       </c>
       <c r="N331">
-        <v>56.80719956100195</v>
+        <v>56.80719956100185</v>
       </c>
       <c r="O331">
-        <v>53.77092581252965</v>
+        <v>53.77092581252928</v>
       </c>
       <c r="P331">
         <v>45790</v>
@@ -22942,10 +22942,10 @@
         <v>56.56833363518013</v>
       </c>
       <c r="N332">
-        <v>56.80719956100195</v>
+        <v>56.80719956100185</v>
       </c>
       <c r="O332">
-        <v>53.77092581252965</v>
+        <v>53.77092581252928</v>
       </c>
       <c r="P332">
         <v>45790</v>
@@ -22956,7 +22956,7 @@
         </is>
       </c>
       <c r="S332">
-        <v>0.3061338125185942</v>
+        <v>0.3061338125184943</v>
       </c>
     </row>
     <row r="333">
@@ -23010,10 +23010,10 @@
         <v>56.56833363518013</v>
       </c>
       <c r="N333">
-        <v>56.80719956100195</v>
+        <v>56.80719956100185</v>
       </c>
       <c r="O333">
-        <v>53.77092581252965</v>
+        <v>53.77092581252928</v>
       </c>
       <c r="P333">
         <v>45790</v>
@@ -23024,7 +23024,7 @@
         </is>
       </c>
       <c r="S333">
-        <v>-2.730139935953713</v>
+        <v>-2.730139935954079</v>
       </c>
     </row>
     <row r="334">
@@ -23078,10 +23078,10 @@
         <v>90.08926438227013</v>
       </c>
       <c r="N334">
-        <v>62.07721827600816</v>
+        <v>62.0772182760082</v>
       </c>
       <c r="O334">
-        <v>94.75407612852125</v>
+        <v>94.75407612852116</v>
       </c>
       <c r="P334">
         <v>48462</v>
@@ -23146,10 +23146,10 @@
         <v>90.08926438227013</v>
       </c>
       <c r="N335">
-        <v>62.07721827600816</v>
+        <v>62.0772182760082</v>
       </c>
       <c r="O335">
-        <v>94.75407612852125</v>
+        <v>94.75407612852116</v>
       </c>
       <c r="P335">
         <v>48462</v>
@@ -23214,10 +23214,10 @@
         <v>90.08926438227013</v>
       </c>
       <c r="N336">
-        <v>62.07721827600816</v>
+        <v>62.0772182760082</v>
       </c>
       <c r="O336">
-        <v>94.75407612852125</v>
+        <v>94.75407612852116</v>
       </c>
       <c r="P336">
         <v>48462</v>
@@ -23228,7 +23228,7 @@
         </is>
       </c>
       <c r="S336">
-        <v>0.244385146496795</v>
+        <v>0.2443851464968394</v>
       </c>
     </row>
     <row r="337">
@@ -23282,10 +23282,10 @@
         <v>90.08926438227013</v>
       </c>
       <c r="N337">
-        <v>62.07721827600816</v>
+        <v>62.0772182760082</v>
       </c>
       <c r="O337">
-        <v>94.75407612852125</v>
+        <v>94.75407612852116</v>
       </c>
       <c r="P337">
         <v>48462</v>
@@ -23296,7 +23296,7 @@
         </is>
       </c>
       <c r="S337">
-        <v>32.92124299900988</v>
+        <v>32.92124299900981</v>
       </c>
     </row>
     <row r="338">
@@ -23350,10 +23350,10 @@
         <v>13.63679623448249</v>
       </c>
       <c r="N338">
-        <v>15.79903111329061</v>
+        <v>15.79903111329064</v>
       </c>
       <c r="O338">
-        <v>15.79902656857579</v>
+        <v>15.7990265685755</v>
       </c>
       <c r="P338">
         <v>60000</v>
@@ -23418,10 +23418,10 @@
         <v>13.63679623448249</v>
       </c>
       <c r="N339">
-        <v>15.79903111329061</v>
+        <v>15.79903111329064</v>
       </c>
       <c r="O339">
-        <v>15.79902656857579</v>
+        <v>15.7990265685755</v>
       </c>
       <c r="P339">
         <v>60000</v>
@@ -23486,10 +23486,10 @@
         <v>13.63679623448249</v>
       </c>
       <c r="N340">
-        <v>15.79903111329061</v>
+        <v>15.79903111329064</v>
       </c>
       <c r="O340">
-        <v>15.79902656857579</v>
+        <v>15.7990265685755</v>
       </c>
       <c r="P340">
         <v>60000</v>
@@ -23500,7 +23500,7 @@
         </is>
       </c>
       <c r="S340">
-        <v>-2.973342908037155</v>
+        <v>-2.97334290803713</v>
       </c>
     </row>
     <row r="341">
@@ -23554,10 +23554,10 @@
         <v>13.63679623448249</v>
       </c>
       <c r="N341">
-        <v>15.79903111329061</v>
+        <v>15.79903111329064</v>
       </c>
       <c r="O341">
-        <v>15.79902656857579</v>
+        <v>15.7990265685755</v>
       </c>
       <c r="P341">
         <v>60000</v>
@@ -23568,7 +23568,7 @@
         </is>
       </c>
       <c r="S341">
-        <v>-2.973347452751979</v>
+        <v>-2.97334745275227</v>
       </c>
     </row>
     <row r="342">
@@ -23622,10 +23622,10 @@
         <v>28.71709917682972</v>
       </c>
       <c r="N342">
-        <v>29.1234330717829</v>
+        <v>29.12343307178292</v>
       </c>
       <c r="O342">
-        <v>29.12342358088578</v>
+        <v>29.12342358088552</v>
       </c>
       <c r="P342">
         <v>60000</v>
@@ -23690,10 +23690,10 @@
         <v>28.71709917682972</v>
       </c>
       <c r="N343">
-        <v>29.1234330717829</v>
+        <v>29.12343307178292</v>
       </c>
       <c r="O343">
-        <v>29.12342358088578</v>
+        <v>29.12342358088552</v>
       </c>
       <c r="P343">
         <v>60000</v>
@@ -23758,10 +23758,10 @@
         <v>28.71709917682972</v>
       </c>
       <c r="N344">
-        <v>29.1234330717829</v>
+        <v>29.12343307178292</v>
       </c>
       <c r="O344">
-        <v>29.12342358088578</v>
+        <v>29.12342358088552</v>
       </c>
       <c r="P344">
         <v>60000</v>
@@ -23772,7 +23772,7 @@
         </is>
       </c>
       <c r="S344">
-        <v>-0.3447521545214938</v>
+        <v>-0.3447521545214771</v>
       </c>
     </row>
     <row r="345">
@@ -23826,10 +23826,10 @@
         <v>28.71709917682972</v>
       </c>
       <c r="N345">
-        <v>29.1234330717829</v>
+        <v>29.12343307178292</v>
       </c>
       <c r="O345">
-        <v>29.12342358088578</v>
+        <v>29.12342358088552</v>
       </c>
       <c r="P345">
         <v>60000</v>
@@ -23840,7 +23840,7 @@
         </is>
       </c>
       <c r="S345">
-        <v>-0.3447616454186175</v>
+        <v>-0.3447616454188729</v>
       </c>
     </row>
     <row r="346">
@@ -23894,10 +23894,10 @@
         <v>49.38494464192657</v>
       </c>
       <c r="N346">
-        <v>60.91535036081953</v>
+        <v>60.91535036081957</v>
       </c>
       <c r="O346">
-        <v>60.91538488022671</v>
+        <v>60.91538488022654</v>
       </c>
       <c r="P346">
         <v>59952</v>
@@ -23962,10 +23962,10 @@
         <v>49.38494464192657</v>
       </c>
       <c r="N347">
-        <v>60.91535036081953</v>
+        <v>60.91535036081957</v>
       </c>
       <c r="O347">
-        <v>60.91538488022671</v>
+        <v>60.91538488022654</v>
       </c>
       <c r="P347">
         <v>59952</v>
@@ -24030,10 +24030,10 @@
         <v>49.38494464192657</v>
       </c>
       <c r="N348">
-        <v>60.91535036081953</v>
+        <v>60.91535036081957</v>
       </c>
       <c r="O348">
-        <v>60.91538488022671</v>
+        <v>60.91538488022654</v>
       </c>
       <c r="P348">
         <v>59952</v>
@@ -24044,7 +24044,7 @@
         </is>
       </c>
       <c r="S348">
-        <v>2.019584098563187</v>
+        <v>2.019584098563221</v>
       </c>
     </row>
     <row r="349">
@@ -24098,10 +24098,10 @@
         <v>49.38494464192657</v>
       </c>
       <c r="N349">
-        <v>60.91535036081953</v>
+        <v>60.91535036081957</v>
       </c>
       <c r="O349">
-        <v>60.91538488022671</v>
+        <v>60.91538488022654</v>
       </c>
       <c r="P349">
         <v>59952</v>
@@ -24112,7 +24112,7 @@
         </is>
       </c>
       <c r="S349">
-        <v>2.019618617970365</v>
+        <v>2.019618617970198</v>
       </c>
     </row>
     <row r="350">
@@ -24166,10 +24166,10 @@
         <v>22.5997561136882</v>
       </c>
       <c r="N350">
-        <v>23.77362779864108</v>
+        <v>23.77362779864106</v>
       </c>
       <c r="O350">
-        <v>23.77362873790611</v>
+        <v>23.77362873790585</v>
       </c>
       <c r="P350">
         <v>55143</v>
@@ -24234,10 +24234,10 @@
         <v>22.5997561136882</v>
       </c>
       <c r="N351">
-        <v>23.77362779864108</v>
+        <v>23.77362779864106</v>
       </c>
       <c r="O351">
-        <v>23.77362873790611</v>
+        <v>23.77362873790585</v>
       </c>
       <c r="P351">
         <v>55143</v>
@@ -24302,10 +24302,10 @@
         <v>22.5997561136882</v>
       </c>
       <c r="N352">
-        <v>23.77362779864108</v>
+        <v>23.77362779864106</v>
       </c>
       <c r="O352">
-        <v>23.77362873790611</v>
+        <v>23.77362873790585</v>
       </c>
       <c r="P352">
         <v>55143</v>
@@ -24316,7 +24316,7 @@
         </is>
       </c>
       <c r="S352">
-        <v>-0.3448162932823545</v>
+        <v>-0.3448162932823767</v>
       </c>
     </row>
     <row r="353">
@@ -24370,10 +24370,10 @@
         <v>22.5997561136882</v>
       </c>
       <c r="N353">
-        <v>23.77362779864108</v>
+        <v>23.77362779864106</v>
       </c>
       <c r="O353">
-        <v>23.77362873790611</v>
+        <v>23.77362873790585</v>
       </c>
       <c r="P353">
         <v>55143</v>
@@ -24384,7 +24384,7 @@
         </is>
       </c>
       <c r="S353">
-        <v>-0.3448153540173249</v>
+        <v>-0.3448153540175858</v>
       </c>
     </row>
     <row r="354">
@@ -24438,10 +24438,10 @@
         <v>91.09254484367177</v>
       </c>
       <c r="N354">
-        <v>86.61759427225223</v>
+        <v>86.61759427225226</v>
       </c>
       <c r="O354">
-        <v>90.83563195911087</v>
+        <v>90.83563195911086</v>
       </c>
       <c r="P354">
         <v>57277</v>
@@ -24506,10 +24506,10 @@
         <v>91.09254484367177</v>
       </c>
       <c r="N355">
-        <v>86.61759427225223</v>
+        <v>86.61759427225226</v>
       </c>
       <c r="O355">
-        <v>90.83563195911087</v>
+        <v>90.83563195911086</v>
       </c>
       <c r="P355">
         <v>57277</v>
@@ -24574,10 +24574,10 @@
         <v>91.09254484367177</v>
       </c>
       <c r="N356">
-        <v>86.61759427225223</v>
+        <v>86.61759427225226</v>
       </c>
       <c r="O356">
-        <v>90.83563195911087</v>
+        <v>90.83563195911086</v>
       </c>
       <c r="P356">
         <v>57277</v>
@@ -24588,7 +24588,7 @@
         </is>
       </c>
       <c r="S356">
-        <v>-2.943012765955744</v>
+        <v>-2.943012765955721</v>
       </c>
     </row>
     <row r="357">
@@ -24642,10 +24642,10 @@
         <v>91.09254484367177</v>
       </c>
       <c r="N357">
-        <v>86.61759427225223</v>
+        <v>86.61759427225226</v>
       </c>
       <c r="O357">
-        <v>90.83563195911087</v>
+        <v>90.83563195911086</v>
       </c>
       <c r="P357">
         <v>57277</v>
@@ -24656,7 +24656,7 @@
         </is>
       </c>
       <c r="S357">
-        <v>1.27502492090289</v>
+        <v>1.275024920902879</v>
       </c>
     </row>
     <row r="358">
@@ -24710,10 +24710,10 @@
         <v>60.99375995409059</v>
       </c>
       <c r="N358">
-        <v>61.01690685229683</v>
+        <v>61.01690685229691</v>
       </c>
       <c r="O358">
-        <v>60.71393243350647</v>
+        <v>60.71393243350624</v>
       </c>
       <c r="P358">
         <v>59908</v>
@@ -24778,10 +24778,10 @@
         <v>60.99375995409059</v>
       </c>
       <c r="N359">
-        <v>61.01690685229683</v>
+        <v>61.01690685229691</v>
       </c>
       <c r="O359">
-        <v>60.71393243350647</v>
+        <v>60.71393243350624</v>
       </c>
       <c r="P359">
         <v>59908</v>
@@ -24846,10 +24846,10 @@
         <v>60.99375995409059</v>
       </c>
       <c r="N360">
-        <v>61.01690685229683</v>
+        <v>61.01690685229691</v>
       </c>
       <c r="O360">
-        <v>60.71393243350647</v>
+        <v>60.71393243350624</v>
       </c>
       <c r="P360">
         <v>59908</v>
@@ -24860,7 +24860,7 @@
         </is>
       </c>
       <c r="S360">
-        <v>-1.764850130809714</v>
+        <v>-1.764850130809625</v>
       </c>
     </row>
     <row r="361">
@@ -24914,10 +24914,10 @@
         <v>60.99375995409059</v>
       </c>
       <c r="N361">
-        <v>61.01690685229683</v>
+        <v>61.01690685229691</v>
       </c>
       <c r="O361">
-        <v>60.71393243350647</v>
+        <v>60.71393243350624</v>
       </c>
       <c r="P361">
         <v>59908</v>
@@ -24928,7 +24928,7 @@
         </is>
       </c>
       <c r="S361">
-        <v>-2.067824549600072</v>
+        <v>-2.067824549600306</v>
       </c>
     </row>
     <row r="362">
@@ -24982,10 +24982,10 @@
         <v>52.20547113980047</v>
       </c>
       <c r="N362">
-        <v>51.58328699371187</v>
+        <v>51.58328699371179</v>
       </c>
       <c r="O362">
-        <v>51.69280674241718</v>
+        <v>51.69280674241715</v>
       </c>
       <c r="P362">
         <v>59563</v>
@@ -25050,10 +25050,10 @@
         <v>52.20547113980047</v>
       </c>
       <c r="N363">
-        <v>51.58328699371187</v>
+        <v>51.58328699371179</v>
       </c>
       <c r="O363">
-        <v>51.69280674241718</v>
+        <v>51.69280674241715</v>
       </c>
       <c r="P363">
         <v>59563</v>
@@ -25118,10 +25118,10 @@
         <v>52.20547113980047</v>
       </c>
       <c r="N364">
-        <v>51.58328699371187</v>
+        <v>51.58328699371179</v>
       </c>
       <c r="O364">
-        <v>51.69280674241718</v>
+        <v>51.69280674241715</v>
       </c>
       <c r="P364">
         <v>59563</v>
@@ -25132,7 +25132,7 @@
         </is>
       </c>
       <c r="S364">
-        <v>-0.5048808339750743</v>
+        <v>-0.504880833975152</v>
       </c>
     </row>
     <row r="365">
@@ -25186,10 +25186,10 @@
         <v>52.20547113980047</v>
       </c>
       <c r="N365">
-        <v>51.58328699371187</v>
+        <v>51.58328699371179</v>
       </c>
       <c r="O365">
-        <v>51.69280674241718</v>
+        <v>51.69280674241715</v>
       </c>
       <c r="P365">
         <v>59563</v>
@@ -25200,7 +25200,7 @@
         </is>
       </c>
       <c r="S365">
-        <v>-0.395361085269752</v>
+        <v>-0.3953610852697853</v>
       </c>
     </row>
     <row r="366">
@@ -25254,10 +25254,10 @@
         <v>94.03545595788032</v>
       </c>
       <c r="N366">
-        <v>89.30448482920681</v>
+        <v>89.30448482920688</v>
       </c>
       <c r="O366">
-        <v>92.04660792596593</v>
+        <v>92.04660792596596</v>
       </c>
       <c r="P366">
         <v>59952</v>
@@ -25322,10 +25322,10 @@
         <v>94.03545595788032</v>
       </c>
       <c r="N367">
-        <v>89.30448482920681</v>
+        <v>89.30448482920688</v>
       </c>
       <c r="O367">
-        <v>92.04660792596593</v>
+        <v>92.04660792596596</v>
       </c>
       <c r="P367">
         <v>59952</v>
@@ -25390,10 +25390,10 @@
         <v>94.03545595788032</v>
       </c>
       <c r="N368">
-        <v>89.30448482920681</v>
+        <v>89.30448482920688</v>
       </c>
       <c r="O368">
-        <v>92.04660792596593</v>
+        <v>92.04660792596596</v>
       </c>
       <c r="P368">
         <v>59952</v>
@@ -25404,7 +25404,7 @@
         </is>
       </c>
       <c r="S368">
-        <v>-0.4456318395810954</v>
+        <v>-0.4456318395810288</v>
       </c>
     </row>
     <row r="369">
@@ -25458,10 +25458,10 @@
         <v>94.03545595788032</v>
       </c>
       <c r="N369">
-        <v>89.30448482920681</v>
+        <v>89.30448482920688</v>
       </c>
       <c r="O369">
-        <v>92.04660792596593</v>
+        <v>92.04660792596596</v>
       </c>
       <c r="P369">
         <v>59952</v>
@@ -25472,7 +25472,7 @@
         </is>
       </c>
       <c r="S369">
-        <v>2.296491257178013</v>
+        <v>2.296491257178046</v>
       </c>
     </row>
     <row r="370">
@@ -25526,10 +25526,10 @@
         <v>90.81416282496983</v>
       </c>
       <c r="N370">
-        <v>92.88968438627357</v>
+        <v>92.88968438627364</v>
       </c>
       <c r="O370">
-        <v>89.61508203055229</v>
+        <v>89.6150820305524</v>
       </c>
       <c r="P370">
         <v>60000</v>
@@ -25594,10 +25594,10 @@
         <v>90.81416282496983</v>
       </c>
       <c r="N371">
-        <v>92.88968438627357</v>
+        <v>92.88968438627364</v>
       </c>
       <c r="O371">
-        <v>89.61508203055229</v>
+        <v>89.6150820305524</v>
       </c>
       <c r="P371">
         <v>60000</v>
@@ -25662,10 +25662,10 @@
         <v>90.81416282496983</v>
       </c>
       <c r="N372">
-        <v>92.88968438627357</v>
+        <v>92.88968438627364</v>
       </c>
       <c r="O372">
-        <v>89.61508203055229</v>
+        <v>89.6150820305524</v>
       </c>
       <c r="P372">
         <v>60000</v>
@@ -25676,7 +25676,7 @@
         </is>
       </c>
       <c r="S372">
-        <v>0.878090403613152</v>
+        <v>0.8780904036132187</v>
       </c>
     </row>
     <row r="373">
@@ -25730,10 +25730,10 @@
         <v>90.81416282496983</v>
       </c>
       <c r="N373">
-        <v>92.88968438627357</v>
+        <v>92.88968438627364</v>
       </c>
       <c r="O373">
-        <v>89.61508203055229</v>
+        <v>89.6150820305524</v>
       </c>
       <c r="P373">
         <v>60000</v>
@@ -25744,7 +25744,7 @@
         </is>
       </c>
       <c r="S373">
-        <v>-2.396511952108138</v>
+        <v>-2.396511952108016</v>
       </c>
     </row>
     <row r="374">
@@ -25798,10 +25798,10 @@
         <v>66.36932631856995</v>
       </c>
       <c r="N374">
-        <v>68.08470983266751</v>
+        <v>68.0847098326675</v>
       </c>
       <c r="O374">
-        <v>65.01271796233431</v>
+        <v>65.01271796233409</v>
       </c>
       <c r="P374">
         <v>40876</v>
@@ -25866,10 +25866,10 @@
         <v>66.36932631856995</v>
       </c>
       <c r="N375">
-        <v>68.08470983266751</v>
+        <v>68.0847098326675</v>
       </c>
       <c r="O375">
-        <v>65.01271796233431</v>
+        <v>65.01271796233409</v>
       </c>
       <c r="P375">
         <v>40876</v>
@@ -25934,10 +25934,10 @@
         <v>66.36932631856995</v>
       </c>
       <c r="N376">
-        <v>68.08470983266751</v>
+        <v>68.0847098326675</v>
       </c>
       <c r="O376">
-        <v>65.01271796233431</v>
+        <v>65.01271796233409</v>
       </c>
       <c r="P376">
         <v>40876</v>
@@ -25948,7 +25948,7 @@
         </is>
       </c>
       <c r="S376">
-        <v>0.6967417540917009</v>
+        <v>0.6967417540916898</v>
       </c>
     </row>
     <row r="377">
@@ -26002,10 +26002,10 @@
         <v>66.36932631856995</v>
       </c>
       <c r="N377">
-        <v>68.08470983266751</v>
+        <v>68.0847098326675</v>
       </c>
       <c r="O377">
-        <v>65.01271796233431</v>
+        <v>65.01271796233409</v>
       </c>
       <c r="P377">
         <v>40876</v>
@@ -26016,7 +26016,7 @@
         </is>
       </c>
       <c r="S377">
-        <v>-2.375250116241501</v>
+        <v>-2.375250116241723</v>
       </c>
     </row>
     <row r="378">
@@ -26070,10 +26070,10 @@
         <v>7.294531710394677</v>
       </c>
       <c r="N378">
-        <v>57.18663105574594</v>
+        <v>57.18663105574592</v>
       </c>
       <c r="O378">
-        <v>14.7348353518708</v>
+        <v>14.73483535187088</v>
       </c>
       <c r="P378">
         <v>47791</v>
@@ -26138,10 +26138,10 @@
         <v>7.294531710394677</v>
       </c>
       <c r="N379">
-        <v>57.18663105574594</v>
+        <v>57.18663105574592</v>
       </c>
       <c r="O379">
-        <v>14.7348353518708</v>
+        <v>14.73483535187088</v>
       </c>
       <c r="P379">
         <v>47791</v>
@@ -26206,10 +26206,10 @@
         <v>7.294531710394677</v>
       </c>
       <c r="N380">
-        <v>57.18663105574594</v>
+        <v>57.18663105574592</v>
       </c>
       <c r="O380">
-        <v>14.7348353518708</v>
+        <v>14.73483535187088</v>
       </c>
       <c r="P380">
         <v>47791</v>
@@ -26220,7 +26220,7 @@
         </is>
       </c>
       <c r="S380">
-        <v>-9.099751255847721E-05</v>
+        <v>-9.099751258068167E-05</v>
       </c>
     </row>
     <row r="381">
@@ -26274,10 +26274,10 @@
         <v>7.294531710394677</v>
       </c>
       <c r="N381">
-        <v>57.18663105574594</v>
+        <v>57.18663105574592</v>
       </c>
       <c r="O381">
-        <v>14.7348353518708</v>
+        <v>14.73483535187088</v>
       </c>
       <c r="P381">
         <v>47791</v>
@@ -26288,7 +26288,7 @@
         </is>
       </c>
       <c r="S381">
-        <v>-42.4518867013877</v>
+        <v>-42.45188670138761</v>
       </c>
     </row>
   </sheetData>

--- a/tables_and_figures/input_tables/national_errors.xlsx
+++ b/tables_and_figures/input_tables/national_errors.xlsx
@@ -5670,10 +5670,10 @@
         <v>19.71418188895098</v>
       </c>
       <c r="N78">
-        <v>21.68983558756392</v>
+        <v>21.68983558756369</v>
       </c>
       <c r="O78">
-        <v>21.68983558756405</v>
+        <v>21.68983558756393</v>
       </c>
       <c r="P78">
         <v>55400</v>
@@ -5738,10 +5738,10 @@
         <v>19.71418188895098</v>
       </c>
       <c r="N79">
-        <v>21.68983558756392</v>
+        <v>21.68983558756369</v>
       </c>
       <c r="O79">
-        <v>21.68983558756405</v>
+        <v>21.68983558756393</v>
       </c>
       <c r="P79">
         <v>55400</v>
@@ -5806,10 +5806,10 @@
         <v>19.71418188895098</v>
       </c>
       <c r="N80">
-        <v>21.68983558756392</v>
+        <v>21.68983558756369</v>
       </c>
       <c r="O80">
-        <v>21.68983558756405</v>
+        <v>21.68983558756393</v>
       </c>
       <c r="P80">
         <v>55400</v>
@@ -5820,7 +5820,7 @@
         </is>
       </c>
       <c r="S80">
-        <v>1.936748087924742</v>
+        <v>1.936748087924511</v>
       </c>
     </row>
     <row r="81">
@@ -5874,10 +5874,10 @@
         <v>19.71418188895098</v>
       </c>
       <c r="N81">
-        <v>21.68983558756392</v>
+        <v>21.68983558756369</v>
       </c>
       <c r="O81">
-        <v>21.68983558756405</v>
+        <v>21.68983558756393</v>
       </c>
       <c r="P81">
         <v>55400</v>
@@ -5888,7 +5888,7 @@
         </is>
       </c>
       <c r="S81">
-        <v>1.936748087924864</v>
+        <v>1.936748087924747</v>
       </c>
     </row>
     <row r="82">
@@ -5942,10 +5942,10 @@
         <v>34.574542787282</v>
       </c>
       <c r="N82">
-        <v>32.13108402346401</v>
+        <v>32.131084023464</v>
       </c>
       <c r="O82">
-        <v>32.13108402346418</v>
+        <v>32.13108402346392</v>
       </c>
       <c r="P82">
         <v>55400</v>
@@ -6010,10 +6010,10 @@
         <v>34.574542787282</v>
       </c>
       <c r="N83">
-        <v>32.13108402346401</v>
+        <v>32.131084023464</v>
       </c>
       <c r="O83">
-        <v>32.13108402346418</v>
+        <v>32.13108402346392</v>
       </c>
       <c r="P83">
         <v>55400</v>
@@ -6078,10 +6078,10 @@
         <v>34.574542787282</v>
       </c>
       <c r="N84">
-        <v>32.13108402346401</v>
+        <v>32.131084023464</v>
       </c>
       <c r="O84">
-        <v>32.13108402346418</v>
+        <v>32.13108402346392</v>
       </c>
       <c r="P84">
         <v>55400</v>
@@ -6092,7 +6092,7 @@
         </is>
       </c>
       <c r="S84">
-        <v>0.4445337920600756</v>
+        <v>0.44453379206007</v>
       </c>
     </row>
     <row r="85">
@@ -6146,10 +6146,10 @@
         <v>34.574542787282</v>
       </c>
       <c r="N85">
-        <v>32.13108402346401</v>
+        <v>32.131084023464</v>
       </c>
       <c r="O85">
-        <v>32.13108402346418</v>
+        <v>32.13108402346392</v>
       </c>
       <c r="P85">
         <v>55400</v>
@@ -6160,7 +6160,7 @@
         </is>
       </c>
       <c r="S85">
-        <v>0.4445337920602477</v>
+        <v>0.4445337920599868</v>
       </c>
     </row>
     <row r="86">
@@ -6214,10 +6214,10 @@
         <v>49.75314441747606</v>
       </c>
       <c r="N86">
-        <v>60.64538348494989</v>
+        <v>60.64538348495072</v>
       </c>
       <c r="O86">
-        <v>60.64538348495076</v>
+        <v>60.64538348495044</v>
       </c>
       <c r="P86">
         <v>55400</v>
@@ -6282,10 +6282,10 @@
         <v>49.75314441747606</v>
       </c>
       <c r="N87">
-        <v>60.64538348494989</v>
+        <v>60.64538348495072</v>
       </c>
       <c r="O87">
-        <v>60.64538348495076</v>
+        <v>60.64538348495044</v>
       </c>
       <c r="P87">
         <v>55400</v>
@@ -6350,10 +6350,10 @@
         <v>49.75314441747606</v>
       </c>
       <c r="N88">
-        <v>60.64538348494989</v>
+        <v>60.64538348495072</v>
       </c>
       <c r="O88">
-        <v>60.64538348495076</v>
+        <v>60.64538348495044</v>
       </c>
       <c r="P88">
         <v>55400</v>
@@ -6364,7 +6364,7 @@
         </is>
       </c>
       <c r="S88">
-        <v>-0.2387361085909201</v>
+        <v>-0.2387361085900874</v>
       </c>
     </row>
     <row r="89">
@@ -6418,10 +6418,10 @@
         <v>49.75314441747606</v>
       </c>
       <c r="N89">
-        <v>60.64538348494989</v>
+        <v>60.64538348495072</v>
       </c>
       <c r="O89">
-        <v>60.64538348495076</v>
+        <v>60.64538348495044</v>
       </c>
       <c r="P89">
         <v>55400</v>
@@ -6432,7 +6432,7 @@
         </is>
       </c>
       <c r="S89">
-        <v>-0.238736108590043</v>
+        <v>-0.238736108590365</v>
       </c>
     </row>
     <row r="90">
@@ -6486,10 +6486,10 @@
         <v>22.91056164538115</v>
       </c>
       <c r="N90">
-        <v>23.19167199619754</v>
+        <v>23.19167199619718</v>
       </c>
       <c r="O90">
-        <v>23.19287782028184</v>
+        <v>23.19287782028157</v>
       </c>
       <c r="P90">
         <v>48612</v>
@@ -6554,10 +6554,10 @@
         <v>22.91056164538115</v>
       </c>
       <c r="N91">
-        <v>23.19167199619754</v>
+        <v>23.19167199619718</v>
       </c>
       <c r="O91">
-        <v>23.19287782028184</v>
+        <v>23.19287782028157</v>
       </c>
       <c r="P91">
         <v>48612</v>
@@ -6622,10 +6622,10 @@
         <v>22.91056164538115</v>
       </c>
       <c r="N92">
-        <v>23.19167199619754</v>
+        <v>23.19167199619718</v>
       </c>
       <c r="O92">
-        <v>23.19287782028184</v>
+        <v>23.19287782028157</v>
       </c>
       <c r="P92">
         <v>48612</v>
@@ -6636,7 +6636,7 @@
         </is>
       </c>
       <c r="S92">
-        <v>-0.2830345174885757</v>
+        <v>-0.2830345174889337</v>
       </c>
     </row>
     <row r="93">
@@ -6690,10 +6690,10 @@
         <v>22.91056164538115</v>
       </c>
       <c r="N93">
-        <v>23.19167199619754</v>
+        <v>23.19167199619718</v>
       </c>
       <c r="O93">
-        <v>23.19287782028184</v>
+        <v>23.19287782028157</v>
       </c>
       <c r="P93">
         <v>48612</v>
@@ -6704,7 +6704,7 @@
         </is>
       </c>
       <c r="S93">
-        <v>-0.2818286934042763</v>
+        <v>-0.2818286934045483</v>
       </c>
     </row>
     <row r="94">
@@ -6758,10 +6758,10 @@
         <v>97.35418313024078</v>
       </c>
       <c r="N94">
-        <v>90.07772910426883</v>
+        <v>90.07772910426878</v>
       </c>
       <c r="O94">
-        <v>95.56945283348823</v>
+        <v>95.5694528334882</v>
       </c>
       <c r="P94">
         <v>49058</v>
@@ -6826,10 +6826,10 @@
         <v>97.35418313024078</v>
       </c>
       <c r="N95">
-        <v>90.07772910426883</v>
+        <v>90.07772910426878</v>
       </c>
       <c r="O95">
-        <v>95.56945283348823</v>
+        <v>95.5694528334882</v>
       </c>
       <c r="P95">
         <v>49058</v>
@@ -6894,10 +6894,10 @@
         <v>97.35418313024078</v>
       </c>
       <c r="N96">
-        <v>90.07772910426883</v>
+        <v>90.07772910426878</v>
       </c>
       <c r="O96">
-        <v>95.56945283348823</v>
+        <v>95.5694528334882</v>
       </c>
       <c r="P96">
         <v>49058</v>
@@ -6908,7 +6908,7 @@
         </is>
       </c>
       <c r="S96">
-        <v>-2.036080868973866</v>
+        <v>-2.0360808689739</v>
       </c>
     </row>
     <row r="97">
@@ -6962,10 +6962,10 @@
         <v>97.35418313024078</v>
       </c>
       <c r="N97">
-        <v>90.07772910426883</v>
+        <v>90.07772910426878</v>
       </c>
       <c r="O97">
-        <v>95.56945283348823</v>
+        <v>95.5694528334882</v>
       </c>
       <c r="P97">
         <v>49058</v>
@@ -6976,7 +6976,7 @@
         </is>
       </c>
       <c r="S97">
-        <v>3.455642860245545</v>
+        <v>3.455642860245511</v>
       </c>
     </row>
     <row r="98">
@@ -7030,10 +7030,10 @@
         <v>61.33920356117392</v>
       </c>
       <c r="N98">
-        <v>60.39792154911977</v>
+        <v>60.39792154911988</v>
       </c>
       <c r="O98">
-        <v>61.3884842702589</v>
+        <v>61.38848427025866</v>
       </c>
       <c r="P98">
         <v>55325</v>
@@ -7098,10 +7098,10 @@
         <v>61.33920356117392</v>
       </c>
       <c r="N99">
-        <v>60.39792154911977</v>
+        <v>60.39792154911988</v>
       </c>
       <c r="O99">
-        <v>61.3884842702589</v>
+        <v>61.38848427025866</v>
       </c>
       <c r="P99">
         <v>55325</v>
@@ -7166,10 +7166,10 @@
         <v>61.33920356117392</v>
       </c>
       <c r="N100">
-        <v>60.39792154911977</v>
+        <v>60.39792154911988</v>
       </c>
       <c r="O100">
-        <v>61.3884842702589</v>
+        <v>61.38848427025866</v>
       </c>
       <c r="P100">
         <v>55325</v>
@@ -7180,7 +7180,7 @@
         </is>
       </c>
       <c r="S100">
-        <v>-1.447053910698781</v>
+        <v>-1.44705391069867</v>
       </c>
     </row>
     <row r="101">
@@ -7234,10 +7234,10 @@
         <v>61.33920356117392</v>
       </c>
       <c r="N101">
-        <v>60.39792154911977</v>
+        <v>60.39792154911988</v>
       </c>
       <c r="O101">
-        <v>61.3884842702589</v>
+        <v>61.38848427025866</v>
       </c>
       <c r="P101">
         <v>55325</v>
@@ -7248,7 +7248,7 @@
         </is>
       </c>
       <c r="S101">
-        <v>-0.4564911895596491</v>
+        <v>-0.4564911895598933</v>
       </c>
     </row>
     <row r="102">
@@ -7302,10 +7302,10 @@
         <v>51.97518434916385</v>
       </c>
       <c r="N102">
-        <v>51.9685103540086</v>
+        <v>51.96851035400858</v>
       </c>
       <c r="O102">
-        <v>55.16820532599615</v>
+        <v>55.16820532599596</v>
       </c>
       <c r="P102">
         <v>55400</v>
@@ -7370,10 +7370,10 @@
         <v>51.97518434916385</v>
       </c>
       <c r="N103">
-        <v>51.9685103540086</v>
+        <v>51.96851035400858</v>
       </c>
       <c r="O103">
-        <v>55.16820532599615</v>
+        <v>55.16820532599596</v>
       </c>
       <c r="P103">
         <v>55400</v>
@@ -7438,10 +7438,10 @@
         <v>51.97518434916385</v>
       </c>
       <c r="N104">
-        <v>51.9685103540086</v>
+        <v>51.96851035400858</v>
       </c>
       <c r="O104">
-        <v>55.16820532599615</v>
+        <v>55.16820532599596</v>
       </c>
       <c r="P104">
         <v>55400</v>
@@ -7452,7 +7452,7 @@
         </is>
       </c>
       <c r="S104">
-        <v>-0.4053152415142924</v>
+        <v>-0.4053152415143146</v>
       </c>
     </row>
     <row r="105">
@@ -7506,10 +7506,10 @@
         <v>51.97518434916385</v>
       </c>
       <c r="N105">
-        <v>51.9685103540086</v>
+        <v>51.96851035400858</v>
       </c>
       <c r="O105">
-        <v>55.16820532599615</v>
+        <v>55.16820532599596</v>
       </c>
       <c r="P105">
         <v>55400</v>
@@ -7520,7 +7520,7 @@
         </is>
       </c>
       <c r="S105">
-        <v>2.794379730473251</v>
+        <v>2.794379730473062</v>
       </c>
     </row>
     <row r="106">
@@ -7574,10 +7574,10 @@
         <v>92.92783958842196</v>
       </c>
       <c r="N106">
-        <v>87.32994267910608</v>
+        <v>87.32994267910654</v>
       </c>
       <c r="O106">
-        <v>92.33804839648158</v>
+        <v>92.33804839648147</v>
       </c>
       <c r="P106">
         <v>55242</v>
@@ -7642,10 +7642,10 @@
         <v>92.92783958842196</v>
       </c>
       <c r="N107">
-        <v>87.32994267910608</v>
+        <v>87.32994267910654</v>
       </c>
       <c r="O107">
-        <v>92.33804839648158</v>
+        <v>92.33804839648147</v>
       </c>
       <c r="P107">
         <v>55242</v>
@@ -7710,10 +7710,10 @@
         <v>92.92783958842196</v>
       </c>
       <c r="N108">
-        <v>87.32994267910608</v>
+        <v>87.32994267910654</v>
       </c>
       <c r="O108">
-        <v>92.33804839648158</v>
+        <v>92.33804839648147</v>
       </c>
       <c r="P108">
         <v>55242</v>
@@ -7724,7 +7724,7 @@
         </is>
       </c>
       <c r="S108">
-        <v>-0.1009559809642679</v>
+        <v>-0.1009559809638128</v>
       </c>
     </row>
     <row r="109">
@@ -7778,10 +7778,10 @@
         <v>92.92783958842196</v>
       </c>
       <c r="N109">
-        <v>87.32994267910608</v>
+        <v>87.32994267910654</v>
       </c>
       <c r="O109">
-        <v>92.33804839648158</v>
+        <v>92.33804839648147</v>
       </c>
       <c r="P109">
         <v>55242</v>
@@ -7792,7 +7792,7 @@
         </is>
       </c>
       <c r="S109">
-        <v>4.907149736411231</v>
+        <v>4.907149736411109</v>
       </c>
     </row>
     <row r="110">
@@ -7846,10 +7846,10 @@
         <v>86.30129201699636</v>
       </c>
       <c r="N110">
-        <v>90.29738719024508</v>
+        <v>90.29738719024533</v>
       </c>
       <c r="O110">
-        <v>85.14002215874885</v>
+        <v>85.14002215874858</v>
       </c>
       <c r="P110">
         <v>55400</v>
@@ -7914,10 +7914,10 @@
         <v>86.30129201699636</v>
       </c>
       <c r="N111">
-        <v>90.29738719024508</v>
+        <v>90.29738719024533</v>
       </c>
       <c r="O111">
-        <v>85.14002215874885</v>
+        <v>85.14002215874858</v>
       </c>
       <c r="P111">
         <v>55400</v>
@@ -7982,10 +7982,10 @@
         <v>86.30129201699636</v>
       </c>
       <c r="N112">
-        <v>90.29738719024508</v>
+        <v>90.29738719024533</v>
       </c>
       <c r="O112">
-        <v>85.14002215874885</v>
+        <v>85.14002215874858</v>
       </c>
       <c r="P112">
         <v>55400</v>
@@ -7996,7 +7996,7 @@
         </is>
       </c>
       <c r="S112">
-        <v>0.729413685619984</v>
+        <v>0.7294136856202504</v>
       </c>
     </row>
     <row r="113">
@@ -8050,10 +8050,10 @@
         <v>86.30129201699636</v>
       </c>
       <c r="N113">
-        <v>90.29738719024508</v>
+        <v>90.29738719024533</v>
       </c>
       <c r="O113">
-        <v>85.14002215874885</v>
+        <v>85.14002215874858</v>
       </c>
       <c r="P113">
         <v>55400</v>
@@ -8064,7 +8064,7 @@
         </is>
       </c>
       <c r="S113">
-        <v>-4.427951345876235</v>
+        <v>-4.427951345876502</v>
       </c>
     </row>
     <row r="114">
@@ -8118,10 +8118,10 @@
         <v>78.40310703823478</v>
       </c>
       <c r="N114">
-        <v>81.97678428265853</v>
+        <v>81.97678428265843</v>
       </c>
       <c r="O114">
-        <v>78.85814310205289</v>
+        <v>78.85814310205271</v>
       </c>
       <c r="P114">
         <v>37859</v>
@@ -8186,10 +8186,10 @@
         <v>78.40310703823478</v>
       </c>
       <c r="N115">
-        <v>81.97678428265853</v>
+        <v>81.97678428265843</v>
       </c>
       <c r="O115">
-        <v>78.85814310205289</v>
+        <v>78.85814310205271</v>
       </c>
       <c r="P115">
         <v>37859</v>
@@ -8254,10 +8254,10 @@
         <v>78.40310703823478</v>
       </c>
       <c r="N116">
-        <v>81.97678428265853</v>
+        <v>81.97678428265843</v>
       </c>
       <c r="O116">
-        <v>78.85814310205289</v>
+        <v>78.85814310205271</v>
       </c>
       <c r="P116">
         <v>37859</v>
@@ -8268,7 +8268,7 @@
         </is>
       </c>
       <c r="S116">
-        <v>-0.8086498910109485</v>
+        <v>-0.8086498910110373</v>
       </c>
     </row>
     <row r="117">
@@ -8322,10 +8322,10 @@
         <v>78.40310703823478</v>
       </c>
       <c r="N117">
-        <v>81.97678428265853</v>
+        <v>81.97678428265843</v>
       </c>
       <c r="O117">
-        <v>78.85814310205289</v>
+        <v>78.85814310205271</v>
       </c>
       <c r="P117">
         <v>37859</v>
@@ -8336,7 +8336,7 @@
         </is>
       </c>
       <c r="S117">
-        <v>-3.927291071616579</v>
+        <v>-3.927291071616756</v>
       </c>
     </row>
     <row r="118">
@@ -8390,10 +8390,10 @@
         <v>27.81811575108459</v>
       </c>
       <c r="N118">
-        <v>61.84561105159655</v>
+        <v>61.84561105159537</v>
       </c>
       <c r="O118">
-        <v>26.29907721541566</v>
+        <v>26.29907721541595</v>
       </c>
       <c r="P118">
         <v>44776</v>
@@ -8458,10 +8458,10 @@
         <v>27.81811575108459</v>
       </c>
       <c r="N119">
-        <v>61.84561105159655</v>
+        <v>61.84561105159537</v>
       </c>
       <c r="O119">
-        <v>26.29907721541566</v>
+        <v>26.29907721541595</v>
       </c>
       <c r="P119">
         <v>44776</v>
@@ -8526,10 +8526,10 @@
         <v>27.81811575108459</v>
       </c>
       <c r="N120">
-        <v>61.84561105159655</v>
+        <v>61.84561105159537</v>
       </c>
       <c r="O120">
-        <v>26.29907721541566</v>
+        <v>26.29907721541595</v>
       </c>
       <c r="P120">
         <v>44776</v>
@@ -8540,7 +8540,7 @@
         </is>
       </c>
       <c r="S120">
-        <v>0.3570698780801185</v>
+        <v>0.3570698780789416</v>
       </c>
     </row>
     <row r="121">
@@ -8594,10 +8594,10 @@
         <v>27.81811575108459</v>
       </c>
       <c r="N121">
-        <v>61.84561105159655</v>
+        <v>61.84561105159537</v>
       </c>
       <c r="O121">
-        <v>26.29907721541566</v>
+        <v>26.29907721541595</v>
       </c>
       <c r="P121">
         <v>44776</v>
@@ -8608,7 +8608,7 @@
         </is>
       </c>
       <c r="S121">
-        <v>-35.18946395810077</v>
+        <v>-35.18946395810048</v>
       </c>
     </row>
     <row r="122">
@@ -8662,10 +8662,10 @@
         <v>19.55956107979261</v>
       </c>
       <c r="N122">
-        <v>18.78381922591106</v>
+        <v>18.78381922591102</v>
       </c>
       <c r="O122">
-        <v>18.78376405592467</v>
+        <v>18.78376405592434</v>
       </c>
       <c r="P122">
         <v>54535</v>
@@ -8730,10 +8730,10 @@
         <v>19.55956107979261</v>
       </c>
       <c r="N123">
-        <v>18.78381922591106</v>
+        <v>18.78381922591102</v>
       </c>
       <c r="O123">
-        <v>18.78376405592467</v>
+        <v>18.78376405592434</v>
       </c>
       <c r="P123">
         <v>54535</v>
@@ -8798,10 +8798,10 @@
         <v>19.55956107979261</v>
       </c>
       <c r="N124">
-        <v>18.78381922591106</v>
+        <v>18.78381922591102</v>
       </c>
       <c r="O124">
-        <v>18.78376405592467</v>
+        <v>18.78376405592434</v>
       </c>
       <c r="P124">
         <v>54535</v>
@@ -8812,7 +8812,7 @@
         </is>
       </c>
       <c r="S124">
-        <v>-0.5877807213773428</v>
+        <v>-0.5877807213773845</v>
       </c>
     </row>
     <row r="125">
@@ -8866,10 +8866,10 @@
         <v>19.55956107979261</v>
       </c>
       <c r="N125">
-        <v>18.78381922591106</v>
+        <v>18.78381922591102</v>
       </c>
       <c r="O125">
-        <v>18.78376405592467</v>
+        <v>18.78376405592434</v>
       </c>
       <c r="P125">
         <v>54535</v>
@@ -8880,7 +8880,7 @@
         </is>
       </c>
       <c r="S125">
-        <v>-0.587835891363736</v>
+        <v>-0.5878358913640636</v>
       </c>
     </row>
     <row r="126">
@@ -8934,10 +8934,10 @@
         <v>30.49659378673363</v>
       </c>
       <c r="N126">
-        <v>30.53786279215646</v>
+        <v>30.53786279215657</v>
       </c>
       <c r="O126">
-        <v>30.53774451303555</v>
+        <v>30.53774451303544</v>
       </c>
       <c r="P126">
         <v>54535</v>
@@ -9002,10 +9002,10 @@
         <v>30.49659378673363</v>
       </c>
       <c r="N127">
-        <v>30.53786279215646</v>
+        <v>30.53786279215657</v>
       </c>
       <c r="O127">
-        <v>30.53774451303555</v>
+        <v>30.53774451303544</v>
       </c>
       <c r="P127">
         <v>54535</v>
@@ -9070,10 +9070,10 @@
         <v>30.49659378673363</v>
       </c>
       <c r="N128">
-        <v>30.53786279215646</v>
+        <v>30.53786279215657</v>
       </c>
       <c r="O128">
-        <v>30.53774451303555</v>
+        <v>30.53774451303544</v>
       </c>
       <c r="P128">
         <v>54535</v>
@@ -9084,7 +9084,7 @@
         </is>
       </c>
       <c r="S128">
-        <v>-0.1367483492706933</v>
+        <v>-0.1367483492705823</v>
       </c>
     </row>
     <row r="129">
@@ -9138,10 +9138,10 @@
         <v>30.49659378673363</v>
       </c>
       <c r="N129">
-        <v>30.53786279215646</v>
+        <v>30.53786279215657</v>
       </c>
       <c r="O129">
-        <v>30.53774451303555</v>
+        <v>30.53774451303544</v>
       </c>
       <c r="P129">
         <v>54535</v>
@@ -9152,7 +9152,7 @@
         </is>
       </c>
       <c r="S129">
-        <v>-0.136866628391602</v>
+        <v>-0.136866628391713</v>
       </c>
     </row>
     <row r="130">
@@ -9206,10 +9206,10 @@
         <v>46.0408366864019</v>
       </c>
       <c r="N130">
-        <v>60.0704815986113</v>
+        <v>60.07048159861138</v>
       </c>
       <c r="O130">
-        <v>60.07051969567441</v>
+        <v>60.07051969567385</v>
       </c>
       <c r="P130">
         <v>54535</v>
@@ -9274,10 +9274,10 @@
         <v>46.0408366864019</v>
       </c>
       <c r="N131">
-        <v>60.0704815986113</v>
+        <v>60.07048159861138</v>
       </c>
       <c r="O131">
-        <v>60.07051969567441</v>
+        <v>60.07051969567385</v>
       </c>
       <c r="P131">
         <v>54535</v>
@@ -9342,10 +9342,10 @@
         <v>46.0408366864019</v>
       </c>
       <c r="N132">
-        <v>60.0704815986113</v>
+        <v>60.07048159861138</v>
       </c>
       <c r="O132">
-        <v>60.07051969567441</v>
+        <v>60.07051969567385</v>
       </c>
       <c r="P132">
         <v>54535</v>
@@ -9356,7 +9356,7 @@
         </is>
       </c>
       <c r="S132">
-        <v>-0.7931925941981666</v>
+        <v>-0.7931925941980889</v>
       </c>
     </row>
     <row r="133">
@@ -9410,10 +9410,10 @@
         <v>46.0408366864019</v>
       </c>
       <c r="N133">
-        <v>60.0704815986113</v>
+        <v>60.07048159861138</v>
       </c>
       <c r="O133">
-        <v>60.07051969567441</v>
+        <v>60.07051969567385</v>
       </c>
       <c r="P133">
         <v>54535</v>
@@ -9424,7 +9424,7 @@
         </is>
       </c>
       <c r="S133">
-        <v>-0.7931544971350624</v>
+        <v>-0.7931544971356175</v>
       </c>
     </row>
     <row r="134">
@@ -9478,10 +9478,10 @@
         <v>22.21829840823713</v>
       </c>
       <c r="N134">
-        <v>22.8075281326633</v>
+        <v>22.80752813266336</v>
       </c>
       <c r="O134">
-        <v>22.80764277056721</v>
+        <v>22.80764277056756</v>
       </c>
       <c r="P134">
         <v>47918</v>
@@ -9546,10 +9546,10 @@
         <v>22.21829840823713</v>
       </c>
       <c r="N135">
-        <v>22.8075281326633</v>
+        <v>22.80752813266336</v>
       </c>
       <c r="O135">
-        <v>22.80764277056721</v>
+        <v>22.80764277056756</v>
       </c>
       <c r="P135">
         <v>47918</v>
@@ -9614,10 +9614,10 @@
         <v>22.21829840823713</v>
       </c>
       <c r="N136">
-        <v>22.8075281326633</v>
+        <v>22.80752813266336</v>
       </c>
       <c r="O136">
-        <v>22.80764277056721</v>
+        <v>22.80764277056756</v>
       </c>
       <c r="P136">
         <v>47918</v>
@@ -9628,7 +9628,7 @@
         </is>
       </c>
       <c r="S136">
-        <v>-0.6564727659102182</v>
+        <v>-0.6564727659101488</v>
       </c>
     </row>
     <row r="137">
@@ -9682,10 +9682,10 @@
         <v>22.21829840823713</v>
       </c>
       <c r="N137">
-        <v>22.8075281326633</v>
+        <v>22.80752813266336</v>
       </c>
       <c r="O137">
-        <v>22.80764277056721</v>
+        <v>22.80764277056756</v>
       </c>
       <c r="P137">
         <v>47918</v>
@@ -9696,7 +9696,7 @@
         </is>
       </c>
       <c r="S137">
-        <v>-0.6563581280063013</v>
+        <v>-0.6563581280059488</v>
       </c>
     </row>
     <row r="138">
@@ -9750,7 +9750,7 @@
         <v>97.70353186034932</v>
       </c>
       <c r="N138">
-        <v>89.057646837029</v>
+        <v>89.05764683702921</v>
       </c>
       <c r="O138">
         <v>96.53969112716689</v>
@@ -9818,7 +9818,7 @@
         <v>97.70353186034932</v>
       </c>
       <c r="N139">
-        <v>89.057646837029</v>
+        <v>89.05764683702921</v>
       </c>
       <c r="O139">
         <v>96.53969112716689</v>
@@ -9886,7 +9886,7 @@
         <v>97.70353186034932</v>
       </c>
       <c r="N140">
-        <v>89.057646837029</v>
+        <v>89.05764683702921</v>
       </c>
       <c r="O140">
         <v>96.53969112716689</v>
@@ -9900,7 +9900,7 @@
         </is>
       </c>
       <c r="S140">
-        <v>-2.609675776510978</v>
+        <v>-2.609675776510767</v>
       </c>
     </row>
     <row r="141">
@@ -9954,7 +9954,7 @@
         <v>97.70353186034932</v>
       </c>
       <c r="N141">
-        <v>89.057646837029</v>
+        <v>89.05764683702921</v>
       </c>
       <c r="O141">
         <v>96.53969112716689</v>
@@ -10022,10 +10022,10 @@
         <v>60.16767859230833</v>
       </c>
       <c r="N142">
-        <v>61.88484918229447</v>
+        <v>61.88484918229459</v>
       </c>
       <c r="O142">
-        <v>61.4772745944154</v>
+        <v>61.47727459441587</v>
       </c>
       <c r="P142">
         <v>54426</v>
@@ -10090,10 +10090,10 @@
         <v>60.16767859230833</v>
       </c>
       <c r="N143">
-        <v>61.88484918229447</v>
+        <v>61.88484918229459</v>
       </c>
       <c r="O143">
-        <v>61.4772745944154</v>
+        <v>61.47727459441587</v>
       </c>
       <c r="P143">
         <v>54426</v>
@@ -10158,10 +10158,10 @@
         <v>60.16767859230833</v>
       </c>
       <c r="N144">
-        <v>61.88484918229447</v>
+        <v>61.88484918229459</v>
       </c>
       <c r="O144">
-        <v>61.4772745944154</v>
+        <v>61.47727459441587</v>
       </c>
       <c r="P144">
         <v>54426</v>
@@ -10172,7 +10172,7 @@
         </is>
       </c>
       <c r="S144">
-        <v>-1.127829715025674</v>
+        <v>-1.127829715025552</v>
       </c>
     </row>
     <row r="145">
@@ -10226,10 +10226,10 @@
         <v>60.16767859230833</v>
       </c>
       <c r="N145">
-        <v>61.88484918229447</v>
+        <v>61.88484918229459</v>
       </c>
       <c r="O145">
-        <v>61.4772745944154</v>
+        <v>61.47727459441587</v>
       </c>
       <c r="P145">
         <v>54426</v>
@@ -10240,7 +10240,7 @@
         </is>
       </c>
       <c r="S145">
-        <v>-1.535404302904742</v>
+        <v>-1.535404302904275</v>
       </c>
     </row>
     <row r="146">
@@ -10294,10 +10294,10 @@
         <v>51.81970969080953</v>
       </c>
       <c r="N146">
-        <v>52.10416026488397</v>
+        <v>52.10416026488398</v>
       </c>
       <c r="O146">
-        <v>53.71180101699645</v>
+        <v>53.71180101699651</v>
       </c>
       <c r="P146">
         <v>54535</v>
@@ -10362,10 +10362,10 @@
         <v>51.81970969080953</v>
       </c>
       <c r="N147">
-        <v>52.10416026488397</v>
+        <v>52.10416026488398</v>
       </c>
       <c r="O147">
-        <v>53.71180101699645</v>
+        <v>53.71180101699651</v>
       </c>
       <c r="P147">
         <v>54535</v>
@@ -10430,10 +10430,10 @@
         <v>51.81970969080953</v>
       </c>
       <c r="N148">
-        <v>52.10416026488397</v>
+        <v>52.10416026488398</v>
       </c>
       <c r="O148">
-        <v>53.71180101699645</v>
+        <v>53.71180101699651</v>
       </c>
       <c r="P148">
         <v>54535</v>
@@ -10444,7 +10444,7 @@
         </is>
       </c>
       <c r="S148">
-        <v>-0.1882192833705831</v>
+        <v>-0.188219283370572</v>
       </c>
     </row>
     <row r="149">
@@ -10498,10 +10498,10 @@
         <v>51.81970969080953</v>
       </c>
       <c r="N149">
-        <v>52.10416026488397</v>
+        <v>52.10416026488398</v>
       </c>
       <c r="O149">
-        <v>53.71180101699645</v>
+        <v>53.71180101699651</v>
       </c>
       <c r="P149">
         <v>54535</v>
@@ -10512,7 +10512,7 @@
         </is>
       </c>
       <c r="S149">
-        <v>1.419421468741899</v>
+        <v>1.419421468741955</v>
       </c>
     </row>
     <row r="150">
@@ -10566,10 +10566,10 @@
         <v>93.85406722827751</v>
       </c>
       <c r="N150">
-        <v>88.10981089169665</v>
+        <v>88.10981089169675</v>
       </c>
       <c r="O150">
-        <v>92.81601489807952</v>
+        <v>92.81601489807957</v>
       </c>
       <c r="P150">
         <v>54281</v>
@@ -10634,10 +10634,10 @@
         <v>93.85406722827751</v>
       </c>
       <c r="N151">
-        <v>88.10981089169665</v>
+        <v>88.10981089169675</v>
       </c>
       <c r="O151">
-        <v>92.81601489807952</v>
+        <v>92.81601489807957</v>
       </c>
       <c r="P151">
         <v>54281</v>
@@ -10702,10 +10702,10 @@
         <v>93.85406722827751</v>
       </c>
       <c r="N152">
-        <v>88.10981089169665</v>
+        <v>88.10981089169675</v>
       </c>
       <c r="O152">
-        <v>92.81601489807952</v>
+        <v>92.81601489807957</v>
       </c>
       <c r="P152">
         <v>54281</v>
@@ -10716,7 +10716,7 @@
         </is>
       </c>
       <c r="S152">
-        <v>0.03641639628380045</v>
+        <v>0.03641639628391147</v>
       </c>
     </row>
     <row r="153">
@@ -10770,10 +10770,10 @@
         <v>93.85406722827751</v>
       </c>
       <c r="N153">
-        <v>88.10981089169665</v>
+        <v>88.10981089169675</v>
       </c>
       <c r="O153">
-        <v>92.81601489807952</v>
+        <v>92.81601489807957</v>
       </c>
       <c r="P153">
         <v>54281</v>
@@ -10784,7 +10784,7 @@
         </is>
       </c>
       <c r="S153">
-        <v>4.742620402666664</v>
+        <v>4.742620402666731</v>
       </c>
     </row>
     <row r="154">
@@ -10838,10 +10838,10 @@
         <v>87.6320105705225</v>
       </c>
       <c r="N154">
-        <v>90.59641787470704</v>
+        <v>90.59641787470699</v>
       </c>
       <c r="O154">
-        <v>86.4560265318876</v>
+        <v>86.45602653188774</v>
       </c>
       <c r="P154">
         <v>54534</v>
@@ -10906,10 +10906,10 @@
         <v>87.6320105705225</v>
       </c>
       <c r="N155">
-        <v>90.59641787470704</v>
+        <v>90.59641787470699</v>
       </c>
       <c r="O155">
-        <v>86.4560265318876</v>
+        <v>86.45602653188774</v>
       </c>
       <c r="P155">
         <v>54534</v>
@@ -10974,10 +10974,10 @@
         <v>87.6320105705225</v>
       </c>
       <c r="N156">
-        <v>90.59641787470704</v>
+        <v>90.59641787470699</v>
       </c>
       <c r="O156">
-        <v>86.4560265318876</v>
+        <v>86.45602653188774</v>
       </c>
       <c r="P156">
         <v>54534</v>
@@ -10988,7 +10988,7 @@
         </is>
       </c>
       <c r="S156">
-        <v>0.6425753431986925</v>
+        <v>0.642575343198637</v>
       </c>
     </row>
     <row r="157">
@@ -11042,10 +11042,10 @@
         <v>87.6320105705225</v>
       </c>
       <c r="N157">
-        <v>90.59641787470704</v>
+        <v>90.59641787470699</v>
       </c>
       <c r="O157">
-        <v>86.4560265318876</v>
+        <v>86.45602653188774</v>
       </c>
       <c r="P157">
         <v>54534</v>
@@ -11056,7 +11056,7 @@
         </is>
       </c>
       <c r="S157">
-        <v>-3.497815999620746</v>
+        <v>-3.497815999620613</v>
       </c>
     </row>
     <row r="158">
@@ -11110,10 +11110,10 @@
         <v>77.14401961658972</v>
       </c>
       <c r="N158">
-        <v>81.45050683818823</v>
+        <v>81.45050683818815</v>
       </c>
       <c r="O158">
-        <v>77.4884120909541</v>
+        <v>77.48841209095431</v>
       </c>
       <c r="P158">
         <v>39772</v>
@@ -11178,10 +11178,10 @@
         <v>77.14401961658972</v>
       </c>
       <c r="N159">
-        <v>81.45050683818823</v>
+        <v>81.45050683818815</v>
       </c>
       <c r="O159">
-        <v>77.4884120909541</v>
+        <v>77.48841209095431</v>
       </c>
       <c r="P159">
         <v>39772</v>
@@ -11246,10 +11246,10 @@
         <v>77.14401961658972</v>
       </c>
       <c r="N160">
-        <v>81.45050683818823</v>
+        <v>81.45050683818815</v>
       </c>
       <c r="O160">
-        <v>77.4884120909541</v>
+        <v>77.48841209095431</v>
       </c>
       <c r="P160">
         <v>39772</v>
@@ -11260,7 +11260,7 @@
         </is>
       </c>
       <c r="S160">
-        <v>-0.5301548422915192</v>
+        <v>-0.5301548422915969</v>
       </c>
     </row>
     <row r="161">
@@ -11314,10 +11314,10 @@
         <v>77.14401961658972</v>
       </c>
       <c r="N161">
-        <v>81.45050683818823</v>
+        <v>81.45050683818815</v>
       </c>
       <c r="O161">
-        <v>77.4884120909541</v>
+        <v>77.48841209095431</v>
       </c>
       <c r="P161">
         <v>39772</v>
@@ -11328,7 +11328,7 @@
         </is>
       </c>
       <c r="S161">
-        <v>-4.492249589525644</v>
+        <v>-4.492249589525443</v>
       </c>
     </row>
     <row r="162">
@@ -11382,10 +11382,10 @@
         <v>94.73858354545469</v>
       </c>
       <c r="N162">
-        <v>53.97907512970576</v>
+        <v>53.97907512970481</v>
       </c>
       <c r="O162">
-        <v>90.77842736117594</v>
+        <v>90.77842736117616</v>
       </c>
       <c r="P162">
         <v>42552</v>
@@ -11450,10 +11450,10 @@
         <v>94.73858354545469</v>
       </c>
       <c r="N163">
-        <v>53.97907512970576</v>
+        <v>53.97907512970481</v>
       </c>
       <c r="O163">
-        <v>90.77842736117594</v>
+        <v>90.77842736117616</v>
       </c>
       <c r="P163">
         <v>42552</v>
@@ -11518,10 +11518,10 @@
         <v>94.73858354545469</v>
       </c>
       <c r="N164">
-        <v>53.97907512970576</v>
+        <v>53.97907512970481</v>
       </c>
       <c r="O164">
-        <v>90.77842736117594</v>
+        <v>90.77842736117616</v>
       </c>
       <c r="P164">
         <v>42552</v>
@@ -11532,7 +11532,7 @@
         </is>
       </c>
       <c r="S164">
-        <v>0.0008416705650216016</v>
+        <v>0.0008416705640779121</v>
       </c>
     </row>
     <row r="165">
@@ -11586,10 +11586,10 @@
         <v>94.73858354545469</v>
       </c>
       <c r="N165">
-        <v>53.97907512970576</v>
+        <v>53.97907512970481</v>
       </c>
       <c r="O165">
-        <v>90.77842736117594</v>
+        <v>90.77842736117616</v>
       </c>
       <c r="P165">
         <v>42552</v>
@@ -11600,7 +11600,7 @@
         </is>
       </c>
       <c r="S165">
-        <v>36.8001939020352</v>
+        <v>36.80019390203542</v>
       </c>
     </row>
     <row r="166">
@@ -20358,10 +20358,10 @@
         <v>13.71421764662618</v>
       </c>
       <c r="N294">
-        <v>15.41815523864194</v>
+        <v>15.41815523864195</v>
       </c>
       <c r="O294">
-        <v>15.39358401703903</v>
+        <v>15.39358401703959</v>
       </c>
       <c r="P294">
         <v>61000</v>
@@ -20426,10 +20426,10 @@
         <v>13.71421764662618</v>
       </c>
       <c r="N295">
-        <v>15.41815523864194</v>
+        <v>15.41815523864195</v>
       </c>
       <c r="O295">
-        <v>15.39358401703903</v>
+        <v>15.39358401703959</v>
       </c>
       <c r="P295">
         <v>61000</v>
@@ -20494,10 +20494,10 @@
         <v>13.71421764662618</v>
       </c>
       <c r="N296">
-        <v>15.41815523864194</v>
+        <v>15.41815523864195</v>
       </c>
       <c r="O296">
-        <v>15.39358401703903</v>
+        <v>15.39358401703959</v>
       </c>
       <c r="P296">
         <v>61000</v>
@@ -20508,7 +20508,7 @@
         </is>
       </c>
       <c r="S296">
-        <v>-2.434066014787231</v>
+        <v>-2.43406601478722</v>
       </c>
     </row>
     <row r="297">
@@ -20562,10 +20562,10 @@
         <v>13.71421764662618</v>
       </c>
       <c r="N297">
-        <v>15.41815523864194</v>
+        <v>15.41815523864195</v>
       </c>
       <c r="O297">
-        <v>15.39358401703903</v>
+        <v>15.39358401703959</v>
       </c>
       <c r="P297">
         <v>61000</v>
@@ -20576,7 +20576,7 @@
         </is>
       </c>
       <c r="S297">
-        <v>-2.458637236390146</v>
+        <v>-2.458637236389585</v>
       </c>
     </row>
     <row r="298">
@@ -20630,10 +20630,10 @@
         <v>29.42277298055462</v>
       </c>
       <c r="N298">
-        <v>28.57244554318082</v>
+        <v>28.57244554318077</v>
       </c>
       <c r="O298">
-        <v>28.56364349950706</v>
+        <v>28.56364349950802</v>
       </c>
       <c r="P298">
         <v>61000</v>
@@ -20698,10 +20698,10 @@
         <v>29.42277298055462</v>
       </c>
       <c r="N299">
-        <v>28.57244554318082</v>
+        <v>28.57244554318077</v>
       </c>
       <c r="O299">
-        <v>28.56364349950706</v>
+        <v>28.56364349950802</v>
       </c>
       <c r="P299">
         <v>61000</v>
@@ -20766,10 +20766,10 @@
         <v>29.42277298055462</v>
       </c>
       <c r="N300">
-        <v>28.57244554318082</v>
+        <v>28.57244554318077</v>
       </c>
       <c r="O300">
-        <v>28.56364349950706</v>
+        <v>28.56364349950802</v>
       </c>
       <c r="P300">
         <v>61000</v>
@@ -20780,7 +20780,7 @@
         </is>
       </c>
       <c r="S300">
-        <v>-0.5880716505328953</v>
+        <v>-0.5880716505329397</v>
       </c>
     </row>
     <row r="301">
@@ -20834,10 +20834,10 @@
         <v>29.42277298055462</v>
       </c>
       <c r="N301">
-        <v>28.57244554318082</v>
+        <v>28.57244554318077</v>
       </c>
       <c r="O301">
-        <v>28.56364349950706</v>
+        <v>28.56364349950802</v>
       </c>
       <c r="P301">
         <v>61000</v>
@@ -20848,7 +20848,7 @@
         </is>
       </c>
       <c r="S301">
-        <v>-0.5968736942066566</v>
+        <v>-0.5968736942056962</v>
       </c>
     </row>
     <row r="302">
@@ -20902,10 +20902,10 @@
         <v>45.4639903673616</v>
       </c>
       <c r="N302">
-        <v>57.98657659676807</v>
+        <v>57.98657659676809</v>
       </c>
       <c r="O302">
-        <v>58.0108328128641</v>
+        <v>58.0108328128659</v>
       </c>
       <c r="P302">
         <v>60966</v>
@@ -20970,10 +20970,10 @@
         <v>45.4639903673616</v>
       </c>
       <c r="N303">
-        <v>57.98657659676807</v>
+        <v>57.98657659676809</v>
       </c>
       <c r="O303">
-        <v>58.0108328128641</v>
+        <v>58.0108328128659</v>
       </c>
       <c r="P303">
         <v>60966</v>
@@ -21038,10 +21038,10 @@
         <v>45.4639903673616</v>
       </c>
       <c r="N304">
-        <v>57.98657659676807</v>
+        <v>57.98657659676809</v>
       </c>
       <c r="O304">
-        <v>58.0108328128641</v>
+        <v>58.0108328128659</v>
       </c>
       <c r="P304">
         <v>60966</v>
@@ -21052,7 +21052,7 @@
         </is>
       </c>
       <c r="S304">
-        <v>0.9354526786854334</v>
+        <v>0.9354526786854556</v>
       </c>
     </row>
     <row r="305">
@@ -21106,10 +21106,10 @@
         <v>45.4639903673616</v>
       </c>
       <c r="N305">
-        <v>57.98657659676807</v>
+        <v>57.98657659676809</v>
       </c>
       <c r="O305">
-        <v>58.0108328128641</v>
+        <v>58.0108328128659</v>
       </c>
       <c r="P305">
         <v>60966</v>
@@ -21120,7 +21120,7 @@
         </is>
       </c>
       <c r="S305">
-        <v>0.9597088947814636</v>
+        <v>0.9597088947832622</v>
       </c>
     </row>
     <row r="306">
@@ -21174,10 +21174,10 @@
         <v>22.87686769960688</v>
       </c>
       <c r="N306">
-        <v>24.28635160555295</v>
+        <v>24.28635160555294</v>
       </c>
       <c r="O306">
-        <v>24.30807920702731</v>
+        <v>24.30807920702841</v>
       </c>
       <c r="P306">
         <v>54906</v>
@@ -21242,10 +21242,10 @@
         <v>22.87686769960688</v>
       </c>
       <c r="N307">
-        <v>24.28635160555295</v>
+        <v>24.28635160555294</v>
       </c>
       <c r="O307">
-        <v>24.30807920702731</v>
+        <v>24.30807920702841</v>
       </c>
       <c r="P307">
         <v>54906</v>
@@ -21310,10 +21310,10 @@
         <v>22.87686769960688</v>
       </c>
       <c r="N308">
-        <v>24.28635160555295</v>
+        <v>24.28635160555294</v>
       </c>
       <c r="O308">
-        <v>24.30807920702731</v>
+        <v>24.30807920702841</v>
       </c>
       <c r="P308">
         <v>54906</v>
@@ -21324,7 +21324,7 @@
         </is>
       </c>
       <c r="S308">
-        <v>-0.3936985826528183</v>
+        <v>-0.3936985826528322</v>
       </c>
     </row>
     <row r="309">
@@ -21378,10 +21378,10 @@
         <v>22.87686769960688</v>
       </c>
       <c r="N309">
-        <v>24.28635160555295</v>
+        <v>24.28635160555294</v>
       </c>
       <c r="O309">
-        <v>24.30807920702731</v>
+        <v>24.30807920702841</v>
       </c>
       <c r="P309">
         <v>54906</v>
@@ -21392,7 +21392,7 @@
         </is>
       </c>
       <c r="S309">
-        <v>-0.3719709811784599</v>
+        <v>-0.3719709811773608</v>
       </c>
     </row>
     <row r="310">
@@ -21446,10 +21446,10 @@
         <v>96.75096455756443</v>
       </c>
       <c r="N310">
-        <v>86.70056156845874</v>
+        <v>86.70056156845875</v>
       </c>
       <c r="O310">
-        <v>96.82340183287779</v>
+        <v>96.82340183287785</v>
       </c>
       <c r="P310">
         <v>55751</v>
@@ -21514,10 +21514,10 @@
         <v>96.75096455756443</v>
       </c>
       <c r="N311">
-        <v>86.70056156845874</v>
+        <v>86.70056156845875</v>
       </c>
       <c r="O311">
-        <v>96.82340183287779</v>
+        <v>96.82340183287785</v>
       </c>
       <c r="P311">
         <v>55751</v>
@@ -21582,10 +21582,10 @@
         <v>96.75096455756443</v>
       </c>
       <c r="N312">
-        <v>86.70056156845874</v>
+        <v>86.70056156845875</v>
       </c>
       <c r="O312">
-        <v>96.82340183287779</v>
+        <v>96.82340183287785</v>
       </c>
       <c r="P312">
         <v>55751</v>
@@ -21596,7 +21596,7 @@
         </is>
       </c>
       <c r="S312">
-        <v>-3.506571111293733</v>
+        <v>-3.50657111129371</v>
       </c>
     </row>
     <row r="313">
@@ -21650,10 +21650,10 @@
         <v>96.75096455756443</v>
       </c>
       <c r="N313">
-        <v>86.70056156845874</v>
+        <v>86.70056156845875</v>
       </c>
       <c r="O313">
-        <v>96.82340183287779</v>
+        <v>96.82340183287785</v>
       </c>
       <c r="P313">
         <v>55751</v>
@@ -21664,7 +21664,7 @@
         </is>
       </c>
       <c r="S313">
-        <v>6.61626915312532</v>
+        <v>6.616269153125376</v>
       </c>
     </row>
     <row r="314">
@@ -21718,10 +21718,10 @@
         <v>60.51866627019677</v>
       </c>
       <c r="N314">
-        <v>59.81528043082663</v>
+        <v>59.81528043082665</v>
       </c>
       <c r="O314">
-        <v>60.34381502084364</v>
+        <v>60.34381502084475</v>
       </c>
       <c r="P314">
         <v>60920</v>
@@ -21786,10 +21786,10 @@
         <v>60.51866627019677</v>
       </c>
       <c r="N315">
-        <v>59.81528043082663</v>
+        <v>59.81528043082665</v>
       </c>
       <c r="O315">
-        <v>60.34381502084364</v>
+        <v>60.34381502084475</v>
       </c>
       <c r="P315">
         <v>60920</v>
@@ -21854,10 +21854,10 @@
         <v>60.51866627019677</v>
       </c>
       <c r="N316">
-        <v>59.81528043082663</v>
+        <v>59.81528043082665</v>
       </c>
       <c r="O316">
-        <v>60.34381502084364</v>
+        <v>60.34381502084475</v>
       </c>
       <c r="P316">
         <v>60920</v>
@@ -21868,7 +21868,7 @@
         </is>
       </c>
       <c r="S316">
-        <v>-1.367740548997154</v>
+        <v>-1.367740548997121</v>
       </c>
     </row>
     <row r="317">
@@ -21922,10 +21922,10 @@
         <v>60.51866627019677</v>
       </c>
       <c r="N317">
-        <v>59.81528043082663</v>
+        <v>59.81528043082665</v>
       </c>
       <c r="O317">
-        <v>60.34381502084364</v>
+        <v>60.34381502084475</v>
       </c>
       <c r="P317">
         <v>60920</v>
@@ -21936,7 +21936,7 @@
         </is>
       </c>
       <c r="S317">
-        <v>-0.8392059589801382</v>
+        <v>-0.8392059589790279</v>
       </c>
     </row>
     <row r="318">
@@ -21990,10 +21990,10 @@
         <v>51.49802933758593</v>
       </c>
       <c r="N318">
-        <v>51.87442533665201</v>
+        <v>51.87442533665195</v>
       </c>
       <c r="O318">
-        <v>55.19320995384727</v>
+        <v>55.19320995384758</v>
       </c>
       <c r="P318">
         <v>61000</v>
@@ -22058,10 +22058,10 @@
         <v>51.49802933758593</v>
       </c>
       <c r="N319">
-        <v>51.87442533665201</v>
+        <v>51.87442533665195</v>
       </c>
       <c r="O319">
-        <v>55.19320995384727</v>
+        <v>55.19320995384758</v>
       </c>
       <c r="P319">
         <v>61000</v>
@@ -22126,10 +22126,10 @@
         <v>51.49802933758593</v>
       </c>
       <c r="N320">
-        <v>51.87442533665201</v>
+        <v>51.87442533665195</v>
       </c>
       <c r="O320">
-        <v>55.19320995384727</v>
+        <v>55.19320995384758</v>
       </c>
       <c r="P320">
         <v>61000</v>
@@ -22140,7 +22140,7 @@
         </is>
       </c>
       <c r="S320">
-        <v>-0.2309273630906716</v>
+        <v>-0.2309273630907271</v>
       </c>
     </row>
     <row r="321">
@@ -22194,10 +22194,10 @@
         <v>51.49802933758593</v>
       </c>
       <c r="N321">
-        <v>51.87442533665201</v>
+        <v>51.87442533665195</v>
       </c>
       <c r="O321">
-        <v>55.19320995384727</v>
+        <v>55.19320995384758</v>
       </c>
       <c r="P321">
         <v>61000</v>
@@ -22208,7 +22208,7 @@
         </is>
       </c>
       <c r="S321">
-        <v>3.087857254104587</v>
+        <v>3.087857254104898</v>
       </c>
     </row>
     <row r="322">
@@ -22262,10 +22262,10 @@
         <v>94.03767983644056</v>
       </c>
       <c r="N322">
-        <v>88.60775405607029</v>
+        <v>88.60775405607038</v>
       </c>
       <c r="O322">
-        <v>92.81092514217536</v>
+        <v>92.81092514217534</v>
       </c>
       <c r="P322">
         <v>60928</v>
@@ -22330,10 +22330,10 @@
         <v>94.03767983644056</v>
       </c>
       <c r="N323">
-        <v>88.60775405607029</v>
+        <v>88.60775405607038</v>
       </c>
       <c r="O323">
-        <v>92.81092514217536</v>
+        <v>92.81092514217534</v>
       </c>
       <c r="P323">
         <v>60928</v>
@@ -22398,10 +22398,10 @@
         <v>94.03767983644056</v>
       </c>
       <c r="N324">
-        <v>88.60775405607029</v>
+        <v>88.60775405607038</v>
       </c>
       <c r="O324">
-        <v>92.81092514217536</v>
+        <v>92.81092514217534</v>
       </c>
       <c r="P324">
         <v>60928</v>
@@ -22412,7 +22412,7 @@
         </is>
       </c>
       <c r="S324">
-        <v>-0.3433119337774126</v>
+        <v>-0.3433119337773349</v>
       </c>
     </row>
     <row r="325">
@@ -22466,10 +22466,10 @@
         <v>94.03767983644056</v>
       </c>
       <c r="N325">
-        <v>88.60775405607029</v>
+        <v>88.60775405607038</v>
       </c>
       <c r="O325">
-        <v>92.81092514217536</v>
+        <v>92.81092514217534</v>
       </c>
       <c r="P325">
         <v>60928</v>
@@ -22480,7 +22480,7 @@
         </is>
       </c>
       <c r="S325">
-        <v>3.859859152327649</v>
+        <v>3.859859152327627</v>
       </c>
     </row>
     <row r="326">
@@ -22534,10 +22534,10 @@
         <v>90.12539655528288</v>
       </c>
       <c r="N326">
-        <v>92.49798818801627</v>
+        <v>92.49798818801629</v>
       </c>
       <c r="O326">
-        <v>89.42387194359372</v>
+        <v>89.42387194359381</v>
       </c>
       <c r="P326">
         <v>61000</v>
@@ -22602,10 +22602,10 @@
         <v>90.12539655528288</v>
       </c>
       <c r="N327">
-        <v>92.49798818801627</v>
+        <v>92.49798818801629</v>
       </c>
       <c r="O327">
-        <v>89.42387194359372</v>
+        <v>89.42387194359381</v>
       </c>
       <c r="P327">
         <v>61000</v>
@@ -22670,10 +22670,10 @@
         <v>90.12539655528288</v>
       </c>
       <c r="N328">
-        <v>92.49798818801627</v>
+        <v>92.49798818801629</v>
       </c>
       <c r="O328">
-        <v>89.42387194359372</v>
+        <v>89.42387194359381</v>
       </c>
       <c r="P328">
         <v>61000</v>
@@ -22684,7 +22684,7 @@
         </is>
       </c>
       <c r="S328">
-        <v>0.9126431762666365</v>
+        <v>0.9126431762666587</v>
       </c>
     </row>
     <row r="329">
@@ -22738,10 +22738,10 @@
         <v>90.12539655528288</v>
       </c>
       <c r="N329">
-        <v>92.49798818801627</v>
+        <v>92.49798818801629</v>
       </c>
       <c r="O329">
-        <v>89.42387194359372</v>
+        <v>89.42387194359381</v>
       </c>
       <c r="P329">
         <v>61000</v>
@@ -22752,7 +22752,7 @@
         </is>
       </c>
       <c r="S329">
-        <v>-2.161473068155906</v>
+        <v>-2.161473068155828</v>
       </c>
     </row>
     <row r="330">
@@ -22806,10 +22806,10 @@
         <v>56.56833363518013</v>
       </c>
       <c r="N330">
-        <v>56.80719956100185</v>
+        <v>56.80719956100195</v>
       </c>
       <c r="O330">
-        <v>53.77092581252928</v>
+        <v>53.77092581252965</v>
       </c>
       <c r="P330">
         <v>45790</v>
@@ -22874,10 +22874,10 @@
         <v>56.56833363518013</v>
       </c>
       <c r="N331">
-        <v>56.80719956100185</v>
+        <v>56.80719956100195</v>
       </c>
       <c r="O331">
-        <v>53.77092581252928</v>
+        <v>53.77092581252965</v>
       </c>
       <c r="P331">
         <v>45790</v>
@@ -22942,10 +22942,10 @@
         <v>56.56833363518013</v>
       </c>
       <c r="N332">
-        <v>56.80719956100185</v>
+        <v>56.80719956100195</v>
       </c>
       <c r="O332">
-        <v>53.77092581252928</v>
+        <v>53.77092581252965</v>
       </c>
       <c r="P332">
         <v>45790</v>
@@ -22956,7 +22956,7 @@
         </is>
       </c>
       <c r="S332">
-        <v>0.3061338125184943</v>
+        <v>0.3061338125185942</v>
       </c>
     </row>
     <row r="333">
@@ -23010,10 +23010,10 @@
         <v>56.56833363518013</v>
       </c>
       <c r="N333">
-        <v>56.80719956100185</v>
+        <v>56.80719956100195</v>
       </c>
       <c r="O333">
-        <v>53.77092581252928</v>
+        <v>53.77092581252965</v>
       </c>
       <c r="P333">
         <v>45790</v>
@@ -23024,7 +23024,7 @@
         </is>
       </c>
       <c r="S333">
-        <v>-2.730139935954079</v>
+        <v>-2.730139935953713</v>
       </c>
     </row>
     <row r="334">
@@ -23078,10 +23078,10 @@
         <v>90.08926438227013</v>
       </c>
       <c r="N334">
-        <v>62.0772182760082</v>
+        <v>62.07721827600816</v>
       </c>
       <c r="O334">
-        <v>94.75407612852116</v>
+        <v>94.75407612852125</v>
       </c>
       <c r="P334">
         <v>48462</v>
@@ -23146,10 +23146,10 @@
         <v>90.08926438227013</v>
       </c>
       <c r="N335">
-        <v>62.0772182760082</v>
+        <v>62.07721827600816</v>
       </c>
       <c r="O335">
-        <v>94.75407612852116</v>
+        <v>94.75407612852125</v>
       </c>
       <c r="P335">
         <v>48462</v>
@@ -23214,10 +23214,10 @@
         <v>90.08926438227013</v>
       </c>
       <c r="N336">
-        <v>62.0772182760082</v>
+        <v>62.07721827600816</v>
       </c>
       <c r="O336">
-        <v>94.75407612852116</v>
+        <v>94.75407612852125</v>
       </c>
       <c r="P336">
         <v>48462</v>
@@ -23228,7 +23228,7 @@
         </is>
       </c>
       <c r="S336">
-        <v>0.2443851464968394</v>
+        <v>0.244385146496795</v>
       </c>
     </row>
     <row r="337">
@@ -23282,10 +23282,10 @@
         <v>90.08926438227013</v>
       </c>
       <c r="N337">
-        <v>62.0772182760082</v>
+        <v>62.07721827600816</v>
       </c>
       <c r="O337">
-        <v>94.75407612852116</v>
+        <v>94.75407612852125</v>
       </c>
       <c r="P337">
         <v>48462</v>
@@ -23296,7 +23296,7 @@
         </is>
       </c>
       <c r="S337">
-        <v>32.92124299900981</v>
+        <v>32.92124299900988</v>
       </c>
     </row>
     <row r="338">
@@ -23350,10 +23350,10 @@
         <v>13.63679623448249</v>
       </c>
       <c r="N338">
-        <v>15.79903111329064</v>
+        <v>15.79903111329061</v>
       </c>
       <c r="O338">
-        <v>15.7990265685755</v>
+        <v>15.79902656857579</v>
       </c>
       <c r="P338">
         <v>60000</v>
@@ -23418,10 +23418,10 @@
         <v>13.63679623448249</v>
       </c>
       <c r="N339">
-        <v>15.79903111329064</v>
+        <v>15.79903111329061</v>
       </c>
       <c r="O339">
-        <v>15.7990265685755</v>
+        <v>15.79902656857579</v>
       </c>
       <c r="P339">
         <v>60000</v>
@@ -23486,10 +23486,10 @@
         <v>13.63679623448249</v>
       </c>
       <c r="N340">
-        <v>15.79903111329064</v>
+        <v>15.79903111329061</v>
       </c>
       <c r="O340">
-        <v>15.7990265685755</v>
+        <v>15.79902656857579</v>
       </c>
       <c r="P340">
         <v>60000</v>
@@ -23500,7 +23500,7 @@
         </is>
       </c>
       <c r="S340">
-        <v>-2.97334290803713</v>
+        <v>-2.973342908037155</v>
       </c>
     </row>
     <row r="341">
@@ -23554,10 +23554,10 @@
         <v>13.63679623448249</v>
       </c>
       <c r="N341">
-        <v>15.79903111329064</v>
+        <v>15.79903111329061</v>
       </c>
       <c r="O341">
-        <v>15.7990265685755</v>
+        <v>15.79902656857579</v>
       </c>
       <c r="P341">
         <v>60000</v>
@@ -23568,7 +23568,7 @@
         </is>
       </c>
       <c r="S341">
-        <v>-2.97334745275227</v>
+        <v>-2.973347452751979</v>
       </c>
     </row>
     <row r="342">
@@ -23622,10 +23622,10 @@
         <v>28.71709917682972</v>
       </c>
       <c r="N342">
-        <v>29.12343307178292</v>
+        <v>29.1234330717829</v>
       </c>
       <c r="O342">
-        <v>29.12342358088552</v>
+        <v>29.12342358088578</v>
       </c>
       <c r="P342">
         <v>60000</v>
@@ -23690,10 +23690,10 @@
         <v>28.71709917682972</v>
       </c>
       <c r="N343">
-        <v>29.12343307178292</v>
+        <v>29.1234330717829</v>
       </c>
       <c r="O343">
-        <v>29.12342358088552</v>
+        <v>29.12342358088578</v>
       </c>
       <c r="P343">
         <v>60000</v>
@@ -23758,10 +23758,10 @@
         <v>28.71709917682972</v>
       </c>
       <c r="N344">
-        <v>29.12343307178292</v>
+        <v>29.1234330717829</v>
       </c>
       <c r="O344">
-        <v>29.12342358088552</v>
+        <v>29.12342358088578</v>
       </c>
       <c r="P344">
         <v>60000</v>
@@ -23772,7 +23772,7 @@
         </is>
       </c>
       <c r="S344">
-        <v>-0.3447521545214771</v>
+        <v>-0.3447521545214938</v>
       </c>
     </row>
     <row r="345">
@@ -23826,10 +23826,10 @@
         <v>28.71709917682972</v>
       </c>
       <c r="N345">
-        <v>29.12343307178292</v>
+        <v>29.1234330717829</v>
       </c>
       <c r="O345">
-        <v>29.12342358088552</v>
+        <v>29.12342358088578</v>
       </c>
       <c r="P345">
         <v>60000</v>
@@ -23840,7 +23840,7 @@
         </is>
       </c>
       <c r="S345">
-        <v>-0.3447616454188729</v>
+        <v>-0.3447616454186175</v>
       </c>
     </row>
     <row r="346">
@@ -23894,10 +23894,10 @@
         <v>49.38494464192657</v>
       </c>
       <c r="N346">
-        <v>60.91535036081957</v>
+        <v>60.91535036081953</v>
       </c>
       <c r="O346">
-        <v>60.91538488022654</v>
+        <v>60.91538488022671</v>
       </c>
       <c r="P346">
         <v>59952</v>
@@ -23962,10 +23962,10 @@
         <v>49.38494464192657</v>
       </c>
       <c r="N347">
-        <v>60.91535036081957</v>
+        <v>60.91535036081953</v>
       </c>
       <c r="O347">
-        <v>60.91538488022654</v>
+        <v>60.91538488022671</v>
       </c>
       <c r="P347">
         <v>59952</v>
@@ -24030,10 +24030,10 @@
         <v>49.38494464192657</v>
       </c>
       <c r="N348">
-        <v>60.91535036081957</v>
+        <v>60.91535036081953</v>
       </c>
       <c r="O348">
-        <v>60.91538488022654</v>
+        <v>60.91538488022671</v>
       </c>
       <c r="P348">
         <v>59952</v>
@@ -24044,7 +24044,7 @@
         </is>
       </c>
       <c r="S348">
-        <v>2.019584098563221</v>
+        <v>2.019584098563187</v>
       </c>
     </row>
     <row r="349">
@@ -24098,10 +24098,10 @@
         <v>49.38494464192657</v>
       </c>
       <c r="N349">
-        <v>60.91535036081957</v>
+        <v>60.91535036081953</v>
       </c>
       <c r="O349">
-        <v>60.91538488022654</v>
+        <v>60.91538488022671</v>
       </c>
       <c r="P349">
         <v>59952</v>
@@ -24112,7 +24112,7 @@
         </is>
       </c>
       <c r="S349">
-        <v>2.019618617970198</v>
+        <v>2.019618617970365</v>
       </c>
     </row>
     <row r="350">
@@ -24166,10 +24166,10 @@
         <v>22.5997561136882</v>
       </c>
       <c r="N350">
-        <v>23.77362779864106</v>
+        <v>23.77362779864108</v>
       </c>
       <c r="O350">
-        <v>23.77362873790585</v>
+        <v>23.77362873790611</v>
       </c>
       <c r="P350">
         <v>55143</v>
@@ -24234,10 +24234,10 @@
         <v>22.5997561136882</v>
       </c>
       <c r="N351">
-        <v>23.77362779864106</v>
+        <v>23.77362779864108</v>
       </c>
       <c r="O351">
-        <v>23.77362873790585</v>
+        <v>23.77362873790611</v>
       </c>
       <c r="P351">
         <v>55143</v>
@@ -24302,10 +24302,10 @@
         <v>22.5997561136882</v>
       </c>
       <c r="N352">
-        <v>23.77362779864106</v>
+        <v>23.77362779864108</v>
       </c>
       <c r="O352">
-        <v>23.77362873790585</v>
+        <v>23.77362873790611</v>
       </c>
       <c r="P352">
         <v>55143</v>
@@ -24316,7 +24316,7 @@
         </is>
       </c>
       <c r="S352">
-        <v>-0.3448162932823767</v>
+        <v>-0.3448162932823545</v>
       </c>
     </row>
     <row r="353">
@@ -24370,10 +24370,10 @@
         <v>22.5997561136882</v>
       </c>
       <c r="N353">
-        <v>23.77362779864106</v>
+        <v>23.77362779864108</v>
       </c>
       <c r="O353">
-        <v>23.77362873790585</v>
+        <v>23.77362873790611</v>
       </c>
       <c r="P353">
         <v>55143</v>
@@ -24384,7 +24384,7 @@
         </is>
       </c>
       <c r="S353">
-        <v>-0.3448153540175858</v>
+        <v>-0.3448153540173249</v>
       </c>
     </row>
     <row r="354">
@@ -24438,10 +24438,10 @@
         <v>91.09254484367177</v>
       </c>
       <c r="N354">
-        <v>86.61759427225226</v>
+        <v>86.61759427225223</v>
       </c>
       <c r="O354">
-        <v>90.83563195911086</v>
+        <v>90.83563195911087</v>
       </c>
       <c r="P354">
         <v>57277</v>
@@ -24506,10 +24506,10 @@
         <v>91.09254484367177</v>
       </c>
       <c r="N355">
-        <v>86.61759427225226</v>
+        <v>86.61759427225223</v>
       </c>
       <c r="O355">
-        <v>90.83563195911086</v>
+        <v>90.83563195911087</v>
       </c>
       <c r="P355">
         <v>57277</v>
@@ -24574,10 +24574,10 @@
         <v>91.09254484367177</v>
       </c>
       <c r="N356">
-        <v>86.61759427225226</v>
+        <v>86.61759427225223</v>
       </c>
       <c r="O356">
-        <v>90.83563195911086</v>
+        <v>90.83563195911087</v>
       </c>
       <c r="P356">
         <v>57277</v>
@@ -24588,7 +24588,7 @@
         </is>
       </c>
       <c r="S356">
-        <v>-2.943012765955721</v>
+        <v>-2.943012765955744</v>
       </c>
     </row>
     <row r="357">
@@ -24642,10 +24642,10 @@
         <v>91.09254484367177</v>
       </c>
       <c r="N357">
-        <v>86.61759427225226</v>
+        <v>86.61759427225223</v>
       </c>
       <c r="O357">
-        <v>90.83563195911086</v>
+        <v>90.83563195911087</v>
       </c>
       <c r="P357">
         <v>57277</v>
@@ -24656,7 +24656,7 @@
         </is>
       </c>
       <c r="S357">
-        <v>1.275024920902879</v>
+        <v>1.27502492090289</v>
       </c>
     </row>
     <row r="358">
@@ -24710,10 +24710,10 @@
         <v>60.99375995409059</v>
       </c>
       <c r="N358">
-        <v>61.01690685229691</v>
+        <v>61.01690685229683</v>
       </c>
       <c r="O358">
-        <v>60.71393243350624</v>
+        <v>60.71393243350647</v>
       </c>
       <c r="P358">
         <v>59908</v>
@@ -24778,10 +24778,10 @@
         <v>60.99375995409059</v>
       </c>
       <c r="N359">
-        <v>61.01690685229691</v>
+        <v>61.01690685229683</v>
       </c>
       <c r="O359">
-        <v>60.71393243350624</v>
+        <v>60.71393243350647</v>
       </c>
       <c r="P359">
         <v>59908</v>
@@ -24846,10 +24846,10 @@
         <v>60.99375995409059</v>
       </c>
       <c r="N360">
-        <v>61.01690685229691</v>
+        <v>61.01690685229683</v>
       </c>
       <c r="O360">
-        <v>60.71393243350624</v>
+        <v>60.71393243350647</v>
       </c>
       <c r="P360">
         <v>59908</v>
@@ -24860,7 +24860,7 @@
         </is>
       </c>
       <c r="S360">
-        <v>-1.764850130809625</v>
+        <v>-1.764850130809714</v>
       </c>
     </row>
     <row r="361">
@@ -24914,10 +24914,10 @@
         <v>60.99375995409059</v>
       </c>
       <c r="N361">
-        <v>61.01690685229691</v>
+        <v>61.01690685229683</v>
       </c>
       <c r="O361">
-        <v>60.71393243350624</v>
+        <v>60.71393243350647</v>
       </c>
       <c r="P361">
         <v>59908</v>
@@ -24928,7 +24928,7 @@
         </is>
       </c>
       <c r="S361">
-        <v>-2.067824549600306</v>
+        <v>-2.067824549600072</v>
       </c>
     </row>
     <row r="362">
@@ -24982,10 +24982,10 @@
         <v>52.20547113980047</v>
       </c>
       <c r="N362">
-        <v>51.58328699371179</v>
+        <v>51.58328699371187</v>
       </c>
       <c r="O362">
-        <v>51.69280674241715</v>
+        <v>51.69280674241718</v>
       </c>
       <c r="P362">
         <v>59563</v>
@@ -25050,10 +25050,10 @@
         <v>52.20547113980047</v>
       </c>
       <c r="N363">
-        <v>51.58328699371179</v>
+        <v>51.58328699371187</v>
       </c>
       <c r="O363">
-        <v>51.69280674241715</v>
+        <v>51.69280674241718</v>
       </c>
       <c r="P363">
         <v>59563</v>
@@ -25118,10 +25118,10 @@
         <v>52.20547113980047</v>
       </c>
       <c r="N364">
-        <v>51.58328699371179</v>
+        <v>51.58328699371187</v>
       </c>
       <c r="O364">
-        <v>51.69280674241715</v>
+        <v>51.69280674241718</v>
       </c>
       <c r="P364">
         <v>59563</v>
@@ -25132,7 +25132,7 @@
         </is>
       </c>
       <c r="S364">
-        <v>-0.504880833975152</v>
+        <v>-0.5048808339750743</v>
       </c>
     </row>
     <row r="365">
@@ -25186,10 +25186,10 @@
         <v>52.20547113980047</v>
       </c>
       <c r="N365">
-        <v>51.58328699371179</v>
+        <v>51.58328699371187</v>
       </c>
       <c r="O365">
-        <v>51.69280674241715</v>
+        <v>51.69280674241718</v>
       </c>
       <c r="P365">
         <v>59563</v>
@@ -25200,7 +25200,7 @@
         </is>
       </c>
       <c r="S365">
-        <v>-0.3953610852697853</v>
+        <v>-0.395361085269752</v>
       </c>
     </row>
     <row r="366">
@@ -25254,10 +25254,10 @@
         <v>94.03545595788032</v>
       </c>
       <c r="N366">
-        <v>89.30448482920688</v>
+        <v>89.30448482920681</v>
       </c>
       <c r="O366">
-        <v>92.04660792596596</v>
+        <v>92.04660792596593</v>
       </c>
       <c r="P366">
         <v>59952</v>
@@ -25322,10 +25322,10 @@
         <v>94.03545595788032</v>
       </c>
       <c r="N367">
-        <v>89.30448482920688</v>
+        <v>89.30448482920681</v>
       </c>
       <c r="O367">
-        <v>92.04660792596596</v>
+        <v>92.04660792596593</v>
       </c>
       <c r="P367">
         <v>59952</v>
@@ -25390,10 +25390,10 @@
         <v>94.03545595788032</v>
       </c>
       <c r="N368">
-        <v>89.30448482920688</v>
+        <v>89.30448482920681</v>
       </c>
       <c r="O368">
-        <v>92.04660792596596</v>
+        <v>92.04660792596593</v>
       </c>
       <c r="P368">
         <v>59952</v>
@@ -25404,7 +25404,7 @@
         </is>
       </c>
       <c r="S368">
-        <v>-0.4456318395810288</v>
+        <v>-0.4456318395810954</v>
       </c>
     </row>
     <row r="369">
@@ -25458,10 +25458,10 @@
         <v>94.03545595788032</v>
       </c>
       <c r="N369">
-        <v>89.30448482920688</v>
+        <v>89.30448482920681</v>
       </c>
       <c r="O369">
-        <v>92.04660792596596</v>
+        <v>92.04660792596593</v>
       </c>
       <c r="P369">
         <v>59952</v>
@@ -25472,7 +25472,7 @@
         </is>
       </c>
       <c r="S369">
-        <v>2.296491257178046</v>
+        <v>2.296491257178013</v>
       </c>
     </row>
     <row r="370">
@@ -25526,10 +25526,10 @@
         <v>90.81416282496983</v>
       </c>
       <c r="N370">
-        <v>92.88968438627364</v>
+        <v>92.88968438627357</v>
       </c>
       <c r="O370">
-        <v>89.6150820305524</v>
+        <v>89.61508203055229</v>
       </c>
       <c r="P370">
         <v>60000</v>
@@ -25594,10 +25594,10 @@
         <v>90.81416282496983</v>
       </c>
       <c r="N371">
-        <v>92.88968438627364</v>
+        <v>92.88968438627357</v>
       </c>
       <c r="O371">
-        <v>89.6150820305524</v>
+        <v>89.61508203055229</v>
       </c>
       <c r="P371">
         <v>60000</v>
@@ -25662,10 +25662,10 @@
         <v>90.81416282496983</v>
       </c>
       <c r="N372">
-        <v>92.88968438627364</v>
+        <v>92.88968438627357</v>
       </c>
       <c r="O372">
-        <v>89.6150820305524</v>
+        <v>89.61508203055229</v>
       </c>
       <c r="P372">
         <v>60000</v>
@@ -25676,7 +25676,7 @@
         </is>
       </c>
       <c r="S372">
-        <v>0.8780904036132187</v>
+        <v>0.878090403613152</v>
       </c>
     </row>
     <row r="373">
@@ -25730,10 +25730,10 @@
         <v>90.81416282496983</v>
       </c>
       <c r="N373">
-        <v>92.88968438627364</v>
+        <v>92.88968438627357</v>
       </c>
       <c r="O373">
-        <v>89.6150820305524</v>
+        <v>89.61508203055229</v>
       </c>
       <c r="P373">
         <v>60000</v>
@@ -25744,7 +25744,7 @@
         </is>
       </c>
       <c r="S373">
-        <v>-2.396511952108016</v>
+        <v>-2.396511952108138</v>
       </c>
     </row>
     <row r="374">
@@ -25798,10 +25798,10 @@
         <v>66.36932631856995</v>
       </c>
       <c r="N374">
-        <v>68.0847098326675</v>
+        <v>68.08470983266751</v>
       </c>
       <c r="O374">
-        <v>65.01271796233409</v>
+        <v>65.01271796233431</v>
       </c>
       <c r="P374">
         <v>40876</v>
@@ -25866,10 +25866,10 @@
         <v>66.36932631856995</v>
       </c>
       <c r="N375">
-        <v>68.0847098326675</v>
+        <v>68.08470983266751</v>
       </c>
       <c r="O375">
-        <v>65.01271796233409</v>
+        <v>65.01271796233431</v>
       </c>
       <c r="P375">
         <v>40876</v>
@@ -25934,10 +25934,10 @@
         <v>66.36932631856995</v>
       </c>
       <c r="N376">
-        <v>68.0847098326675</v>
+        <v>68.08470983266751</v>
       </c>
       <c r="O376">
-        <v>65.01271796233409</v>
+        <v>65.01271796233431</v>
       </c>
       <c r="P376">
         <v>40876</v>
@@ -25948,7 +25948,7 @@
         </is>
       </c>
       <c r="S376">
-        <v>0.6967417540916898</v>
+        <v>0.6967417540917009</v>
       </c>
     </row>
     <row r="377">
@@ -26002,10 +26002,10 @@
         <v>66.36932631856995</v>
       </c>
       <c r="N377">
-        <v>68.0847098326675</v>
+        <v>68.08470983266751</v>
       </c>
       <c r="O377">
-        <v>65.01271796233409</v>
+        <v>65.01271796233431</v>
       </c>
       <c r="P377">
         <v>40876</v>
@@ -26016,7 +26016,7 @@
         </is>
       </c>
       <c r="S377">
-        <v>-2.375250116241723</v>
+        <v>-2.375250116241501</v>
       </c>
     </row>
     <row r="378">
@@ -26070,10 +26070,10 @@
         <v>7.294531710394677</v>
       </c>
       <c r="N378">
-        <v>57.18663105574592</v>
+        <v>57.18663105574594</v>
       </c>
       <c r="O378">
-        <v>14.73483535187088</v>
+        <v>14.7348353518708</v>
       </c>
       <c r="P378">
         <v>47791</v>
@@ -26138,10 +26138,10 @@
         <v>7.294531710394677</v>
       </c>
       <c r="N379">
-        <v>57.18663105574592</v>
+        <v>57.18663105574594</v>
       </c>
       <c r="O379">
-        <v>14.73483535187088</v>
+        <v>14.7348353518708</v>
       </c>
       <c r="P379">
         <v>47791</v>
@@ -26206,10 +26206,10 @@
         <v>7.294531710394677</v>
       </c>
       <c r="N380">
-        <v>57.18663105574592</v>
+        <v>57.18663105574594</v>
       </c>
       <c r="O380">
-        <v>14.73483535187088</v>
+        <v>14.7348353518708</v>
       </c>
       <c r="P380">
         <v>47791</v>
@@ -26220,7 +26220,7 @@
         </is>
       </c>
       <c r="S380">
-        <v>-9.099751258068167E-05</v>
+        <v>-9.099751255847721E-05</v>
       </c>
     </row>
     <row r="381">
@@ -26274,10 +26274,10 @@
         <v>7.294531710394677</v>
       </c>
       <c r="N381">
-        <v>57.18663105574592</v>
+        <v>57.18663105574594</v>
       </c>
       <c r="O381">
-        <v>14.73483535187088</v>
+        <v>14.7348353518708</v>
       </c>
       <c r="P381">
         <v>47791</v>
@@ -26288,7 +26288,7 @@
         </is>
       </c>
       <c r="S381">
-        <v>-42.45188670138761</v>
+        <v>-42.4518867013877</v>
       </c>
     </row>
   </sheetData>

--- a/tables_and_figures/input_tables/national_errors.xlsx
+++ b/tables_and_figures/input_tables/national_errors.xlsx
@@ -472,7 +472,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>40-49</t>
+          <t>18-29</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -493,19 +493,19 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>20.60587267680489</v>
+        <v>20.97276423076744</v>
       </c>
       <c r="L2">
-        <v>22.53644875209357</v>
+        <v>12.21548008017353</v>
       </c>
       <c r="M2">
-        <v>28.81622393309206</v>
+        <v>15.7093591479827</v>
       </c>
       <c r="N2">
-        <v>20.37996353536422</v>
+        <v>20.97257570511645</v>
       </c>
       <c r="O2">
-        <v>20.37987916940357</v>
+        <v>20.97276423076732</v>
       </c>
       <c r="P2">
         <v>36421</v>
@@ -516,7 +516,7 @@
         </is>
       </c>
       <c r="S2">
-        <v>1.930576075288684</v>
+        <v>-8.757284150593916</v>
       </c>
     </row>
     <row r="3">
@@ -540,7 +540,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>40-49</t>
+          <t>18-29</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -561,19 +561,19 @@
         <v>0</v>
       </c>
       <c r="K3">
-        <v>20.60587267680489</v>
+        <v>20.97276423076744</v>
       </c>
       <c r="L3">
-        <v>22.53644875209357</v>
+        <v>12.21548008017353</v>
       </c>
       <c r="M3">
-        <v>28.81622393309206</v>
+        <v>15.7093591479827</v>
       </c>
       <c r="N3">
-        <v>20.37996353536422</v>
+        <v>20.97257570511645</v>
       </c>
       <c r="O3">
-        <v>20.37987916940357</v>
+        <v>20.97276423076732</v>
       </c>
       <c r="P3">
         <v>36421</v>
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="S3">
-        <v>8.210351256287174</v>
+        <v>-5.263405082784745</v>
       </c>
     </row>
     <row r="4">
@@ -608,7 +608,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>40-49</t>
+          <t>18-29</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -629,19 +629,19 @@
         <v>0</v>
       </c>
       <c r="K4">
-        <v>20.60587267680489</v>
+        <v>20.97276423076744</v>
       </c>
       <c r="L4">
-        <v>22.53644875209357</v>
+        <v>12.21548008017353</v>
       </c>
       <c r="M4">
-        <v>28.81622393309206</v>
+        <v>15.7093591479827</v>
       </c>
       <c r="N4">
-        <v>20.37996353536422</v>
+        <v>20.97257570511645</v>
       </c>
       <c r="O4">
-        <v>20.37987916940357</v>
+        <v>20.97276423076732</v>
       </c>
       <c r="P4">
         <v>36421</v>
@@ -652,7 +652,7 @@
         </is>
       </c>
       <c r="S4">
-        <v>-0.2259091414406722</v>
+        <v>-0.0001885256509875921</v>
       </c>
     </row>
     <row r="5">
@@ -676,7 +676,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>40-49</t>
+          <t>18-29</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -697,19 +697,19 @@
         <v>0</v>
       </c>
       <c r="K5">
-        <v>20.60587267680489</v>
+        <v>20.97276423076744</v>
       </c>
       <c r="L5">
-        <v>22.53644875209357</v>
+        <v>12.21548008017353</v>
       </c>
       <c r="M5">
-        <v>28.81622393309206</v>
+        <v>15.7093591479827</v>
       </c>
       <c r="N5">
-        <v>20.37996353536422</v>
+        <v>20.97257570511645</v>
       </c>
       <c r="O5">
-        <v>20.37987916940357</v>
+        <v>20.97276423076732</v>
       </c>
       <c r="P5">
         <v>36421</v>
@@ -720,7 +720,7 @@
         </is>
       </c>
       <c r="S5">
-        <v>-0.2259935074013231</v>
+        <v>-1.165734175856414E-13</v>
       </c>
     </row>
     <row r="6">
@@ -765,7 +765,7 @@
         <v>0</v>
       </c>
       <c r="K6">
-        <v>32.4139496834677</v>
+        <v>32.26672641913058</v>
       </c>
       <c r="L6">
         <v>31.20701986026297</v>
@@ -788,7 +788,7 @@
         </is>
       </c>
       <c r="S6">
-        <v>-1.206929823204733</v>
+        <v>-1.059706558867612</v>
       </c>
     </row>
     <row r="7">
@@ -833,7 +833,7 @@
         <v>0</v>
       </c>
       <c r="K7">
-        <v>32.4139496834677</v>
+        <v>32.26672641913058</v>
       </c>
       <c r="L7">
         <v>31.20701986026297</v>
@@ -856,7 +856,7 @@
         </is>
       </c>
       <c r="S7">
-        <v>9.23507771203017</v>
+        <v>9.382300976367292</v>
       </c>
     </row>
     <row r="8">
@@ -901,7 +901,7 @@
         <v>0</v>
       </c>
       <c r="K8">
-        <v>32.4139496834677</v>
+        <v>32.26672641913058</v>
       </c>
       <c r="L8">
         <v>31.20701986026297</v>
@@ -924,7 +924,7 @@
         </is>
       </c>
       <c r="S8">
-        <v>-0.1467443606560037</v>
+        <v>0.0004789036811170266</v>
       </c>
     </row>
     <row r="9">
@@ -969,7 +969,7 @@
         <v>0</v>
       </c>
       <c r="K9">
-        <v>32.4139496834677</v>
+        <v>32.26672641913058</v>
       </c>
       <c r="L9">
         <v>31.20701986026297</v>
@@ -992,7 +992,7 @@
         </is>
       </c>
       <c r="S9">
-        <v>-0.1472232643371374</v>
+        <v>-1.665334536937735E-14</v>
       </c>
     </row>
     <row r="10">
@@ -1037,7 +1037,7 @@
         <v>0</v>
       </c>
       <c r="K10">
-        <v>64.90458092820026</v>
+        <v>64.40774340258872</v>
       </c>
       <c r="L10">
         <v>57.16374672368602</v>
@@ -1060,7 +1060,7 @@
         </is>
       </c>
       <c r="S10">
-        <v>-7.740834204514235</v>
+        <v>-7.243996678902698</v>
       </c>
     </row>
     <row r="11">
@@ -1105,7 +1105,7 @@
         <v>0</v>
       </c>
       <c r="K11">
-        <v>64.90458092820026</v>
+        <v>64.40774340258872</v>
       </c>
       <c r="L11">
         <v>57.16374672368602</v>
@@ -1128,7 +1128,7 @@
         </is>
       </c>
       <c r="S11">
-        <v>-1.811251642663625</v>
+        <v>-1.314414117052087</v>
       </c>
     </row>
     <row r="12">
@@ -1173,7 +1173,7 @@
         <v>0</v>
       </c>
       <c r="K12">
-        <v>64.90458092820026</v>
+        <v>64.40774340258872</v>
       </c>
       <c r="L12">
         <v>57.16374672368602</v>
@@ -1196,7 +1196,7 @@
         </is>
       </c>
       <c r="S12">
-        <v>-0.4970641375120266</v>
+        <v>-0.0002266119004890044</v>
       </c>
     </row>
     <row r="13">
@@ -1241,7 +1241,7 @@
         <v>0</v>
       </c>
       <c r="K13">
-        <v>64.90458092820026</v>
+        <v>64.40774340258872</v>
       </c>
       <c r="L13">
         <v>57.16374672368602</v>
@@ -1264,7 +1264,7 @@
         </is>
       </c>
       <c r="S13">
-        <v>-0.4968375256110713</v>
+        <v>4.662936703425657E-13</v>
       </c>
     </row>
     <row r="14">
@@ -1309,7 +1309,7 @@
         <v>0</v>
       </c>
       <c r="K14">
-        <v>24.14440225112303</v>
+        <v>23.90891074517583</v>
       </c>
       <c r="L14">
         <v>27.32318882189683</v>
@@ -1332,7 +1332,7 @@
         </is>
       </c>
       <c r="S14">
-        <v>3.178786570773798</v>
+        <v>3.414278076721</v>
       </c>
     </row>
     <row r="15">
@@ -1377,7 +1377,7 @@
         <v>0</v>
       </c>
       <c r="K15">
-        <v>24.14440225112303</v>
+        <v>23.90891074517583</v>
       </c>
       <c r="L15">
         <v>27.32318882189683</v>
@@ -1400,7 +1400,7 @@
         </is>
       </c>
       <c r="S15">
-        <v>3.105938169687719</v>
+        <v>3.341429675634922</v>
       </c>
     </row>
     <row r="16">
@@ -1445,7 +1445,7 @@
         <v>0</v>
       </c>
       <c r="K16">
-        <v>24.14440225112303</v>
+        <v>23.90891074517583</v>
       </c>
       <c r="L16">
         <v>27.32318882189683</v>
@@ -1468,7 +1468,7 @@
         </is>
       </c>
       <c r="S16">
-        <v>-0.2354752725120757</v>
+        <v>1.623343512668907E-05</v>
       </c>
     </row>
     <row r="17">
@@ -1513,7 +1513,7 @@
         <v>0</v>
       </c>
       <c r="K17">
-        <v>24.14440225112303</v>
+        <v>23.90891074517583</v>
       </c>
       <c r="L17">
         <v>27.32318882189683</v>
@@ -1536,7 +1536,7 @@
         </is>
       </c>
       <c r="S17">
-        <v>-0.2354915059469637</v>
+        <v>2.386979502944087E-13</v>
       </c>
     </row>
     <row r="18">
@@ -1581,7 +1581,7 @@
         <v>1</v>
       </c>
       <c r="K18">
-        <v>52.59701365956568</v>
+        <v>52.18745796266161</v>
       </c>
       <c r="L18">
         <v>52.18143378819912</v>
@@ -1604,7 +1604,7 @@
         </is>
       </c>
       <c r="S18">
-        <v>-0.4155798713665559</v>
+        <v>-0.00602417446249337</v>
       </c>
     </row>
     <row r="19">
@@ -1649,7 +1649,7 @@
         <v>1</v>
       </c>
       <c r="K19">
-        <v>52.59701365956568</v>
+        <v>52.18745796266161</v>
       </c>
       <c r="L19">
         <v>52.18143378819912</v>
@@ -1672,7 +1672,7 @@
         </is>
       </c>
       <c r="S19">
-        <v>-0.6494091240444089</v>
+        <v>-0.2398534271403463</v>
       </c>
     </row>
     <row r="20">
@@ -1717,7 +1717,7 @@
         <v>1</v>
       </c>
       <c r="K20">
-        <v>52.59701365956568</v>
+        <v>52.18745796266161</v>
       </c>
       <c r="L20">
         <v>52.18143378819912</v>
@@ -1740,7 +1740,7 @@
         </is>
       </c>
       <c r="S20">
-        <v>-0.4096308012482064</v>
+        <v>-7.510434414381706E-05</v>
       </c>
     </row>
     <row r="21">
@@ -1785,7 +1785,7 @@
         <v>1</v>
       </c>
       <c r="K21">
-        <v>52.59701365956568</v>
+        <v>52.18745796266161</v>
       </c>
       <c r="L21">
         <v>52.18143378819912</v>
@@ -1808,7 +1808,7 @@
         </is>
       </c>
       <c r="S21">
-        <v>-1.010857273582988</v>
+        <v>-0.6013015766789254</v>
       </c>
     </row>
     <row r="22">
@@ -1853,7 +1853,7 @@
         <v>1</v>
       </c>
       <c r="K22">
-        <v>87.30607100951718</v>
+        <v>87.20709012470589</v>
       </c>
       <c r="L22">
         <v>91.49594979403389</v>
@@ -1876,7 +1876,7 @@
         </is>
       </c>
       <c r="S22">
-        <v>4.18987878451671</v>
+        <v>4.288859669328005</v>
       </c>
     </row>
     <row r="23">
@@ -1921,7 +1921,7 @@
         <v>1</v>
       </c>
       <c r="K23">
-        <v>87.30607100951718</v>
+        <v>87.20709012470589</v>
       </c>
       <c r="L23">
         <v>91.49594979403389</v>
@@ -1944,7 +1944,7 @@
         </is>
       </c>
       <c r="S23">
-        <v>3.965281653228248</v>
+        <v>4.064262538039543</v>
       </c>
     </row>
     <row r="24">
@@ -1989,7 +1989,7 @@
         <v>1</v>
       </c>
       <c r="K24">
-        <v>87.30607100951718</v>
+        <v>87.20709012470589</v>
       </c>
       <c r="L24">
         <v>91.49594979403389</v>
@@ -2012,7 +2012,7 @@
         </is>
       </c>
       <c r="S24">
-        <v>-0.09873872360182112</v>
+        <v>0.0002421612094738457</v>
       </c>
     </row>
     <row r="25">
@@ -2057,7 +2057,7 @@
         <v>1</v>
       </c>
       <c r="K25">
-        <v>87.30607100951718</v>
+        <v>87.20709012470589</v>
       </c>
       <c r="L25">
         <v>91.49594979403389</v>
@@ -2080,7 +2080,7 @@
         </is>
       </c>
       <c r="S25">
-        <v>4.558107207148909</v>
+        <v>4.657088091960205</v>
       </c>
     </row>
     <row r="26">
@@ -2125,7 +2125,7 @@
         <v>1</v>
       </c>
       <c r="K26">
-        <v>88.20928721561053</v>
+        <v>88.86751429572016</v>
       </c>
       <c r="L26">
         <v>80.1690202879401</v>
@@ -2148,7 +2148,7 @@
         </is>
       </c>
       <c r="S26">
-        <v>-8.040266927670437</v>
+        <v>-8.698494007780056</v>
       </c>
     </row>
     <row r="27">
@@ -2193,7 +2193,7 @@
         <v>1</v>
       </c>
       <c r="K27">
-        <v>88.20928721561053</v>
+        <v>88.86751429572016</v>
       </c>
       <c r="L27">
         <v>80.1690202879401</v>
@@ -2216,7 +2216,7 @@
         </is>
       </c>
       <c r="S27">
-        <v>-3.769602111547532</v>
+        <v>-4.427829191657151</v>
       </c>
     </row>
     <row r="28">
@@ -2261,7 +2261,7 @@
         <v>1</v>
       </c>
       <c r="K28">
-        <v>88.20928721561053</v>
+        <v>88.86751429572016</v>
       </c>
       <c r="L28">
         <v>80.1690202879401</v>
@@ -2284,7 +2284,7 @@
         </is>
       </c>
       <c r="S28">
-        <v>0.6581879115972189</v>
+        <v>-3.916851240015617E-05</v>
       </c>
     </row>
     <row r="29">
@@ -2329,7 +2329,7 @@
         <v>1</v>
       </c>
       <c r="K29">
-        <v>88.20928721561053</v>
+        <v>88.86751429572016</v>
       </c>
       <c r="L29">
         <v>80.1690202879401</v>
@@ -2352,7 +2352,7 @@
         </is>
       </c>
       <c r="S29">
-        <v>-5.939104675445151</v>
+        <v>-6.597331755554769</v>
       </c>
     </row>
     <row r="30">
@@ -2397,7 +2397,7 @@
         <v>1</v>
       </c>
       <c r="K30">
-        <v>86.75167357347785</v>
+        <v>86.23135014450705</v>
       </c>
       <c r="L30">
         <v>81.13531064171318</v>
@@ -2420,7 +2420,7 @@
         </is>
       </c>
       <c r="S30">
-        <v>-5.616362931764673</v>
+        <v>-5.09603950279387</v>
       </c>
     </row>
     <row r="31">
@@ -2465,7 +2465,7 @@
         <v>1</v>
       </c>
       <c r="K31">
-        <v>86.75167357347785</v>
+        <v>86.23135014450705</v>
       </c>
       <c r="L31">
         <v>81.13531064171318</v>
@@ -2488,7 +2488,7 @@
         </is>
       </c>
       <c r="S31">
-        <v>-3.680671789420498</v>
+        <v>-3.160348360449694</v>
       </c>
     </row>
     <row r="32">
@@ -2533,7 +2533,7 @@
         <v>1</v>
       </c>
       <c r="K32">
-        <v>86.75167357347785</v>
+        <v>86.23135014450705</v>
       </c>
       <c r="L32">
         <v>81.13531064171318</v>
@@ -2556,7 +2556,7 @@
         </is>
       </c>
       <c r="S32">
-        <v>-0.5203464291617221</v>
+        <v>-2.300019091849848E-05</v>
       </c>
     </row>
     <row r="33">
@@ -2601,7 +2601,7 @@
         <v>1</v>
       </c>
       <c r="K33">
-        <v>86.75167357347785</v>
+        <v>86.23135014450705</v>
       </c>
       <c r="L33">
         <v>81.13531064171318</v>
@@ -2624,7 +2624,7 @@
         </is>
       </c>
       <c r="S33">
-        <v>-5.433508213812067</v>
+        <v>-4.913184784841262</v>
       </c>
     </row>
     <row r="34">
@@ -2941,7 +2941,7 @@
         <v>0</v>
       </c>
       <c r="K38">
-        <v>19.52891516910966</v>
+        <v>21.35715098116489</v>
       </c>
       <c r="L38">
         <v>17.5640243902439</v>
@@ -2964,7 +2964,7 @@
         </is>
       </c>
       <c r="S38">
-        <v>-1.964890778865758</v>
+        <v>-3.793126590920984</v>
       </c>
     </row>
     <row r="39">
@@ -3009,7 +3009,7 @@
         <v>0</v>
       </c>
       <c r="K39">
-        <v>19.52891516910966</v>
+        <v>21.35715098116489</v>
       </c>
       <c r="L39">
         <v>17.5640243902439</v>
@@ -3032,7 +3032,7 @@
         </is>
       </c>
       <c r="S39">
-        <v>4.871831764416299</v>
+        <v>3.043595952361072</v>
       </c>
     </row>
     <row r="40">
@@ -3077,7 +3077,7 @@
         <v>0</v>
       </c>
       <c r="K40">
-        <v>19.52891516910966</v>
+        <v>21.35715098116489</v>
       </c>
       <c r="L40">
         <v>17.5640243902439</v>
@@ -3100,7 +3100,7 @@
         </is>
       </c>
       <c r="S40">
-        <v>1.828235812055187</v>
+        <v>-3.885780586188048E-14</v>
       </c>
     </row>
     <row r="41">
@@ -3145,7 +3145,7 @@
         <v>0</v>
       </c>
       <c r="K41">
-        <v>19.52891516910966</v>
+        <v>21.35715098116489</v>
       </c>
       <c r="L41">
         <v>17.5640243902439</v>
@@ -3168,7 +3168,7 @@
         </is>
       </c>
       <c r="S41">
-        <v>1.828235812055176</v>
+        <v>-4.996003610813204E-14</v>
       </c>
     </row>
     <row r="42">
@@ -3213,7 +3213,7 @@
         <v>0</v>
       </c>
       <c r="K42">
-        <v>31.97552852334052</v>
+        <v>31.69759345188885</v>
       </c>
       <c r="L42">
         <v>34.80792682926829</v>
@@ -3236,7 +3236,7 @@
         </is>
       </c>
       <c r="S42">
-        <v>2.832398305927775</v>
+        <v>3.110333377379443</v>
       </c>
     </row>
     <row r="43">
@@ -3281,7 +3281,7 @@
         <v>0</v>
       </c>
       <c r="K43">
-        <v>31.97552852334052</v>
+        <v>31.69759345188885</v>
       </c>
       <c r="L43">
         <v>34.80792682926829</v>
@@ -3304,7 +3304,7 @@
         </is>
       </c>
       <c r="S43">
-        <v>-0.3168113916178383</v>
+        <v>-0.03887632016617015</v>
       </c>
     </row>
     <row r="44">
@@ -3349,7 +3349,7 @@
         <v>0</v>
       </c>
       <c r="K44">
-        <v>31.97552852334052</v>
+        <v>31.69759345188885</v>
       </c>
       <c r="L44">
         <v>34.80792682926829</v>
@@ -3372,7 +3372,7 @@
         </is>
       </c>
       <c r="S44">
-        <v>-0.2779350714515794</v>
+        <v>8.881784197001252E-14</v>
       </c>
     </row>
     <row r="45">
@@ -3417,7 +3417,7 @@
         <v>0</v>
       </c>
       <c r="K45">
-        <v>31.97552852334052</v>
+        <v>31.69759345188885</v>
       </c>
       <c r="L45">
         <v>34.80792682926829</v>
@@ -3440,7 +3440,7 @@
         </is>
       </c>
       <c r="S45">
-        <v>-0.2779350714510742</v>
+        <v>5.939693181744587E-13</v>
       </c>
     </row>
     <row r="46">
@@ -3485,7 +3485,7 @@
         <v>0</v>
       </c>
       <c r="K46">
-        <v>64.19692948866368</v>
+        <v>63.69587112910116</v>
       </c>
       <c r="L46">
         <v>57.49390243902439</v>
@@ -3508,7 +3508,7 @@
         </is>
       </c>
       <c r="S46">
-        <v>-6.703027049639299</v>
+        <v>-6.201968690076775</v>
       </c>
     </row>
     <row r="47">
@@ -3553,7 +3553,7 @@
         <v>0</v>
       </c>
       <c r="K47">
-        <v>64.19692948866368</v>
+        <v>63.69587112910116</v>
       </c>
       <c r="L47">
         <v>57.49390243902439</v>
@@ -3576,7 +3576,7 @@
         </is>
       </c>
       <c r="S47">
-        <v>-10.12745133003281</v>
+        <v>-9.626392970470288</v>
       </c>
     </row>
     <row r="48">
@@ -3621,7 +3621,7 @@
         <v>0</v>
       </c>
       <c r="K48">
-        <v>64.19692948866368</v>
+        <v>63.69587112910116</v>
       </c>
       <c r="L48">
         <v>57.49390243902439</v>
@@ -3644,7 +3644,7 @@
         </is>
       </c>
       <c r="S48">
-        <v>-0.5010583595620455</v>
+        <v>4.773959005888173E-13</v>
       </c>
     </row>
     <row r="49">
@@ -3689,7 +3689,7 @@
         <v>0</v>
       </c>
       <c r="K49">
-        <v>64.19692948866368</v>
+        <v>63.69587112910116</v>
       </c>
       <c r="L49">
         <v>57.49390243902439</v>
@@ -3712,7 +3712,7 @@
         </is>
       </c>
       <c r="S49">
-        <v>-0.5010583595627005</v>
+        <v>-1.77635683940025E-13</v>
       </c>
     </row>
     <row r="50">
@@ -3757,7 +3757,7 @@
         <v>0</v>
       </c>
       <c r="K50">
-        <v>25.12007537578334</v>
+        <v>24.76618218000426</v>
       </c>
       <c r="L50">
         <v>26.35941105730166</v>
@@ -3780,7 +3780,7 @@
         </is>
       </c>
       <c r="S50">
-        <v>1.239335681518317</v>
+        <v>1.593228877297392</v>
       </c>
     </row>
     <row r="51">
@@ -3825,7 +3825,7 @@
         <v>0</v>
       </c>
       <c r="K51">
-        <v>25.12007537578334</v>
+        <v>24.76618218000426</v>
       </c>
       <c r="L51">
         <v>26.35941105730166</v>
@@ -3848,7 +3848,7 @@
         </is>
       </c>
       <c r="S51">
-        <v>-1.700397360458791</v>
+        <v>-1.346504164679716</v>
       </c>
     </row>
     <row r="52">
@@ -3893,7 +3893,7 @@
         <v>0</v>
       </c>
       <c r="K52">
-        <v>25.12007537578334</v>
+        <v>24.76618218000426</v>
       </c>
       <c r="L52">
         <v>26.35941105730166</v>
@@ -3916,7 +3916,7 @@
         </is>
       </c>
       <c r="S52">
-        <v>-0.3538931957790148</v>
+        <v>6.106226635438361E-14</v>
       </c>
     </row>
     <row r="53">
@@ -3961,7 +3961,7 @@
         <v>0</v>
       </c>
       <c r="K53">
-        <v>25.12007537578334</v>
+        <v>24.76618218000426</v>
       </c>
       <c r="L53">
         <v>26.35941105730166</v>
@@ -3984,7 +3984,7 @@
         </is>
       </c>
       <c r="S53">
-        <v>-0.3538931957792119</v>
+        <v>-1.360023205165817E-13</v>
       </c>
     </row>
     <row r="54">
@@ -4029,7 +4029,7 @@
         <v>1</v>
       </c>
       <c r="K54">
-        <v>60.3320097475291</v>
+        <v>59.13503660841504</v>
       </c>
       <c r="L54">
         <v>57.17382675338158</v>
@@ -4052,7 +4052,7 @@
         </is>
       </c>
       <c r="S54">
-        <v>-3.158182994147529</v>
+        <v>-1.961209855033463</v>
       </c>
     </row>
     <row r="55">
@@ -4097,7 +4097,7 @@
         <v>1</v>
       </c>
       <c r="K55">
-        <v>60.3320097475291</v>
+        <v>59.13503660841504</v>
       </c>
       <c r="L55">
         <v>57.17382675338158</v>
@@ -4120,7 +4120,7 @@
         </is>
       </c>
       <c r="S55">
-        <v>-6.179287657447807</v>
+        <v>-4.982314518333741</v>
       </c>
     </row>
     <row r="56">
@@ -4165,7 +4165,7 @@
         <v>1</v>
       </c>
       <c r="K56">
-        <v>60.3320097475291</v>
+        <v>59.13503660841504</v>
       </c>
       <c r="L56">
         <v>57.17382675338158</v>
@@ -4188,7 +4188,7 @@
         </is>
       </c>
       <c r="S56">
-        <v>-1.196973139114077</v>
+        <v>-1.110223024625157E-14</v>
       </c>
     </row>
     <row r="57">
@@ -4233,7 +4233,7 @@
         <v>1</v>
       </c>
       <c r="K57">
-        <v>60.3320097475291</v>
+        <v>59.13503660841504</v>
       </c>
       <c r="L57">
         <v>57.17382675338158</v>
@@ -4256,7 +4256,7 @@
         </is>
       </c>
       <c r="S57">
-        <v>-4.556052530971311</v>
+        <v>-3.359079391857245</v>
       </c>
     </row>
     <row r="58">
@@ -4301,7 +4301,7 @@
         <v>0</v>
       </c>
       <c r="K58">
-        <v>52.50289418846955</v>
+        <v>52.11350542657888</v>
       </c>
       <c r="L58">
         <v>51.6890243902439</v>
@@ -4324,7 +4324,7 @@
         </is>
       </c>
       <c r="S58">
-        <v>-0.8138697982256526</v>
+        <v>-0.4244810363349782</v>
       </c>
     </row>
     <row r="59">
@@ -4369,7 +4369,7 @@
         <v>0</v>
       </c>
       <c r="K59">
-        <v>52.50289418846955</v>
+        <v>52.11350542657888</v>
       </c>
       <c r="L59">
         <v>51.6890243902439</v>
@@ -4392,7 +4392,7 @@
         </is>
       </c>
       <c r="S59">
-        <v>-0.7633824165910852</v>
+        <v>-0.3739936547004108</v>
       </c>
     </row>
     <row r="60">
@@ -4437,7 +4437,7 @@
         <v>0</v>
       </c>
       <c r="K60">
-        <v>52.50289418846955</v>
+        <v>52.11350542657888</v>
       </c>
       <c r="L60">
         <v>51.6890243902439</v>
@@ -4460,7 +4460,7 @@
         </is>
       </c>
       <c r="S60">
-        <v>-0.3893887618906966</v>
+        <v>-2.220446049250313E-14</v>
       </c>
     </row>
     <row r="61">
@@ -4505,7 +4505,7 @@
         <v>0</v>
       </c>
       <c r="K61">
-        <v>52.50289418846955</v>
+        <v>52.11350542657888</v>
       </c>
       <c r="L61">
         <v>51.6890243902439</v>
@@ -4528,7 +4528,7 @@
         </is>
       </c>
       <c r="S61">
-        <v>-1.939835931252698</v>
+        <v>-1.550447169362024</v>
       </c>
     </row>
     <row r="62">
@@ -4573,7 +4573,7 @@
         <v>1</v>
       </c>
       <c r="K62">
-        <v>86.94672440706984</v>
+        <v>86.87247193255007</v>
       </c>
       <c r="L62">
         <v>86.12559023732139</v>
@@ -4596,7 +4596,7 @@
         </is>
       </c>
       <c r="S62">
-        <v>-0.8211341697484498</v>
+        <v>-0.7468816952286739</v>
       </c>
     </row>
     <row r="63">
@@ -4641,7 +4641,7 @@
         <v>1</v>
       </c>
       <c r="K63">
-        <v>86.94672440706984</v>
+        <v>86.87247193255007</v>
       </c>
       <c r="L63">
         <v>86.12559023732139</v>
@@ -4664,7 +4664,7 @@
         </is>
       </c>
       <c r="S63">
-        <v>-0.8288414460252747</v>
+        <v>-0.7545889715054988</v>
       </c>
     </row>
     <row r="64">
@@ -4709,7 +4709,7 @@
         <v>1</v>
       </c>
       <c r="K64">
-        <v>86.94672440706984</v>
+        <v>86.87247193255007</v>
       </c>
       <c r="L64">
         <v>86.12559023732139</v>
@@ -4732,7 +4732,7 @@
         </is>
       </c>
       <c r="S64">
-        <v>-0.5496108705599911</v>
+        <v>-0.4753583960402152</v>
       </c>
     </row>
     <row r="65">
@@ -4777,7 +4777,7 @@
         <v>1</v>
       </c>
       <c r="K65">
-        <v>86.94672440706984</v>
+        <v>86.87247193255007</v>
       </c>
       <c r="L65">
         <v>86.12559023732139</v>
@@ -4800,7 +4800,7 @@
         </is>
       </c>
       <c r="S65">
-        <v>-0.8577777030573053</v>
+        <v>-0.7835252285375294</v>
       </c>
     </row>
     <row r="66">
@@ -4845,7 +4845,7 @@
         <v>1</v>
       </c>
       <c r="K66">
-        <v>88.90683513268041</v>
+        <v>89.60497359944833</v>
       </c>
       <c r="L66">
         <v>83.47865853658537</v>
@@ -4868,7 +4868,7 @@
         </is>
       </c>
       <c r="S66">
-        <v>-5.428176596095035</v>
+        <v>-6.126315062862964</v>
       </c>
     </row>
     <row r="67">
@@ -4913,7 +4913,7 @@
         <v>1</v>
       </c>
       <c r="K67">
-        <v>88.90683513268041</v>
+        <v>89.60497359944833</v>
       </c>
       <c r="L67">
         <v>83.47865853658537</v>
@@ -4936,7 +4936,7 @@
         </is>
       </c>
       <c r="S67">
-        <v>-2.566913667535742</v>
+        <v>-3.26505213430367</v>
       </c>
     </row>
     <row r="68">
@@ -4981,7 +4981,7 @@
         <v>1</v>
       </c>
       <c r="K68">
-        <v>88.90683513268041</v>
+        <v>89.60497359944833</v>
       </c>
       <c r="L68">
         <v>83.47865853658537</v>
@@ -5004,7 +5004,7 @@
         </is>
       </c>
       <c r="S68">
-        <v>0.6981384667678836</v>
+        <v>-4.440892098500626E-14</v>
       </c>
     </row>
     <row r="69">
@@ -5049,7 +5049,7 @@
         <v>1</v>
       </c>
       <c r="K69">
-        <v>88.90683513268041</v>
+        <v>89.60497359944833</v>
       </c>
       <c r="L69">
         <v>83.47865853658537</v>
@@ -5072,7 +5072,7 @@
         </is>
       </c>
       <c r="S69">
-        <v>-4.746741862052517</v>
+        <v>-5.444880328820445</v>
       </c>
     </row>
     <row r="70">
@@ -5117,7 +5117,7 @@
         <v>1</v>
       </c>
       <c r="K70">
-        <v>84.12379757423672</v>
+        <v>83.57810410759151</v>
       </c>
       <c r="L70">
         <v>80.24319868095631</v>
@@ -5140,7 +5140,7 @@
         </is>
       </c>
       <c r="S70">
-        <v>-3.880598893280418</v>
+        <v>-3.334905426635204</v>
       </c>
     </row>
     <row r="71">
@@ -5185,7 +5185,7 @@
         <v>1</v>
       </c>
       <c r="K71">
-        <v>84.12379757423672</v>
+        <v>83.57810410759151</v>
       </c>
       <c r="L71">
         <v>80.24319868095631</v>
@@ -5208,7 +5208,7 @@
         </is>
       </c>
       <c r="S71">
-        <v>-3.306004430420639</v>
+        <v>-2.760310963775425</v>
       </c>
     </row>
     <row r="72">
@@ -5253,7 +5253,7 @@
         <v>1</v>
       </c>
       <c r="K72">
-        <v>84.12379757423672</v>
+        <v>83.57810410759151</v>
       </c>
       <c r="L72">
         <v>80.24319868095631</v>
@@ -5276,7 +5276,7 @@
         </is>
       </c>
       <c r="S72">
-        <v>-0.5456934666451363</v>
+        <v>7.771561172376096E-14</v>
       </c>
     </row>
     <row r="73">
@@ -5321,7 +5321,7 @@
         <v>1</v>
       </c>
       <c r="K73">
-        <v>84.12379757423672</v>
+        <v>83.57810410759151</v>
       </c>
       <c r="L73">
         <v>80.24319868095631</v>
@@ -5344,7 +5344,7 @@
         </is>
       </c>
       <c r="S73">
-        <v>-3.883872007048739</v>
+        <v>-3.338178540403525</v>
       </c>
     </row>
     <row r="74">
@@ -5661,7 +5661,7 @@
         <v>0</v>
       </c>
       <c r="K78">
-        <v>19.75308749963918</v>
+        <v>21.57058826361387</v>
       </c>
       <c r="L78">
         <v>9.467509025270758</v>
@@ -5684,7 +5684,7 @@
         </is>
       </c>
       <c r="S78">
-        <v>-10.28557847436842</v>
+        <v>-12.10307923834311</v>
       </c>
     </row>
     <row r="79">
@@ -5729,7 +5729,7 @@
         <v>0</v>
       </c>
       <c r="K79">
-        <v>19.75308749963918</v>
+        <v>21.57058826361387</v>
       </c>
       <c r="L79">
         <v>9.467509025270758</v>
@@ -5752,7 +5752,7 @@
         </is>
       </c>
       <c r="S79">
-        <v>-0.03890561068820297</v>
+        <v>-1.856406374662889</v>
       </c>
     </row>
     <row r="80">
@@ -5797,7 +5797,7 @@
         <v>0</v>
       </c>
       <c r="K80">
-        <v>19.75308749963918</v>
+        <v>21.57058826361387</v>
       </c>
       <c r="L80">
         <v>9.467509025270758</v>
@@ -5820,7 +5820,7 @@
         </is>
       </c>
       <c r="S80">
-        <v>1.936748087924511</v>
+        <v>0.1192473239498254</v>
       </c>
     </row>
     <row r="81">
@@ -5865,7 +5865,7 @@
         <v>0</v>
       </c>
       <c r="K81">
-        <v>19.75308749963918</v>
+        <v>21.57058826361387</v>
       </c>
       <c r="L81">
         <v>9.467509025270758</v>
@@ -5888,7 +5888,7 @@
         </is>
       </c>
       <c r="S81">
-        <v>1.936748087924747</v>
+        <v>0.1192473239500613</v>
       </c>
     </row>
     <row r="82">
@@ -5933,7 +5933,7 @@
         <v>0</v>
       </c>
       <c r="K82">
-        <v>31.68655023140393</v>
+        <v>31.52554697968674</v>
       </c>
       <c r="L82">
         <v>18.985559566787</v>
@@ -5956,7 +5956,7 @@
         </is>
       </c>
       <c r="S82">
-        <v>-12.70099066461693</v>
+        <v>-12.53998741289973</v>
       </c>
     </row>
     <row r="83">
@@ -6001,7 +6001,7 @@
         <v>0</v>
       </c>
       <c r="K83">
-        <v>31.68655023140393</v>
+        <v>31.52554697968674</v>
       </c>
       <c r="L83">
         <v>18.985559566787</v>
@@ -6024,7 +6024,7 @@
         </is>
       </c>
       <c r="S83">
-        <v>2.887992555878066</v>
+        <v>3.048995807595261</v>
       </c>
     </row>
     <row r="84">
@@ -6069,7 +6069,7 @@
         <v>0</v>
       </c>
       <c r="K84">
-        <v>31.68655023140393</v>
+        <v>31.52554697968674</v>
       </c>
       <c r="L84">
         <v>18.985559566787</v>
@@ -6092,7 +6092,7 @@
         </is>
       </c>
       <c r="S84">
-        <v>0.44453379206007</v>
+        <v>0.6055370437772656</v>
       </c>
     </row>
     <row r="85">
@@ -6137,7 +6137,7 @@
         <v>0</v>
       </c>
       <c r="K85">
-        <v>31.68655023140393</v>
+        <v>31.52554697968674</v>
       </c>
       <c r="L85">
         <v>18.985559566787</v>
@@ -6160,7 +6160,7 @@
         </is>
       </c>
       <c r="S85">
-        <v>0.4445337920599868</v>
+        <v>0.6055370437771823</v>
       </c>
     </row>
     <row r="86">
@@ -6205,7 +6205,7 @@
         <v>0</v>
       </c>
       <c r="K86">
-        <v>60.88411959354081</v>
+        <v>60.03962247724475</v>
       </c>
       <c r="L86">
         <v>50.90794223826715</v>
@@ -6228,7 +6228,7 @@
         </is>
       </c>
       <c r="S86">
-        <v>-9.976177355273663</v>
+        <v>-9.131680238977602</v>
       </c>
     </row>
     <row r="87">
@@ -6273,7 +6273,7 @@
         <v>0</v>
       </c>
       <c r="K87">
-        <v>60.88411959354081</v>
+        <v>60.03962247724475</v>
       </c>
       <c r="L87">
         <v>50.90794223826715</v>
@@ -6296,7 +6296,7 @@
         </is>
       </c>
       <c r="S87">
-        <v>-11.13097517606475</v>
+        <v>-10.28647805976869</v>
       </c>
     </row>
     <row r="88">
@@ -6341,7 +6341,7 @@
         <v>0</v>
       </c>
       <c r="K88">
-        <v>60.88411959354081</v>
+        <v>60.03962247724475</v>
       </c>
       <c r="L88">
         <v>50.90794223826715</v>
@@ -6364,7 +6364,7 @@
         </is>
       </c>
       <c r="S88">
-        <v>-0.2387361085900874</v>
+        <v>0.6057610077059739</v>
       </c>
     </row>
     <row r="89">
@@ -6409,7 +6409,7 @@
         <v>0</v>
       </c>
       <c r="K89">
-        <v>60.88411959354081</v>
+        <v>60.03962247724475</v>
       </c>
       <c r="L89">
         <v>50.90794223826715</v>
@@ -6432,7 +6432,7 @@
         </is>
       </c>
       <c r="S89">
-        <v>-0.238736108590365</v>
+        <v>0.6057610077056963</v>
       </c>
     </row>
     <row r="90">
@@ -6477,7 +6477,7 @@
         <v>0</v>
       </c>
       <c r="K90">
-        <v>23.47470651368612</v>
+        <v>23.00721016905442</v>
       </c>
       <c r="L90">
         <v>27.20521681889245</v>
@@ -6500,7 +6500,7 @@
         </is>
       </c>
       <c r="S90">
-        <v>3.730510305206339</v>
+        <v>4.198006649838032</v>
       </c>
     </row>
     <row r="91">
@@ -6545,7 +6545,7 @@
         <v>0</v>
       </c>
       <c r="K91">
-        <v>23.47470651368612</v>
+        <v>23.00721016905442</v>
       </c>
       <c r="L91">
         <v>27.20521681889245</v>
@@ -6568,7 +6568,7 @@
         </is>
       </c>
       <c r="S91">
-        <v>-0.5641448683049666</v>
+        <v>-0.09664852367327337</v>
       </c>
     </row>
     <row r="92">
@@ -6613,7 +6613,7 @@
         <v>0</v>
       </c>
       <c r="K92">
-        <v>23.47470651368612</v>
+        <v>23.00721016905442</v>
       </c>
       <c r="L92">
         <v>27.20521681889245</v>
@@ -6636,7 +6636,7 @@
         </is>
       </c>
       <c r="S92">
-        <v>-0.2830345174889337</v>
+        <v>0.1844618271427595</v>
       </c>
     </row>
     <row r="93">
@@ -6681,7 +6681,7 @@
         <v>0</v>
       </c>
       <c r="K93">
-        <v>23.47470651368612</v>
+        <v>23.00721016905442</v>
       </c>
       <c r="L93">
         <v>27.20521681889245</v>
@@ -6704,7 +6704,7 @@
         </is>
       </c>
       <c r="S93">
-        <v>-0.2818286934045483</v>
+        <v>0.1856676512271449</v>
       </c>
     </row>
     <row r="94">
@@ -6749,7 +6749,7 @@
         <v>1</v>
       </c>
       <c r="K94">
-        <v>92.1138099732427</v>
+        <v>90.14654435448541</v>
       </c>
       <c r="L94">
         <v>96.79155285580333</v>
@@ -6772,7 +6772,7 @@
         </is>
       </c>
       <c r="S94">
-        <v>4.677742882560643</v>
+        <v>6.645008501317918</v>
       </c>
     </row>
     <row r="95">
@@ -6817,7 +6817,7 @@
         <v>1</v>
       </c>
       <c r="K95">
-        <v>92.1138099732427</v>
+        <v>90.14654435448541</v>
       </c>
       <c r="L95">
         <v>96.79155285580333</v>
@@ -6840,7 +6840,7 @@
         </is>
       </c>
       <c r="S95">
-        <v>5.240373156998102</v>
+        <v>7.207638775755376</v>
       </c>
     </row>
     <row r="96">
@@ -6885,7 +6885,7 @@
         <v>1</v>
       </c>
       <c r="K96">
-        <v>92.1138099732427</v>
+        <v>90.14654435448541</v>
       </c>
       <c r="L96">
         <v>96.79155285580333</v>
@@ -6908,7 +6908,7 @@
         </is>
       </c>
       <c r="S96">
-        <v>-2.0360808689739</v>
+        <v>-0.06881525021662505</v>
       </c>
     </row>
     <row r="97">
@@ -6953,7 +6953,7 @@
         <v>1</v>
       </c>
       <c r="K97">
-        <v>92.1138099732427</v>
+        <v>90.14654435448541</v>
       </c>
       <c r="L97">
         <v>96.79155285580333</v>
@@ -6976,7 +6976,7 @@
         </is>
       </c>
       <c r="S97">
-        <v>3.455642860245511</v>
+        <v>5.422908479002785</v>
       </c>
     </row>
     <row r="98">
@@ -7021,7 +7021,7 @@
         <v>1</v>
       </c>
       <c r="K98">
-        <v>61.84497545981855</v>
+        <v>60.46333721327933</v>
       </c>
       <c r="L98">
         <v>69.0429281518301</v>
@@ -7044,7 +7044,7 @@
         </is>
       </c>
       <c r="S98">
-        <v>7.197952692011544</v>
+        <v>8.579590938550762</v>
       </c>
     </row>
     <row r="99">
@@ -7089,7 +7089,7 @@
         <v>1</v>
       </c>
       <c r="K99">
-        <v>61.84497545981855</v>
+        <v>60.46333721327933</v>
       </c>
       <c r="L99">
         <v>69.0429281518301</v>
@@ -7112,7 +7112,7 @@
         </is>
       </c>
       <c r="S99">
-        <v>-0.5057718986446358</v>
+        <v>0.8758663478945827</v>
       </c>
     </row>
     <row r="100">
@@ -7157,7 +7157,7 @@
         <v>1</v>
       </c>
       <c r="K100">
-        <v>61.84497545981855</v>
+        <v>60.46333721327933</v>
       </c>
       <c r="L100">
         <v>69.0429281518301</v>
@@ -7180,7 +7180,7 @@
         </is>
       </c>
       <c r="S100">
-        <v>-1.44705391069867</v>
+        <v>-0.06541566415945166</v>
       </c>
     </row>
     <row r="101">
@@ -7225,7 +7225,7 @@
         <v>1</v>
       </c>
       <c r="K101">
-        <v>61.84497545981855</v>
+        <v>60.46333721327933</v>
       </c>
       <c r="L101">
         <v>69.0429281518301</v>
@@ -7248,7 +7248,7 @@
         </is>
       </c>
       <c r="S101">
-        <v>-0.4564911895598933</v>
+        <v>0.9251470569793252</v>
       </c>
     </row>
     <row r="102">
@@ -7293,7 +7293,7 @@
         <v>0</v>
       </c>
       <c r="K102">
-        <v>52.3738255955229</v>
+        <v>52.04157376914979</v>
       </c>
       <c r="L102">
         <v>51.76353790613718</v>
@@ -7316,7 +7316,7 @@
         </is>
       </c>
       <c r="S102">
-        <v>-0.6102876893857134</v>
+        <v>-0.2780358630126156</v>
       </c>
     </row>
     <row r="103">
@@ -7361,7 +7361,7 @@
         <v>0</v>
       </c>
       <c r="K103">
-        <v>52.3738255955229</v>
+        <v>52.04157376914979</v>
       </c>
       <c r="L103">
         <v>51.76353790613718</v>
@@ -7384,7 +7384,7 @@
         </is>
       </c>
       <c r="S103">
-        <v>-0.3986412463590439</v>
+        <v>-0.06638941998594605</v>
       </c>
     </row>
     <row r="104">
@@ -7429,7 +7429,7 @@
         <v>0</v>
       </c>
       <c r="K104">
-        <v>52.3738255955229</v>
+        <v>52.04157376914979</v>
       </c>
       <c r="L104">
         <v>51.76353790613718</v>
@@ -7452,7 +7452,7 @@
         </is>
       </c>
       <c r="S104">
-        <v>-0.4053152415143146</v>
+        <v>-0.07306341514121684</v>
       </c>
     </row>
     <row r="105">
@@ -7497,7 +7497,7 @@
         <v>0</v>
       </c>
       <c r="K105">
-        <v>52.3738255955229</v>
+        <v>52.04157376914979</v>
       </c>
       <c r="L105">
         <v>51.76353790613718</v>
@@ -7520,7 +7520,7 @@
         </is>
       </c>
       <c r="S105">
-        <v>2.794379730473062</v>
+        <v>3.12663155684616</v>
       </c>
     </row>
     <row r="106">
@@ -7565,7 +7565,7 @@
         <v>1</v>
       </c>
       <c r="K106">
-        <v>87.43089866007035</v>
+        <v>87.46401726455349</v>
       </c>
       <c r="L106">
         <v>92.40070960501068</v>
@@ -7588,7 +7588,7 @@
         </is>
       </c>
       <c r="S106">
-        <v>4.969810944940322</v>
+        <v>4.936692340457194</v>
       </c>
     </row>
     <row r="107">
@@ -7633,7 +7633,7 @@
         <v>1</v>
       </c>
       <c r="K107">
-        <v>87.43089866007035</v>
+        <v>87.46401726455349</v>
       </c>
       <c r="L107">
         <v>92.40070960501068</v>
@@ -7656,7 +7656,7 @@
         </is>
       </c>
       <c r="S107">
-        <v>5.496940928351601</v>
+        <v>5.463822323868472</v>
       </c>
     </row>
     <row r="108">
@@ -7701,7 +7701,7 @@
         <v>1</v>
       </c>
       <c r="K108">
-        <v>87.43089866007035</v>
+        <v>87.46401726455349</v>
       </c>
       <c r="L108">
         <v>92.40070960501068</v>
@@ -7724,7 +7724,7 @@
         </is>
       </c>
       <c r="S108">
-        <v>-0.1009559809638128</v>
+        <v>-0.1340745854469416</v>
       </c>
     </row>
     <row r="109">
@@ -7769,7 +7769,7 @@
         <v>1</v>
       </c>
       <c r="K109">
-        <v>87.43089866007035</v>
+        <v>87.46401726455349</v>
       </c>
       <c r="L109">
         <v>92.40070960501068</v>
@@ -7792,7 +7792,7 @@
         </is>
       </c>
       <c r="S109">
-        <v>4.907149736411109</v>
+        <v>4.87403113192798</v>
       </c>
     </row>
     <row r="110">
@@ -7837,7 +7837,7 @@
         <v>1</v>
       </c>
       <c r="K110">
-        <v>89.56797350462509</v>
+        <v>90.23260494442984</v>
       </c>
       <c r="L110">
         <v>80.38447653429603</v>
@@ -7860,7 +7860,7 @@
         </is>
       </c>
       <c r="S110">
-        <v>-9.183496970329053</v>
+        <v>-9.848128410133805</v>
       </c>
     </row>
     <row r="111">
@@ -7905,7 +7905,7 @@
         <v>1</v>
       </c>
       <c r="K111">
-        <v>89.56797350462509</v>
+        <v>90.23260494442984</v>
       </c>
       <c r="L111">
         <v>80.38447653429603</v>
@@ -7928,7 +7928,7 @@
         </is>
       </c>
       <c r="S111">
-        <v>-3.266681487628731</v>
+        <v>-3.931312927433483</v>
       </c>
     </row>
     <row r="112">
@@ -7973,7 +7973,7 @@
         <v>1</v>
       </c>
       <c r="K112">
-        <v>89.56797350462509</v>
+        <v>90.23260494442984</v>
       </c>
       <c r="L112">
         <v>80.38447653429603</v>
@@ -7996,7 +7996,7 @@
         </is>
       </c>
       <c r="S112">
-        <v>0.7294136856202504</v>
+        <v>0.06478224581549785</v>
       </c>
     </row>
     <row r="113">
@@ -8041,7 +8041,7 @@
         <v>1</v>
       </c>
       <c r="K113">
-        <v>89.56797350462509</v>
+        <v>90.23260494442984</v>
       </c>
       <c r="L113">
         <v>80.38447653429603</v>
@@ -8064,7 +8064,7 @@
         </is>
       </c>
       <c r="S113">
-        <v>-4.427951345876502</v>
+        <v>-5.092582785681254</v>
       </c>
     </row>
     <row r="114">
@@ -8109,7 +8109,7 @@
         <v>1</v>
       </c>
       <c r="K114">
-        <v>82.78543417366947</v>
+        <v>81.84942286375633</v>
       </c>
       <c r="L114">
         <v>78.0739058083943</v>
@@ -8132,7 +8132,7 @@
         </is>
       </c>
       <c r="S114">
-        <v>-4.711528365275164</v>
+        <v>-3.775517055362032</v>
       </c>
     </row>
     <row r="115">
@@ -8177,7 +8177,7 @@
         <v>1</v>
       </c>
       <c r="K115">
-        <v>82.78543417366947</v>
+        <v>81.84942286375633</v>
       </c>
       <c r="L115">
         <v>78.0739058083943</v>
@@ -8200,7 +8200,7 @@
         </is>
       </c>
       <c r="S115">
-        <v>-4.382327135434694</v>
+        <v>-3.446315825521562</v>
       </c>
     </row>
     <row r="116">
@@ -8245,7 +8245,7 @@
         <v>1</v>
       </c>
       <c r="K116">
-        <v>82.78543417366947</v>
+        <v>81.84942286375633</v>
       </c>
       <c r="L116">
         <v>78.0739058083943</v>
@@ -8268,7 +8268,7 @@
         </is>
       </c>
       <c r="S116">
-        <v>-0.8086498910110373</v>
+        <v>0.1273614189020944</v>
       </c>
     </row>
     <row r="117">
@@ -8313,7 +8313,7 @@
         <v>1</v>
       </c>
       <c r="K117">
-        <v>82.78543417366947</v>
+        <v>81.84942286375633</v>
       </c>
       <c r="L117">
         <v>78.0739058083943</v>
@@ -8336,7 +8336,7 @@
         </is>
       </c>
       <c r="S117">
-        <v>-3.927291071616756</v>
+        <v>-2.991279761703625</v>
       </c>
     </row>
     <row r="118">
@@ -8632,7 +8632,7 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>50-59</t>
+          <t>18-29</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -8653,19 +8653,19 @@
         <v>0</v>
       </c>
       <c r="K122">
-        <v>19.3715999472884</v>
+        <v>21.31743571607208</v>
       </c>
       <c r="L122">
-        <v>24.9637847254057</v>
+        <v>14.39625928302925</v>
       </c>
       <c r="M122">
-        <v>19.55956107979261</v>
+        <v>21.36018528433921</v>
       </c>
       <c r="N122">
-        <v>18.78381922591102</v>
+        <v>21.31738426079025</v>
       </c>
       <c r="O122">
-        <v>18.78376405592434</v>
+        <v>21.31743571607218</v>
       </c>
       <c r="P122">
         <v>54535</v>
@@ -8676,7 +8676,7 @@
         </is>
       </c>
       <c r="S122">
-        <v>5.592184778117298</v>
+        <v>-6.921176433042827</v>
       </c>
     </row>
     <row r="123">
@@ -8700,7 +8700,7 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>50-59</t>
+          <t>18-29</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -8721,19 +8721,19 @@
         <v>0</v>
       </c>
       <c r="K123">
-        <v>19.3715999472884</v>
+        <v>21.31743571607208</v>
       </c>
       <c r="L123">
-        <v>24.9637847254057</v>
+        <v>14.39625928302925</v>
       </c>
       <c r="M123">
-        <v>19.55956107979261</v>
+        <v>21.36018528433921</v>
       </c>
       <c r="N123">
-        <v>18.78381922591102</v>
+        <v>21.31738426079025</v>
       </c>
       <c r="O123">
-        <v>18.78376405592434</v>
+        <v>21.31743571607218</v>
       </c>
       <c r="P123">
         <v>54535</v>
@@ -8744,7 +8744,7 @@
         </is>
       </c>
       <c r="S123">
-        <v>0.1879611325042052</v>
+        <v>0.04274956826713083</v>
       </c>
     </row>
     <row r="124">
@@ -8768,7 +8768,7 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>50-59</t>
+          <t>18-29</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -8789,19 +8789,19 @@
         <v>0</v>
       </c>
       <c r="K124">
-        <v>19.3715999472884</v>
+        <v>21.31743571607208</v>
       </c>
       <c r="L124">
-        <v>24.9637847254057</v>
+        <v>14.39625928302925</v>
       </c>
       <c r="M124">
-        <v>19.55956107979261</v>
+        <v>21.36018528433921</v>
       </c>
       <c r="N124">
-        <v>18.78381922591102</v>
+        <v>21.31738426079025</v>
       </c>
       <c r="O124">
-        <v>18.78376405592434</v>
+        <v>21.31743571607218</v>
       </c>
       <c r="P124">
         <v>54535</v>
@@ -8812,7 +8812,7 @@
         </is>
       </c>
       <c r="S124">
-        <v>-0.5877807213773845</v>
+        <v>-5.145528182426418E-05</v>
       </c>
     </row>
     <row r="125">
@@ -8836,7 +8836,7 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>50-59</t>
+          <t>18-29</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -8857,19 +8857,19 @@
         <v>0</v>
       </c>
       <c r="K125">
-        <v>19.3715999472884</v>
+        <v>21.31743571607208</v>
       </c>
       <c r="L125">
-        <v>24.9637847254057</v>
+        <v>14.39625928302925</v>
       </c>
       <c r="M125">
-        <v>19.55956107979261</v>
+        <v>21.36018528433921</v>
       </c>
       <c r="N125">
-        <v>18.78381922591102</v>
+        <v>21.31738426079025</v>
       </c>
       <c r="O125">
-        <v>18.78376405592434</v>
+        <v>21.31743571607218</v>
       </c>
       <c r="P125">
         <v>54535</v>
@@ -8880,7 +8880,7 @@
         </is>
       </c>
       <c r="S125">
-        <v>-0.5878358913640636</v>
+        <v>1.054711873393899E-13</v>
       </c>
     </row>
     <row r="126">
@@ -8925,7 +8925,7 @@
         <v>0</v>
       </c>
       <c r="K126">
-        <v>30.67461114142716</v>
+        <v>30.53774451303564</v>
       </c>
       <c r="L126">
         <v>25.33235536811222</v>
@@ -8948,7 +8948,7 @@
         </is>
       </c>
       <c r="S126">
-        <v>-5.342255773314935</v>
+        <v>-5.205389144923423</v>
       </c>
     </row>
     <row r="127">
@@ -8993,7 +8993,7 @@
         <v>0</v>
       </c>
       <c r="K127">
-        <v>30.67461114142716</v>
+        <v>30.53774451303564</v>
       </c>
       <c r="L127">
         <v>25.33235536811222</v>
@@ -9016,7 +9016,7 @@
         </is>
       </c>
       <c r="S127">
-        <v>-0.1780173546935215</v>
+        <v>-0.04115072630200833</v>
       </c>
     </row>
     <row r="128">
@@ -9061,7 +9061,7 @@
         <v>0</v>
       </c>
       <c r="K128">
-        <v>30.67461114142716</v>
+        <v>30.53774451303564</v>
       </c>
       <c r="L128">
         <v>25.33235536811222</v>
@@ -9084,7 +9084,7 @@
         </is>
       </c>
       <c r="S128">
-        <v>-0.1367483492705823</v>
+        <v>0.0001182791209308753</v>
       </c>
     </row>
     <row r="129">
@@ -9129,7 +9129,7 @@
         <v>0</v>
       </c>
       <c r="K129">
-        <v>30.67461114142716</v>
+        <v>30.53774451303564</v>
       </c>
       <c r="L129">
         <v>25.33235536811222</v>
@@ -9152,7 +9152,7 @@
         </is>
       </c>
       <c r="S129">
-        <v>-0.136866628391713</v>
+        <v>-1.998401444325282E-13</v>
       </c>
     </row>
     <row r="130">
@@ -9197,7 +9197,7 @@
         <v>0</v>
       </c>
       <c r="K130">
-        <v>60.86367419280947</v>
+        <v>60.07051969567413</v>
       </c>
       <c r="L130">
         <v>44.92527734482443</v>
@@ -9220,7 +9220,7 @@
         </is>
       </c>
       <c r="S130">
-        <v>-15.93839684798504</v>
+        <v>-15.1452423508497</v>
       </c>
     </row>
     <row r="131">
@@ -9265,7 +9265,7 @@
         <v>0</v>
       </c>
       <c r="K131">
-        <v>60.86367419280947</v>
+        <v>60.07051969567413</v>
       </c>
       <c r="L131">
         <v>44.92527734482443</v>
@@ -9288,7 +9288,7 @@
         </is>
       </c>
       <c r="S131">
-        <v>-14.82283750640757</v>
+        <v>-14.02968300927223</v>
       </c>
     </row>
     <row r="132">
@@ -9333,7 +9333,7 @@
         <v>0</v>
       </c>
       <c r="K132">
-        <v>60.86367419280947</v>
+        <v>60.07051969567413</v>
       </c>
       <c r="L132">
         <v>44.92527734482443</v>
@@ -9356,7 +9356,7 @@
         </is>
       </c>
       <c r="S132">
-        <v>-0.7931925941980889</v>
+        <v>-3.809706274893188E-05</v>
       </c>
     </row>
     <row r="133">
@@ -9401,7 +9401,7 @@
         <v>0</v>
       </c>
       <c r="K133">
-        <v>60.86367419280947</v>
+        <v>60.07051969567413</v>
       </c>
       <c r="L133">
         <v>44.92527734482443</v>
@@ -9424,7 +9424,7 @@
         </is>
       </c>
       <c r="S133">
-        <v>-0.7931544971356175</v>
+        <v>-2.775557561562891E-13</v>
       </c>
     </row>
     <row r="134">
@@ -9469,7 +9469,7 @@
         <v>0</v>
       </c>
       <c r="K134">
-        <v>23.46400089857351</v>
+        <v>22.80764277056749</v>
       </c>
       <c r="L134">
         <v>24.05985224758963</v>
@@ -9492,7 +9492,7 @@
         </is>
       </c>
       <c r="S134">
-        <v>0.5958513490161188</v>
+        <v>1.252209477022145</v>
       </c>
     </row>
     <row r="135">
@@ -9537,7 +9537,7 @@
         <v>0</v>
       </c>
       <c r="K135">
-        <v>23.46400089857351</v>
+        <v>22.80764277056749</v>
       </c>
       <c r="L135">
         <v>24.05985224758963</v>
@@ -9560,7 +9560,7 @@
         </is>
       </c>
       <c r="S135">
-        <v>-1.245702490336381</v>
+        <v>-0.5893443623303546</v>
       </c>
     </row>
     <row r="136">
@@ -9605,7 +9605,7 @@
         <v>0</v>
       </c>
       <c r="K136">
-        <v>23.46400089857351</v>
+        <v>22.80764277056749</v>
       </c>
       <c r="L136">
         <v>24.05985224758963</v>
@@ -9628,7 +9628,7 @@
         </is>
       </c>
       <c r="S136">
-        <v>-0.6564727659101488</v>
+        <v>-0.0001146379041222501</v>
       </c>
     </row>
     <row r="137">
@@ -9673,7 +9673,7 @@
         <v>0</v>
       </c>
       <c r="K137">
-        <v>23.46400089857351</v>
+        <v>22.80764277056749</v>
       </c>
       <c r="L137">
         <v>24.05985224758963</v>
@@ -9696,7 +9696,7 @@
         </is>
       </c>
       <c r="S137">
-        <v>-0.6563581280059488</v>
+        <v>7.771561172376096E-14</v>
       </c>
     </row>
     <row r="138">
@@ -9741,7 +9741,7 @@
         <v>1</v>
       </c>
       <c r="K138">
-        <v>91.66732261353998</v>
+        <v>89.0572167868261</v>
       </c>
       <c r="L138">
         <v>97.08795799021362</v>
@@ -9764,7 +9764,7 @@
         </is>
       </c>
       <c r="S138">
-        <v>5.420635376673644</v>
+        <v>8.030741203387526</v>
       </c>
     </row>
     <row r="139">
@@ -9809,7 +9809,7 @@
         <v>1</v>
       </c>
       <c r="K139">
-        <v>91.66732261353998</v>
+        <v>89.0572167868261</v>
       </c>
       <c r="L139">
         <v>97.08795799021362</v>
@@ -9832,7 +9832,7 @@
         </is>
       </c>
       <c r="S139">
-        <v>6.036209246809332</v>
+        <v>8.646315073523214</v>
       </c>
     </row>
     <row r="140">
@@ -9877,7 +9877,7 @@
         <v>1</v>
       </c>
       <c r="K140">
-        <v>91.66732261353998</v>
+        <v>89.0572167868261</v>
       </c>
       <c r="L140">
         <v>97.08795799021362</v>
@@ -9900,7 +9900,7 @@
         </is>
       </c>
       <c r="S140">
-        <v>-2.609675776510767</v>
+        <v>0.000430050203115151</v>
       </c>
     </row>
     <row r="141">
@@ -9945,7 +9945,7 @@
         <v>1</v>
       </c>
       <c r="K141">
-        <v>91.66732261353998</v>
+        <v>89.0572167868261</v>
       </c>
       <c r="L141">
         <v>97.08795799021362</v>
@@ -9968,7 +9968,7 @@
         </is>
       </c>
       <c r="S141">
-        <v>4.872368513626912</v>
+        <v>7.482474340340795</v>
       </c>
     </row>
     <row r="142">
@@ -10013,7 +10013,7 @@
         <v>1</v>
       </c>
       <c r="K142">
-        <v>63.01267889732014</v>
+        <v>61.88492946075386</v>
       </c>
       <c r="L142">
         <v>66.85958916694227</v>
@@ -10036,7 +10036,7 @@
         </is>
       </c>
       <c r="S142">
-        <v>3.846910269622128</v>
+        <v>4.974659706188412</v>
       </c>
     </row>
     <row r="143">
@@ -10081,7 +10081,7 @@
         <v>1</v>
       </c>
       <c r="K143">
-        <v>63.01267889732014</v>
+        <v>61.88492946075386</v>
       </c>
       <c r="L143">
         <v>66.85958916694227</v>
@@ -10104,7 +10104,7 @@
         </is>
       </c>
       <c r="S143">
-        <v>-2.845000305011802</v>
+        <v>-1.717250868445519</v>
       </c>
     </row>
     <row r="144">
@@ -10149,7 +10149,7 @@
         <v>1</v>
       </c>
       <c r="K144">
-        <v>63.01267889732014</v>
+        <v>61.88492946075386</v>
       </c>
       <c r="L144">
         <v>66.85958916694227</v>
@@ -10172,7 +10172,7 @@
         </is>
       </c>
       <c r="S144">
-        <v>-1.127829715025552</v>
+        <v>-8.027845926905641E-05</v>
       </c>
     </row>
     <row r="145">
@@ -10217,7 +10217,7 @@
         <v>1</v>
       </c>
       <c r="K145">
-        <v>63.01267889732014</v>
+        <v>61.88492946075386</v>
       </c>
       <c r="L145">
         <v>66.85958916694227</v>
@@ -10240,7 +10240,7 @@
         </is>
       </c>
       <c r="S145">
-        <v>-1.535404302904275</v>
+        <v>-0.407654866337992</v>
       </c>
     </row>
     <row r="146">
@@ -10285,7 +10285,7 @@
         <v>0</v>
       </c>
       <c r="K146">
-        <v>52.29237954825455</v>
+        <v>52.1042074369422</v>
       </c>
       <c r="L146">
         <v>53.07600623452829</v>
@@ -10308,7 +10308,7 @@
         </is>
       </c>
       <c r="S146">
-        <v>0.7836266862737307</v>
+        <v>0.9717987975860765</v>
       </c>
     </row>
     <row r="147">
@@ -10353,7 +10353,7 @@
         <v>0</v>
       </c>
       <c r="K147">
-        <v>52.29237954825455</v>
+        <v>52.1042074369422</v>
       </c>
       <c r="L147">
         <v>53.07600623452829</v>
@@ -10376,7 +10376,7 @@
         </is>
       </c>
       <c r="S147">
-        <v>-0.4726698574450183</v>
+        <v>-0.2844977461326725</v>
       </c>
     </row>
     <row r="148">
@@ -10421,7 +10421,7 @@
         <v>0</v>
       </c>
       <c r="K148">
-        <v>52.29237954825455</v>
+        <v>52.1042074369422</v>
       </c>
       <c r="L148">
         <v>53.07600623452829</v>
@@ -10444,7 +10444,7 @@
         </is>
       </c>
       <c r="S148">
-        <v>-0.188219283370572</v>
+        <v>-4.717205822624138E-05</v>
       </c>
     </row>
     <row r="149">
@@ -10489,7 +10489,7 @@
         <v>0</v>
       </c>
       <c r="K149">
-        <v>52.29237954825455</v>
+        <v>52.1042074369422</v>
       </c>
       <c r="L149">
         <v>53.07600623452829</v>
@@ -10512,7 +10512,7 @@
         </is>
       </c>
       <c r="S149">
-        <v>1.419421468741955</v>
+        <v>1.607593580054301</v>
       </c>
     </row>
     <row r="150">
@@ -10557,7 +10557,7 @@
         <v>1</v>
       </c>
       <c r="K150">
-        <v>88.07339449541286</v>
+        <v>88.10966117041913</v>
       </c>
       <c r="L150">
         <v>93.45258930380797</v>
@@ -10580,7 +10580,7 @@
         </is>
       </c>
       <c r="S150">
-        <v>5.379194808395116</v>
+        <v>5.342928133388836</v>
       </c>
     </row>
     <row r="151">
@@ -10625,7 +10625,7 @@
         <v>1</v>
       </c>
       <c r="K151">
-        <v>88.07339449541286</v>
+        <v>88.10966117041913</v>
       </c>
       <c r="L151">
         <v>93.45258930380797</v>
@@ -10648,7 +10648,7 @@
         </is>
       </c>
       <c r="S151">
-        <v>5.780672732864667</v>
+        <v>5.744406057858386</v>
       </c>
     </row>
     <row r="152">
@@ -10693,7 +10693,7 @@
         <v>1</v>
       </c>
       <c r="K152">
-        <v>88.07339449541286</v>
+        <v>88.10966117041913</v>
       </c>
       <c r="L152">
         <v>93.45258930380797</v>
@@ -10716,7 +10716,7 @@
         </is>
       </c>
       <c r="S152">
-        <v>0.03641639628391147</v>
+        <v>0.0001497212776313539</v>
       </c>
     </row>
     <row r="153">
@@ -10761,7 +10761,7 @@
         <v>1</v>
       </c>
       <c r="K153">
-        <v>88.07339449541286</v>
+        <v>88.10966117041913</v>
       </c>
       <c r="L153">
         <v>93.45258930380797</v>
@@ -10784,7 +10784,7 @@
         </is>
       </c>
       <c r="S153">
-        <v>4.742620402666731</v>
+        <v>4.706353727660451</v>
       </c>
     </row>
     <row r="154">
@@ -10829,7 +10829,7 @@
         <v>1</v>
       </c>
       <c r="K154">
-        <v>89.95384253150836</v>
+        <v>90.59652362851101</v>
       </c>
       <c r="L154">
         <v>82.55400300729821</v>
@@ -10852,7 +10852,7 @@
         </is>
       </c>
       <c r="S154">
-        <v>-7.39983952421015</v>
+        <v>-8.042520621212802</v>
       </c>
     </row>
     <row r="155">
@@ -10897,7 +10897,7 @@
         <v>1</v>
       </c>
       <c r="K155">
-        <v>89.95384253150836</v>
+        <v>90.59652362851101</v>
       </c>
       <c r="L155">
         <v>82.55400300729821</v>
@@ -10920,7 +10920,7 @@
         </is>
       </c>
       <c r="S155">
-        <v>-2.321831960985865</v>
+        <v>-2.964513057988516</v>
       </c>
     </row>
     <row r="156">
@@ -10965,7 +10965,7 @@
         <v>1</v>
       </c>
       <c r="K156">
-        <v>89.95384253150836</v>
+        <v>90.59652362851101</v>
       </c>
       <c r="L156">
         <v>82.55400300729821</v>
@@ -10988,7 +10988,7 @@
         </is>
       </c>
       <c r="S156">
-        <v>0.642575343198637</v>
+        <v>-0.0001057538040138972</v>
       </c>
     </row>
     <row r="157">
@@ -11033,7 +11033,7 @@
         <v>1</v>
       </c>
       <c r="K157">
-        <v>89.95384253150836</v>
+        <v>90.59652362851101</v>
       </c>
       <c r="L157">
         <v>82.55400300729821</v>
@@ -11056,7 +11056,7 @@
         </is>
       </c>
       <c r="S157">
-        <v>-3.497815999620613</v>
+        <v>-4.140497096623264</v>
       </c>
     </row>
     <row r="158">
@@ -11101,7 +11101,7 @@
         <v>1</v>
       </c>
       <c r="K158">
-        <v>81.98066168047976</v>
+        <v>81.45049616276734</v>
       </c>
       <c r="L158">
         <v>75.76938549733481</v>
@@ -11124,7 +11124,7 @@
         </is>
       </c>
       <c r="S158">
-        <v>-6.211276183144943</v>
+        <v>-5.681110665432532</v>
       </c>
     </row>
     <row r="159">
@@ -11169,7 +11169,7 @@
         <v>1</v>
       </c>
       <c r="K159">
-        <v>81.98066168047976</v>
+        <v>81.45049616276734</v>
       </c>
       <c r="L159">
         <v>75.76938549733481</v>
@@ -11192,7 +11192,7 @@
         </is>
       </c>
       <c r="S159">
-        <v>-4.836642063890039</v>
+        <v>-4.306476546177629</v>
       </c>
     </row>
     <row r="160">
@@ -11237,7 +11237,7 @@
         <v>1</v>
       </c>
       <c r="K160">
-        <v>81.98066168047976</v>
+        <v>81.45049616276734</v>
       </c>
       <c r="L160">
         <v>75.76938549733481</v>
@@ -11260,7 +11260,7 @@
         </is>
       </c>
       <c r="S160">
-        <v>-0.5301548422915969</v>
+        <v>1.067542081401029E-05</v>
       </c>
     </row>
     <row r="161">
@@ -11305,7 +11305,7 @@
         <v>1</v>
       </c>
       <c r="K161">
-        <v>81.98066168047976</v>
+        <v>81.45049616276734</v>
       </c>
       <c r="L161">
         <v>75.76938549733481</v>
@@ -11328,7 +11328,7 @@
         </is>
       </c>
       <c r="S161">
-        <v>-4.492249589525443</v>
+        <v>-3.962084071813032</v>
       </c>
     </row>
     <row r="162">
@@ -11624,7 +11624,7 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>50-59</t>
+          <t>18-29</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
@@ -11645,19 +11645,19 @@
         <v>0</v>
       </c>
       <c r="K166">
-        <v>19.2144759724393</v>
+        <v>21.22698328526761</v>
       </c>
       <c r="L166">
-        <v>22.94306049822064</v>
+        <v>17.77758007117438</v>
       </c>
       <c r="M166">
-        <v>18.87289580050048</v>
+        <v>21.59593382066384</v>
       </c>
       <c r="N166">
-        <v>18.59235097750854</v>
+        <v>21.22698242643645</v>
       </c>
       <c r="O166">
-        <v>18.59235067238975</v>
+        <v>21.22698328526814</v>
       </c>
       <c r="P166">
         <v>56200</v>
@@ -11668,7 +11668,7 @@
         </is>
       </c>
       <c r="S166">
-        <v>3.728584525781342</v>
+        <v>-3.449403214093236</v>
       </c>
     </row>
     <row r="167">
@@ -11692,7 +11692,7 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>50-59</t>
+          <t>18-29</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
@@ -11713,19 +11713,19 @@
         <v>0</v>
       </c>
       <c r="K167">
-        <v>19.2144759724393</v>
+        <v>21.22698328526761</v>
       </c>
       <c r="L167">
-        <v>22.94306049822064</v>
+        <v>17.77758007117438</v>
       </c>
       <c r="M167">
-        <v>18.87289580050048</v>
+        <v>21.59593382066384</v>
       </c>
       <c r="N167">
-        <v>18.59235097750854</v>
+        <v>21.22698242643645</v>
       </c>
       <c r="O167">
-        <v>18.59235067238975</v>
+        <v>21.22698328526814</v>
       </c>
       <c r="P167">
         <v>56200</v>
@@ -11736,7 +11736,7 @@
         </is>
       </c>
       <c r="S167">
-        <v>-0.3415801719388156</v>
+        <v>0.3689505353962286</v>
       </c>
     </row>
     <row r="168">
@@ -11760,7 +11760,7 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>50-59</t>
+          <t>18-29</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
@@ -11781,19 +11781,19 @@
         <v>0</v>
       </c>
       <c r="K168">
-        <v>19.2144759724393</v>
+        <v>21.22698328526761</v>
       </c>
       <c r="L168">
-        <v>22.94306049822064</v>
+        <v>17.77758007117438</v>
       </c>
       <c r="M168">
-        <v>18.87289580050048</v>
+        <v>21.59593382066384</v>
       </c>
       <c r="N168">
-        <v>18.59235097750854</v>
+        <v>21.22698242643645</v>
       </c>
       <c r="O168">
-        <v>18.59235067238975</v>
+        <v>21.22698328526814</v>
       </c>
       <c r="P168">
         <v>56200</v>
@@ -11804,7 +11804,7 @@
         </is>
       </c>
       <c r="S168">
-        <v>-0.6221249949307561</v>
+        <v>-8.588311645185698E-07</v>
       </c>
     </row>
     <row r="169">
@@ -11828,7 +11828,7 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>50-59</t>
+          <t>18-29</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
@@ -11849,19 +11849,19 @@
         <v>0</v>
       </c>
       <c r="K169">
-        <v>19.2144759724393</v>
+        <v>21.22698328526761</v>
       </c>
       <c r="L169">
-        <v>22.94306049822064</v>
+        <v>17.77758007117438</v>
       </c>
       <c r="M169">
-        <v>18.87289580050048</v>
+        <v>21.59593382066384</v>
       </c>
       <c r="N169">
-        <v>18.59235097750854</v>
+        <v>21.22698242643645</v>
       </c>
       <c r="O169">
-        <v>18.59235067238975</v>
+        <v>21.22698328526814</v>
       </c>
       <c r="P169">
         <v>56200</v>
@@ -11872,7 +11872,7 @@
         </is>
       </c>
       <c r="S169">
-        <v>-0.6221253000495502</v>
+        <v>5.245803791353865E-13</v>
       </c>
     </row>
     <row r="170">
@@ -11917,7 +11917,7 @@
         <v>0</v>
       </c>
       <c r="K170">
-        <v>30.39425892090607</v>
+        <v>30.21566715129605</v>
       </c>
       <c r="L170">
         <v>27.94128113879004</v>
@@ -11940,7 +11940,7 @@
         </is>
       </c>
       <c r="S170">
-        <v>-2.452977782116034</v>
+        <v>-2.274386012506013</v>
       </c>
     </row>
     <row r="171">
@@ -11985,7 +11985,7 @@
         <v>0</v>
       </c>
       <c r="K171">
-        <v>30.39425892090607</v>
+        <v>30.21566715129605</v>
       </c>
       <c r="L171">
         <v>27.94128113879004</v>
@@ -12008,7 +12008,7 @@
         </is>
       </c>
       <c r="S171">
-        <v>1.095493037841716</v>
+        <v>1.274084807451736</v>
       </c>
     </row>
     <row r="172">
@@ -12053,7 +12053,7 @@
         <v>0</v>
       </c>
       <c r="K172">
-        <v>30.39425892090607</v>
+        <v>30.21566715129605</v>
       </c>
       <c r="L172">
         <v>27.94128113879004</v>
@@ -12076,7 +12076,7 @@
         </is>
       </c>
       <c r="S172">
-        <v>-0.1785991280642607</v>
+        <v>-7.358454240380397E-06</v>
       </c>
     </row>
     <row r="173">
@@ -12121,7 +12121,7 @@
         <v>0</v>
       </c>
       <c r="K173">
-        <v>30.39425892090607</v>
+        <v>30.21566715129605</v>
       </c>
       <c r="L173">
         <v>27.94128113879004</v>
@@ -12144,7 +12144,7 @@
         </is>
       </c>
       <c r="S173">
-        <v>-0.1785917696101313</v>
+        <v>-1.110223024625157E-13</v>
       </c>
     </row>
     <row r="174">
@@ -12189,7 +12189,7 @@
         <v>0</v>
       </c>
       <c r="K174">
-        <v>60.76245404715257</v>
+        <v>60.37577965233139</v>
       </c>
       <c r="L174">
         <v>49.47952810548231</v>
@@ -12212,7 +12212,7 @@
         </is>
       </c>
       <c r="S174">
-        <v>-11.28292594167026</v>
+        <v>-10.89625154684908</v>
       </c>
     </row>
     <row r="175">
@@ -12257,7 +12257,7 @@
         <v>0</v>
       </c>
       <c r="K175">
-        <v>60.76245404715257</v>
+        <v>60.37577965233139</v>
       </c>
       <c r="L175">
         <v>49.47952810548231</v>
@@ -12280,7 +12280,7 @@
         </is>
       </c>
       <c r="S175">
-        <v>-12.42113780896157</v>
+        <v>-12.03446341414038</v>
       </c>
     </row>
     <row r="176">
@@ -12325,7 +12325,7 @@
         <v>0</v>
       </c>
       <c r="K176">
-        <v>60.76245404715257</v>
+        <v>60.37577965233139</v>
       </c>
       <c r="L176">
         <v>49.47952810548231</v>
@@ -12348,7 +12348,7 @@
         </is>
       </c>
       <c r="S176">
-        <v>-0.3866732388689953</v>
+        <v>1.155952189524356E-06</v>
       </c>
     </row>
     <row r="177">
@@ -12393,7 +12393,7 @@
         <v>0</v>
       </c>
       <c r="K177">
-        <v>60.76245404715257</v>
+        <v>60.37577965233139</v>
       </c>
       <c r="L177">
         <v>49.47952810548231</v>
@@ -12416,7 +12416,7 @@
         </is>
       </c>
       <c r="S177">
-        <v>-0.3866743948207296</v>
+        <v>4.551914400963142E-13</v>
       </c>
     </row>
     <row r="178">
@@ -12461,7 +12461,7 @@
         <v>0</v>
       </c>
       <c r="K178">
-        <v>23.5069892354767</v>
+        <v>22.97492199572419</v>
       </c>
       <c r="L178">
         <v>24.37456043403999</v>
@@ -12484,7 +12484,7 @@
         </is>
       </c>
       <c r="S178">
-        <v>0.8675711985632883</v>
+        <v>1.399638438315798</v>
       </c>
     </row>
     <row r="179">
@@ -12529,7 +12529,7 @@
         <v>0</v>
       </c>
       <c r="K179">
-        <v>23.5069892354767</v>
+        <v>22.97492199572419</v>
       </c>
       <c r="L179">
         <v>24.37456043403999</v>
@@ -12552,7 +12552,7 @@
         </is>
       </c>
       <c r="S179">
-        <v>-0.02427051737503849</v>
+        <v>0.507796722377471</v>
       </c>
     </row>
     <row r="180">
@@ -12597,7 +12597,7 @@
         <v>0</v>
       </c>
       <c r="K180">
-        <v>23.5069892354767</v>
+        <v>22.97492199572419</v>
       </c>
       <c r="L180">
         <v>24.37456043403999</v>
@@ -12620,7 +12620,7 @@
         </is>
       </c>
       <c r="S180">
-        <v>-0.5320684992069724</v>
+        <v>-1.259454462942955E-06</v>
       </c>
     </row>
     <row r="181">
@@ -12665,7 +12665,7 @@
         <v>0</v>
       </c>
       <c r="K181">
-        <v>23.5069892354767</v>
+        <v>22.97492199572419</v>
       </c>
       <c r="L181">
         <v>24.37456043403999</v>
@@ -12688,7 +12688,7 @@
         </is>
       </c>
       <c r="S181">
-        <v>-0.5320672397529369</v>
+        <v>-4.274358644806853E-13</v>
       </c>
     </row>
     <row r="182">
@@ -12733,7 +12733,7 @@
         <v>1</v>
       </c>
       <c r="K182">
-        <v>91.1347876813349</v>
+        <v>88.59254555058355</v>
       </c>
       <c r="L182">
         <v>96.61712532361683</v>
@@ -12756,7 +12756,7 @@
         </is>
       </c>
       <c r="S182">
-        <v>5.482337642281943</v>
+        <v>8.024579773033292</v>
       </c>
     </row>
     <row r="183">
@@ -12801,7 +12801,7 @@
         <v>1</v>
       </c>
       <c r="K183">
-        <v>91.1347876813349</v>
+        <v>88.59254555058355</v>
       </c>
       <c r="L183">
         <v>96.61712532361683</v>
@@ -12824,7 +12824,7 @@
         </is>
       </c>
       <c r="S183">
-        <v>5.675031768162331</v>
+        <v>8.21727389891368</v>
       </c>
     </row>
     <row r="184">
@@ -12869,7 +12869,7 @@
         <v>1</v>
       </c>
       <c r="K184">
-        <v>91.1347876813349</v>
+        <v>88.59254555058355</v>
       </c>
       <c r="L184">
         <v>96.61712532361683</v>
@@ -12892,7 +12892,7 @@
         </is>
       </c>
       <c r="S184">
-        <v>-2.542235706831963</v>
+        <v>6.423919385323273E-06</v>
       </c>
     </row>
     <row r="185">
@@ -12937,7 +12937,7 @@
         <v>1</v>
       </c>
       <c r="K185">
-        <v>91.1347876813349</v>
+        <v>88.59254555058355</v>
       </c>
       <c r="L185">
         <v>96.61712532361683</v>
@@ -12960,7 +12960,7 @@
         </is>
       </c>
       <c r="S185">
-        <v>5.148365909188679</v>
+        <v>7.690608039940027</v>
       </c>
     </row>
     <row r="186">
@@ -13005,7 +13005,7 @@
         <v>1</v>
       </c>
       <c r="K186">
-        <v>62.04143288735434</v>
+        <v>60.62870890285603</v>
       </c>
       <c r="L186">
         <v>63.47000231642345</v>
@@ -13028,7 +13028,7 @@
         </is>
       </c>
       <c r="S186">
-        <v>1.428569429069104</v>
+        <v>2.841293413567414</v>
       </c>
     </row>
     <row r="187">
@@ -13073,7 +13073,7 @@
         <v>1</v>
       </c>
       <c r="K187">
-        <v>62.04143288735434</v>
+        <v>60.62870890285603</v>
       </c>
       <c r="L187">
         <v>63.47000231642345</v>
@@ -13096,7 +13096,7 @@
         </is>
       </c>
       <c r="S187">
-        <v>-0.07315682812987223</v>
+        <v>1.339567156368437</v>
       </c>
     </row>
     <row r="188">
@@ -13141,7 +13141,7 @@
         <v>1</v>
       </c>
       <c r="K188">
-        <v>62.04143288735434</v>
+        <v>60.62870890285603</v>
       </c>
       <c r="L188">
         <v>63.47000231642345</v>
@@ -13164,7 +13164,7 @@
         </is>
       </c>
       <c r="S188">
-        <v>-1.412722934799582</v>
+        <v>1.049698727939585E-06</v>
       </c>
     </row>
     <row r="189">
@@ -13209,7 +13209,7 @@
         <v>1</v>
       </c>
       <c r="K189">
-        <v>62.04143288735434</v>
+        <v>60.62870890285603</v>
       </c>
       <c r="L189">
         <v>63.47000231642345</v>
@@ -13232,7 +13232,7 @@
         </is>
       </c>
       <c r="S189">
-        <v>-0.8127482160319</v>
+        <v>0.5999757684664098</v>
       </c>
     </row>
     <row r="190">
@@ -13277,7 +13277,7 @@
         <v>0</v>
       </c>
       <c r="K190">
-        <v>52.29321768992009</v>
+        <v>52.06423858113006</v>
       </c>
       <c r="L190">
         <v>53.23309608540925</v>
@@ -13300,7 +13300,7 @@
         </is>
       </c>
       <c r="S190">
-        <v>0.9398783954891576</v>
+        <v>1.168857504279186</v>
       </c>
     </row>
     <row r="191">
@@ -13345,7 +13345,7 @@
         <v>0</v>
       </c>
       <c r="K191">
-        <v>52.29321768992009</v>
+        <v>52.06423858113006</v>
       </c>
       <c r="L191">
         <v>53.23309608540925</v>
@@ -13368,7 +13368,7 @@
         </is>
       </c>
       <c r="S191">
-        <v>-0.5107772096967889</v>
+        <v>-0.2817981009067605</v>
       </c>
     </row>
     <row r="192">
@@ -13413,7 +13413,7 @@
         <v>0</v>
       </c>
       <c r="K192">
-        <v>52.29321768992009</v>
+        <v>52.06423858113006</v>
       </c>
       <c r="L192">
         <v>53.23309608540925</v>
@@ -13436,7 +13436,7 @@
         </is>
       </c>
       <c r="S192">
-        <v>-0.2289791087903281</v>
+        <v>-2.997602166487923E-13</v>
       </c>
     </row>
     <row r="193">
@@ -13481,7 +13481,7 @@
         <v>0</v>
       </c>
       <c r="K193">
-        <v>52.29321768992009</v>
+        <v>52.06423858113006</v>
       </c>
       <c r="L193">
         <v>53.23309608540925</v>
@@ -13504,7 +13504,7 @@
         </is>
       </c>
       <c r="S193">
-        <v>1.068146201369269</v>
+        <v>1.297125310159297</v>
       </c>
     </row>
     <row r="194">
@@ -13549,7 +13549,7 @@
         <v>1</v>
       </c>
       <c r="K194">
-        <v>88.30997332775482</v>
+        <v>88.30666955144444</v>
       </c>
       <c r="L194">
         <v>93.09120747783585</v>
@@ -13572,7 +13572,7 @@
         </is>
       </c>
       <c r="S194">
-        <v>4.781234150081026</v>
+        <v>4.784537926391408</v>
       </c>
     </row>
     <row r="195">
@@ -13617,7 +13617,7 @@
         <v>1</v>
       </c>
       <c r="K195">
-        <v>88.30997332775482</v>
+        <v>88.30666955144444</v>
       </c>
       <c r="L195">
         <v>93.09120747783585</v>
@@ -13640,7 +13640,7 @@
         </is>
       </c>
       <c r="S195">
-        <v>4.822373246801015</v>
+        <v>4.825677023111396</v>
       </c>
     </row>
     <row r="196">
@@ -13685,7 +13685,7 @@
         <v>1</v>
       </c>
       <c r="K196">
-        <v>88.30997332775482</v>
+        <v>88.30666955144444</v>
       </c>
       <c r="L196">
         <v>93.09120747783585</v>
@@ -13708,7 +13708,7 @@
         </is>
       </c>
       <c r="S196">
-        <v>-0.003301598526983529</v>
+        <v>2.17778339806074E-06</v>
       </c>
     </row>
     <row r="197">
@@ -13753,7 +13753,7 @@
         <v>1</v>
       </c>
       <c r="K197">
-        <v>88.30997332775482</v>
+        <v>88.30666955144444</v>
       </c>
       <c r="L197">
         <v>93.09120747783585</v>
@@ -13776,7 +13776,7 @@
         </is>
       </c>
       <c r="S197">
-        <v>4.156586147279251</v>
+        <v>4.159889923589633</v>
       </c>
     </row>
     <row r="198">
@@ -13821,7 +13821,7 @@
         <v>1</v>
       </c>
       <c r="K198">
-        <v>90.55029913524169</v>
+        <v>91.13465758695089</v>
       </c>
       <c r="L198">
         <v>85.68505338078292</v>
@@ -13844,7 +13844,7 @@
         </is>
       </c>
       <c r="S198">
-        <v>-4.865245754458769</v>
+        <v>-5.449604206167979</v>
       </c>
     </row>
     <row r="199">
@@ -13889,7 +13889,7 @@
         <v>1</v>
       </c>
       <c r="K199">
-        <v>90.55029913524169</v>
+        <v>91.13465758695089</v>
       </c>
       <c r="L199">
         <v>85.68505338078292</v>
@@ -13912,7 +13912,7 @@
         </is>
       </c>
       <c r="S199">
-        <v>-2.660147559375148</v>
+        <v>-3.244506011084358</v>
       </c>
     </row>
     <row r="200">
@@ -13957,7 +13957,7 @@
         <v>1</v>
       </c>
       <c r="K200">
-        <v>90.55029913524169</v>
+        <v>91.13465758695089</v>
       </c>
       <c r="L200">
         <v>85.68505338078292</v>
@@ -13980,7 +13980,7 @@
         </is>
       </c>
       <c r="S200">
-        <v>0.5843534653477422</v>
+        <v>-4.986361468173328E-06</v>
       </c>
     </row>
     <row r="201">
@@ -14025,7 +14025,7 @@
         <v>1</v>
       </c>
       <c r="K201">
-        <v>90.55029913524169</v>
+        <v>91.13465758695089</v>
       </c>
       <c r="L201">
         <v>85.68505338078292</v>
@@ -14048,7 +14048,7 @@
         </is>
       </c>
       <c r="S201">
-        <v>-3.149999339036358</v>
+        <v>-3.734357790745568</v>
       </c>
     </row>
     <row r="202">
@@ -14093,7 +14093,7 @@
         <v>1</v>
       </c>
       <c r="K202">
-        <v>80.29434656477747</v>
+        <v>79.06613982126586</v>
       </c>
       <c r="L202">
         <v>75.07809393991026</v>
@@ -14116,7 +14116,7 @@
         </is>
       </c>
       <c r="S202">
-        <v>-5.216252624867213</v>
+        <v>-3.988045881355595</v>
       </c>
     </row>
     <row r="203">
@@ -14161,7 +14161,7 @@
         <v>1</v>
       </c>
       <c r="K203">
-        <v>80.29434656477747</v>
+        <v>79.06613982126586</v>
       </c>
       <c r="L203">
         <v>75.07809393991026</v>
@@ -14184,7 +14184,7 @@
         </is>
       </c>
       <c r="S203">
-        <v>-3.363234190711606</v>
+        <v>-2.135027447199989</v>
       </c>
     </row>
     <row r="204">
@@ -14229,7 +14229,7 @@
         <v>1</v>
       </c>
       <c r="K204">
-        <v>80.29434656477747</v>
+        <v>79.06613982126586</v>
       </c>
       <c r="L204">
         <v>75.07809393991026</v>
@@ -14252,7 +14252,7 @@
         </is>
       </c>
       <c r="S204">
-        <v>-1.228210898965021</v>
+        <v>-4.155453403598131E-06</v>
       </c>
     </row>
     <row r="205">
@@ -14297,7 +14297,7 @@
         <v>1</v>
       </c>
       <c r="K205">
-        <v>80.29434656477747</v>
+        <v>79.06613982126586</v>
       </c>
       <c r="L205">
         <v>75.07809393991026</v>
@@ -14320,7 +14320,7 @@
         </is>
       </c>
       <c r="S205">
-        <v>-4.329313654334122</v>
+        <v>-3.101106910822504</v>
       </c>
     </row>
     <row r="206">
@@ -14637,7 +14637,7 @@
         <v>0</v>
       </c>
       <c r="K210">
-        <v>18.7024176609912</v>
+        <v>21.03892003378582</v>
       </c>
       <c r="L210">
         <v>17.48297213622291</v>
@@ -14660,7 +14660,7 @@
         </is>
       </c>
       <c r="S210">
-        <v>-1.219445524768287</v>
+        <v>-3.555947897562914</v>
       </c>
     </row>
     <row r="211">
@@ -14705,7 +14705,7 @@
         <v>0</v>
       </c>
       <c r="K211">
-        <v>18.7024176609912</v>
+        <v>21.03892003378582</v>
       </c>
       <c r="L211">
         <v>17.48297213622291</v>
@@ -14728,7 +14728,7 @@
         </is>
       </c>
       <c r="S211">
-        <v>2.853929388603802</v>
+        <v>0.5174270158091743</v>
       </c>
     </row>
     <row r="212">
@@ -14773,7 +14773,7 @@
         <v>0</v>
       </c>
       <c r="K212">
-        <v>18.7024176609912</v>
+        <v>21.03892003378582</v>
       </c>
       <c r="L212">
         <v>17.48297213622291</v>
@@ -14796,7 +14796,7 @@
         </is>
       </c>
       <c r="S212">
-        <v>2.336528220427131</v>
+        <v>2.584763250379485E-05</v>
       </c>
     </row>
     <row r="213">
@@ -14841,7 +14841,7 @@
         <v>0</v>
       </c>
       <c r="K213">
-        <v>18.7024176609912</v>
+        <v>21.03892003378582</v>
       </c>
       <c r="L213">
         <v>17.48297213622291</v>
@@ -14864,7 +14864,7 @@
         </is>
       </c>
       <c r="S213">
-        <v>2.336502372794893</v>
+        <v>2.664535259100376E-13</v>
       </c>
     </row>
     <row r="214">
@@ -14909,7 +14909,7 @@
         <v>0</v>
       </c>
       <c r="K214">
-        <v>29.93573758770166</v>
+        <v>29.4082466350237</v>
       </c>
       <c r="L214">
         <v>25.35758513931888</v>
@@ -14932,7 +14932,7 @@
         </is>
       </c>
       <c r="S214">
-        <v>-4.578152448382777</v>
+        <v>-4.050661495704816</v>
       </c>
     </row>
     <row r="215">
@@ -14977,7 +14977,7 @@
         <v>0</v>
       </c>
       <c r="K215">
-        <v>29.93573758770166</v>
+        <v>29.4082466350237</v>
       </c>
       <c r="L215">
         <v>25.35758513931888</v>
@@ -15000,7 +15000,7 @@
         </is>
       </c>
       <c r="S215">
-        <v>3.276715712389766</v>
+        <v>3.804206665067728</v>
       </c>
     </row>
     <row r="216">
@@ -15045,7 +15045,7 @@
         <v>0</v>
       </c>
       <c r="K216">
-        <v>29.93573758770166</v>
+        <v>29.4082466350237</v>
       </c>
       <c r="L216">
         <v>25.35758513931888</v>
@@ -15068,7 +15068,7 @@
         </is>
       </c>
       <c r="S216">
-        <v>-0.5273932192158104</v>
+        <v>9.773346215102841E-05</v>
       </c>
     </row>
     <row r="217">
@@ -15113,7 +15113,7 @@
         <v>0</v>
       </c>
       <c r="K217">
-        <v>29.93573758770166</v>
+        <v>29.4082466350237</v>
       </c>
       <c r="L217">
         <v>25.35758513931888</v>
@@ -15136,7 +15136,7 @@
         </is>
       </c>
       <c r="S217">
-        <v>-0.5274909526775784</v>
+        <v>3.83026943495679E-13</v>
       </c>
     </row>
     <row r="218">
@@ -15181,7 +15181,7 @@
         <v>0</v>
       </c>
       <c r="K218">
-        <v>60.59623720784735</v>
+        <v>61.1342015656405</v>
       </c>
       <c r="L218">
         <v>53.96904024767802</v>
@@ -15204,7 +15204,7 @@
         </is>
       </c>
       <c r="S218">
-        <v>-6.627196960169323</v>
+        <v>-7.165161317962476</v>
       </c>
     </row>
     <row r="219">
@@ -15249,7 +15249,7 @@
         <v>0</v>
       </c>
       <c r="K219">
-        <v>60.59623720784735</v>
+        <v>61.1342015656405</v>
       </c>
       <c r="L219">
         <v>53.96904024767802</v>
@@ -15272,7 +15272,7 @@
         </is>
       </c>
       <c r="S219">
-        <v>-11.06835640287924</v>
+        <v>-11.60632076067239</v>
       </c>
     </row>
     <row r="220">
@@ -15317,7 +15317,7 @@
         <v>0</v>
       </c>
       <c r="K220">
-        <v>60.59623720784735</v>
+        <v>61.1342015656405</v>
       </c>
       <c r="L220">
         <v>53.96904024767802</v>
@@ -15340,7 +15340,7 @@
         </is>
       </c>
       <c r="S220">
-        <v>0.5377445020277705</v>
+        <v>-0.0002198557653820821</v>
       </c>
     </row>
     <row r="221">
@@ -15385,7 +15385,7 @@
         <v>0</v>
       </c>
       <c r="K221">
-        <v>60.59623720784735</v>
+        <v>61.1342015656405</v>
       </c>
       <c r="L221">
         <v>53.96904024767802</v>
@@ -15408,7 +15408,7 @@
         </is>
       </c>
       <c r="S221">
-        <v>0.5379643577930193</v>
+        <v>-1.332267629550188E-13</v>
       </c>
     </row>
     <row r="222">
@@ -15453,7 +15453,7 @@
         <v>0</v>
       </c>
       <c r="K222">
-        <v>23.53228761674934</v>
+        <v>23.36212016212871</v>
       </c>
       <c r="L222">
         <v>25.54968232924121</v>
@@ -15476,7 +15476,7 @@
         </is>
       </c>
       <c r="S222">
-        <v>2.017394712491866</v>
+        <v>2.187562167112494</v>
       </c>
     </row>
     <row r="223">
@@ -15521,7 +15521,7 @@
         <v>0</v>
       </c>
       <c r="K223">
-        <v>23.53228761674934</v>
+        <v>23.36212016212871</v>
       </c>
       <c r="L223">
         <v>25.54968232924121</v>
@@ -15544,7 +15544,7 @@
         </is>
       </c>
       <c r="S223">
-        <v>-0.1710750415828854</v>
+        <v>-0.000907586962256568</v>
       </c>
     </row>
     <row r="224">
@@ -15589,7 +15589,7 @@
         <v>0</v>
       </c>
       <c r="K224">
-        <v>23.53228761674934</v>
+        <v>23.36212016212871</v>
       </c>
       <c r="L224">
         <v>25.54968232924121</v>
@@ -15612,7 +15612,7 @@
         </is>
       </c>
       <c r="S224">
-        <v>-0.17028602345254</v>
+        <v>-0.0001185688319110811</v>
       </c>
     </row>
     <row r="225">
@@ -15657,7 +15657,7 @@
         <v>0</v>
       </c>
       <c r="K225">
-        <v>23.53228761674934</v>
+        <v>23.36212016212871</v>
       </c>
       <c r="L225">
         <v>25.54968232924121</v>
@@ -15680,7 +15680,7 @@
         </is>
       </c>
       <c r="S225">
-        <v>-0.1701674546210563</v>
+        <v>-4.274358644806853E-13</v>
       </c>
     </row>
     <row r="226">
@@ -15725,7 +15725,7 @@
         <v>1</v>
       </c>
       <c r="K226">
-        <v>90.69937882647361</v>
+        <v>88.0839043719476</v>
       </c>
       <c r="L226">
         <v>96.18427726120034</v>
@@ -15748,7 +15748,7 @@
         </is>
       </c>
       <c r="S226">
-        <v>5.484898434726726</v>
+        <v>8.100372889252739</v>
       </c>
     </row>
     <row r="227">
@@ -15793,7 +15793,7 @@
         <v>1</v>
       </c>
       <c r="K227">
-        <v>90.69937882647361</v>
+        <v>88.0839043719476</v>
       </c>
       <c r="L227">
         <v>96.18427726120034</v>
@@ -15816,7 +15816,7 @@
         </is>
       </c>
       <c r="S227">
-        <v>6.372887020981189</v>
+        <v>8.988361475507201</v>
       </c>
     </row>
     <row r="228">
@@ -15861,7 +15861,7 @@
         <v>1</v>
       </c>
       <c r="K228">
-        <v>90.69937882647361</v>
+        <v>88.0839043719476</v>
       </c>
       <c r="L228">
         <v>96.18427726120034</v>
@@ -15884,7 +15884,7 @@
         </is>
       </c>
       <c r="S228">
-        <v>-2.615236261996057</v>
+        <v>0.0002381925299554943</v>
       </c>
     </row>
     <row r="229">
@@ -15929,7 +15929,7 @@
         <v>1</v>
       </c>
       <c r="K229">
-        <v>90.69937882647361</v>
+        <v>88.0839043719476</v>
       </c>
       <c r="L229">
         <v>96.18427726120034</v>
@@ -15952,7 +15952,7 @@
         </is>
       </c>
       <c r="S229">
-        <v>5.385752705399549</v>
+        <v>8.001227159925561</v>
       </c>
     </row>
     <row r="230">
@@ -15997,7 +15997,7 @@
         <v>1</v>
       </c>
       <c r="K230">
-        <v>60.71463666289982</v>
+        <v>59.78250240986893</v>
       </c>
       <c r="L230">
         <v>61.06167250627887</v>
@@ -16020,7 +16020,7 @@
         </is>
       </c>
       <c r="S230">
-        <v>0.347035843379051</v>
+        <v>1.279170096409943</v>
       </c>
     </row>
     <row r="231">
@@ -16065,7 +16065,7 @@
         <v>1</v>
       </c>
       <c r="K231">
-        <v>60.71463666289982</v>
+        <v>59.78250240986893</v>
       </c>
       <c r="L231">
         <v>61.06167250627887</v>
@@ -16088,7 +16088,7 @@
         </is>
       </c>
       <c r="S231">
-        <v>0.01433663654404338</v>
+        <v>0.9464708895749352</v>
       </c>
     </row>
     <row r="232">
@@ -16133,7 +16133,7 @@
         <v>1</v>
       </c>
       <c r="K232">
-        <v>60.71463666289982</v>
+        <v>59.78250240986893</v>
       </c>
       <c r="L232">
         <v>61.06167250627887</v>
@@ -16156,7 +16156,7 @@
         </is>
       </c>
       <c r="S232">
-        <v>-1.582009644500326</v>
+        <v>-0.6498753914694344</v>
       </c>
     </row>
     <row r="233">
@@ -16201,7 +16201,7 @@
         <v>1</v>
       </c>
       <c r="K233">
-        <v>60.71463666289982</v>
+        <v>59.78250240986893</v>
       </c>
       <c r="L233">
         <v>61.06167250627887</v>
@@ -16224,7 +16224,7 @@
         </is>
       </c>
       <c r="S233">
-        <v>0.6348231903349544</v>
+        <v>1.566957443365846</v>
       </c>
     </row>
     <row r="234">
@@ -16269,7 +16269,7 @@
         <v>0</v>
       </c>
       <c r="K234">
-        <v>52.34741028734862</v>
+        <v>51.98194203929331</v>
       </c>
       <c r="L234">
         <v>54.28637770897833</v>
@@ -16292,7 +16292,7 @@
         </is>
       </c>
       <c r="S234">
-        <v>1.938967421629711</v>
+        <v>2.304435669685023</v>
       </c>
     </row>
     <row r="235">
@@ -16337,7 +16337,7 @@
         <v>0</v>
       </c>
       <c r="K235">
-        <v>52.34741028734862</v>
+        <v>51.98194203929331</v>
       </c>
       <c r="L235">
         <v>54.28637770897833</v>
@@ -16360,7 +16360,7 @@
         </is>
       </c>
       <c r="S235">
-        <v>-0.5760478944512371</v>
+        <v>-0.2105796463959253</v>
       </c>
     </row>
     <row r="236">
@@ -16405,7 +16405,7 @@
         <v>0</v>
       </c>
       <c r="K236">
-        <v>52.34741028734862</v>
+        <v>51.98194203929331</v>
       </c>
       <c r="L236">
         <v>54.28637770897833</v>
@@ -16428,7 +16428,7 @@
         </is>
       </c>
       <c r="S236">
-        <v>-0.365694561214347</v>
+        <v>-0.0002263131590352074</v>
       </c>
     </row>
     <row r="237">
@@ -16473,7 +16473,7 @@
         <v>0</v>
       </c>
       <c r="K237">
-        <v>52.34741028734862</v>
+        <v>51.98194203929331</v>
       </c>
       <c r="L237">
         <v>54.28637770897833</v>
@@ -16496,7 +16496,7 @@
         </is>
       </c>
       <c r="S237">
-        <v>0.6099987695122988</v>
+        <v>0.9754670175676106</v>
       </c>
     </row>
     <row r="238">
@@ -16541,7 +16541,7 @@
         <v>1</v>
       </c>
       <c r="K238">
-        <v>89.05729909652877</v>
+        <v>88.62047920240057</v>
       </c>
       <c r="L238">
         <v>92.5475473922621</v>
@@ -16564,7 +16564,7 @@
         </is>
       </c>
       <c r="S238">
-        <v>3.490248295733345</v>
+        <v>3.927068189861538</v>
       </c>
     </row>
     <row r="239">
@@ -16609,7 +16609,7 @@
         <v>1</v>
       </c>
       <c r="K239">
-        <v>89.05729909652877</v>
+        <v>88.62047920240057</v>
       </c>
       <c r="L239">
         <v>92.5475473922621</v>
@@ -16632,7 +16632,7 @@
         </is>
       </c>
       <c r="S239">
-        <v>4.231507735467932</v>
+        <v>4.668327629596125</v>
       </c>
     </row>
     <row r="240">
@@ -16677,7 +16677,7 @@
         <v>1</v>
       </c>
       <c r="K240">
-        <v>89.05729909652877</v>
+        <v>88.62047920240057</v>
       </c>
       <c r="L240">
         <v>92.5475473922621</v>
@@ -16700,7 +16700,7 @@
         </is>
       </c>
       <c r="S240">
-        <v>-0.4367550889019522</v>
+        <v>6.480522624086049E-05</v>
       </c>
     </row>
     <row r="241">
@@ -16745,7 +16745,7 @@
         <v>1</v>
       </c>
       <c r="K241">
-        <v>89.05729909652877</v>
+        <v>88.62047920240057</v>
       </c>
       <c r="L241">
         <v>92.5475473922621</v>
@@ -16768,7 +16768,7 @@
         </is>
       </c>
       <c r="S241">
-        <v>3.076631668859475</v>
+        <v>3.513451562987668</v>
       </c>
     </row>
     <row r="242">
@@ -16813,7 +16813,7 @@
         <v>1</v>
       </c>
       <c r="K242">
-        <v>90.90746629476332</v>
+        <v>91.61098668710515</v>
       </c>
       <c r="L242">
         <v>88.28328173374614</v>
@@ -16836,7 +16836,7 @@
         </is>
       </c>
       <c r="S242">
-        <v>-2.624184561017195</v>
+        <v>-3.327704953359023</v>
       </c>
     </row>
     <row r="243">
@@ -16881,7 +16881,7 @@
         <v>1</v>
       </c>
       <c r="K243">
-        <v>90.90746629476332</v>
+        <v>91.61098668710515</v>
       </c>
       <c r="L243">
         <v>88.28328173374614</v>
@@ -16904,7 +16904,7 @@
         </is>
       </c>
       <c r="S243">
-        <v>-1.640953570363834</v>
+        <v>-2.344473962705662</v>
       </c>
     </row>
     <row r="244">
@@ -16949,7 +16949,7 @@
         <v>1</v>
       </c>
       <c r="K244">
-        <v>90.90746629476332</v>
+        <v>91.61098668710515</v>
       </c>
       <c r="L244">
         <v>88.28328173374614</v>
@@ -16972,7 +16972,7 @@
         </is>
       </c>
       <c r="S244">
-        <v>0.7035172961438851</v>
+        <v>-3.096197942475953E-06</v>
       </c>
     </row>
     <row r="245">
@@ -17017,7 +17017,7 @@
         <v>1</v>
       </c>
       <c r="K245">
-        <v>90.90746629476332</v>
+        <v>91.61098668710515</v>
       </c>
       <c r="L245">
         <v>88.28328173374614</v>
@@ -17040,7 +17040,7 @@
         </is>
       </c>
       <c r="S245">
-        <v>-2.599647873990474</v>
+        <v>-3.303168266332301</v>
       </c>
     </row>
     <row r="246">
@@ -17085,7 +17085,7 @@
         <v>1</v>
       </c>
       <c r="K246">
-        <v>79.83321608126427</v>
+        <v>78.97645050477405</v>
       </c>
       <c r="L246">
         <v>75.73275197639339</v>
@@ -17108,7 +17108,7 @@
         </is>
       </c>
       <c r="S246">
-        <v>-4.100464104870882</v>
+        <v>-3.243698528380667</v>
       </c>
     </row>
     <row r="247">
@@ -17153,7 +17153,7 @@
         <v>1</v>
       </c>
       <c r="K247">
-        <v>79.83321608126427</v>
+        <v>78.97645050477405</v>
       </c>
       <c r="L247">
         <v>75.73275197639339</v>
@@ -17176,7 +17176,7 @@
         </is>
       </c>
       <c r="S247">
-        <v>-2.999155503292494</v>
+        <v>-2.142389926802279</v>
       </c>
     </row>
     <row r="248">
@@ -17221,7 +17221,7 @@
         <v>1</v>
       </c>
       <c r="K248">
-        <v>79.83321608126427</v>
+        <v>78.97645050477405</v>
       </c>
       <c r="L248">
         <v>75.73275197639339</v>
@@ -17244,7 +17244,7 @@
         </is>
       </c>
       <c r="S248">
-        <v>-0.856766039520207</v>
+        <v>-4.630299921259962E-07</v>
       </c>
     </row>
     <row r="249">
@@ -17289,7 +17289,7 @@
         <v>1</v>
       </c>
       <c r="K249">
-        <v>79.83321608126427</v>
+        <v>78.97645050477405</v>
       </c>
       <c r="L249">
         <v>75.73275197639339</v>
@@ -17312,7 +17312,7 @@
         </is>
       </c>
       <c r="S249">
-        <v>-4.012996670880375</v>
+        <v>-3.156231094390161</v>
       </c>
     </row>
     <row r="250">
@@ -17629,7 +17629,7 @@
         <v>0</v>
       </c>
       <c r="K254">
-        <v>18.14331114239048</v>
+        <v>20.88991652567149</v>
       </c>
       <c r="L254">
         <v>20.11833333333333</v>
@@ -17652,7 +17652,7 @@
         </is>
       </c>
       <c r="S254">
-        <v>1.975022190942849</v>
+        <v>-0.77158319233816</v>
       </c>
     </row>
     <row r="255">
@@ -17697,7 +17697,7 @@
         <v>0</v>
       </c>
       <c r="K255">
-        <v>18.14331114239048</v>
+        <v>20.88991652567149</v>
       </c>
       <c r="L255">
         <v>20.11833333333333</v>
@@ -17720,7 +17720,7 @@
         </is>
       </c>
       <c r="S255">
-        <v>3.238471208398281</v>
+        <v>0.4918658251172714</v>
       </c>
     </row>
     <row r="256">
@@ -17765,7 +17765,7 @@
         <v>0</v>
       </c>
       <c r="K256">
-        <v>18.14331114239048</v>
+        <v>20.88991652567149</v>
       </c>
       <c r="L256">
         <v>20.11833333333333</v>
@@ -17788,7 +17788,7 @@
         </is>
       </c>
       <c r="S256">
-        <v>2.746625368257763</v>
+        <v>1.998497675403943E-05</v>
       </c>
     </row>
     <row r="257">
@@ -17833,7 +17833,7 @@
         <v>0</v>
       </c>
       <c r="K257">
-        <v>18.14331114239048</v>
+        <v>20.88991652567149</v>
       </c>
       <c r="L257">
         <v>20.11833333333333</v>
@@ -17856,7 +17856,7 @@
         </is>
       </c>
       <c r="S257">
-        <v>2.74660538328102</v>
+        <v>1.110223024625157E-14</v>
       </c>
     </row>
     <row r="258">
@@ -17901,7 +17901,7 @@
         <v>0</v>
       </c>
       <c r="K258">
-        <v>29.56982778000091</v>
+        <v>29.08416921339044</v>
       </c>
       <c r="L258">
         <v>27.695</v>
@@ -17924,7 +17924,7 @@
         </is>
       </c>
       <c r="S258">
-        <v>-1.874827780000915</v>
+        <v>-1.389169213390445</v>
       </c>
     </row>
     <row r="259">
@@ -17969,7 +17969,7 @@
         <v>0</v>
       </c>
       <c r="K259">
-        <v>29.56982778000091</v>
+        <v>29.08416921339044</v>
       </c>
       <c r="L259">
         <v>27.695</v>
@@ -17992,7 +17992,7 @@
         </is>
       </c>
       <c r="S259">
-        <v>-0.5566560943429499</v>
+        <v>-0.07099752773248036</v>
       </c>
     </row>
     <row r="260">
@@ -18037,7 +18037,7 @@
         <v>0</v>
       </c>
       <c r="K260">
-        <v>29.56982778000091</v>
+        <v>29.08416921339044</v>
       </c>
       <c r="L260">
         <v>27.695</v>
@@ -18060,7 +18060,7 @@
         </is>
       </c>
       <c r="S260">
-        <v>-0.4853991898388088</v>
+        <v>0.0002593767716607687</v>
       </c>
     </row>
     <row r="261">
@@ -18105,7 +18105,7 @@
         <v>0</v>
       </c>
       <c r="K261">
-        <v>29.56982778000091</v>
+        <v>29.08416921339044</v>
       </c>
       <c r="L261">
         <v>27.695</v>
@@ -18128,7 +18128,7 @@
         </is>
       </c>
       <c r="S261">
-        <v>-0.4856585666103863</v>
+        <v>8.326672684688674E-14</v>
       </c>
     </row>
     <row r="262">
@@ -18173,7 +18173,7 @@
         <v>0</v>
       </c>
       <c r="K262">
-        <v>60.77436036636043</v>
+        <v>61.74569966247353</v>
       </c>
       <c r="L262">
         <v>50.86308977801498</v>
@@ -18196,7 +18196,7 @@
         </is>
       </c>
       <c r="S262">
-        <v>-9.911270588345456</v>
+        <v>-10.88260988445855</v>
       </c>
     </row>
     <row r="263">
@@ -18241,7 +18241,7 @@
         <v>0</v>
       </c>
       <c r="K263">
-        <v>60.77436036636043</v>
+        <v>61.74569966247353</v>
       </c>
       <c r="L263">
         <v>50.86308977801498</v>
@@ -18264,7 +18264,7 @@
         </is>
       </c>
       <c r="S263">
-        <v>-11.90455069947164</v>
+        <v>-12.87588999558473</v>
       </c>
     </row>
     <row r="264">
@@ -18309,7 +18309,7 @@
         <v>0</v>
       </c>
       <c r="K264">
-        <v>60.77436036636043</v>
+        <v>61.74569966247353</v>
       </c>
       <c r="L264">
         <v>50.86308977801498</v>
@@ -18332,7 +18332,7 @@
         </is>
       </c>
       <c r="S264">
-        <v>0.9704933880536726</v>
+        <v>-0.0008459080594214186</v>
       </c>
     </row>
     <row r="265">
@@ -18377,7 +18377,7 @@
         <v>0</v>
       </c>
       <c r="K265">
-        <v>60.77436036636043</v>
+        <v>61.74569966247353</v>
       </c>
       <c r="L265">
         <v>50.86308977801498</v>
@@ -18400,7 +18400,7 @@
         </is>
       </c>
       <c r="S265">
-        <v>0.9713392961126166</v>
+        <v>-4.773959005888173E-13</v>
       </c>
     </row>
     <row r="266">
@@ -18445,7 +18445,7 @@
         <v>0</v>
       </c>
       <c r="K266">
-        <v>23.94802897974832</v>
+        <v>23.91662622988876</v>
       </c>
       <c r="L266">
         <v>24.9084044709777</v>
@@ -18468,7 +18468,7 @@
         </is>
       </c>
       <c r="S266">
-        <v>0.9603754912293871</v>
+        <v>0.9917782410889447</v>
       </c>
     </row>
     <row r="267">
@@ -18513,7 +18513,7 @@
         <v>0</v>
       </c>
       <c r="K267">
-        <v>23.94802897974832</v>
+        <v>23.91662622988876</v>
       </c>
       <c r="L267">
         <v>24.9084044709777</v>
@@ -18536,7 +18536,7 @@
         </is>
       </c>
       <c r="S267">
-        <v>-0.4234524090596437</v>
+        <v>-0.3920496592000861</v>
       </c>
     </row>
     <row r="268">
@@ -18581,7 +18581,7 @@
         <v>0</v>
       </c>
       <c r="K268">
-        <v>23.94802897974832</v>
+        <v>23.91662622988876</v>
       </c>
       <c r="L268">
         <v>24.9084044709777</v>
@@ -18604,7 +18604,7 @@
         </is>
       </c>
       <c r="S268">
-        <v>-0.03181003093948309</v>
+        <v>-0.0004072810799254922</v>
       </c>
     </row>
     <row r="269">
@@ -18649,7 +18649,7 @@
         <v>0</v>
       </c>
       <c r="K269">
-        <v>23.94802897974832</v>
+        <v>23.91662622988876</v>
       </c>
       <c r="L269">
         <v>24.9084044709777</v>
@@ -18672,7 +18672,7 @@
         </is>
       </c>
       <c r="S269">
-        <v>-0.0314027498595465</v>
+        <v>1.110223024625157E-14</v>
       </c>
     </row>
     <row r="270">
@@ -18717,7 +18717,7 @@
         <v>1</v>
       </c>
       <c r="K270">
-        <v>90.28635550841885</v>
+        <v>87.37047875398824</v>
       </c>
       <c r="L270">
         <v>96.63494391573192</v>
@@ -18740,7 +18740,7 @@
         </is>
       </c>
       <c r="S270">
-        <v>6.348588407313082</v>
+        <v>9.264465161743695</v>
       </c>
     </row>
     <row r="271">
@@ -18785,7 +18785,7 @@
         <v>1</v>
       </c>
       <c r="K271">
-        <v>90.28635550841885</v>
+        <v>87.37047875398824</v>
       </c>
       <c r="L271">
         <v>96.63494391573192</v>
@@ -18808,7 +18808,7 @@
         </is>
       </c>
       <c r="S271">
-        <v>6.459968263155591</v>
+        <v>9.375845017586204</v>
       </c>
     </row>
     <row r="272">
@@ -18853,7 +18853,7 @@
         <v>1</v>
       </c>
       <c r="K272">
-        <v>90.28635550841885</v>
+        <v>87.37047875398824</v>
       </c>
       <c r="L272">
         <v>96.63494391573192</v>
@@ -18876,7 +18876,7 @@
         </is>
       </c>
       <c r="S272">
-        <v>-2.913906598939231</v>
+        <v>0.00197015549138202</v>
       </c>
     </row>
     <row r="273">
@@ -18921,7 +18921,7 @@
         <v>1</v>
       </c>
       <c r="K273">
-        <v>90.28635550841885</v>
+        <v>87.37047875398824</v>
       </c>
       <c r="L273">
         <v>96.63494391573192</v>
@@ -18944,7 +18944,7 @@
         </is>
       </c>
       <c r="S273">
-        <v>6.321391536824805</v>
+        <v>9.237268291255418</v>
       </c>
     </row>
     <row r="274">
@@ -18989,7 +18989,7 @@
         <v>0</v>
       </c>
       <c r="K274">
-        <v>52.29786793450734</v>
+        <v>51.94822224461573</v>
       </c>
       <c r="L274">
         <v>56.95166666666667</v>
@@ -19012,7 +19012,7 @@
         </is>
       </c>
       <c r="S274">
-        <v>4.653798732159331</v>
+        <v>5.00344442205094</v>
       </c>
     </row>
     <row r="275">
@@ -19057,7 +19057,7 @@
         <v>0</v>
       </c>
       <c r="K275">
-        <v>52.29786793450734</v>
+        <v>51.94822224461573</v>
       </c>
       <c r="L275">
         <v>56.95166666666667</v>
@@ -19080,7 +19080,7 @@
         </is>
       </c>
       <c r="S275">
-        <v>-0.7980327516663221</v>
+        <v>-0.4483870617747132</v>
       </c>
     </row>
     <row r="276">
@@ -19125,7 +19125,7 @@
         <v>0</v>
       </c>
       <c r="K276">
-        <v>52.29786793450734</v>
+        <v>51.94822224461573</v>
       </c>
       <c r="L276">
         <v>56.95166666666667</v>
@@ -19148,7 +19148,7 @@
         </is>
       </c>
       <c r="S276">
-        <v>-0.3489853170382085</v>
+        <v>0.0006603728534004816</v>
       </c>
     </row>
     <row r="277">
@@ -19193,7 +19193,7 @@
         <v>0</v>
       </c>
       <c r="K277">
-        <v>52.29786793450734</v>
+        <v>51.94822224461573</v>
       </c>
       <c r="L277">
         <v>56.95166666666667</v>
@@ -19216,7 +19216,7 @@
         </is>
       </c>
       <c r="S277">
-        <v>2.540189077570598</v>
+        <v>2.889834767462207</v>
       </c>
     </row>
     <row r="278">
@@ -19261,7 +19261,7 @@
         <v>1</v>
       </c>
       <c r="K278">
-        <v>89.18537787513691</v>
+        <v>88.81688255591112</v>
       </c>
       <c r="L278">
         <v>93.76136685965996</v>
@@ -19284,7 +19284,7 @@
         </is>
       </c>
       <c r="S278">
-        <v>4.575988984523049</v>
+        <v>4.944484303748842</v>
       </c>
     </row>
     <row r="279">
@@ -19329,7 +19329,7 @@
         <v>1</v>
       </c>
       <c r="K279">
-        <v>89.18537787513691</v>
+        <v>88.81688255591112</v>
       </c>
       <c r="L279">
         <v>93.76136685965996</v>
@@ -19352,7 +19352,7 @@
         </is>
       </c>
       <c r="S279">
-        <v>4.921785071913076</v>
+        <v>5.290280391138868</v>
       </c>
     </row>
     <row r="280">
@@ -19397,7 +19397,7 @@
         <v>1</v>
       </c>
       <c r="K280">
-        <v>89.18537787513691</v>
+        <v>88.81688255591112</v>
       </c>
       <c r="L280">
         <v>93.76136685965996</v>
@@ -19420,7 +19420,7 @@
         </is>
       </c>
       <c r="S280">
-        <v>-0.3680525797035372</v>
+        <v>0.0004427395222550423</v>
       </c>
     </row>
     <row r="281">
@@ -19465,7 +19465,7 @@
         <v>1</v>
       </c>
       <c r="K281">
-        <v>89.18537787513691</v>
+        <v>88.81688255591112</v>
       </c>
       <c r="L281">
         <v>93.76136685965996</v>
@@ -19488,7 +19488,7 @@
         </is>
       </c>
       <c r="S281">
-        <v>3.853774514999975</v>
+        <v>4.222269834225767</v>
       </c>
     </row>
     <row r="282">
@@ -19533,7 +19533,7 @@
         <v>1</v>
       </c>
       <c r="K282">
-        <v>91.29247683720668</v>
+        <v>92.02554441496299</v>
       </c>
       <c r="L282">
         <v>88.72</v>
@@ -19556,7 +19556,7 @@
         </is>
       </c>
       <c r="S282">
-        <v>-2.572476837206683</v>
+        <v>-3.305544414962991</v>
       </c>
     </row>
     <row r="283">
@@ -19601,7 +19601,7 @@
         <v>1</v>
       </c>
       <c r="K283">
-        <v>91.29247683720668</v>
+        <v>92.02554441496299</v>
       </c>
       <c r="L283">
         <v>88.72</v>
@@ -19624,7 +19624,7 @@
         </is>
       </c>
       <c r="S283">
-        <v>-1.477346511013466</v>
+        <v>-2.210414088769774</v>
       </c>
     </row>
     <row r="284">
@@ -19669,7 +19669,7 @@
         <v>1</v>
       </c>
       <c r="K284">
-        <v>91.29247683720668</v>
+        <v>92.02554441496299</v>
       </c>
       <c r="L284">
         <v>88.72</v>
@@ -19692,7 +19692,7 @@
         </is>
       </c>
       <c r="S284">
-        <v>0.7329824829258258</v>
+        <v>-8.509483048202426E-05</v>
       </c>
     </row>
     <row r="285">
@@ -19737,7 +19737,7 @@
         <v>1</v>
       </c>
       <c r="K285">
-        <v>91.29247683720668</v>
+        <v>92.02554441496299</v>
       </c>
       <c r="L285">
         <v>88.72</v>
@@ -19760,7 +19760,7 @@
         </is>
       </c>
       <c r="S285">
-        <v>-2.610801596668999</v>
+        <v>-3.343869174425307</v>
       </c>
     </row>
     <row r="286">
@@ -19805,7 +19805,7 @@
         <v>1</v>
       </c>
       <c r="K286">
-        <v>77.78308747143154</v>
+        <v>76.75124320078025</v>
       </c>
       <c r="L286">
         <v>73.57492239676418</v>
@@ -19828,7 +19828,7 @@
         </is>
       </c>
       <c r="S286">
-        <v>-4.208165074667369</v>
+        <v>-3.176320804016075</v>
       </c>
     </row>
     <row r="287">
@@ -19873,7 +19873,7 @@
         <v>1</v>
       </c>
       <c r="K287">
-        <v>77.78308747143154</v>
+        <v>76.75124320078025</v>
       </c>
       <c r="L287">
         <v>73.57492239676418</v>
@@ -19896,7 +19896,7 @@
         </is>
       </c>
       <c r="S287">
-        <v>-3.311840903614349</v>
+        <v>-2.279996632963055</v>
       </c>
     </row>
     <row r="288">
@@ -19941,7 +19941,7 @@
         <v>1</v>
       </c>
       <c r="K288">
-        <v>77.78308747143154</v>
+        <v>76.75124320078025</v>
       </c>
       <c r="L288">
         <v>73.57492239676418</v>
@@ -19964,7 +19964,7 @@
         </is>
       </c>
       <c r="S288">
-        <v>-1.031761349143301</v>
+        <v>8.292150799338316E-05</v>
       </c>
     </row>
     <row r="289">
@@ -20009,7 +20009,7 @@
         <v>1</v>
       </c>
       <c r="K289">
-        <v>77.78308747143154</v>
+        <v>76.75124320078025</v>
       </c>
       <c r="L289">
         <v>73.57492239676418</v>
@@ -20032,7 +20032,7 @@
         </is>
       </c>
       <c r="S289">
-        <v>-3.648203972631248</v>
+        <v>-2.616359701979953</v>
       </c>
     </row>
     <row r="290">
@@ -20328,7 +20328,7 @@
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>70+</t>
+          <t>18-29</t>
         </is>
       </c>
       <c r="F294" t="inlineStr">
@@ -20349,19 +20349,19 @@
         <v>0</v>
       </c>
       <c r="K294">
-        <v>17.85222125342917</v>
+        <v>20.44825700998186</v>
       </c>
       <c r="L294">
-        <v>13.27377049180328</v>
+        <v>19.44918032786885</v>
       </c>
       <c r="M294">
-        <v>13.71421764662618</v>
+        <v>21.02671173378868</v>
       </c>
       <c r="N294">
-        <v>15.41815523864195</v>
+        <v>20.45555891210151</v>
       </c>
       <c r="O294">
-        <v>15.39358401703959</v>
+        <v>20.44825700998192</v>
       </c>
       <c r="P294">
         <v>61000</v>
@@ -20372,7 +20372,7 @@
         </is>
       </c>
       <c r="S294">
-        <v>-4.578450761625893</v>
+        <v>-0.9990766821130009</v>
       </c>
     </row>
     <row r="295">
@@ -20396,7 +20396,7 @@
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>70+</t>
+          <t>18-29</t>
         </is>
       </c>
       <c r="F295" t="inlineStr">
@@ -20417,19 +20417,19 @@
         <v>0</v>
       </c>
       <c r="K295">
-        <v>17.85222125342917</v>
+        <v>20.44825700998186</v>
       </c>
       <c r="L295">
-        <v>13.27377049180328</v>
+        <v>19.44918032786885</v>
       </c>
       <c r="M295">
-        <v>13.71421764662618</v>
+        <v>21.02671173378868</v>
       </c>
       <c r="N295">
-        <v>15.41815523864195</v>
+        <v>20.45555891210151</v>
       </c>
       <c r="O295">
-        <v>15.39358401703959</v>
+        <v>20.44825700998192</v>
       </c>
       <c r="P295">
         <v>61000</v>
@@ -20440,7 +20440,7 @@
         </is>
       </c>
       <c r="S295">
-        <v>-4.138003606802992</v>
+        <v>0.5784547238068288</v>
       </c>
     </row>
     <row r="296">
@@ -20464,7 +20464,7 @@
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>70+</t>
+          <t>18-29</t>
         </is>
       </c>
       <c r="F296" t="inlineStr">
@@ -20485,19 +20485,19 @@
         <v>0</v>
       </c>
       <c r="K296">
-        <v>17.85222125342917</v>
+        <v>20.44825700998186</v>
       </c>
       <c r="L296">
-        <v>13.27377049180328</v>
+        <v>19.44918032786885</v>
       </c>
       <c r="M296">
-        <v>13.71421764662618</v>
+        <v>21.02671173378868</v>
       </c>
       <c r="N296">
-        <v>15.41815523864195</v>
+        <v>20.45555891210151</v>
       </c>
       <c r="O296">
-        <v>15.39358401703959</v>
+        <v>20.44825700998192</v>
       </c>
       <c r="P296">
         <v>61000</v>
@@ -20508,7 +20508,7 @@
         </is>
       </c>
       <c r="S296">
-        <v>-2.43406601478722</v>
+        <v>0.007301902119655201</v>
       </c>
     </row>
     <row r="297">
@@ -20532,7 +20532,7 @@
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>70+</t>
+          <t>18-29</t>
         </is>
       </c>
       <c r="F297" t="inlineStr">
@@ -20553,19 +20553,19 @@
         <v>0</v>
       </c>
       <c r="K297">
-        <v>17.85222125342917</v>
+        <v>20.44825700998186</v>
       </c>
       <c r="L297">
-        <v>13.27377049180328</v>
+        <v>19.44918032786885</v>
       </c>
       <c r="M297">
-        <v>13.71421764662618</v>
+        <v>21.02671173378868</v>
       </c>
       <c r="N297">
-        <v>15.41815523864195</v>
+        <v>20.45555891210151</v>
       </c>
       <c r="O297">
-        <v>15.39358401703959</v>
+        <v>20.44825700998192</v>
       </c>
       <c r="P297">
         <v>61000</v>
@@ -20576,7 +20576,7 @@
         </is>
       </c>
       <c r="S297">
-        <v>-2.458637236389585</v>
+        <v>6.938893903907228E-14</v>
       </c>
     </row>
     <row r="298">
@@ -20621,7 +20621,7 @@
         <v>0</v>
       </c>
       <c r="K298">
-        <v>29.16051719371372</v>
+        <v>28.56364349950798</v>
       </c>
       <c r="L298">
         <v>27.24262295081967</v>
@@ -20644,7 +20644,7 @@
         </is>
       </c>
       <c r="S298">
-        <v>-1.917894242894042</v>
+        <v>-1.321020548688301</v>
       </c>
     </row>
     <row r="299">
@@ -20689,7 +20689,7 @@
         <v>0</v>
       </c>
       <c r="K299">
-        <v>29.16051719371372</v>
+        <v>28.56364349950798</v>
       </c>
       <c r="L299">
         <v>27.24262295081967</v>
@@ -20712,7 +20712,7 @@
         </is>
       </c>
       <c r="S299">
-        <v>0.2622557868409037</v>
+        <v>0.8591294810466443</v>
       </c>
     </row>
     <row r="300">
@@ -20757,7 +20757,7 @@
         <v>0</v>
       </c>
       <c r="K300">
-        <v>29.16051719371372</v>
+        <v>28.56364349950798</v>
       </c>
       <c r="L300">
         <v>27.24262295081967</v>
@@ -20780,7 +20780,7 @@
         </is>
       </c>
       <c r="S300">
-        <v>-0.5880716505329397</v>
+        <v>0.008802043672800908</v>
       </c>
     </row>
     <row r="301">
@@ -20825,7 +20825,7 @@
         <v>0</v>
       </c>
       <c r="K301">
-        <v>29.16051719371372</v>
+        <v>28.56364349950798</v>
       </c>
       <c r="L301">
         <v>27.24262295081967</v>
@@ -20848,7 +20848,7 @@
         </is>
       </c>
       <c r="S301">
-        <v>-0.5968736942056962</v>
+        <v>4.440892098500626E-14</v>
       </c>
     </row>
     <row r="302">
@@ -20893,7 +20893,7 @@
         <v>0</v>
       </c>
       <c r="K302">
-        <v>57.05112391808264</v>
+        <v>58.01083281286581</v>
       </c>
       <c r="L302">
         <v>47.0934619296001</v>
@@ -20916,7 +20916,7 @@
         </is>
       </c>
       <c r="S302">
-        <v>-9.957661988482529</v>
+        <v>-10.9173708832657</v>
       </c>
     </row>
     <row r="303">
@@ -20961,7 +20961,7 @@
         <v>0</v>
       </c>
       <c r="K303">
-        <v>57.05112391808264</v>
+        <v>58.01083281286581</v>
       </c>
       <c r="L303">
         <v>47.0934619296001</v>
@@ -20984,7 +20984,7 @@
         </is>
       </c>
       <c r="S303">
-        <v>-11.58713355072103</v>
+        <v>-12.54684244550421</v>
       </c>
     </row>
     <row r="304">
@@ -21029,7 +21029,7 @@
         <v>0</v>
       </c>
       <c r="K304">
-        <v>57.05112391808264</v>
+        <v>58.01083281286581</v>
       </c>
       <c r="L304">
         <v>47.0934619296001</v>
@@ -21052,7 +21052,7 @@
         </is>
       </c>
       <c r="S304">
-        <v>0.9354526786854556</v>
+        <v>-0.02425621609771778</v>
       </c>
     </row>
     <row r="305">
@@ -21097,7 +21097,7 @@
         <v>0</v>
       </c>
       <c r="K305">
-        <v>57.05112391808264</v>
+        <v>58.01083281286581</v>
       </c>
       <c r="L305">
         <v>47.0934619296001</v>
@@ -21120,7 +21120,7 @@
         </is>
       </c>
       <c r="S305">
-        <v>0.9597088947832622</v>
+        <v>8.881784197001252E-14</v>
       </c>
     </row>
     <row r="306">
@@ -21165,7 +21165,7 @@
         <v>0</v>
       </c>
       <c r="K306">
-        <v>24.68005018820577</v>
+        <v>24.30807920702783</v>
       </c>
       <c r="L306">
         <v>23.90267001784869</v>
@@ -21188,7 +21188,7 @@
         </is>
       </c>
       <c r="S306">
-        <v>-0.7773801703570837</v>
+        <v>-0.4054091891791484</v>
       </c>
     </row>
     <row r="307">
@@ -21233,7 +21233,7 @@
         <v>0</v>
       </c>
       <c r="K307">
-        <v>24.68005018820577</v>
+        <v>24.30807920702783</v>
       </c>
       <c r="L307">
         <v>23.90267001784869</v>
@@ -21256,7 +21256,7 @@
         </is>
       </c>
       <c r="S307">
-        <v>-1.803182488598895</v>
+        <v>-1.43121150742096</v>
       </c>
     </row>
     <row r="308">
@@ -21301,7 +21301,7 @@
         <v>0</v>
       </c>
       <c r="K308">
-        <v>24.68005018820577</v>
+        <v>24.30807920702783</v>
       </c>
       <c r="L308">
         <v>23.90267001784869</v>
@@ -21324,7 +21324,7 @@
         </is>
       </c>
       <c r="S308">
-        <v>-0.3936985826528322</v>
+        <v>-0.02172760147489683</v>
       </c>
     </row>
     <row r="309">
@@ -21369,7 +21369,7 @@
         <v>0</v>
       </c>
       <c r="K309">
-        <v>24.68005018820577</v>
+        <v>24.30807920702783</v>
       </c>
       <c r="L309">
         <v>23.90267001784869</v>
@@ -21392,7 +21392,7 @@
         </is>
       </c>
       <c r="S309">
-        <v>-0.3719709811773608</v>
+        <v>5.745404152435185E-13</v>
       </c>
     </row>
     <row r="310">
@@ -21437,7 +21437,7 @@
         <v>1</v>
       </c>
       <c r="K310">
-        <v>90.20713267975246</v>
+        <v>86.62346554656978</v>
       </c>
       <c r="L310">
         <v>96.77494574088357</v>
@@ -21460,7 +21460,7 @@
         </is>
       </c>
       <c r="S310">
-        <v>6.5678130611311</v>
+        <v>10.15148019431379</v>
       </c>
     </row>
     <row r="311">
@@ -21505,7 +21505,7 @@
         <v>1</v>
       </c>
       <c r="K311">
-        <v>90.20713267975246</v>
+        <v>86.62346554656978</v>
       </c>
       <c r="L311">
         <v>96.77494574088357</v>
@@ -21528,7 +21528,7 @@
         </is>
       </c>
       <c r="S311">
-        <v>6.543831877811956</v>
+        <v>10.12749901099465</v>
       </c>
     </row>
     <row r="312">
@@ -21573,7 +21573,7 @@
         <v>1</v>
       </c>
       <c r="K312">
-        <v>90.20713267975246</v>
+        <v>86.62346554656978</v>
       </c>
       <c r="L312">
         <v>96.77494574088357</v>
@@ -21596,7 +21596,7 @@
         </is>
       </c>
       <c r="S312">
-        <v>-3.50657111129371</v>
+        <v>0.07709602188897824</v>
       </c>
     </row>
     <row r="313">
@@ -21641,7 +21641,7 @@
         <v>1</v>
       </c>
       <c r="K313">
-        <v>90.20713267975246</v>
+        <v>86.62346554656978</v>
       </c>
       <c r="L313">
         <v>96.77494574088357</v>
@@ -21664,7 +21664,7 @@
         </is>
       </c>
       <c r="S313">
-        <v>6.616269153125376</v>
+        <v>10.19993628630806</v>
       </c>
     </row>
     <row r="314">
@@ -21709,7 +21709,7 @@
         <v>1</v>
       </c>
       <c r="K314">
-        <v>61.18302097982378</v>
+        <v>59.79566855189433</v>
       </c>
       <c r="L314">
         <v>59.65856861457649</v>
@@ -21732,7 +21732,7 @@
         </is>
       </c>
       <c r="S314">
-        <v>-1.524452365247286</v>
+        <v>-0.1370999373178416</v>
       </c>
     </row>
     <row r="315">
@@ -21777,7 +21777,7 @@
         <v>1</v>
       </c>
       <c r="K315">
-        <v>61.18302097982378</v>
+        <v>59.79566855189433</v>
       </c>
       <c r="L315">
         <v>59.65856861457649</v>
@@ -21800,7 +21800,7 @@
         </is>
       </c>
       <c r="S315">
-        <v>-0.6643547096270019</v>
+        <v>0.7229977183024427</v>
       </c>
     </row>
     <row r="316">
@@ -21845,7 +21845,7 @@
         <v>1</v>
       </c>
       <c r="K316">
-        <v>61.18302097982378</v>
+        <v>59.79566855189433</v>
       </c>
       <c r="L316">
         <v>59.65856861457649</v>
@@ -21868,7 +21868,7 @@
         </is>
       </c>
       <c r="S316">
-        <v>-1.367740548997121</v>
+        <v>0.01961187893232408</v>
       </c>
     </row>
     <row r="317">
@@ -21913,7 +21913,7 @@
         <v>1</v>
       </c>
       <c r="K317">
-        <v>61.18302097982378</v>
+        <v>59.79566855189433</v>
       </c>
       <c r="L317">
         <v>59.65856861457649</v>
@@ -21936,7 +21936,7 @@
         </is>
       </c>
       <c r="S317">
-        <v>-0.8392059589790279</v>
+        <v>0.5481464689504167</v>
       </c>
     </row>
     <row r="318">
@@ -21981,7 +21981,7 @@
         <v>0</v>
       </c>
       <c r="K318">
-        <v>52.10535269974268</v>
+        <v>51.86516463412201</v>
       </c>
       <c r="L318">
         <v>57.71967213114754</v>
@@ -22004,7 +22004,7 @@
         </is>
       </c>
       <c r="S318">
-        <v>5.614319431404857</v>
+        <v>5.85450749702553</v>
       </c>
     </row>
     <row r="319">
@@ -22049,7 +22049,7 @@
         <v>0</v>
       </c>
       <c r="K319">
-        <v>52.10535269974268</v>
+        <v>51.86516463412201</v>
       </c>
       <c r="L319">
         <v>57.71967213114754</v>
@@ -22072,7 +22072,7 @@
         </is>
       </c>
       <c r="S319">
-        <v>-0.6073233621567531</v>
+        <v>-0.3671352965360808</v>
       </c>
     </row>
     <row r="320">
@@ -22117,7 +22117,7 @@
         <v>0</v>
       </c>
       <c r="K320">
-        <v>52.10535269974268</v>
+        <v>51.86516463412201</v>
       </c>
       <c r="L320">
         <v>57.71967213114754</v>
@@ -22140,7 +22140,7 @@
         </is>
       </c>
       <c r="S320">
-        <v>-0.2309273630907271</v>
+        <v>0.009260702529945153</v>
       </c>
     </row>
     <row r="321">
@@ -22185,7 +22185,7 @@
         <v>0</v>
       </c>
       <c r="K321">
-        <v>52.10535269974268</v>
+        <v>51.86516463412201</v>
       </c>
       <c r="L321">
         <v>57.71967213114754</v>
@@ -22208,7 +22208,7 @@
         </is>
       </c>
       <c r="S321">
-        <v>3.087857254104898</v>
+        <v>3.32804531972557</v>
       </c>
     </row>
     <row r="322">
@@ -22253,7 +22253,7 @@
         <v>1</v>
       </c>
       <c r="K322">
-        <v>88.95106598984771</v>
+        <v>88.5990480214931</v>
       </c>
       <c r="L322">
         <v>93.71060924369748</v>
@@ -22276,7 +22276,7 @@
         </is>
       </c>
       <c r="S322">
-        <v>4.759543253849763</v>
+        <v>5.111561222204375</v>
       </c>
     </row>
     <row r="323">
@@ -22321,7 +22321,7 @@
         <v>1</v>
       </c>
       <c r="K323">
-        <v>88.95106598984771</v>
+        <v>88.5990480214931</v>
       </c>
       <c r="L323">
         <v>93.71060924369748</v>
@@ -22344,7 +22344,7 @@
         </is>
       </c>
       <c r="S323">
-        <v>5.086613846592847</v>
+        <v>5.438631814947459</v>
       </c>
     </row>
     <row r="324">
@@ -22389,7 +22389,7 @@
         <v>1</v>
       </c>
       <c r="K324">
-        <v>88.95106598984771</v>
+        <v>88.5990480214931</v>
       </c>
       <c r="L324">
         <v>93.71060924369748</v>
@@ -22412,7 +22412,7 @@
         </is>
       </c>
       <c r="S324">
-        <v>-0.3433119337773349</v>
+        <v>0.008706034577277144</v>
       </c>
     </row>
     <row r="325">
@@ -22457,7 +22457,7 @@
         <v>1</v>
       </c>
       <c r="K325">
-        <v>88.95106598984771</v>
+        <v>88.5990480214931</v>
       </c>
       <c r="L325">
         <v>93.71060924369748</v>
@@ -22480,7 +22480,7 @@
         </is>
       </c>
       <c r="S325">
-        <v>3.859859152327627</v>
+        <v>4.211877120682239</v>
       </c>
     </row>
     <row r="326">
@@ -22525,7 +22525,7 @@
         <v>1</v>
       </c>
       <c r="K326">
-        <v>91.58534501174962</v>
+        <v>92.50024047603399</v>
       </c>
       <c r="L326">
         <v>89.74590163934425</v>
@@ -22548,7 +22548,7 @@
         </is>
       </c>
       <c r="S326">
-        <v>-1.839443372405369</v>
+        <v>-2.754338836689729</v>
       </c>
     </row>
     <row r="327">
@@ -22593,7 +22593,7 @@
         <v>1</v>
       </c>
       <c r="K327">
-        <v>91.58534501174962</v>
+        <v>92.50024047603399</v>
       </c>
       <c r="L327">
         <v>89.74590163934425</v>
@@ -22616,7 +22616,7 @@
         </is>
       </c>
       <c r="S327">
-        <v>-1.459948456466753</v>
+        <v>-2.374843920751113</v>
       </c>
     </row>
     <row r="328">
@@ -22661,7 +22661,7 @@
         <v>1</v>
       </c>
       <c r="K328">
-        <v>91.58534501174962</v>
+        <v>92.50024047603399</v>
       </c>
       <c r="L328">
         <v>89.74590163934425</v>
@@ -22684,7 +22684,7 @@
         </is>
       </c>
       <c r="S328">
-        <v>0.9126431762666587</v>
+        <v>-0.002252288017701165</v>
       </c>
     </row>
     <row r="329">
@@ -22729,7 +22729,7 @@
         <v>1</v>
       </c>
       <c r="K329">
-        <v>91.58534501174962</v>
+        <v>92.50024047603399</v>
       </c>
       <c r="L329">
         <v>89.74590163934425</v>
@@ -22752,7 +22752,7 @@
         </is>
       </c>
       <c r="S329">
-        <v>-2.161473068155828</v>
+        <v>-3.076368532440188</v>
       </c>
     </row>
     <row r="330">
@@ -22797,7 +22797,7 @@
         <v>1</v>
       </c>
       <c r="K330">
-        <v>56.50106574848336</v>
+        <v>56.80513953523788</v>
       </c>
       <c r="L330">
         <v>52.88054160297008</v>
@@ -22820,7 +22820,7 @@
         </is>
       </c>
       <c r="S330">
-        <v>-3.620524145513282</v>
+        <v>-3.924597932267804</v>
       </c>
     </row>
     <row r="331">
@@ -22865,7 +22865,7 @@
         <v>1</v>
       </c>
       <c r="K331">
-        <v>56.50106574848336</v>
+        <v>56.80513953523788</v>
       </c>
       <c r="L331">
         <v>52.88054160297008</v>
@@ -22888,7 +22888,7 @@
         </is>
       </c>
       <c r="S331">
-        <v>0.06726788669677575</v>
+        <v>-0.236805900057746</v>
       </c>
     </row>
     <row r="332">
@@ -22933,7 +22933,7 @@
         <v>1</v>
       </c>
       <c r="K332">
-        <v>56.50106574848336</v>
+        <v>56.80513953523788</v>
       </c>
       <c r="L332">
         <v>52.88054160297008</v>
@@ -22956,7 +22956,7 @@
         </is>
       </c>
       <c r="S332">
-        <v>0.3061338125185942</v>
+        <v>0.002060025764072382</v>
       </c>
     </row>
     <row r="333">
@@ -23001,7 +23001,7 @@
         <v>1</v>
       </c>
       <c r="K333">
-        <v>56.50106574848336</v>
+        <v>56.80513953523788</v>
       </c>
       <c r="L333">
         <v>52.88054160297008</v>
@@ -23024,7 +23024,7 @@
         </is>
       </c>
       <c r="S333">
-        <v>-2.730139935953713</v>
+        <v>-3.034213722708234</v>
       </c>
     </row>
     <row r="334">
@@ -23320,7 +23320,7 @@
       </c>
       <c r="E338" t="inlineStr">
         <is>
-          <t>70+</t>
+          <t>18-29</t>
         </is>
       </c>
       <c r="F338" t="inlineStr">
@@ -23341,19 +23341,19 @@
         <v>0</v>
       </c>
       <c r="K338">
-        <v>18.77237402132777</v>
+        <v>19.78925504151841</v>
       </c>
       <c r="L338">
-        <v>15.06666666666667</v>
+        <v>15.42166666666667</v>
       </c>
       <c r="M338">
-        <v>13.63679623448249</v>
+        <v>20.46698332765539</v>
       </c>
       <c r="N338">
-        <v>15.79903111329061</v>
+        <v>19.78924728850102</v>
       </c>
       <c r="O338">
-        <v>15.79902656857579</v>
+        <v>19.78925504151825</v>
       </c>
       <c r="P338">
         <v>60000</v>
@@ -23364,7 +23364,7 @@
         </is>
       </c>
       <c r="S338">
-        <v>-3.7057073546611</v>
+        <v>-4.367588374851739</v>
       </c>
     </row>
     <row r="339">
@@ -23388,7 +23388,7 @@
       </c>
       <c r="E339" t="inlineStr">
         <is>
-          <t>70+</t>
+          <t>18-29</t>
         </is>
       </c>
       <c r="F339" t="inlineStr">
@@ -23409,19 +23409,19 @@
         <v>0</v>
       </c>
       <c r="K339">
-        <v>18.77237402132777</v>
+        <v>19.78925504151841</v>
       </c>
       <c r="L339">
-        <v>15.06666666666667</v>
+        <v>15.42166666666667</v>
       </c>
       <c r="M339">
-        <v>13.63679623448249</v>
+        <v>20.46698332765539</v>
       </c>
       <c r="N339">
-        <v>15.79903111329061</v>
+        <v>19.78924728850102</v>
       </c>
       <c r="O339">
-        <v>15.79902656857579</v>
+        <v>19.78925504151825</v>
       </c>
       <c r="P339">
         <v>60000</v>
@@ -23432,7 +23432,7 @@
         </is>
       </c>
       <c r="S339">
-        <v>-5.135577786845275</v>
+        <v>0.6777282861369832</v>
       </c>
     </row>
     <row r="340">
@@ -23456,7 +23456,7 @@
       </c>
       <c r="E340" t="inlineStr">
         <is>
-          <t>70+</t>
+          <t>18-29</t>
         </is>
       </c>
       <c r="F340" t="inlineStr">
@@ -23477,19 +23477,19 @@
         <v>0</v>
       </c>
       <c r="K340">
-        <v>18.77237402132777</v>
+        <v>19.78925504151841</v>
       </c>
       <c r="L340">
-        <v>15.06666666666667</v>
+        <v>15.42166666666667</v>
       </c>
       <c r="M340">
-        <v>13.63679623448249</v>
+        <v>20.46698332765539</v>
       </c>
       <c r="N340">
-        <v>15.79903111329061</v>
+        <v>19.78924728850102</v>
       </c>
       <c r="O340">
-        <v>15.79902656857579</v>
+        <v>19.78925504151825</v>
       </c>
       <c r="P340">
         <v>60000</v>
@@ -23500,7 +23500,7 @@
         </is>
       </c>
       <c r="S340">
-        <v>-2.973342908037155</v>
+        <v>-7.753017383649308E-06</v>
       </c>
     </row>
     <row r="341">
@@ -23524,7 +23524,7 @@
       </c>
       <c r="E341" t="inlineStr">
         <is>
-          <t>70+</t>
+          <t>18-29</t>
         </is>
       </c>
       <c r="F341" t="inlineStr">
@@ -23545,19 +23545,19 @@
         <v>0</v>
       </c>
       <c r="K341">
-        <v>18.77237402132777</v>
+        <v>19.78925504151841</v>
       </c>
       <c r="L341">
-        <v>15.06666666666667</v>
+        <v>15.42166666666667</v>
       </c>
       <c r="M341">
-        <v>13.63679623448249</v>
+        <v>20.46698332765539</v>
       </c>
       <c r="N341">
-        <v>15.79903111329061</v>
+        <v>19.78924728850102</v>
       </c>
       <c r="O341">
-        <v>15.79902656857579</v>
+        <v>19.78925504151825</v>
       </c>
       <c r="P341">
         <v>60000</v>
@@ -23568,7 +23568,7 @@
         </is>
       </c>
       <c r="S341">
-        <v>-2.973347452751979</v>
+        <v>-1.554312234475219E-13</v>
       </c>
     </row>
     <row r="342">
@@ -23613,7 +23613,7 @@
         <v>0</v>
       </c>
       <c r="K342">
-        <v>29.4681852263044</v>
+        <v>29.12342358088533</v>
       </c>
       <c r="L342">
         <v>27.75333333333333</v>
@@ -23636,7 +23636,7 @@
         </is>
       </c>
       <c r="S342">
-        <v>-1.714851892971059</v>
+        <v>-1.370090247551997</v>
       </c>
     </row>
     <row r="343">
@@ -23681,7 +23681,7 @@
         <v>0</v>
       </c>
       <c r="K343">
-        <v>29.4681852263044</v>
+        <v>29.12342358088533</v>
       </c>
       <c r="L343">
         <v>27.75333333333333</v>
@@ -23704,7 +23704,7 @@
         </is>
       </c>
       <c r="S343">
-        <v>-0.7510860494746696</v>
+        <v>-0.406324404055608</v>
       </c>
     </row>
     <row r="344">
@@ -23749,7 +23749,7 @@
         <v>0</v>
       </c>
       <c r="K344">
-        <v>29.4681852263044</v>
+        <v>29.12342358088533</v>
       </c>
       <c r="L344">
         <v>27.75333333333333</v>
@@ -23772,7 +23772,7 @@
         </is>
       </c>
       <c r="S344">
-        <v>-0.3447521545214938</v>
+        <v>9.490897567854262E-06</v>
       </c>
     </row>
     <row r="345">
@@ -23817,7 +23817,7 @@
         <v>0</v>
       </c>
       <c r="K345">
-        <v>29.4681852263044</v>
+        <v>29.12342358088533</v>
       </c>
       <c r="L345">
         <v>27.75333333333333</v>
@@ -23840,7 +23840,7 @@
         </is>
       </c>
       <c r="S345">
-        <v>-0.3447616454186175</v>
+        <v>4.440892098500626E-13</v>
       </c>
     </row>
     <row r="346">
@@ -23885,7 +23885,7 @@
         <v>0</v>
       </c>
       <c r="K346">
-        <v>58.89576626225634</v>
+        <v>60.91538488022662</v>
       </c>
       <c r="L346">
         <v>50.27522017614091</v>
@@ -23908,7 +23908,7 @@
         </is>
       </c>
       <c r="S346">
-        <v>-8.620546086115432</v>
+        <v>-10.64016470408571</v>
       </c>
     </row>
     <row r="347">
@@ -23953,7 +23953,7 @@
         <v>0</v>
       </c>
       <c r="K347">
-        <v>58.89576626225634</v>
+        <v>60.91538488022662</v>
       </c>
       <c r="L347">
         <v>50.27522017614091</v>
@@ -23976,7 +23976,7 @@
         </is>
       </c>
       <c r="S347">
-        <v>-9.510821620329773</v>
+        <v>-11.53044023830005</v>
       </c>
     </row>
     <row r="348">
@@ -24021,7 +24021,7 @@
         <v>0</v>
       </c>
       <c r="K348">
-        <v>58.89576626225634</v>
+        <v>60.91538488022662</v>
       </c>
       <c r="L348">
         <v>50.27522017614091</v>
@@ -24044,7 +24044,7 @@
         </is>
       </c>
       <c r="S348">
-        <v>2.019584098563187</v>
+        <v>-3.451940708831813E-05</v>
       </c>
     </row>
     <row r="349">
@@ -24089,7 +24089,7 @@
         <v>0</v>
       </c>
       <c r="K349">
-        <v>58.89576626225634</v>
+        <v>60.91538488022662</v>
       </c>
       <c r="L349">
         <v>50.27522017614091</v>
@@ -24112,7 +24112,7 @@
         </is>
       </c>
       <c r="S349">
-        <v>2.019618617970365</v>
+        <v>8.881784197001252E-14</v>
       </c>
     </row>
     <row r="350">
@@ -24157,7 +24157,7 @@
         <v>0</v>
       </c>
       <c r="K350">
-        <v>24.11844409192344</v>
+        <v>23.77362873790565</v>
       </c>
       <c r="L350">
         <v>23.25408483397711</v>
@@ -24180,7 +24180,7 @@
         </is>
       </c>
       <c r="S350">
-        <v>-0.8643592579463233</v>
+        <v>-0.5195439039285377</v>
       </c>
     </row>
     <row r="351">
@@ -24225,7 +24225,7 @@
         <v>0</v>
       </c>
       <c r="K351">
-        <v>24.11844409192344</v>
+        <v>23.77362873790565</v>
       </c>
       <c r="L351">
         <v>23.25408483397711</v>
@@ -24248,7 +24248,7 @@
         </is>
       </c>
       <c r="S351">
-        <v>-1.518687978235234</v>
+        <v>-1.173872624217448</v>
       </c>
     </row>
     <row r="352">
@@ -24293,7 +24293,7 @@
         <v>0</v>
       </c>
       <c r="K352">
-        <v>24.11844409192344</v>
+        <v>23.77362873790565</v>
       </c>
       <c r="L352">
         <v>23.25408483397711</v>
@@ -24316,7 +24316,7 @@
         </is>
       </c>
       <c r="S352">
-        <v>-0.3448162932823545</v>
+        <v>-9.392645688999224E-07</v>
       </c>
     </row>
     <row r="353">
@@ -24361,7 +24361,7 @@
         <v>0</v>
       </c>
       <c r="K353">
-        <v>24.11844409192344</v>
+        <v>23.77362873790565</v>
       </c>
       <c r="L353">
         <v>23.25408483397711</v>
@@ -24384,7 +24384,7 @@
         </is>
       </c>
       <c r="S353">
-        <v>-0.3448153540173249</v>
+        <v>4.6074255521944E-13</v>
       </c>
     </row>
     <row r="354">
@@ -24429,7 +24429,7 @@
         <v>1</v>
       </c>
       <c r="K354">
-        <v>89.56060703820799</v>
+        <v>86.61759112435755</v>
       </c>
       <c r="L354">
         <v>91.071459748241</v>
@@ -24452,7 +24452,7 @@
         </is>
       </c>
       <c r="S354">
-        <v>1.510852710033017</v>
+        <v>4.45386862388345</v>
       </c>
     </row>
     <row r="355">
@@ -24497,7 +24497,7 @@
         <v>1</v>
       </c>
       <c r="K355">
-        <v>89.56060703820799</v>
+        <v>86.61759112435755</v>
       </c>
       <c r="L355">
         <v>91.071459748241</v>
@@ -24520,7 +24520,7 @@
         </is>
       </c>
       <c r="S355">
-        <v>1.53193780546379</v>
+        <v>4.474953719314223</v>
       </c>
     </row>
     <row r="356">
@@ -24565,7 +24565,7 @@
         <v>1</v>
       </c>
       <c r="K356">
-        <v>89.56060703820799</v>
+        <v>86.61759112435755</v>
       </c>
       <c r="L356">
         <v>91.071459748241</v>
@@ -24588,7 +24588,7 @@
         </is>
       </c>
       <c r="S356">
-        <v>-2.943012765955744</v>
+        <v>3.147894689359276E-06</v>
       </c>
     </row>
     <row r="357">
@@ -24633,7 +24633,7 @@
         <v>1</v>
       </c>
       <c r="K357">
-        <v>89.56060703820799</v>
+        <v>86.61759112435755</v>
       </c>
       <c r="L357">
         <v>91.071459748241</v>
@@ -24656,7 +24656,7 @@
         </is>
       </c>
       <c r="S357">
-        <v>1.27502492090289</v>
+        <v>4.218040834753323</v>
       </c>
     </row>
     <row r="358">
@@ -24701,7 +24701,7 @@
         <v>1</v>
       </c>
       <c r="K358">
-        <v>62.78175698310654</v>
+        <v>61.01690685229693</v>
       </c>
       <c r="L358">
         <v>61.71963677639047</v>
@@ -24724,7 +24724,7 @@
         </is>
       </c>
       <c r="S358">
-        <v>-1.062120206716077</v>
+        <v>0.7027299240935259</v>
       </c>
     </row>
     <row r="359">
@@ -24769,7 +24769,7 @@
         <v>1</v>
       </c>
       <c r="K359">
-        <v>62.78175698310654</v>
+        <v>61.01690685229693</v>
       </c>
       <c r="L359">
         <v>61.71963677639047</v>
@@ -24792,7 +24792,7 @@
         </is>
       </c>
       <c r="S359">
-        <v>-1.787997029015953</v>
+        <v>-0.02314689820634985</v>
       </c>
     </row>
     <row r="360">
@@ -24837,7 +24837,7 @@
         <v>1</v>
       </c>
       <c r="K360">
-        <v>62.78175698310654</v>
+        <v>61.01690685229693</v>
       </c>
       <c r="L360">
         <v>61.71963677639047</v>
@@ -24860,7 +24860,7 @@
         </is>
       </c>
       <c r="S360">
-        <v>-1.764850130809714</v>
+        <v>-1.110223024625157E-13</v>
       </c>
     </row>
     <row r="361">
@@ -24905,7 +24905,7 @@
         <v>1</v>
       </c>
       <c r="K361">
-        <v>62.78175698310654</v>
+        <v>61.01690685229693</v>
       </c>
       <c r="L361">
         <v>61.71963677639047</v>
@@ -24928,7 +24928,7 @@
         </is>
       </c>
       <c r="S361">
-        <v>-2.067824549600072</v>
+        <v>-0.3029744187904693</v>
       </c>
     </row>
     <row r="362">
@@ -24973,7 +24973,7 @@
         <v>0</v>
       </c>
       <c r="K362">
-        <v>52.08816782768694</v>
+        <v>51.5832883890786</v>
       </c>
       <c r="L362">
         <v>53.54498598122996</v>
@@ -24996,7 +24996,7 @@
         </is>
       </c>
       <c r="S362">
-        <v>1.456818153543016</v>
+        <v>1.961697592151357</v>
       </c>
     </row>
     <row r="363">
@@ -25041,7 +25041,7 @@
         <v>0</v>
       </c>
       <c r="K363">
-        <v>52.08816782768694</v>
+        <v>51.5832883890786</v>
       </c>
       <c r="L363">
         <v>53.54498598122996</v>
@@ -25064,7 +25064,7 @@
         </is>
       </c>
       <c r="S363">
-        <v>0.1173033121135258</v>
+        <v>0.6221827507218669</v>
       </c>
     </row>
     <row r="364">
@@ -25109,7 +25109,7 @@
         <v>0</v>
       </c>
       <c r="K364">
-        <v>52.08816782768694</v>
+        <v>51.5832883890786</v>
       </c>
       <c r="L364">
         <v>53.54498598122996</v>
@@ -25132,7 +25132,7 @@
         </is>
       </c>
       <c r="S364">
-        <v>-0.5048808339750743</v>
+        <v>-1.395366733270009E-06</v>
       </c>
     </row>
     <row r="365">
@@ -25177,7 +25177,7 @@
         <v>0</v>
       </c>
       <c r="K365">
-        <v>52.08816782768694</v>
+        <v>51.5832883890786</v>
       </c>
       <c r="L365">
         <v>53.54498598122996</v>
@@ -25200,7 +25200,7 @@
         </is>
       </c>
       <c r="S365">
-        <v>-0.395361085269752</v>
+        <v>0.1095183533385891</v>
       </c>
     </row>
     <row r="366">
@@ -25245,7 +25245,7 @@
         <v>1</v>
       </c>
       <c r="K366">
-        <v>89.75011666878791</v>
+        <v>89.30448723235355</v>
       </c>
       <c r="L366">
         <v>93.26294368828397</v>
@@ -25268,7 +25268,7 @@
         </is>
       </c>
       <c r="S366">
-        <v>3.512827019496045</v>
+        <v>3.958456455930404</v>
       </c>
     </row>
     <row r="367">
@@ -25313,7 +25313,7 @@
         <v>1</v>
       </c>
       <c r="K367">
-        <v>89.75011666878791</v>
+        <v>89.30448723235355</v>
       </c>
       <c r="L367">
         <v>93.26294368828397</v>
@@ -25336,7 +25336,7 @@
         </is>
       </c>
       <c r="S367">
-        <v>4.285339289092393</v>
+        <v>4.730968725526752</v>
       </c>
     </row>
     <row r="368">
@@ -25381,7 +25381,7 @@
         <v>1</v>
       </c>
       <c r="K368">
-        <v>89.75011666878791</v>
+        <v>89.30448723235355</v>
       </c>
       <c r="L368">
         <v>93.26294368828397</v>
@@ -25404,7 +25404,7 @@
         </is>
       </c>
       <c r="S368">
-        <v>-0.4456318395810954</v>
+        <v>-2.403146737162132E-06</v>
       </c>
     </row>
     <row r="369">
@@ -25449,7 +25449,7 @@
         <v>1</v>
       </c>
       <c r="K369">
-        <v>89.75011666878791</v>
+        <v>89.30448723235355</v>
       </c>
       <c r="L369">
         <v>93.26294368828397</v>
@@ -25472,7 +25472,7 @@
         </is>
       </c>
       <c r="S369">
-        <v>2.296491257178013</v>
+        <v>2.742120693612371</v>
       </c>
     </row>
     <row r="370">
@@ -25517,7 +25517,7 @@
         <v>1</v>
       </c>
       <c r="K370">
-        <v>92.01159398266043</v>
+        <v>92.88968695888619</v>
       </c>
       <c r="L370">
         <v>89.36833333333334</v>
@@ -25540,7 +25540,7 @@
         </is>
       </c>
       <c r="S370">
-        <v>-2.643260649327084</v>
+        <v>-3.521353625552848</v>
       </c>
     </row>
     <row r="371">
@@ -25585,7 +25585,7 @@
         <v>1</v>
       </c>
       <c r="K371">
-        <v>92.01159398266043</v>
+        <v>92.88968695888619</v>
       </c>
       <c r="L371">
         <v>89.36833333333334</v>
@@ -25608,7 +25608,7 @@
         </is>
       </c>
       <c r="S371">
-        <v>-1.197431157690598</v>
+        <v>-2.075524133916362</v>
       </c>
     </row>
     <row r="372">
@@ -25653,7 +25653,7 @@
         <v>1</v>
       </c>
       <c r="K372">
-        <v>92.01159398266043</v>
+        <v>92.88968695888619</v>
       </c>
       <c r="L372">
         <v>89.36833333333334</v>
@@ -25676,7 +25676,7 @@
         </is>
       </c>
       <c r="S372">
-        <v>0.878090403613152</v>
+        <v>-2.572612611828617E-06</v>
       </c>
     </row>
     <row r="373">
@@ -25721,7 +25721,7 @@
         <v>1</v>
       </c>
       <c r="K373">
-        <v>92.01159398266043</v>
+        <v>92.88968695888619</v>
       </c>
       <c r="L373">
         <v>89.36833333333334</v>
@@ -25744,7 +25744,7 @@
         </is>
       </c>
       <c r="S373">
-        <v>-2.396511952108138</v>
+        <v>-3.274604928333902</v>
       </c>
     </row>
     <row r="374">
@@ -25789,7 +25789,7 @@
         <v>1</v>
       </c>
       <c r="K374">
-        <v>67.38796807857581</v>
+        <v>68.08471087366537</v>
       </c>
       <c r="L374">
         <v>64.47793326157158</v>
@@ -25812,7 +25812,7 @@
         </is>
       </c>
       <c r="S374">
-        <v>-2.910034817004226</v>
+        <v>-3.606777612093781</v>
       </c>
     </row>
     <row r="375">
@@ -25857,7 +25857,7 @@
         <v>1</v>
       </c>
       <c r="K375">
-        <v>67.38796807857581</v>
+        <v>68.08471087366537</v>
       </c>
       <c r="L375">
         <v>64.47793326157158</v>
@@ -25880,7 +25880,7 @@
         </is>
       </c>
       <c r="S375">
-        <v>-1.018641760005867</v>
+        <v>-1.715384555095423</v>
       </c>
     </row>
     <row r="376">
@@ -25925,7 +25925,7 @@
         <v>1</v>
       </c>
       <c r="K376">
-        <v>67.38796807857581</v>
+        <v>68.08471087366537</v>
       </c>
       <c r="L376">
         <v>64.47793326157158</v>
@@ -25948,7 +25948,7 @@
         </is>
       </c>
       <c r="S376">
-        <v>0.6967417540917009</v>
+        <v>-1.040997854584447E-06</v>
       </c>
     </row>
     <row r="377">
@@ -25993,7 +25993,7 @@
         <v>1</v>
       </c>
       <c r="K377">
-        <v>67.38796807857581</v>
+        <v>68.08471087366537</v>
       </c>
       <c r="L377">
         <v>64.47793326157158</v>
@@ -26016,7 +26016,7 @@
         </is>
       </c>
       <c r="S377">
-        <v>-2.375250116241501</v>
+        <v>-3.071992911331056</v>
       </c>
     </row>
     <row r="378">

--- a/tables_and_figures/input_tables/national_errors.xlsx
+++ b/tables_and_figures/input_tables/national_errors.xlsx
@@ -18701,7 +18701,7 @@
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>Secondary</t>
+          <t>Primary</t>
         </is>
       </c>
       <c r="G270" t="b">
@@ -18714,7 +18714,7 @@
         <v>0</v>
       </c>
       <c r="J270" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K270">
         <v>87.37047875398824</v>
@@ -18769,7 +18769,7 @@
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>Secondary</t>
+          <t>Primary</t>
         </is>
       </c>
       <c r="G271" t="b">
@@ -18782,7 +18782,7 @@
         <v>0</v>
       </c>
       <c r="J271" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K271">
         <v>87.37047875398824</v>
@@ -18837,7 +18837,7 @@
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>Secondary</t>
+          <t>Primary</t>
         </is>
       </c>
       <c r="G272" t="b">
@@ -18850,7 +18850,7 @@
         <v>0</v>
       </c>
       <c r="J272" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K272">
         <v>87.37047875398824</v>
@@ -18905,7 +18905,7 @@
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>Secondary</t>
+          <t>Primary</t>
         </is>
       </c>
       <c r="G273" t="b">
@@ -18918,7 +18918,7 @@
         <v>0</v>
       </c>
       <c r="J273" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K273">
         <v>87.37047875398824</v>
@@ -21421,7 +21421,7 @@
       </c>
       <c r="F310" t="inlineStr">
         <is>
-          <t>Secondary</t>
+          <t>Primary</t>
         </is>
       </c>
       <c r="G310" t="b">
@@ -21434,7 +21434,7 @@
         <v>0</v>
       </c>
       <c r="J310" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K310">
         <v>86.62346554656978</v>
@@ -21489,7 +21489,7 @@
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t>Secondary</t>
+          <t>Primary</t>
         </is>
       </c>
       <c r="G311" t="b">
@@ -21502,7 +21502,7 @@
         <v>0</v>
       </c>
       <c r="J311" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K311">
         <v>86.62346554656978</v>
@@ -21557,7 +21557,7 @@
       </c>
       <c r="F312" t="inlineStr">
         <is>
-          <t>Secondary</t>
+          <t>Primary</t>
         </is>
       </c>
       <c r="G312" t="b">
@@ -21570,7 +21570,7 @@
         <v>0</v>
       </c>
       <c r="J312" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K312">
         <v>86.62346554656978</v>
@@ -21625,7 +21625,7 @@
       </c>
       <c r="F313" t="inlineStr">
         <is>
-          <t>Secondary</t>
+          <t>Primary</t>
         </is>
       </c>
       <c r="G313" t="b">
@@ -21638,7 +21638,7 @@
         <v>0</v>
       </c>
       <c r="J313" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K313">
         <v>86.62346554656978</v>
@@ -24413,7 +24413,7 @@
       </c>
       <c r="F354" t="inlineStr">
         <is>
-          <t>Secondary</t>
+          <t>Primary</t>
         </is>
       </c>
       <c r="G354" t="b">
@@ -24426,7 +24426,7 @@
         <v>0</v>
       </c>
       <c r="J354" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K354">
         <v>86.61759112435755</v>
@@ -24481,7 +24481,7 @@
       </c>
       <c r="F355" t="inlineStr">
         <is>
-          <t>Secondary</t>
+          <t>Primary</t>
         </is>
       </c>
       <c r="G355" t="b">
@@ -24494,7 +24494,7 @@
         <v>0</v>
       </c>
       <c r="J355" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K355">
         <v>86.61759112435755</v>
@@ -24549,7 +24549,7 @@
       </c>
       <c r="F356" t="inlineStr">
         <is>
-          <t>Secondary</t>
+          <t>Primary</t>
         </is>
       </c>
       <c r="G356" t="b">
@@ -24562,7 +24562,7 @@
         <v>0</v>
       </c>
       <c r="J356" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K356">
         <v>86.61759112435755</v>
@@ -24617,7 +24617,7 @@
       </c>
       <c r="F357" t="inlineStr">
         <is>
-          <t>Secondary</t>
+          <t>Primary</t>
         </is>
       </c>
       <c r="G357" t="b">
@@ -24630,7 +24630,7 @@
         <v>0</v>
       </c>
       <c r="J357" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K357">
         <v>86.61759112435755</v>
